--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t xml:space="preserve">date_local</t>
   </si>
@@ -32,61 +32,403 @@
     <t xml:space="preserve">odds_3_plus</t>
   </si>
   <si>
-    <t xml:space="preserve">essendon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nate Caddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hussien El Achkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Langford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sullivan Robey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nik Cox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archer Day-Wicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archie Perkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Duursma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zach Merrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Durham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elijah Tsatas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Setterfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Bryan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Redman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saad El-Hawli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Kondogiannis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Blakiston</t>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Treacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Amiss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Voss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Frederick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Dudley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shai Bolton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murphy Reid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Switkowski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Brayshaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan O'Driscoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaeger O'Meara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neil Erasmus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Wagner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar McDonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Pearce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Cameron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shannon Neale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaun Mannagh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Dangerfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Dempsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Wiltshire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryan Miers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bowes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Holmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Blicavs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Atkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oisin Mullin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanner Bruhn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark O'Connor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Walter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Humphrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Petracca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Gulbin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Lombard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touk Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned Moyle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Rowell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachie Weller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarrod Witts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Rioli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Jeffrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mabior Chol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ginnivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Macdonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Nairn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Newcombe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Hardwick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned Reeves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lloyd Meek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Weddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massimo D'Ambrosio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cam Mackenzie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Sicily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarman Impey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Thilthorpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darcy Fogarty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Rachele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Keays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Pedlar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Dawson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Neal-Bullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Soligo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brayden Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Peatling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Curtin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan McAndrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Nankervis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Hall-Kahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry McKay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Kemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Ainsworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch McGovern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flynn Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talor Byrne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jagga Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Cripps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Acres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marc Pittonet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Hewett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Cerra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Florent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wade Derksen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Greene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Stringer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Cadman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Gruzewski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix Gothard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callum Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brent Daniels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Bedford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Coniglio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby McMullin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finn Callaghan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conor Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leek Aleer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clayton Oliver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kieren Briggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Himmelberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Fonti</t>
   </si>
   <si>
     <t xml:space="preserve">melbourne</t>
@@ -144,462 +486,6 @@
   </si>
   <si>
     <t xml:space="preserve">Koltyn Tholstrup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Larkey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Curtis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Trembath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Darling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Zurhaar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Duursma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Konstanty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Spargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colby McKercher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jy Simpkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Sheezel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Davies-Uniacke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Parker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">George Wardlaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tristan Xerri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Stephens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wil Dawson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Fisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Georgiades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Durdin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Whitlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Cochrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Horne-Francis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Richards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Moraes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todd Marshall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Byrne-Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ewan Mackinlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordon Sweet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zak Butters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ollie Wines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jase Burgoyne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Wehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willem Drew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson Mead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Curnow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Amartey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan McDonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Heeney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malcolm Rosas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chad Warner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caiden Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin McInerney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Jordon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Lloyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Rowbottom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Grundy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Sheldrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Serong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Blakey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Wicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">west coast eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Waterman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobe Shanahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan Murdock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malakai Champion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Duff-Tytler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elliot Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harley Reid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willem Duursma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey J. Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Cole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Baker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bo Allan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Maric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brady Hough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom McCarthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Morris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Cameron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Bailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kai Lohmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cam Rayner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conor McKenna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Draper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Ashcroft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levi Ashcroft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachie Neale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarrod Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tunstill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruce Reville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Fort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Dunkley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaspa Fletcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty Gallop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Gardiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Greene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Stringer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Cadman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Gruzewski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Gothard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callum Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brent Daniels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Bedford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Coniglio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby McMullin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finn Callaghan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conor Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leek Aleer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clayton Oliver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kieren Briggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Himmelberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Fonti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">richmond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Fawcett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Roberts-Thomson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mykelti Lefau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seth Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasper Alger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Cumming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steely Green</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyler Sonsie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Taranto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Balta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Hayes-Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dion Prestia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Retschko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Hopper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Banks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Trezise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Ryan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Sharman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Owens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campbell Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattaes Phillipou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nasiah Wanganeen-Milera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rowan Marshall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom De Koning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Garcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anthony Caminiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradley Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Silvagni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alix Tauru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Windhager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Sinclair</t>
   </si>
 </sst>
 </file>
@@ -965,7 +851,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -974,18 +860,18 @@
         <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2.95</v>
+        <v>1.91</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>8.23</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
@@ -994,18 +880,18 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4.25</v>
+        <v>2.07</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>15.05</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
@@ -1014,18 +900,18 @@
         <v>9</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4.54</v>
+        <v>2.1</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>16.76</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>6</v>
@@ -1034,18 +920,18 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5.48</v>
+        <v>3.05</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>22.72</v>
+        <v>8.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>6</v>
@@ -1054,18 +940,18 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>25.58</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -1074,18 +960,18 @@
         <v>12</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7.43</v>
+        <v>3.82</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>36.95</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>6</v>
@@ -1094,18 +980,18 @@
         <v>13</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7.54</v>
+        <v>4.25</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>37.87</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>6</v>
@@ -1114,18 +1000,18 @@
         <v>14</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2.17</v>
+        <v>1.81</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7.79</v>
+        <v>5.18</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>39.88</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>6</v>
@@ -1134,18 +1020,18 @@
         <v>15</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14.31</v>
+        <v>5.54</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>103.6</v>
+        <v>23.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>6</v>
@@ -1154,18 +1040,18 @@
         <v>16</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3.07</v>
+        <v>2.31</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.64</v>
+        <v>8.99</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>130.93</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
@@ -1174,18 +1060,18 @@
         <v>17</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>19.28</v>
+        <v>16.92</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>164.47</v>
+        <v>134.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>6</v>
@@ -1194,18 +1080,18 @@
         <v>18</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.16</v>
+        <v>3.51</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>31.74</v>
+        <v>22.11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>354.81</v>
+        <v>203.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>6</v>
@@ -1214,18 +1100,18 @@
         <v>19</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.7</v>
+        <v>3.87</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>40.91</v>
+        <v>27.3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>523.54</v>
+        <v>281.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>6</v>
@@ -1234,18 +1120,18 @@
         <v>20</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5.6</v>
+        <v>3.98</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>58.8</v>
+        <v>28.96</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>911.46</v>
+        <v>308.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -1254,18 +1140,18 @@
         <v>21</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>6.53</v>
+        <v>4.06</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>80.71</v>
+        <v>30.16</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1476.51</v>
+        <v>327.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -1274,18 +1160,18 @@
         <v>22</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>7.43</v>
+        <v>6.13</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>105.34</v>
+        <v>70.91</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2213.19</v>
+        <v>1212.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>6</v>
@@ -1294,18 +1180,18 @@
         <v>23</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>7.93</v>
+        <v>6.46</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>120.4</v>
+        <v>78.97</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2710.82</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>6</v>
@@ -1314,18 +1200,18 @@
         <v>24</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>9.25</v>
+        <v>10.34</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>164.87</v>
+        <v>206.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>4365.31</v>
+        <v>6151.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>25</v>
@@ -1334,18 +1220,18 @@
         <v>26</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.03</v>
+        <v>1.38</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4.34</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>25</v>
@@ -1354,18 +1240,18 @@
         <v>27</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4.51</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>25</v>
@@ -1374,18 +1260,18 @@
         <v>28</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>5.31</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>25</v>
@@ -1394,18 +1280,18 @@
         <v>29</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6.06</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>25</v>
@@ -1414,18 +1300,18 @@
         <v>30</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>8.83</v>
+        <v>9.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>25</v>
@@ -1437,15 +1323,15 @@
         <v>1.51</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10.24</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>25</v>
@@ -1454,18 +1340,18 @@
         <v>32</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>3.69</v>
+        <v>4.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>11.97</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>25</v>
@@ -1474,18 +1360,18 @@
         <v>33</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.76</v>
+        <v>4.53</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.33</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>25</v>
@@ -1494,18 +1380,18 @@
         <v>34</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>4.81</v>
+        <v>7.22</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>18.4</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>25</v>
@@ -1514,18 +1400,18 @@
         <v>35</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.94</v>
+        <v>7.45</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>19.23</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>25</v>
@@ -1534,18 +1420,18 @@
         <v>36</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8.38</v>
+        <v>14.56</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>44.75</v>
+        <v>106.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>25</v>
@@ -1554,18 +1440,18 @@
         <v>37</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.59</v>
+        <v>3.02</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>11.55</v>
+        <v>16.1</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>74.07</v>
+        <v>124.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>25</v>
@@ -1574,18 +1460,18 @@
         <v>38</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>2.71</v>
+        <v>3.43</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>12.74</v>
+        <v>21.15</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>86.42</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>25</v>
@@ -1594,18 +1480,18 @@
         <v>39</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>3.32</v>
+        <v>5.55</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.71</v>
+        <v>57.77</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>170.21</v>
+        <v>887.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>25</v>
@@ -1614,18 +1500,18 @@
         <v>40</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3.39</v>
+        <v>6.01</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>20.6</v>
+        <v>68.1</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>182.24</v>
+        <v>1139.93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>25</v>
@@ -1634,18 +1520,18 @@
         <v>41</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>3.42</v>
+        <v>6.09</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>21</v>
+        <v>69.96</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>187.8</v>
+        <v>1187.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>25</v>
@@ -1654,18 +1540,18 @@
         <v>42</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>3.71</v>
+        <v>7.5</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>24.97</v>
+        <v>107.27</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>245.28</v>
+        <v>2274.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46186</v>
+        <v>46191</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>25</v>
@@ -1674,18 +1560,18 @@
         <v>43</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>4.98</v>
+        <v>7.88</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46.12</v>
+        <v>118.97</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>628.95</v>
+        <v>2662.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>44</v>
@@ -1694,18 +1580,18 @@
         <v>45</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>3.61</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>44</v>
@@ -1714,18 +1600,18 @@
         <v>46</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>5.88</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>44</v>
@@ -1740,12 +1626,12 @@
         <v>2.72</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>7.19</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>44</v>
@@ -1754,18 +1640,18 @@
         <v>48</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>3.21</v>
+        <v>3.89</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>9.46</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>44</v>
@@ -1774,18 +1660,18 @@
         <v>49</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>3.22</v>
+        <v>4.26</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>9.51</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>44</v>
@@ -1794,18 +1680,18 @@
         <v>50</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>4.19</v>
+        <v>4.87</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>14.7</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>44</v>
@@ -1814,18 +1700,18 @@
         <v>51</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>6.21</v>
+        <v>4.99</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>27.76</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>44</v>
@@ -1834,18 +1720,18 @@
         <v>52</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>6.64</v>
+        <v>5.59</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>30.91</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>44</v>
@@ -1854,18 +1740,18 @@
         <v>53</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>9.29</v>
+        <v>6.71</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>52.65</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>44</v>
@@ -1874,18 +1760,18 @@
         <v>54</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>11.31</v>
+        <v>12.23</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>71.73</v>
+        <v>81.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>44</v>
@@ -1894,18 +1780,18 @@
         <v>55</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.04</v>
+        <v>2.71</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>16.38</v>
+        <v>12.71</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>127.78</v>
+        <v>86.09</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>44</v>
@@ -1914,18 +1800,18 @@
         <v>56</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3.31</v>
+        <v>3.11</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>19.63</v>
+        <v>17.12</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>169.21</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>44</v>
@@ -1934,18 +1820,18 @@
         <v>57</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>3.38</v>
+        <v>3.19</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>20.47</v>
+        <v>18.05</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>180.51</v>
+        <v>148.58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>44</v>
@@ -1954,18 +1840,18 @@
         <v>58</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>21.59</v>
+        <v>21.72</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>196</v>
+        <v>197.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>44</v>
@@ -1974,18 +1860,18 @@
         <v>59</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>3.82</v>
+        <v>4.36</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>26.48</v>
+        <v>34.91</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>268.47</v>
+        <v>410.63</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>44</v>
@@ -1994,18 +1880,18 @@
         <v>60</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>4.57</v>
+        <v>4.67</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>38.68</v>
+        <v>40.43</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>480.51</v>
+        <v>514.13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>44</v>
@@ -2014,18 +1900,18 @@
         <v>61</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>4.87</v>
+        <v>4.72</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>44.14</v>
+        <v>41.31</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>588.15</v>
+        <v>531.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>44</v>
@@ -2034,18 +1920,18 @@
         <v>62</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>6.43</v>
+        <v>4.95</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>78.21</v>
+        <v>45.61</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1407.53</v>
+        <v>618.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>63</v>
@@ -2054,18 +1940,18 @@
         <v>64</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>63</v>
@@ -2074,18 +1960,18 @@
         <v>65</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>12.01</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>63</v>
@@ -2094,18 +1980,18 @@
         <v>66</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>3.74</v>
+        <v>2.15</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>12.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>63</v>
@@ -2114,18 +2000,18 @@
         <v>67</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>3.94</v>
+        <v>2.94</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>13.29</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>63</v>
@@ -2134,18 +2020,18 @@
         <v>68</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>4.67</v>
+        <v>3.09</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>17.59</v>
+        <v>8.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>63</v>
@@ -2154,18 +2040,18 @@
         <v>69</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>5.79</v>
+        <v>3.48</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>24.84</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>63</v>
@@ -2174,18 +2060,18 @@
         <v>70</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>5.9</v>
+        <v>3.85</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>25.58</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>63</v>
@@ -2194,18 +2080,18 @@
         <v>71</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>8.44</v>
+        <v>11.7</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>45.21</v>
+        <v>75.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>63</v>
@@ -2214,18 +2100,18 @@
         <v>72</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>2.33</v>
+        <v>2.72</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>9.2</v>
+        <v>12.82</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>51.88</v>
+        <v>87.19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>63</v>
@@ -2234,18 +2120,18 @@
         <v>73</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>11.02</v>
+        <v>14.55</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>68.89</v>
+        <v>106.24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>63</v>
@@ -2254,18 +2140,18 @@
         <v>74</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>15.57</v>
+        <v>14.94</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>118.15</v>
+        <v>110.76</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>63</v>
@@ -2274,18 +2160,18 @@
         <v>75</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>3.63</v>
+        <v>3.14</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>23.78</v>
+        <v>17.45</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>227.45</v>
+        <v>140.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>63</v>
@@ -2294,18 +2180,18 @@
         <v>76</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>3.92</v>
+        <v>3.19</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>27.96</v>
+        <v>18.06</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>291.89</v>
+        <v>148.66</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>63</v>
@@ -2314,18 +2200,18 @@
         <v>77</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>4.45</v>
+        <v>3.42</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>36.49</v>
+        <v>20.98</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>439.46</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>63</v>
@@ -2334,18 +2220,18 @@
         <v>78</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>4.49</v>
+        <v>4.08</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>37.16</v>
+        <v>30.42</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>451.93</v>
+        <v>332.34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>63</v>
@@ -2354,18 +2240,18 @@
         <v>79</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>5.11</v>
+        <v>5.76</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>48.63</v>
+        <v>62.49</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>681.89</v>
+        <v>999.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>63</v>
@@ -2374,18 +2260,18 @@
         <v>80</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>5.62</v>
+        <v>5.94</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>59.34</v>
+        <v>66.46</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>924.14</v>
+        <v>1098.47</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>63</v>
@@ -2394,18 +2280,18 @@
         <v>81</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>7.61</v>
+        <v>6.8</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>110.62</v>
+        <v>87.92</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2383.77</v>
+        <v>1681.74</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>82</v>
@@ -2414,18 +2300,18 @@
         <v>83</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>3.25</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>82</v>
@@ -2434,18 +2320,18 @@
         <v>84</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>5.51</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>82</v>
@@ -2454,18 +2340,18 @@
         <v>85</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2.71</v>
+        <v>2.17</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>7.13</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>82</v>
@@ -2474,18 +2360,18 @@
         <v>86</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>7.45</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>82</v>
@@ -2494,18 +2380,18 @@
         <v>87</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>8.38</v>
+        <v>9.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>82</v>
@@ -2514,18 +2400,18 @@
         <v>88</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>3.47</v>
+        <v>3.81</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>10.81</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>82</v>
@@ -2534,18 +2420,18 @@
         <v>89</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>3.68</v>
+        <v>5.08</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>11.88</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>82</v>
@@ -2554,18 +2440,18 @@
         <v>90</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>8.28</v>
+        <v>5.11</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>43.86</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>82</v>
@@ -2574,18 +2460,18 @@
         <v>91</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>8.96</v>
+        <v>6.18</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>49.74</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>82</v>
@@ -2594,18 +2480,18 @@
         <v>92</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>2.46</v>
+        <v>1.96</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>10.36</v>
+        <v>6.23</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>62.53</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>82</v>
@@ -2614,18 +2500,18 @@
         <v>93</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>10.87</v>
+        <v>11.16</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>67.43</v>
+        <v>70.26</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>82</v>
@@ -2634,18 +2520,18 @@
         <v>94</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>13.02</v>
+        <v>12.98</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>89.39</v>
+        <v>88.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>82</v>
@@ -2654,18 +2540,18 @@
         <v>95</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>18.19</v>
+        <v>14.95</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>150.39</v>
+        <v>110.92</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>82</v>
@@ -2674,18 +2560,18 @@
         <v>96</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>27.33</v>
+        <v>17.07</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>281.84</v>
+        <v>136.19</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>82</v>
@@ -2694,18 +2580,18 @@
         <v>97</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>27.92</v>
+        <v>25.63</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>291.37</v>
+        <v>255.36</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>82</v>
@@ -2714,18 +2600,18 @@
         <v>98</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>4.76</v>
+        <v>7.03</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>42.07</v>
+        <v>94.15</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>546.37</v>
+        <v>1866.18</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>82</v>
@@ -2734,18 +2620,18 @@
         <v>99</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>5.59</v>
+        <v>8.47</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>58.69</v>
+        <v>137.6</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>908.84</v>
+        <v>3319.31</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>82</v>
@@ -2754,18 +2640,18 @@
         <v>100</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>7.3</v>
+        <v>8.96</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>101.46</v>
+        <v>154.35</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2090.43</v>
+        <v>3950.34</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>101</v>
@@ -2774,18 +2660,18 @@
         <v>102</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.09</v>
+        <v>2.82</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>4.55</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>101</v>
@@ -2794,18 +2680,18 @@
         <v>103</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>3.68</v>
+        <v>3.86</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>11.89</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>101</v>
@@ -2814,18 +2700,18 @@
         <v>104</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>4.11</v>
+        <v>4.47</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>14.24</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>101</v>
@@ -2834,18 +2720,18 @@
         <v>105</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>5.48</v>
+        <v>5.02</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>22.73</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>101</v>
@@ -2854,18 +2740,18 @@
         <v>106</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>5.97</v>
+        <v>5.22</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>26.05</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>101</v>
@@ -2874,18 +2760,18 @@
         <v>107</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>6.88</v>
+        <v>5.36</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>32.73</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>101</v>
@@ -2894,18 +2780,18 @@
         <v>108</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>8.34</v>
+        <v>5.89</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>44.41</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>101</v>
@@ -2914,18 +2800,18 @@
         <v>109</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>9.08</v>
+        <v>5.92</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>50.82</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>101</v>
@@ -2934,18 +2820,18 @@
         <v>110</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>11.16</v>
+        <v>6.54</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>70.25</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>101</v>
@@ -2954,18 +2840,18 @@
         <v>111</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>2.87</v>
+        <v>2.44</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>14.39</v>
+        <v>10.1</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>104.46</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>101</v>
@@ -2974,18 +2860,18 @@
         <v>112</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>14.39</v>
+        <v>12.77</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>104.52</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>101</v>
@@ -2994,18 +2880,18 @@
         <v>113</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>26.29</v>
+        <v>26.97</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>265.5</v>
+        <v>276.15</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>101</v>
@@ -3014,18 +2900,18 @@
         <v>114</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>3.98</v>
+        <v>3.87</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>28.91</v>
+        <v>27.21</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>307.36</v>
+        <v>280</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>101</v>
@@ -3034,18 +2920,18 @@
         <v>115</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>40.09</v>
+        <v>29.23</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>507.62</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>101</v>
@@ -3054,18 +2940,18 @@
         <v>116</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>4.81</v>
+        <v>4.45</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>42.94</v>
+        <v>36.47</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>563.89</v>
+        <v>438.95</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>101</v>
@@ -3074,18 +2960,18 @@
         <v>117</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>5.35</v>
+        <v>4.5</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>53.63</v>
+        <v>37.36</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>791.96</v>
+        <v>455.61</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>101</v>
@@ -3094,18 +2980,18 @@
         <v>118</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>9.96</v>
+        <v>9.04</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>191.62</v>
+        <v>157.36</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>5481.19</v>
+        <v>4067.67</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>101</v>
@@ -3114,18 +3000,18 @@
         <v>119</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>13.04</v>
+        <v>12.71</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>331.25</v>
+        <v>314.37</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>12538.11</v>
+        <v>11586.34</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>120</v>
@@ -3134,18 +3020,18 @@
         <v>121</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>120</v>
@@ -3154,18 +3040,18 @@
         <v>122</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>2.78</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>120</v>
@@ -3177,15 +3063,15 @@
         <v>1.22</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>120</v>
@@ -3194,18 +3080,18 @@
         <v>124</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>4.13</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>120</v>
@@ -3214,18 +3100,18 @@
         <v>125</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>2.21</v>
+        <v>2.61</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>5.02</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>120</v>
@@ -3234,18 +3120,18 @@
         <v>126</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>3.72</v>
+        <v>2.88</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>12.09</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>120</v>
@@ -3254,18 +3140,18 @@
         <v>127</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>5.03</v>
+        <v>2.94</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>19.83</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>120</v>
@@ -3274,18 +3160,18 @@
         <v>128</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>8.42</v>
+        <v>3.98</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>45.1</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>120</v>
@@ -3294,18 +3180,18 @@
         <v>129</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>2.36</v>
+        <v>2.01</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>9.39</v>
+        <v>6.63</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>53.58</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>120</v>
@@ -3314,18 +3200,18 @@
         <v>130</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>2.69</v>
+        <v>2.07</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>12.57</v>
+        <v>7.01</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>84.64</v>
+        <v>33.69</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>120</v>
@@ -3334,18 +3220,18 @@
         <v>131</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>13.05</v>
+        <v>10.11</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>89.74</v>
+        <v>60.13</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>120</v>
@@ -3354,18 +3240,18 @@
         <v>132</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>2.79</v>
+        <v>3.08</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>13.61</v>
+        <v>16.73</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>95.81</v>
+        <v>132.09</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>120</v>
@@ -3374,18 +3260,18 @@
         <v>133</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>2.88</v>
+        <v>3.64</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>14.49</v>
+        <v>24</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>105.59</v>
+        <v>230.76</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>120</v>
@@ -3394,18 +3280,18 @@
         <v>134</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>3</v>
+        <v>3.87</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>15.85</v>
+        <v>27.3</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>121.35</v>
+        <v>281.46</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>120</v>
@@ -3414,18 +3300,18 @@
         <v>135</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>3.75</v>
+        <v>4.08</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>25.54</v>
+        <v>30.41</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>254.01</v>
+        <v>332.26</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>120</v>
@@ -3434,18 +3320,18 @@
         <v>136</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>3.96</v>
+        <v>4.21</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>28.53</v>
+        <v>32.55</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>301.08</v>
+        <v>368.82</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>120</v>
@@ -3454,18 +3340,18 @@
         <v>137</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>4.37</v>
+        <v>6.35</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>35.15</v>
+        <v>76.27</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>414.95</v>
+        <v>1354.59</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>120</v>
@@ -3474,18 +3360,18 @@
         <v>138</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>5.02</v>
+        <v>11.52</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>46.87</v>
+        <v>257.55</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>644.7</v>
+        <v>8572.97</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>139</v>
@@ -3494,18 +3380,18 @@
         <v>140</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>4.04</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>139</v>
@@ -3514,18 +3400,18 @@
         <v>141</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>4.23</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>139</v>
@@ -3534,18 +3420,18 @@
         <v>142</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>2.13</v>
+        <v>3.06</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>4.72</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>139</v>
@@ -3554,18 +3440,18 @@
         <v>143</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>2.42</v>
+        <v>3.32</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>5.89</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>139</v>
@@ -3574,18 +3460,18 @@
         <v>144</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>2.89</v>
+        <v>4.26</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>7.94</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>139</v>
@@ -3594,18 +3480,18 @@
         <v>145</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>3.2</v>
+        <v>4.69</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>9.42</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>139</v>
@@ -3614,18 +3500,18 @@
         <v>146</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>3.26</v>
+        <v>5.2</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>9.73</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>139</v>
@@ -3634,18 +3520,18 @@
         <v>147</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>4.47</v>
+        <v>5.3</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>16.33</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>139</v>
@@ -3654,18 +3540,18 @@
         <v>148</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>7.56</v>
+        <v>6.93</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>38.03</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>139</v>
@@ -3674,18 +3560,18 @@
         <v>149</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>8.02</v>
+        <v>7.08</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>41.77</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>139</v>
@@ -3694,18 +3580,18 @@
         <v>150</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>11.55</v>
+        <v>12.49</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>74.16</v>
+        <v>83.79</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>139</v>
@@ -3714,18 +3600,18 @@
         <v>151</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>19.29</v>
+        <v>17.37</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>164.6</v>
+        <v>139.92</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>139</v>
@@ -3734,18 +3620,18 @@
         <v>152</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>3.91</v>
+        <v>3.28</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>27.9</v>
+        <v>19.22</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>291.02</v>
+        <v>163.77</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>139</v>
@@ -3754,18 +3640,18 @@
         <v>153</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>4.16</v>
+        <v>4.07</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>31.73</v>
+        <v>30.25</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>354.66</v>
+        <v>329.47</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>139</v>
@@ -3774,18 +3660,18 @@
         <v>154</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>4.38</v>
+        <v>4.14</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>35.35</v>
+        <v>31.46</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>418.49</v>
+        <v>349.91</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>139</v>
@@ -3794,18 +3680,18 @@
         <v>155</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>4.53</v>
+        <v>4.2</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>37.86</v>
+        <v>32.32</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>464.93</v>
+        <v>364.71</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>139</v>
@@ -3814,18 +3700,18 @@
         <v>156</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>6.83</v>
+        <v>4.55</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>88.7</v>
+        <v>38.29</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>1704.49</v>
+        <v>473.14</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>139</v>
@@ -3834,733 +3720,13 @@
         <v>157</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>12.47</v>
+        <v>6.18</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>302.65</v>
+        <v>72.04</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>10940.12</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D146" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>12.14</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D147" s="3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>14.46</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D148" s="3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>15.25</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D149" s="3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>17.86</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D150" s="3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>19.17</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D151" s="3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>21.88</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>24.03</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D153" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>12.87</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>87.76</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D154" s="3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>104.42</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D155" s="3" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>26.71</v>
-      </c>
-      <c r="F155" s="3" t="n">
-        <v>272.17</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D156" s="3" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>33.37</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>383.03</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D157" s="3" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="F157" s="3" t="n">
-        <v>414.86</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D158" s="3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>36.32</v>
-      </c>
-      <c r="F158" s="3" t="n">
-        <v>436.3</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D159" s="3" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>47.01</v>
-      </c>
-      <c r="F159" s="3" t="n">
-        <v>647.57</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D160" s="3" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>53.03</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>778.38</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D161" s="3" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>55.66</v>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>838.22</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D162" s="3" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>114.7</v>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>2518.35</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D163" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>256.91</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>8540.54</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D164" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>7.26</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D165" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>7.73</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D166" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>7.85</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D167" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="F167" s="3" t="n">
-        <v>10.09</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D168" s="3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="F168" s="3" t="n">
-        <v>12.36</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D169" s="3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="F169" s="3" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D170" s="3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F170" s="3" t="n">
-        <v>20.89</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D171" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E171" s="3" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F171" s="3" t="n">
-        <v>29.37</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D172" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E172" s="3" t="n">
-        <v>9.87</v>
-      </c>
-      <c r="F172" s="3" t="n">
-        <v>57.89</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D173" s="3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="F173" s="3" t="n">
-        <v>75.7</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D174" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E174" s="3" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="F174" s="3" t="n">
-        <v>79.83</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D175" s="3" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E175" s="3" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="F175" s="3" t="n">
-        <v>182.88</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D176" s="3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>23.18</v>
-      </c>
-      <c r="F176" s="3" t="n">
-        <v>218.69</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D177" s="3" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="E177" s="3" t="n">
-        <v>24.59</v>
-      </c>
-      <c r="F177" s="3" t="n">
-        <v>239.59</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D178" s="3" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="E178" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="F178" s="3" t="n">
-        <v>347.18</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C179" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D179" s="3" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="E179" s="3" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="F179" s="3" t="n">
-        <v>487.17</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D180" s="3" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="E180" s="3" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="F180" s="3" t="n">
-        <v>498.05</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D181" s="3" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E181" s="3" t="n">
-        <v>42.14</v>
-      </c>
-      <c r="F181" s="3" t="n">
-        <v>547.82</v>
+        <v>1242</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -2306,7 +2306,7 @@
         <v>1.84</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="75">
@@ -2326,7 +2326,7 @@
         <v>2.15</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="76">
@@ -2346,7 +2346,7 @@
         <v>2.17</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="77">
@@ -2366,7 +2366,7 @@
         <v>2.56</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="78">
@@ -2383,10 +2383,10 @@
         <v>1.49</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>9.7</v>
+        <v>9.72</v>
       </c>
     </row>
     <row r="79">
@@ -2403,10 +2403,10 @@
         <v>1.59</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>12.6</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="80">
@@ -2423,10 +2423,10 @@
         <v>1.79</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>20.13</v>
+        <v>20.17</v>
       </c>
     </row>
     <row r="81">
@@ -2443,10 +2443,10 @@
         <v>1.8</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>20.33</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="82">
@@ -2463,10 +2463,10 @@
         <v>1.95</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>6.18</v>
+        <v>6.19</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>27.54</v>
+        <v>27.61</v>
       </c>
     </row>
     <row r="83">
@@ -2483,10 +2483,10 @@
         <v>1.96</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>6.23</v>
+        <v>6.24</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>27.93</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
@@ -2503,10 +2503,10 @@
         <v>2.55</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>11.16</v>
+        <v>11.18</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>70.26</v>
+        <v>70.44</v>
       </c>
     </row>
     <row r="85">
@@ -2523,10 +2523,10 @@
         <v>2.73</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>12.98</v>
+        <v>13</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>88.92</v>
+        <v>89.15</v>
       </c>
     </row>
     <row r="86">
@@ -2543,10 +2543,10 @@
         <v>2.92</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>14.95</v>
+        <v>14.98</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>110.92</v>
+        <v>111.22</v>
       </c>
     </row>
     <row r="87">
@@ -2560,13 +2560,13 @@
         <v>96</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>17.07</v>
+        <v>17.1</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>136.19</v>
+        <v>136.55</v>
       </c>
     </row>
     <row r="88">
@@ -2583,10 +2583,10 @@
         <v>3.76</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>25.63</v>
+        <v>25.68</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>255.36</v>
+        <v>256.06</v>
       </c>
     </row>
     <row r="89">
@@ -2600,13 +2600,13 @@
         <v>98</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>7.03</v>
+        <v>7.04</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>94.15</v>
+        <v>94.33</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>1866.18</v>
+        <v>1871.52</v>
       </c>
     </row>
     <row r="90">
@@ -2623,10 +2623,10 @@
         <v>8.47</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>137.6</v>
+        <v>137.86</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>3319.31</v>
+        <v>3328.86</v>
       </c>
     </row>
     <row r="91">
@@ -2643,10 +2643,10 @@
         <v>8.96</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>154.35</v>
+        <v>154.64</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>3950.34</v>
+        <v>3961.73</v>
       </c>
     </row>
     <row r="92">
@@ -3383,10 +3383,10 @@
         <v>1.37</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>6.96</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="129">
@@ -3403,10 +3403,10 @@
         <v>1.39</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>7.27</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="130">
@@ -3426,7 +3426,7 @@
         <v>3.06</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="131">
@@ -3443,10 +3443,10 @@
         <v>1.5</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>10.05</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="132">
@@ -3466,7 +3466,7 @@
         <v>4.26</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>15.09</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="133">
@@ -3483,10 +3483,10 @@
         <v>1.73</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>17.67</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="134">
@@ -3503,10 +3503,10 @@
         <v>1.81</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>20.86</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="135">
@@ -3523,10 +3523,10 @@
         <v>1.83</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>21.52</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="136">
@@ -3543,10 +3543,10 @@
         <v>2.06</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>6.93</v>
+        <v>6.95</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>33.1</v>
+        <v>33.22</v>
       </c>
     </row>
     <row r="137">
@@ -3560,13 +3560,13 @@
         <v>149</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="E137" s="3" t="n">
-        <v>7.08</v>
+        <v>7.1</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>34.24</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="138">
@@ -3580,13 +3580,13 @@
         <v>150</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>12.49</v>
+        <v>12.52</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>83.79</v>
+        <v>84.12</v>
       </c>
     </row>
     <row r="139">
@@ -3603,10 +3603,10 @@
         <v>3.13</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>17.37</v>
+        <v>17.41</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>139.92</v>
+        <v>140.49</v>
       </c>
     </row>
     <row r="140">
@@ -3620,13 +3620,13 @@
         <v>152</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>19.22</v>
+        <v>19.27</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>163.77</v>
+        <v>164.44</v>
       </c>
     </row>
     <row r="141">
@@ -3643,10 +3643,10 @@
         <v>4.07</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>30.25</v>
+        <v>30.33</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>329.47</v>
+        <v>330.84</v>
       </c>
     </row>
     <row r="142">
@@ -3660,13 +3660,13 @@
         <v>154</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>31.46</v>
+        <v>31.54</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>349.91</v>
+        <v>351.37</v>
       </c>
     </row>
     <row r="143">
@@ -3683,10 +3683,10 @@
         <v>4.2</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>32.32</v>
+        <v>32.4</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>364.71</v>
+        <v>366.23</v>
       </c>
     </row>
     <row r="144">
@@ -3700,13 +3700,13 @@
         <v>156</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>38.29</v>
+        <v>38.4</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>473.14</v>
+        <v>475.12</v>
       </c>
     </row>
     <row r="145">
@@ -3723,10 +3723,10 @@
         <v>6.18</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>72.04</v>
+        <v>72.24</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>1242</v>
+        <v>1247.3</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -1481,16 +1481,16 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>1.51613539098051</v>
+        <v>1.51381114346757</v>
       </c>
       <c r="F2" t="n">
         <v>1.28</v>
       </c>
       <c r="G2" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="H2" t="n">
-        <v>5.12</v>
+        <v>5.14</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>1.34726094667619</v>
+        <v>1.34524427972639</v>
       </c>
       <c r="F3" t="n">
         <v>1.35</v>
@@ -1522,7 +1522,7 @@
         <v>2.57</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
@@ -1545,16 +1545,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>1.11014120605024</v>
+        <v>1.10859112772821</v>
       </c>
       <c r="F4" t="n">
         <v>1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="H4" t="n">
-        <v>9.84</v>
+        <v>9.87</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
@@ -1577,16 +1577,16 @@
         <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>1.06695946259624</v>
+        <v>1.06538524330885</v>
       </c>
       <c r="F5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G5" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="H5" t="n">
-        <v>10.75</v>
+        <v>10.79</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
@@ -1609,16 +1609,16 @@
         <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>0.681342118016117</v>
+        <v>0.680637734837064</v>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="H6" t="n">
-        <v>31.34</v>
+        <v>31.42</v>
       </c>
       <c r="I6" t="s">
         <v>13</v>
@@ -1641,16 +1641,16 @@
         <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>0.656318823590928</v>
+        <v>0.655658155115063</v>
       </c>
       <c r="F7" t="n">
         <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.1</v>
+        <v>7.12</v>
       </c>
       <c r="H7" t="n">
-        <v>34.43</v>
+        <v>34.52</v>
       </c>
       <c r="I7" t="s">
         <v>13</v>
@@ -1673,16 +1673,16 @@
         <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>0.645213039700714</v>
+        <v>0.644428601716949</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="G8" t="n">
-        <v>7.3</v>
+        <v>7.31</v>
       </c>
       <c r="H8" t="n">
-        <v>35.95</v>
+        <v>36.06</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
@@ -1705,16 +1705,16 @@
         <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>0.600179682653485</v>
+        <v>0.599171724408163</v>
       </c>
       <c r="F9" t="n">
         <v>2.22</v>
       </c>
       <c r="G9" t="n">
-        <v>8.2</v>
+        <v>8.22</v>
       </c>
       <c r="H9" t="n">
-        <v>43.23</v>
+        <v>43.41</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
@@ -1737,16 +1737,16 @@
         <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>0.491819232967952</v>
+        <v>0.491225947875653</v>
       </c>
       <c r="F10" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4</v>
+        <v>11.42</v>
       </c>
       <c r="H10" t="n">
-        <v>72.6</v>
+        <v>72.83</v>
       </c>
       <c r="I10" t="s">
         <v>13</v>
@@ -1769,16 +1769,16 @@
         <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>0.431156656700401</v>
+        <v>0.430414378555135</v>
       </c>
       <c r="F11" t="n">
         <v>2.86</v>
       </c>
       <c r="G11" t="n">
-        <v>14.27</v>
+        <v>14.31</v>
       </c>
       <c r="H11" t="n">
-        <v>103.07</v>
+        <v>103.55</v>
       </c>
       <c r="I11" t="s">
         <v>13</v>
@@ -1801,16 +1801,16 @@
         <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.382713220138015</v>
+        <v>0.38205394994734</v>
       </c>
       <c r="F12" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="G12" t="n">
-        <v>17.55</v>
+        <v>17.6</v>
       </c>
       <c r="H12" t="n">
-        <v>142.22</v>
+        <v>142.89</v>
       </c>
       <c r="I12" t="s">
         <v>13</v>
@@ -1833,16 +1833,16 @@
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>0.318468725099546</v>
+        <v>0.317916487918839</v>
       </c>
       <c r="F13" t="n">
         <v>3.67</v>
       </c>
       <c r="G13" t="n">
-        <v>24.31</v>
+        <v>24.39</v>
       </c>
       <c r="H13" t="n">
-        <v>235.42</v>
+        <v>236.55</v>
       </c>
       <c r="I13" t="s">
         <v>13</v>
@@ -1865,16 +1865,16 @@
         <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>0.292899719717768</v>
+        <v>0.292407815882842</v>
       </c>
       <c r="F14" t="n">
         <v>3.94</v>
       </c>
       <c r="G14" t="n">
-        <v>28.27</v>
+        <v>28.36</v>
       </c>
       <c r="H14" t="n">
-        <v>296.95</v>
+        <v>298.35</v>
       </c>
       <c r="I14" t="s">
         <v>13</v>
@@ -1897,16 +1897,16 @@
         <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>0.249066940520245</v>
+        <v>0.248648650658741</v>
       </c>
       <c r="F15" t="n">
         <v>4.54</v>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>38.11</v>
       </c>
       <c r="H15" t="n">
-        <v>467.54</v>
+        <v>469.76</v>
       </c>
       <c r="I15" t="s">
         <v>13</v>
@@ -1929,16 +1929,16 @@
         <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>0.242534764946256</v>
+        <v>0.242102260577995</v>
       </c>
       <c r="F16" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="G16" t="n">
-        <v>39.9</v>
+        <v>40.03</v>
       </c>
       <c r="H16" t="n">
-        <v>503.9</v>
+        <v>506.44</v>
       </c>
       <c r="I16" t="s">
         <v>13</v>
@@ -1961,16 +1961,16 @@
         <v>29</v>
       </c>
       <c r="E17" t="n">
-        <v>0.240697340296286</v>
+        <v>0.240271261632711</v>
       </c>
       <c r="F17" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="G17" t="n">
-        <v>40.46</v>
+        <v>40.6</v>
       </c>
       <c r="H17" t="n">
-        <v>514.82</v>
+        <v>517.41</v>
       </c>
       <c r="I17" t="s">
         <v>13</v>
@@ -1993,16 +1993,16 @@
         <v>30</v>
       </c>
       <c r="E18" t="n">
-        <v>0.235044588544733</v>
+        <v>0.234632233137249</v>
       </c>
       <c r="F18" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="G18" t="n">
-        <v>42.28</v>
+        <v>42.41</v>
       </c>
       <c r="H18" t="n">
-        <v>550.56</v>
+        <v>553.3</v>
       </c>
       <c r="I18" t="s">
         <v>13</v>
@@ -2025,16 +2025,16 @@
         <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>0.218842624931593</v>
+        <v>0.218475094615917</v>
       </c>
       <c r="F19" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="G19" t="n">
-        <v>48.26</v>
+        <v>48.41</v>
       </c>
       <c r="H19" t="n">
-        <v>673.97</v>
+        <v>677.2</v>
       </c>
       <c r="I19" t="s">
         <v>13</v>
@@ -2057,16 +2057,16 @@
         <v>33</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9977968320934</v>
+        <v>1.99996653326283</v>
       </c>
       <c r="F20" t="n">
         <v>1.16</v>
       </c>
       <c r="G20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="I20" t="s">
         <v>13</v>
@@ -2089,7 +2089,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="n">
-        <v>1.14957611910087</v>
+        <v>1.15114246225419</v>
       </c>
       <c r="F21" t="n">
         <v>1.46</v>
@@ -2098,7 +2098,7 @@
         <v>3.13</v>
       </c>
       <c r="H21" t="n">
-        <v>9.11</v>
+        <v>9.08</v>
       </c>
       <c r="I21" t="s">
         <v>13</v>
@@ -2121,7 +2121,7 @@
         <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>1.14933961871709</v>
+        <v>1.15087560275108</v>
       </c>
       <c r="F22" t="n">
         <v>1.46</v>
@@ -2130,7 +2130,7 @@
         <v>3.13</v>
       </c>
       <c r="H22" t="n">
-        <v>9.11</v>
+        <v>9.09</v>
       </c>
       <c r="I22" t="s">
         <v>13</v>
@@ -2153,7 +2153,7 @@
         <v>36</v>
       </c>
       <c r="E23" t="n">
-        <v>1.13334206491664</v>
+        <v>1.1346832635884</v>
       </c>
       <c r="F23" t="n">
         <v>1.47</v>
@@ -2162,7 +2162,7 @@
         <v>3.19</v>
       </c>
       <c r="H23" t="n">
-        <v>9.4</v>
+        <v>9.38</v>
       </c>
       <c r="I23" t="s">
         <v>13</v>
@@ -2185,16 +2185,16 @@
         <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>1.08477079587214</v>
+        <v>1.0857805210668</v>
       </c>
       <c r="F24" t="n">
         <v>1.51</v>
       </c>
       <c r="G24" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="H24" t="n">
-        <v>10.36</v>
+        <v>10.34</v>
       </c>
       <c r="I24" t="s">
         <v>13</v>
@@ -2217,7 +2217,7 @@
         <v>38</v>
       </c>
       <c r="E25" t="n">
-        <v>1.05551263633751</v>
+        <v>1.05698131771225</v>
       </c>
       <c r="F25" t="n">
         <v>1.53</v>
@@ -2226,7 +2226,7 @@
         <v>3.51</v>
       </c>
       <c r="H25" t="n">
-        <v>11.01</v>
+        <v>10.98</v>
       </c>
       <c r="I25" t="s">
         <v>13</v>
@@ -2249,16 +2249,16 @@
         <v>39</v>
       </c>
       <c r="E26" t="n">
-        <v>0.845119090983346</v>
+        <v>0.846333500491058</v>
       </c>
       <c r="F26" t="n">
         <v>1.75</v>
       </c>
       <c r="G26" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="H26" t="n">
-        <v>18.47</v>
+        <v>18.41</v>
       </c>
       <c r="I26" t="s">
         <v>13</v>
@@ -2281,16 +2281,16 @@
         <v>40</v>
       </c>
       <c r="E27" t="n">
-        <v>0.702936613350312</v>
+        <v>0.703583305175053</v>
       </c>
       <c r="F27" t="n">
         <v>1.98</v>
       </c>
       <c r="G27" t="n">
-        <v>6.38</v>
+        <v>6.37</v>
       </c>
       <c r="H27" t="n">
-        <v>28.99</v>
+        <v>28.92</v>
       </c>
       <c r="I27" t="s">
         <v>13</v>
@@ -2313,16 +2313,16 @@
         <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>0.695535588679218</v>
+        <v>0.696488281731039</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G28" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="H28" t="n">
-        <v>29.76</v>
+        <v>29.66</v>
       </c>
       <c r="I28" t="s">
         <v>13</v>
@@ -2345,16 +2345,16 @@
         <v>42</v>
       </c>
       <c r="E29" t="n">
-        <v>0.685827282064823</v>
+        <v>0.686911783833426</v>
       </c>
       <c r="F29" t="n">
         <v>2.01</v>
       </c>
       <c r="G29" t="n">
-        <v>6.63</v>
+        <v>6.61</v>
       </c>
       <c r="H29" t="n">
-        <v>30.83</v>
+        <v>30.7</v>
       </c>
       <c r="I29" t="s">
         <v>13</v>
@@ -2377,16 +2377,16 @@
         <v>43</v>
       </c>
       <c r="E30" t="n">
-        <v>0.515908574660956</v>
+        <v>0.516399143683515</v>
       </c>
       <c r="F30" t="n">
         <v>2.48</v>
       </c>
       <c r="G30" t="n">
-        <v>10.52</v>
+        <v>10.5</v>
       </c>
       <c r="H30" t="n">
-        <v>64.01</v>
+        <v>63.85</v>
       </c>
       <c r="I30" t="s">
         <v>13</v>
@@ -2409,16 +2409,16 @@
         <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>0.509716441248058</v>
+        <v>0.510181019239827</v>
       </c>
       <c r="F31" t="n">
         <v>2.5</v>
       </c>
       <c r="G31" t="n">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
       <c r="H31" t="n">
-        <v>66.07</v>
+        <v>65.91</v>
       </c>
       <c r="I31" t="s">
         <v>13</v>
@@ -2441,16 +2441,16 @@
         <v>45</v>
       </c>
       <c r="E32" t="n">
-        <v>0.487450347643821</v>
+        <v>0.487884187779968</v>
       </c>
       <c r="F32" t="n">
         <v>2.59</v>
       </c>
       <c r="G32" t="n">
-        <v>11.57</v>
+        <v>11.55</v>
       </c>
       <c r="H32" t="n">
-        <v>74.33</v>
+        <v>74.15</v>
       </c>
       <c r="I32" t="s">
         <v>13</v>
@@ -2473,16 +2473,16 @@
         <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>0.393776889530407</v>
+        <v>0.394125893017811</v>
       </c>
       <c r="F33" t="n">
         <v>3.07</v>
       </c>
       <c r="G33" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
       <c r="H33" t="n">
-        <v>131.64</v>
+        <v>131.32</v>
       </c>
       <c r="I33" t="s">
         <v>13</v>
@@ -2505,16 +2505,16 @@
         <v>47</v>
       </c>
       <c r="E34" t="n">
-        <v>0.366726634623014</v>
+        <v>0.367053973033265</v>
       </c>
       <c r="F34" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="G34" t="n">
-        <v>18.92</v>
+        <v>18.89</v>
       </c>
       <c r="H34" t="n">
-        <v>159.76</v>
+        <v>159.37</v>
       </c>
       <c r="I34" t="s">
         <v>13</v>
@@ -2537,16 +2537,16 @@
         <v>48</v>
       </c>
       <c r="E35" t="n">
-        <v>0.287165558114907</v>
+        <v>0.287438619145633</v>
       </c>
       <c r="F35" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>29.3</v>
+        <v>29.25</v>
       </c>
       <c r="H35" t="n">
-        <v>313.77</v>
+        <v>312.94</v>
       </c>
       <c r="I35" t="s">
         <v>13</v>
@@ -2569,16 +2569,16 @@
         <v>49</v>
       </c>
       <c r="E36" t="n">
-        <v>0.284372380691955</v>
+        <v>0.284618976827181</v>
       </c>
       <c r="F36" t="n">
         <v>4.04</v>
       </c>
       <c r="G36" t="n">
-        <v>29.83</v>
+        <v>29.78</v>
       </c>
       <c r="H36" t="n">
-        <v>322.44</v>
+        <v>321.66</v>
       </c>
       <c r="I36" t="s">
         <v>13</v>
@@ -2601,16 +2601,16 @@
         <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>0.209830010846054</v>
+        <v>0.210029534770214</v>
       </c>
       <c r="F37" t="n">
         <v>5.28</v>
       </c>
       <c r="G37" t="n">
-        <v>52.18</v>
+        <v>52.09</v>
       </c>
       <c r="H37" t="n">
-        <v>759.51</v>
+        <v>757.46</v>
       </c>
       <c r="I37" t="s">
         <v>13</v>
@@ -2633,7 +2633,7 @@
         <v>53</v>
       </c>
       <c r="E38" t="n">
-        <v>1.78379848100669</v>
+        <v>1.78365542509246</v>
       </c>
       <c r="F38" t="n">
         <v>1.2</v>
@@ -2665,7 +2665,7 @@
         <v>54</v>
       </c>
       <c r="E39" t="n">
-        <v>1.62265053642428</v>
+        <v>1.62251695601847</v>
       </c>
       <c r="F39" t="n">
         <v>1.25</v>
@@ -2697,7 +2697,7 @@
         <v>55</v>
       </c>
       <c r="E40" t="n">
-        <v>1.60013213982278</v>
+        <v>1.60005710216352</v>
       </c>
       <c r="F40" t="n">
         <v>1.25</v>
@@ -2729,7 +2729,7 @@
         <v>56</v>
       </c>
       <c r="E41" t="n">
-        <v>1.43748532499241</v>
+        <v>1.43741300649558</v>
       </c>
       <c r="F41" t="n">
         <v>1.31</v>
@@ -2761,7 +2761,7 @@
         <v>57</v>
       </c>
       <c r="E42" t="n">
-        <v>1.14043498863364</v>
+        <v>1.14040517121881</v>
       </c>
       <c r="F42" t="n">
         <v>1.47</v>
@@ -2793,13 +2793,13 @@
         <v>58</v>
       </c>
       <c r="E43" t="n">
-        <v>1.0662432270765</v>
+        <v>1.06629108436953</v>
       </c>
       <c r="F43" t="n">
         <v>1.53</v>
       </c>
       <c r="G43" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="H43" t="n">
         <v>10.77</v>
@@ -2825,7 +2825,7 @@
         <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>0.954619958798151</v>
+        <v>0.954769941529156</v>
       </c>
       <c r="F44" t="n">
         <v>1.63</v>
@@ -2857,16 +2857,16 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>0.566278786512451</v>
+        <v>0.566130892107736</v>
       </c>
       <c r="F45" t="n">
         <v>2.31</v>
       </c>
       <c r="G45" t="n">
-        <v>9.01</v>
+        <v>9.02</v>
       </c>
       <c r="H45" t="n">
-        <v>50.21</v>
+        <v>50.25</v>
       </c>
       <c r="I45" t="s">
         <v>13</v>
@@ -2889,7 +2889,7 @@
         <v>61</v>
       </c>
       <c r="E46" t="n">
-        <v>0.559824801949174</v>
+        <v>0.559677684420676</v>
       </c>
       <c r="F46" t="n">
         <v>2.33</v>
@@ -2898,7 +2898,7 @@
         <v>9.19</v>
       </c>
       <c r="H46" t="n">
-        <v>51.73</v>
+        <v>51.76</v>
       </c>
       <c r="I46" t="s">
         <v>13</v>
@@ -2921,7 +2921,7 @@
         <v>62</v>
       </c>
       <c r="E47" t="n">
-        <v>0.529949214206662</v>
+        <v>0.529828854730528</v>
       </c>
       <c r="F47" t="n">
         <v>2.43</v>
@@ -2930,7 +2930,7 @@
         <v>10.06</v>
       </c>
       <c r="H47" t="n">
-        <v>59.66</v>
+        <v>59.7</v>
       </c>
       <c r="I47" t="s">
         <v>13</v>
@@ -2953,7 +2953,7 @@
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>0.443001123207011</v>
+        <v>0.442879253358156</v>
       </c>
       <c r="F48" t="n">
         <v>2.79</v>
@@ -2962,7 +2962,7 @@
         <v>13.62</v>
       </c>
       <c r="H48" t="n">
-        <v>95.85</v>
+        <v>95.92</v>
       </c>
       <c r="I48" t="s">
         <v>13</v>
@@ -2985,16 +2985,16 @@
         <v>64</v>
       </c>
       <c r="E49" t="n">
-        <v>0.344673142664439</v>
+        <v>0.344576179645181</v>
       </c>
       <c r="F49" t="n">
         <v>3.43</v>
       </c>
       <c r="G49" t="n">
-        <v>21.11</v>
+        <v>21.12</v>
       </c>
       <c r="H49" t="n">
-        <v>189.33</v>
+        <v>189.47</v>
       </c>
       <c r="I49" t="s">
         <v>13</v>
@@ -3017,16 +3017,16 @@
         <v>65</v>
       </c>
       <c r="E50" t="n">
-        <v>0.32451421636572</v>
+        <v>0.324420361174029</v>
       </c>
       <c r="F50" t="n">
         <v>3.61</v>
       </c>
       <c r="G50" t="n">
-        <v>23.51</v>
+        <v>23.52</v>
       </c>
       <c r="H50" t="n">
-        <v>223.5</v>
+        <v>223.68</v>
       </c>
       <c r="I50" t="s">
         <v>13</v>
@@ -3049,16 +3049,16 @@
         <v>66</v>
       </c>
       <c r="E51" t="n">
-        <v>0.298749736550858</v>
+        <v>0.29864507455497</v>
       </c>
       <c r="F51" t="n">
         <v>3.87</v>
       </c>
       <c r="G51" t="n">
-        <v>27.28</v>
+        <v>27.3</v>
       </c>
       <c r="H51" t="n">
-        <v>281.06</v>
+        <v>281.33</v>
       </c>
       <c r="I51" t="s">
         <v>13</v>
@@ -3081,16 +3081,16 @@
         <v>67</v>
       </c>
       <c r="E52" t="n">
-        <v>0.271430730681305</v>
+        <v>0.271351099591445</v>
       </c>
       <c r="F52" t="n">
         <v>4.21</v>
       </c>
       <c r="G52" t="n">
-        <v>32.46</v>
+        <v>32.48</v>
       </c>
       <c r="H52" t="n">
-        <v>367.26</v>
+        <v>367.56</v>
       </c>
       <c r="I52" t="s">
         <v>13</v>
@@ -3113,16 +3113,16 @@
         <v>68</v>
       </c>
       <c r="E53" t="n">
-        <v>0.269939555199826</v>
+        <v>0.269878247847007</v>
       </c>
       <c r="F53" t="n">
         <v>4.23</v>
       </c>
       <c r="G53" t="n">
-        <v>32.79</v>
+        <v>32.81</v>
       </c>
       <c r="H53" t="n">
-        <v>372.97</v>
+        <v>373.21</v>
       </c>
       <c r="I53" t="s">
         <v>13</v>
@@ -3145,16 +3145,16 @@
         <v>69</v>
       </c>
       <c r="E54" t="n">
-        <v>0.19621979072782</v>
+        <v>0.196175226247703</v>
       </c>
       <c r="F54" t="n">
         <v>5.61</v>
       </c>
       <c r="G54" t="n">
-        <v>59.14</v>
+        <v>59.17</v>
       </c>
       <c r="H54" t="n">
-        <v>919.43</v>
+        <v>920.03</v>
       </c>
       <c r="I54" t="s">
         <v>13</v>
@@ -3177,16 +3177,16 @@
         <v>70</v>
       </c>
       <c r="E55" t="n">
-        <v>0.169853452819981</v>
+        <v>0.169814876533702</v>
       </c>
       <c r="F55" t="n">
         <v>6.4</v>
       </c>
       <c r="G55" t="n">
-        <v>77.57</v>
+        <v>77.61</v>
       </c>
       <c r="H55" t="n">
-        <v>1390</v>
+        <v>1390.91</v>
       </c>
       <c r="I55" t="s">
         <v>13</v>
@@ -3209,7 +3209,7 @@
         <v>72</v>
       </c>
       <c r="E56" t="n">
-        <v>2.27291584273111</v>
+        <v>2.27307547403726</v>
       </c>
       <c r="F56" t="n">
         <v>1.11</v>
@@ -3241,7 +3241,7 @@
         <v>73</v>
       </c>
       <c r="E57" t="n">
-        <v>1.66802423952758</v>
+        <v>1.66818849132798</v>
       </c>
       <c r="F57" t="n">
         <v>1.23</v>
@@ -3273,7 +3273,7 @@
         <v>74</v>
       </c>
       <c r="E58" t="n">
-        <v>1.40062832737612</v>
+        <v>1.40080205787563</v>
       </c>
       <c r="F58" t="n">
         <v>1.33</v>
@@ -3305,7 +3305,7 @@
         <v>75</v>
       </c>
       <c r="E59" t="n">
-        <v>1.26195093105089</v>
+        <v>1.26218429322884</v>
       </c>
       <c r="F59" t="n">
         <v>1.39</v>
@@ -3337,7 +3337,7 @@
         <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>0.951349025085441</v>
+        <v>0.951514514900314</v>
       </c>
       <c r="F60" t="n">
         <v>1.63</v>
@@ -3369,7 +3369,7 @@
         <v>77</v>
       </c>
       <c r="E61" t="n">
-        <v>0.899839633293228</v>
+        <v>0.900006184850799</v>
       </c>
       <c r="F61" t="n">
         <v>1.69</v>
@@ -3378,7 +3378,7 @@
         <v>4.4</v>
       </c>
       <c r="H61" t="n">
-        <v>15.92</v>
+        <v>15.91</v>
       </c>
       <c r="I61" t="s">
         <v>13</v>
@@ -3401,7 +3401,7 @@
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>0.781886118297629</v>
+        <v>0.782057551296671</v>
       </c>
       <c r="F62" t="n">
         <v>1.84</v>
@@ -3410,7 +3410,7 @@
         <v>5.41</v>
       </c>
       <c r="H62" t="n">
-        <v>22.29</v>
+        <v>22.28</v>
       </c>
       <c r="I62" t="s">
         <v>13</v>
@@ -3433,16 +3433,16 @@
         <v>79</v>
       </c>
       <c r="E63" t="n">
-        <v>0.695783262186059</v>
+        <v>0.69625431519354</v>
       </c>
       <c r="F63" t="n">
         <v>1.99</v>
       </c>
       <c r="G63" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="H63" t="n">
-        <v>29.73</v>
+        <v>29.68</v>
       </c>
       <c r="I63" t="s">
         <v>13</v>
@@ -3465,7 +3465,7 @@
         <v>80</v>
       </c>
       <c r="E64" t="n">
-        <v>0.435537767742466</v>
+        <v>0.435488705957019</v>
       </c>
       <c r="F64" t="n">
         <v>2.83</v>
@@ -3474,7 +3474,7 @@
         <v>14.02</v>
       </c>
       <c r="H64" t="n">
-        <v>100.31</v>
+        <v>100.34</v>
       </c>
       <c r="I64" t="s">
         <v>13</v>
@@ -3497,7 +3497,7 @@
         <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>0.327495757596626</v>
+        <v>0.327462316224717</v>
       </c>
       <c r="F65" t="n">
         <v>3.58</v>
@@ -3506,7 +3506,7 @@
         <v>23.13</v>
       </c>
       <c r="H65" t="n">
-        <v>217.93</v>
+        <v>217.99</v>
       </c>
       <c r="I65" t="s">
         <v>13</v>
@@ -3529,7 +3529,7 @@
         <v>82</v>
       </c>
       <c r="E66" t="n">
-        <v>0.31874173142813</v>
+        <v>0.318701122346743</v>
       </c>
       <c r="F66" t="n">
         <v>3.66</v>
@@ -3538,7 +3538,7 @@
         <v>24.28</v>
       </c>
       <c r="H66" t="n">
-        <v>234.86</v>
+        <v>234.95</v>
       </c>
       <c r="I66" t="s">
         <v>13</v>
@@ -3561,16 +3561,16 @@
         <v>83</v>
       </c>
       <c r="E67" t="n">
-        <v>0.289228124206085</v>
+        <v>0.289212532788095</v>
       </c>
       <c r="F67" t="n">
         <v>3.98</v>
       </c>
       <c r="G67" t="n">
-        <v>28.92</v>
+        <v>28.93</v>
       </c>
       <c r="H67" t="n">
-        <v>307.57</v>
+        <v>307.62</v>
       </c>
       <c r="I67" t="s">
         <v>13</v>
@@ -3593,16 +3593,16 @@
         <v>84</v>
       </c>
       <c r="E68" t="n">
-        <v>0.279476376735735</v>
+        <v>0.279461311005112</v>
       </c>
       <c r="F68" t="n">
         <v>4.1</v>
       </c>
       <c r="G68" t="n">
-        <v>30.78</v>
+        <v>30.79</v>
       </c>
       <c r="H68" t="n">
-        <v>338.46</v>
+        <v>338.51</v>
       </c>
       <c r="I68" t="s">
         <v>13</v>
@@ -3625,16 +3625,16 @@
         <v>85</v>
       </c>
       <c r="E69" t="n">
-        <v>0.246692113490428</v>
+        <v>0.2466788150608</v>
       </c>
       <c r="F69" t="n">
         <v>4.57</v>
       </c>
       <c r="G69" t="n">
-        <v>38.67</v>
+        <v>38.68</v>
       </c>
       <c r="H69" t="n">
-        <v>480.33</v>
+        <v>480.4</v>
       </c>
       <c r="I69" t="s">
         <v>13</v>
@@ -3657,7 +3657,7 @@
         <v>86</v>
       </c>
       <c r="E70" t="n">
-        <v>0.245476441300386</v>
+        <v>0.245445637718261</v>
       </c>
       <c r="F70" t="n">
         <v>4.59</v>
@@ -3666,7 +3666,7 @@
         <v>39.03</v>
       </c>
       <c r="H70" t="n">
-        <v>487.06</v>
+        <v>487.23</v>
       </c>
       <c r="I70" t="s">
         <v>13</v>
@@ -3689,16 +3689,16 @@
         <v>87</v>
       </c>
       <c r="E71" t="n">
-        <v>0.235675300692841</v>
+        <v>0.2356419026065</v>
       </c>
       <c r="F71" t="n">
         <v>4.76</v>
       </c>
       <c r="G71" t="n">
-        <v>42.07</v>
+        <v>42.08</v>
       </c>
       <c r="H71" t="n">
-        <v>546.41</v>
+        <v>546.62</v>
       </c>
       <c r="I71" t="s">
         <v>13</v>
@@ -3721,16 +3721,16 @@
         <v>88</v>
       </c>
       <c r="E72" t="n">
-        <v>0.210152321414834</v>
+        <v>0.210123609094484</v>
       </c>
       <c r="F72" t="n">
         <v>5.28</v>
       </c>
       <c r="G72" t="n">
-        <v>52.03</v>
+        <v>52.05</v>
       </c>
       <c r="H72" t="n">
-        <v>756.2</v>
+        <v>756.49</v>
       </c>
       <c r="I72" t="s">
         <v>13</v>
@@ -3753,16 +3753,16 @@
         <v>89</v>
       </c>
       <c r="E73" t="n">
-        <v>0.153964386349704</v>
+        <v>0.153956086592861</v>
       </c>
       <c r="F73" t="n">
         <v>7.01</v>
       </c>
       <c r="G73" t="n">
-        <v>93.43</v>
+        <v>93.44</v>
       </c>
       <c r="H73" t="n">
-        <v>1844.36</v>
+        <v>1844.64</v>
       </c>
       <c r="I73" t="s">
         <v>13</v>
@@ -3785,7 +3785,7 @@
         <v>92</v>
       </c>
       <c r="E74" t="n">
-        <v>1.21147902907502</v>
+        <v>1.21106868732022</v>
       </c>
       <c r="F74" t="n">
         <v>1.42</v>
@@ -3794,7 +3794,7 @@
         <v>2.93</v>
       </c>
       <c r="H74" t="n">
-        <v>8.13</v>
+        <v>8.14</v>
       </c>
       <c r="I74" t="s">
         <v>13</v>
@@ -3817,16 +3817,16 @@
         <v>93</v>
       </c>
       <c r="E75" t="n">
-        <v>1.00371229369865</v>
+        <v>1.00315248162894</v>
       </c>
       <c r="F75" t="n">
         <v>1.58</v>
       </c>
       <c r="G75" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="H75" t="n">
-        <v>12.35</v>
+        <v>12.36</v>
       </c>
       <c r="I75" t="s">
         <v>13</v>
@@ -3849,7 +3849,7 @@
         <v>94</v>
       </c>
       <c r="E76" t="n">
-        <v>0.867358148403263</v>
+        <v>0.867322393183396</v>
       </c>
       <c r="F76" t="n">
         <v>1.72</v>
@@ -3858,7 +3858,7 @@
         <v>4.64</v>
       </c>
       <c r="H76" t="n">
-        <v>17.36</v>
+        <v>17.37</v>
       </c>
       <c r="I76" t="s">
         <v>13</v>
@@ -3881,7 +3881,7 @@
         <v>95</v>
       </c>
       <c r="E77" t="n">
-        <v>0.709034397081739</v>
+        <v>0.709010300890367</v>
       </c>
       <c r="F77" t="n">
         <v>1.97</v>
@@ -3913,7 +3913,7 @@
         <v>96</v>
       </c>
       <c r="E78" t="n">
-        <v>0.667433289368539</v>
+        <v>0.667347183926424</v>
       </c>
       <c r="F78" t="n">
         <v>2.05</v>
@@ -3922,7 +3922,7 @@
         <v>6.92</v>
       </c>
       <c r="H78" t="n">
-        <v>33</v>
+        <v>33.01</v>
       </c>
       <c r="I78" t="s">
         <v>13</v>
@@ -3945,7 +3945,7 @@
         <v>97</v>
       </c>
       <c r="E79" t="n">
-        <v>0.617012904658901</v>
+        <v>0.617083761718777</v>
       </c>
       <c r="F79" t="n">
         <v>2.17</v>
@@ -3954,7 +3954,7 @@
         <v>7.84</v>
       </c>
       <c r="H79" t="n">
-        <v>40.28</v>
+        <v>40.26</v>
       </c>
       <c r="I79" t="s">
         <v>13</v>
@@ -3977,7 +3977,7 @@
         <v>98</v>
       </c>
       <c r="E80" t="n">
-        <v>0.607873245810125</v>
+        <v>0.607904486615774</v>
       </c>
       <c r="F80" t="n">
         <v>2.2</v>
@@ -4009,7 +4009,7 @@
         <v>99</v>
       </c>
       <c r="E81" t="n">
-        <v>0.595264839450189</v>
+        <v>0.595317531789673</v>
       </c>
       <c r="F81" t="n">
         <v>2.23</v>
@@ -4018,7 +4018,7 @@
         <v>8.31</v>
       </c>
       <c r="H81" t="n">
-        <v>44.15</v>
+        <v>44.14</v>
       </c>
       <c r="I81" t="s">
         <v>13</v>
@@ -4041,7 +4041,7 @@
         <v>100</v>
       </c>
       <c r="E82" t="n">
-        <v>0.498690539770832</v>
+        <v>0.498701125482944</v>
       </c>
       <c r="F82" t="n">
         <v>2.55</v>
@@ -4050,7 +4050,7 @@
         <v>11.13</v>
       </c>
       <c r="H82" t="n">
-        <v>69.99</v>
+        <v>69.98</v>
       </c>
       <c r="I82" t="s">
         <v>13</v>
@@ -4073,16 +4073,16 @@
         <v>101</v>
       </c>
       <c r="E83" t="n">
-        <v>0.357866526622082</v>
+        <v>0.357649639104965</v>
       </c>
       <c r="F83" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="G83" t="n">
-        <v>19.75</v>
+        <v>19.77</v>
       </c>
       <c r="H83" t="n">
-        <v>170.8</v>
+        <v>171.08</v>
       </c>
       <c r="I83" t="s">
         <v>13</v>
@@ -4105,16 +4105,16 @@
         <v>102</v>
       </c>
       <c r="E84" t="n">
-        <v>0.352790683686581</v>
+        <v>0.352577918898899</v>
       </c>
       <c r="F84" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="G84" t="n">
-        <v>20.26</v>
+        <v>20.28</v>
       </c>
       <c r="H84" t="n">
-        <v>177.61</v>
+        <v>177.91</v>
       </c>
       <c r="I84" t="s">
         <v>13</v>
@@ -4137,16 +4137,16 @@
         <v>103</v>
       </c>
       <c r="E85" t="n">
-        <v>0.230666603780007</v>
+        <v>0.230511930435308</v>
       </c>
       <c r="F85" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="G85" t="n">
-        <v>43.77</v>
+        <v>43.83</v>
       </c>
       <c r="H85" t="n">
-        <v>580.62</v>
+        <v>581.72</v>
       </c>
       <c r="I85" t="s">
         <v>13</v>
@@ -4169,16 +4169,16 @@
         <v>104</v>
       </c>
       <c r="E86" t="n">
-        <v>0.145426987441522</v>
+        <v>0.145345876765342</v>
       </c>
       <c r="F86" t="n">
         <v>7.39</v>
       </c>
       <c r="G86" t="n">
-        <v>104.13</v>
+        <v>104.24</v>
       </c>
       <c r="H86" t="n">
-        <v>2174.76</v>
+        <v>2178.27</v>
       </c>
       <c r="I86" t="s">
         <v>13</v>
@@ -4201,16 +4201,16 @@
         <v>105</v>
       </c>
       <c r="E87" t="n">
-        <v>0.142343795339049</v>
+        <v>0.142264404287271</v>
       </c>
       <c r="F87" t="n">
         <v>7.54</v>
       </c>
       <c r="G87" t="n">
-        <v>108.47</v>
+        <v>108.59</v>
       </c>
       <c r="H87" t="n">
-        <v>2313.84</v>
+        <v>2317.58</v>
       </c>
       <c r="I87" t="s">
         <v>13</v>
@@ -4233,16 +4233,16 @@
         <v>106</v>
       </c>
       <c r="E88" t="n">
-        <v>0.100074941891133</v>
+        <v>0.100019125936006</v>
       </c>
       <c r="F88" t="n">
-        <v>10.5</v>
+        <v>10.51</v>
       </c>
       <c r="G88" t="n">
-        <v>213.42</v>
+        <v>213.65</v>
       </c>
       <c r="H88" t="n">
-        <v>6451.93</v>
+        <v>6462.47</v>
       </c>
       <c r="I88" t="s">
         <v>13</v>
@@ -4265,16 +4265,16 @@
         <v>107</v>
       </c>
       <c r="E89" t="n">
-        <v>0.091578353534612</v>
+        <v>0.0915272764800071</v>
       </c>
       <c r="F89" t="n">
         <v>11.43</v>
       </c>
       <c r="G89" t="n">
-        <v>253.43</v>
+        <v>253.7</v>
       </c>
       <c r="H89" t="n">
-        <v>8366.29</v>
+        <v>8379.99</v>
       </c>
       <c r="I89" t="s">
         <v>13</v>
@@ -4297,16 +4297,16 @@
         <v>108</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0821353870652086</v>
+        <v>0.0820895767455402</v>
       </c>
       <c r="F90" t="n">
-        <v>12.68</v>
+        <v>12.69</v>
       </c>
       <c r="G90" t="n">
-        <v>313.09</v>
+        <v>313.43</v>
       </c>
       <c r="H90" t="n">
-        <v>11514.85</v>
+        <v>11533.75</v>
       </c>
       <c r="I90" t="s">
         <v>13</v>
@@ -4329,16 +4329,16 @@
         <v>109</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0780380528856239</v>
+        <v>0.0779945278195504</v>
       </c>
       <c r="F91" t="n">
-        <v>13.32</v>
+        <v>13.33</v>
       </c>
       <c r="G91" t="n">
-        <v>345.89</v>
+        <v>346.27</v>
       </c>
       <c r="H91" t="n">
-        <v>13384.46</v>
+        <v>13406.44</v>
       </c>
       <c r="I91" t="s">
         <v>13</v>
@@ -4361,7 +4361,7 @@
         <v>111</v>
       </c>
       <c r="E92" t="n">
-        <v>2.25800863200733</v>
+        <v>2.25820845656544</v>
       </c>
       <c r="F92" t="n">
         <v>1.12</v>
@@ -4393,7 +4393,7 @@
         <v>112</v>
       </c>
       <c r="E93" t="n">
-        <v>1.82822982506333</v>
+        <v>1.82842902751644</v>
       </c>
       <c r="F93" t="n">
         <v>1.19</v>
@@ -4425,7 +4425,7 @@
         <v>113</v>
       </c>
       <c r="E94" t="n">
-        <v>1.7098873763378</v>
+        <v>1.71011992875817</v>
       </c>
       <c r="F94" t="n">
         <v>1.22</v>
@@ -4434,7 +4434,7 @@
         <v>1.96</v>
       </c>
       <c r="H94" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="I94" t="s">
         <v>13</v>
@@ -4457,7 +4457,7 @@
         <v>114</v>
       </c>
       <c r="E95" t="n">
-        <v>1.50018892890678</v>
+        <v>1.50088830969636</v>
       </c>
       <c r="F95" t="n">
         <v>1.29</v>
@@ -4489,7 +4489,7 @@
         <v>115</v>
       </c>
       <c r="E96" t="n">
-        <v>1.40314654443206</v>
+        <v>1.40339756244072</v>
       </c>
       <c r="F96" t="n">
         <v>1.33</v>
@@ -4521,7 +4521,7 @@
         <v>116</v>
       </c>
       <c r="E97" t="n">
-        <v>1.34980144423999</v>
+        <v>1.35029007390136</v>
       </c>
       <c r="F97" t="n">
         <v>1.35</v>
@@ -4553,7 +4553,7 @@
         <v>117</v>
       </c>
       <c r="E98" t="n">
-        <v>1.3313995661253</v>
+        <v>1.3312631272927</v>
       </c>
       <c r="F98" t="n">
         <v>1.36</v>
@@ -4585,7 +4585,7 @@
         <v>118</v>
       </c>
       <c r="E99" t="n">
-        <v>1.13793465363255</v>
+        <v>1.13818930691707</v>
       </c>
       <c r="F99" t="n">
         <v>1.47</v>
@@ -4594,7 +4594,7 @@
         <v>3.18</v>
       </c>
       <c r="H99" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
       <c r="I99" t="s">
         <v>13</v>
@@ -4617,7 +4617,7 @@
         <v>119</v>
       </c>
       <c r="E100" t="n">
-        <v>0.980393885243755</v>
+        <v>0.980690006413569</v>
       </c>
       <c r="F100" t="n">
         <v>1.6</v>
@@ -4626,7 +4626,7 @@
         <v>3.89</v>
       </c>
       <c r="H100" t="n">
-        <v>13.03</v>
+        <v>13.02</v>
       </c>
       <c r="I100" t="s">
         <v>13</v>
@@ -4649,7 +4649,7 @@
         <v>120</v>
       </c>
       <c r="E101" t="n">
-        <v>0.535087959076013</v>
+        <v>0.535013904619693</v>
       </c>
       <c r="F101" t="n">
         <v>2.41</v>
@@ -4658,7 +4658,7 @@
         <v>9.9</v>
       </c>
       <c r="H101" t="n">
-        <v>58.18</v>
+        <v>58.2</v>
       </c>
       <c r="I101" t="s">
         <v>13</v>
@@ -4681,16 +4681,16 @@
         <v>121</v>
       </c>
       <c r="E102" t="n">
-        <v>0.433311434694966</v>
+        <v>0.433245562639357</v>
       </c>
       <c r="F102" t="n">
         <v>2.84</v>
       </c>
       <c r="G102" t="n">
-        <v>14.14</v>
+        <v>14.15</v>
       </c>
       <c r="H102" t="n">
-        <v>101.7</v>
+        <v>101.74</v>
       </c>
       <c r="I102" t="s">
         <v>13</v>
@@ -4713,7 +4713,7 @@
         <v>122</v>
       </c>
       <c r="E103" t="n">
-        <v>0.430757209086018</v>
+        <v>0.430695350015619</v>
       </c>
       <c r="F103" t="n">
         <v>2.86</v>
@@ -4722,7 +4722,7 @@
         <v>14.29</v>
       </c>
       <c r="H103" t="n">
-        <v>103.33</v>
+        <v>103.37</v>
       </c>
       <c r="I103" t="s">
         <v>13</v>
@@ -4745,16 +4745,16 @@
         <v>123</v>
       </c>
       <c r="E104" t="n">
-        <v>0.321910274623967</v>
+        <v>0.321859201995858</v>
       </c>
       <c r="F104" t="n">
         <v>3.63</v>
       </c>
       <c r="G104" t="n">
-        <v>23.85</v>
+        <v>23.86</v>
       </c>
       <c r="H104" t="n">
-        <v>228.53</v>
+        <v>228.63</v>
       </c>
       <c r="I104" t="s">
         <v>13</v>
@@ -4777,7 +4777,7 @@
         <v>124</v>
       </c>
       <c r="E105" t="n">
-        <v>0.291796130050184</v>
+        <v>0.291743615680027</v>
       </c>
       <c r="F105" t="n">
         <v>3.95</v>
@@ -4786,7 +4786,7 @@
         <v>28.47</v>
       </c>
       <c r="H105" t="n">
-        <v>300.09</v>
+        <v>300.24</v>
       </c>
       <c r="I105" t="s">
         <v>13</v>
@@ -4809,7 +4809,7 @@
         <v>125</v>
       </c>
       <c r="E106" t="n">
-        <v>0.257773240762</v>
+        <v>0.257752139592647</v>
       </c>
       <c r="F106" t="n">
         <v>4.4</v>
@@ -4818,7 +4818,7 @@
         <v>35.68</v>
       </c>
       <c r="H106" t="n">
-        <v>424.47</v>
+        <v>424.57</v>
       </c>
       <c r="I106" t="s">
         <v>13</v>
@@ -4841,16 +4841,16 @@
         <v>126</v>
       </c>
       <c r="E107" t="n">
-        <v>0.213328676704705</v>
+        <v>0.213311213741824</v>
       </c>
       <c r="F107" t="n">
         <v>5.21</v>
       </c>
       <c r="G107" t="n">
-        <v>50.6</v>
+        <v>50.61</v>
       </c>
       <c r="H107" t="n">
-        <v>724.63</v>
+        <v>724.79</v>
       </c>
       <c r="I107" t="s">
         <v>13</v>
@@ -4873,16 +4873,16 @@
         <v>127</v>
       </c>
       <c r="E108" t="n">
-        <v>0.202482632110687</v>
+        <v>0.202466056998784</v>
       </c>
       <c r="F108" t="n">
         <v>5.46</v>
       </c>
       <c r="G108" t="n">
-        <v>55.77</v>
+        <v>55.78</v>
       </c>
       <c r="H108" t="n">
-        <v>840.63</v>
+        <v>840.82</v>
       </c>
       <c r="I108" t="s">
         <v>13</v>
@@ -4905,16 +4905,16 @@
         <v>128</v>
       </c>
       <c r="E109" t="n">
-        <v>0.182130775113771</v>
+        <v>0.182115865993186</v>
       </c>
       <c r="F109" t="n">
         <v>6.01</v>
       </c>
       <c r="G109" t="n">
-        <v>68.01</v>
+        <v>68.02</v>
       </c>
       <c r="H109" t="n">
-        <v>1137.76</v>
+        <v>1138.03</v>
       </c>
       <c r="I109" t="s">
         <v>13</v>
@@ -4937,7 +4937,7 @@
         <v>131</v>
       </c>
       <c r="E110" t="n">
-        <v>1.78883065971307</v>
+        <v>1.78900623723813</v>
       </c>
       <c r="F110" t="n">
         <v>1.2</v>
@@ -4969,7 +4969,7 @@
         <v>132</v>
       </c>
       <c r="E111" t="n">
-        <v>1.6588527856269</v>
+        <v>1.65902597931022</v>
       </c>
       <c r="F111" t="n">
         <v>1.24</v>
@@ -5001,7 +5001,7 @@
         <v>133</v>
       </c>
       <c r="E112" t="n">
-        <v>1.58401846704878</v>
+        <v>1.5842524137416</v>
       </c>
       <c r="F112" t="n">
         <v>1.26</v>
@@ -5010,7 +5010,7 @@
         <v>2.13</v>
       </c>
       <c r="H112" t="n">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
       <c r="I112" t="s">
         <v>13</v>
@@ -5033,7 +5033,7 @@
         <v>134</v>
       </c>
       <c r="E113" t="n">
-        <v>1.21910488174206</v>
+        <v>1.21932129159191</v>
       </c>
       <c r="F113" t="n">
         <v>1.42</v>
@@ -5065,7 +5065,7 @@
         <v>135</v>
       </c>
       <c r="E114" t="n">
-        <v>1.08885172487367</v>
+        <v>1.08913579307909</v>
       </c>
       <c r="F114" t="n">
         <v>1.51</v>
@@ -5097,7 +5097,7 @@
         <v>136</v>
       </c>
       <c r="E115" t="n">
-        <v>0.864697664635552</v>
+        <v>0.864640234741791</v>
       </c>
       <c r="F115" t="n">
         <v>1.73</v>
@@ -5129,7 +5129,7 @@
         <v>137</v>
       </c>
       <c r="E116" t="n">
-        <v>0.846277816207525</v>
+        <v>0.846525292486517</v>
       </c>
       <c r="F116" t="n">
         <v>1.75</v>
@@ -5138,7 +5138,7 @@
         <v>4.81</v>
       </c>
       <c r="H116" t="n">
-        <v>18.41</v>
+        <v>18.4</v>
       </c>
       <c r="I116" t="s">
         <v>13</v>
@@ -5161,7 +5161,7 @@
         <v>138</v>
       </c>
       <c r="E117" t="n">
-        <v>0.845741616745546</v>
+        <v>0.845703160519456</v>
       </c>
       <c r="F117" t="n">
         <v>1.75</v>
@@ -5193,7 +5193,7 @@
         <v>139</v>
       </c>
       <c r="E118" t="n">
-        <v>0.74470653755096</v>
+        <v>0.744937418777094</v>
       </c>
       <c r="F118" t="n">
         <v>1.9</v>
@@ -5202,7 +5202,7 @@
         <v>5.83</v>
       </c>
       <c r="H118" t="n">
-        <v>25.12</v>
+        <v>25.1</v>
       </c>
       <c r="I118" t="s">
         <v>13</v>
@@ -5225,7 +5225,7 @@
         <v>140</v>
       </c>
       <c r="E119" t="n">
-        <v>0.395479451939577</v>
+        <v>0.395441561272928</v>
       </c>
       <c r="F119" t="n">
         <v>3.06</v>
@@ -5234,7 +5234,7 @@
         <v>16.57</v>
       </c>
       <c r="H119" t="n">
-        <v>130.1</v>
+        <v>130.14</v>
       </c>
       <c r="I119" t="s">
         <v>13</v>
@@ -5257,7 +5257,7 @@
         <v>141</v>
       </c>
       <c r="E120" t="n">
-        <v>0.336547926051916</v>
+        <v>0.336532623076542</v>
       </c>
       <c r="F120" t="n">
         <v>3.5</v>
@@ -5266,7 +5266,7 @@
         <v>22.03</v>
       </c>
       <c r="H120" t="n">
-        <v>202.16</v>
+        <v>202.18</v>
       </c>
       <c r="I120" t="s">
         <v>13</v>
@@ -5289,16 +5289,16 @@
         <v>142</v>
       </c>
       <c r="E121" t="n">
-        <v>0.324197397951412</v>
+        <v>0.324156299821521</v>
       </c>
       <c r="F121" t="n">
         <v>3.61</v>
       </c>
       <c r="G121" t="n">
-        <v>23.55</v>
+        <v>23.56</v>
       </c>
       <c r="H121" t="n">
-        <v>224.1</v>
+        <v>224.18</v>
       </c>
       <c r="I121" t="s">
         <v>13</v>
@@ -5321,7 +5321,7 @@
         <v>143</v>
       </c>
       <c r="E122" t="n">
-        <v>0.307679670498537</v>
+        <v>0.307647555061358</v>
       </c>
       <c r="F122" t="n">
         <v>3.78</v>
@@ -5330,7 +5330,7 @@
         <v>25.87</v>
       </c>
       <c r="H122" t="n">
-        <v>258.99</v>
+        <v>259.07</v>
       </c>
       <c r="I122" t="s">
         <v>13</v>
@@ -5353,7 +5353,7 @@
         <v>144</v>
       </c>
       <c r="E123" t="n">
-        <v>0.30612297779303</v>
+        <v>0.306086978783765</v>
       </c>
       <c r="F123" t="n">
         <v>3.79</v>
@@ -5362,7 +5362,7 @@
         <v>26.11</v>
       </c>
       <c r="H123" t="n">
-        <v>262.66</v>
+        <v>262.75</v>
       </c>
       <c r="I123" t="s">
         <v>13</v>
@@ -5385,16 +5385,16 @@
         <v>145</v>
       </c>
       <c r="E124" t="n">
-        <v>0.271580919132481</v>
+        <v>0.271546945732338</v>
       </c>
       <c r="F124" t="n">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="G124" t="n">
-        <v>32.43</v>
+        <v>32.44</v>
       </c>
       <c r="H124" t="n">
-        <v>366.69</v>
+        <v>366.82</v>
       </c>
       <c r="I124" t="s">
         <v>13</v>
@@ -5417,16 +5417,16 @@
         <v>146</v>
       </c>
       <c r="E125" t="n">
-        <v>0.183760791969835</v>
+        <v>0.183728783293214</v>
       </c>
       <c r="F125" t="n">
         <v>5.96</v>
       </c>
       <c r="G125" t="n">
-        <v>66.88</v>
+        <v>66.91</v>
       </c>
       <c r="H125" t="n">
-        <v>1109.1</v>
+        <v>1109.65</v>
       </c>
       <c r="I125" t="s">
         <v>13</v>
@@ -5449,16 +5449,16 @@
         <v>147</v>
       </c>
       <c r="E126" t="n">
-        <v>0.15426815721375</v>
+        <v>0.154261142575928</v>
       </c>
       <c r="F126" t="n">
         <v>7</v>
       </c>
       <c r="G126" t="n">
-        <v>93.08</v>
+        <v>93.09</v>
       </c>
       <c r="H126" t="n">
-        <v>1833.9</v>
+        <v>1834.14</v>
       </c>
       <c r="I126" t="s">
         <v>13</v>
@@ -5481,16 +5481,16 @@
         <v>148</v>
       </c>
       <c r="E127" t="n">
-        <v>0.102663728524477</v>
+        <v>0.102659060361675</v>
       </c>
       <c r="F127" t="n">
         <v>10.25</v>
       </c>
       <c r="G127" t="n">
-        <v>203.14</v>
+        <v>203.16</v>
       </c>
       <c r="H127" t="n">
-        <v>5987.61</v>
+        <v>5988.41</v>
       </c>
       <c r="I127" t="s">
         <v>13</v>
@@ -5513,7 +5513,7 @@
         <v>150</v>
       </c>
       <c r="E128" t="n">
-        <v>1.37458569938787</v>
+        <v>1.37443197280739</v>
       </c>
       <c r="F128" t="n">
         <v>1.34</v>
@@ -5522,7 +5522,7 @@
         <v>2.5</v>
       </c>
       <c r="H128" t="n">
-        <v>6.23</v>
+        <v>6.24</v>
       </c>
       <c r="I128" t="s">
         <v>13</v>
@@ -5545,7 +5545,7 @@
         <v>151</v>
       </c>
       <c r="E129" t="n">
-        <v>1.29199948744332</v>
+        <v>1.2918425411144</v>
       </c>
       <c r="F129" t="n">
         <v>1.38</v>
@@ -5577,16 +5577,16 @@
         <v>152</v>
       </c>
       <c r="E130" t="n">
-        <v>1.01550779018311</v>
+        <v>1.01518865784657</v>
       </c>
       <c r="F130" t="n">
         <v>1.57</v>
       </c>
       <c r="G130" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="H130" t="n">
-        <v>12.02</v>
+        <v>12.03</v>
       </c>
       <c r="I130" t="s">
         <v>13</v>
@@ -5609,10 +5609,10 @@
         <v>153</v>
       </c>
       <c r="E131" t="n">
-        <v>0.891510052177326</v>
+        <v>0.891535387523654</v>
       </c>
       <c r="F131" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G131" t="n">
         <v>4.46</v>
@@ -5641,7 +5641,7 @@
         <v>154</v>
       </c>
       <c r="E132" t="n">
-        <v>0.881239886066207</v>
+        <v>0.881333183378775</v>
       </c>
       <c r="F132" t="n">
         <v>1.71</v>
@@ -5673,7 +5673,7 @@
         <v>155</v>
       </c>
       <c r="E133" t="n">
-        <v>0.749543763127755</v>
+        <v>0.749537550129479</v>
       </c>
       <c r="F133" t="n">
         <v>1.9</v>
@@ -5705,7 +5705,7 @@
         <v>156</v>
       </c>
       <c r="E134" t="n">
-        <v>0.641643371294221</v>
+        <v>0.641832260886132</v>
       </c>
       <c r="F134" t="n">
         <v>2.11</v>
@@ -5714,7 +5714,7 @@
         <v>7.36</v>
       </c>
       <c r="H134" t="n">
-        <v>36.46</v>
+        <v>36.43</v>
       </c>
       <c r="I134" t="s">
         <v>13</v>
@@ -5737,16 +5737,16 @@
         <v>157</v>
       </c>
       <c r="E135" t="n">
-        <v>0.630543528676216</v>
+        <v>0.630335333657752</v>
       </c>
       <c r="F135" t="n">
         <v>2.14</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57</v>
+        <v>7.58</v>
       </c>
       <c r="H135" t="n">
-        <v>38.11</v>
+        <v>38.14</v>
       </c>
       <c r="I135" t="s">
         <v>13</v>
@@ -5769,7 +5769,7 @@
         <v>158</v>
       </c>
       <c r="E136" t="n">
-        <v>0.609704267057993</v>
+        <v>0.609830591361404</v>
       </c>
       <c r="F136" t="n">
         <v>2.19</v>
@@ -5778,7 +5778,7 @@
         <v>7.99</v>
       </c>
       <c r="H136" t="n">
-        <v>41.52</v>
+        <v>41.5</v>
       </c>
       <c r="I136" t="s">
         <v>13</v>
@@ -5801,7 +5801,7 @@
         <v>159</v>
       </c>
       <c r="E137" t="n">
-        <v>0.608447268371338</v>
+        <v>0.608266096354695</v>
       </c>
       <c r="F137" t="n">
         <v>2.19</v>
@@ -5810,7 +5810,7 @@
         <v>8.02</v>
       </c>
       <c r="H137" t="n">
-        <v>41.74</v>
+        <v>41.77</v>
       </c>
       <c r="I137" t="s">
         <v>13</v>
@@ -5833,16 +5833,16 @@
         <v>160</v>
       </c>
       <c r="E138" t="n">
-        <v>0.607620107256993</v>
+        <v>0.607774050816055</v>
       </c>
       <c r="F138" t="n">
         <v>2.2</v>
       </c>
       <c r="G138" t="n">
-        <v>8.04</v>
+        <v>8.03</v>
       </c>
       <c r="H138" t="n">
-        <v>41.89</v>
+        <v>41.86</v>
       </c>
       <c r="I138" t="s">
         <v>13</v>
@@ -5865,16 +5865,16 @@
         <v>161</v>
       </c>
       <c r="E139" t="n">
-        <v>0.40259759517684</v>
+        <v>0.402477717215337</v>
       </c>
       <c r="F139" t="n">
         <v>3.02</v>
       </c>
       <c r="G139" t="n">
-        <v>16.06</v>
+        <v>16.07</v>
       </c>
       <c r="H139" t="n">
-        <v>123.97</v>
+        <v>124.07</v>
       </c>
       <c r="I139" t="s">
         <v>13</v>
@@ -5897,16 +5897,16 @@
         <v>162</v>
       </c>
       <c r="E140" t="n">
-        <v>0.385249941774244</v>
+        <v>0.385118484033602</v>
       </c>
       <c r="F140" t="n">
         <v>3.13</v>
       </c>
       <c r="G140" t="n">
-        <v>17.35</v>
+        <v>17.36</v>
       </c>
       <c r="H140" t="n">
-        <v>139.69</v>
+        <v>139.82</v>
       </c>
       <c r="I140" t="s">
         <v>13</v>
@@ -5929,16 +5929,16 @@
         <v>163</v>
       </c>
       <c r="E141" t="n">
-        <v>0.380505316049103</v>
+        <v>0.380374331448174</v>
       </c>
       <c r="F141" t="n">
         <v>3.16</v>
       </c>
       <c r="G141" t="n">
-        <v>17.73</v>
+        <v>17.74</v>
       </c>
       <c r="H141" t="n">
-        <v>144.48</v>
+        <v>144.61</v>
       </c>
       <c r="I141" t="s">
         <v>13</v>
@@ -5961,16 +5961,16 @@
         <v>164</v>
       </c>
       <c r="E142" t="n">
-        <v>0.261245353292283</v>
+        <v>0.261136441181371</v>
       </c>
       <c r="F142" t="n">
         <v>4.35</v>
       </c>
       <c r="G142" t="n">
-        <v>34.81</v>
+        <v>34.84</v>
       </c>
       <c r="H142" t="n">
-        <v>408.82</v>
+        <v>409.3</v>
       </c>
       <c r="I142" t="s">
         <v>13</v>
@@ -5993,16 +5993,16 @@
         <v>165</v>
       </c>
       <c r="E143" t="n">
-        <v>0.226047071161826</v>
+        <v>0.225962817366282</v>
       </c>
       <c r="F143" t="n">
         <v>4.94</v>
       </c>
       <c r="G143" t="n">
-        <v>45.44</v>
+        <v>45.47</v>
       </c>
       <c r="H143" t="n">
-        <v>614.84</v>
+        <v>615.49</v>
       </c>
       <c r="I143" t="s">
         <v>13</v>
@@ -6025,16 +6025,16 @@
         <v>166</v>
       </c>
       <c r="E144" t="n">
-        <v>0.171484557906616</v>
+        <v>0.171433496451016</v>
       </c>
       <c r="F144" t="n">
         <v>6.35</v>
       </c>
       <c r="G144" t="n">
-        <v>76.19</v>
+        <v>76.23</v>
       </c>
       <c r="H144" t="n">
-        <v>1352.35</v>
+        <v>1353.51</v>
       </c>
       <c r="I144" t="s">
         <v>13</v>
@@ -6057,16 +6057,16 @@
         <v>167</v>
       </c>
       <c r="E145" t="n">
-        <v>0.131051712661375</v>
+        <v>0.131012690540147</v>
       </c>
       <c r="F145" t="n">
         <v>8.14</v>
       </c>
       <c r="G145" t="n">
-        <v>127.02</v>
+        <v>127.09</v>
       </c>
       <c r="H145" t="n">
-        <v>2940.14</v>
+        <v>2942.69</v>
       </c>
       <c r="I145" t="s">
         <v>13</v>
@@ -6089,7 +6089,7 @@
         <v>170</v>
       </c>
       <c r="E146" t="n">
-        <v>1.51747698763049</v>
+        <v>1.51744091022657</v>
       </c>
       <c r="F146" t="n">
         <v>1.28</v>
@@ -6121,7 +6121,7 @@
         <v>171</v>
       </c>
       <c r="E147" t="n">
-        <v>0.98632941573758</v>
+        <v>0.986414120842694</v>
       </c>
       <c r="F147" t="n">
         <v>1.59</v>
@@ -6153,7 +6153,7 @@
         <v>172</v>
       </c>
       <c r="E148" t="n">
-        <v>0.837946278882307</v>
+        <v>0.838116944219314</v>
       </c>
       <c r="F148" t="n">
         <v>1.76</v>
@@ -6162,7 +6162,7 @@
         <v>4.88</v>
       </c>
       <c r="H148" t="n">
-        <v>18.86</v>
+        <v>18.85</v>
       </c>
       <c r="I148" t="s">
         <v>13</v>
@@ -6185,7 +6185,7 @@
         <v>173</v>
       </c>
       <c r="E149" t="n">
-        <v>0.728503002618658</v>
+        <v>0.728364812091525</v>
       </c>
       <c r="F149" t="n">
         <v>1.93</v>
@@ -6194,7 +6194,7 @@
         <v>6.03</v>
       </c>
       <c r="H149" t="n">
-        <v>26.52</v>
+        <v>26.54</v>
       </c>
       <c r="I149" t="s">
         <v>13</v>
@@ -6217,7 +6217,7 @@
         <v>174</v>
       </c>
       <c r="E150" t="n">
-        <v>0.717964018453761</v>
+        <v>0.718121447436495</v>
       </c>
       <c r="F150" t="n">
         <v>1.95</v>
@@ -6226,7 +6226,7 @@
         <v>6.17</v>
       </c>
       <c r="H150" t="n">
-        <v>27.5</v>
+        <v>27.49</v>
       </c>
       <c r="I150" t="s">
         <v>13</v>
@@ -6249,7 +6249,7 @@
         <v>175</v>
       </c>
       <c r="E151" t="n">
-        <v>0.703389137346057</v>
+        <v>0.703696616218723</v>
       </c>
       <c r="F151" t="n">
         <v>1.98</v>
@@ -6258,7 +6258,7 @@
         <v>6.37</v>
       </c>
       <c r="H151" t="n">
-        <v>28.94</v>
+        <v>28.91</v>
       </c>
       <c r="I151" t="s">
         <v>13</v>
@@ -6281,7 +6281,7 @@
         <v>176</v>
       </c>
       <c r="E152" t="n">
-        <v>0.680267546760492</v>
+        <v>0.680562530239794</v>
       </c>
       <c r="F152" t="n">
         <v>2.03</v>
@@ -6290,7 +6290,7 @@
         <v>6.71</v>
       </c>
       <c r="H152" t="n">
-        <v>31.46</v>
+        <v>31.43</v>
       </c>
       <c r="I152" t="s">
         <v>13</v>
@@ -6313,7 +6313,7 @@
         <v>177</v>
       </c>
       <c r="E153" t="n">
-        <v>0.60228083032565</v>
+        <v>0.602437325173111</v>
       </c>
       <c r="F153" t="n">
         <v>2.21</v>
@@ -6322,7 +6322,7 @@
         <v>8.15</v>
       </c>
       <c r="H153" t="n">
-        <v>42.84</v>
+        <v>42.81</v>
       </c>
       <c r="I153" t="s">
         <v>13</v>
@@ -6345,16 +6345,16 @@
         <v>178</v>
       </c>
       <c r="E154" t="n">
-        <v>0.581526122854658</v>
+        <v>0.581822602784851</v>
       </c>
       <c r="F154" t="n">
         <v>2.27</v>
       </c>
       <c r="G154" t="n">
-        <v>8.63</v>
+        <v>8.62</v>
       </c>
       <c r="H154" t="n">
-        <v>46.88</v>
+        <v>46.82</v>
       </c>
       <c r="I154" t="s">
         <v>13</v>
@@ -6377,16 +6377,16 @@
         <v>179</v>
       </c>
       <c r="E155" t="n">
-        <v>0.406063207204931</v>
+        <v>0.406266336841939</v>
       </c>
       <c r="F155" t="n">
         <v>3</v>
       </c>
       <c r="G155" t="n">
-        <v>15.83</v>
+        <v>15.81</v>
       </c>
       <c r="H155" t="n">
-        <v>121.13</v>
+        <v>120.97</v>
       </c>
       <c r="I155" t="s">
         <v>13</v>
@@ -6409,7 +6409,7 @@
         <v>180</v>
       </c>
       <c r="E156" t="n">
-        <v>0.30663803997396</v>
+        <v>0.306587109321969</v>
       </c>
       <c r="F156" t="n">
         <v>3.79</v>
@@ -6418,7 +6418,7 @@
         <v>26.03</v>
       </c>
       <c r="H156" t="n">
-        <v>261.44</v>
+        <v>261.56</v>
       </c>
       <c r="I156" t="s">
         <v>13</v>
@@ -6441,16 +6441,16 @@
         <v>181</v>
       </c>
       <c r="E157" t="n">
-        <v>0.284189452431615</v>
+        <v>0.284142250348982</v>
       </c>
       <c r="F157" t="n">
         <v>4.04</v>
       </c>
       <c r="G157" t="n">
-        <v>29.86</v>
+        <v>29.87</v>
       </c>
       <c r="H157" t="n">
-        <v>323.02</v>
+        <v>323.17</v>
       </c>
       <c r="I157" t="s">
         <v>13</v>
@@ -6473,16 +6473,16 @@
         <v>182</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2693435997536</v>
+        <v>0.269298863473827</v>
       </c>
       <c r="F158" t="n">
         <v>4.24</v>
       </c>
       <c r="G158" t="n">
-        <v>32.92</v>
+        <v>32.93</v>
       </c>
       <c r="H158" t="n">
-        <v>375.29</v>
+        <v>375.46</v>
       </c>
       <c r="I158" t="s">
         <v>13</v>
@@ -6505,16 +6505,16 @@
         <v>183</v>
       </c>
       <c r="E159" t="n">
-        <v>0.252518483691506</v>
+        <v>0.252460966230495</v>
       </c>
       <c r="F159" t="n">
         <v>4.48</v>
       </c>
       <c r="G159" t="n">
-        <v>37.05</v>
+        <v>37.06</v>
       </c>
       <c r="H159" t="n">
-        <v>449.78</v>
+        <v>450.06</v>
       </c>
       <c r="I159" t="s">
         <v>13</v>
@@ -6537,16 +6537,16 @@
         <v>184</v>
       </c>
       <c r="E160" t="n">
-        <v>0.18807746188024</v>
+        <v>0.188030362265354</v>
       </c>
       <c r="F160" t="n">
         <v>5.83</v>
       </c>
       <c r="G160" t="n">
-        <v>64.03</v>
+        <v>64.06</v>
       </c>
       <c r="H160" t="n">
-        <v>1037.79</v>
+        <v>1038.54</v>
       </c>
       <c r="I160" t="s">
         <v>13</v>
@@ -6569,16 +6569,16 @@
         <v>185</v>
       </c>
       <c r="E161" t="n">
-        <v>0.156415686070069</v>
+        <v>0.156389706407292</v>
       </c>
       <c r="F161" t="n">
         <v>6.91</v>
       </c>
       <c r="G161" t="n">
-        <v>90.67</v>
+        <v>90.7</v>
       </c>
       <c r="H161" t="n">
-        <v>1762.21</v>
+        <v>1763.05</v>
       </c>
       <c r="I161" t="s">
         <v>13</v>
@@ -6601,16 +6601,16 @@
         <v>186</v>
       </c>
       <c r="E162" t="n">
-        <v>0.155728040068052</v>
+        <v>0.155687206228101</v>
       </c>
       <c r="F162" t="n">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
       <c r="G162" t="n">
-        <v>91.43</v>
+        <v>91.48</v>
       </c>
       <c r="H162" t="n">
-        <v>1784.74</v>
+        <v>1786.09</v>
       </c>
       <c r="I162" t="s">
         <v>13</v>
@@ -6633,16 +6633,16 @@
         <v>187</v>
       </c>
       <c r="E163" t="n">
-        <v>0.0926763876874697</v>
+        <v>0.0926609947217127</v>
       </c>
       <c r="F163" t="n">
         <v>11.3</v>
       </c>
       <c r="G163" t="n">
-        <v>247.64</v>
+        <v>247.72</v>
       </c>
       <c r="H163" t="n">
-        <v>8079.05</v>
+        <v>8082.98</v>
       </c>
       <c r="I163" t="s">
         <v>13</v>
@@ -6665,7 +6665,7 @@
         <v>189</v>
       </c>
       <c r="E164" t="n">
-        <v>2.25889173093496</v>
+        <v>2.25852778401473</v>
       </c>
       <c r="F164" t="n">
         <v>1.12</v>
@@ -6697,7 +6697,7 @@
         <v>190</v>
       </c>
       <c r="E165" t="n">
-        <v>1.56469906189508</v>
+        <v>1.56459765882402</v>
       </c>
       <c r="F165" t="n">
         <v>1.26</v>
@@ -6729,7 +6729,7 @@
         <v>191</v>
       </c>
       <c r="E166" t="n">
-        <v>1.20513677922709</v>
+        <v>1.20507420727449</v>
       </c>
       <c r="F166" t="n">
         <v>1.43</v>
@@ -6761,7 +6761,7 @@
         <v>192</v>
       </c>
       <c r="E167" t="n">
-        <v>1.20175698819679</v>
+        <v>1.20139714120554</v>
       </c>
       <c r="F167" t="n">
         <v>1.43</v>
@@ -6770,7 +6770,7 @@
         <v>2.96</v>
       </c>
       <c r="H167" t="n">
-        <v>8.27</v>
+        <v>8.28</v>
       </c>
       <c r="I167" t="s">
         <v>13</v>
@@ -6793,7 +6793,7 @@
         <v>193</v>
       </c>
       <c r="E168" t="n">
-        <v>1.05007654399624</v>
+        <v>1.05005802036278</v>
       </c>
       <c r="F168" t="n">
         <v>1.54</v>
@@ -6825,7 +6825,7 @@
         <v>194</v>
       </c>
       <c r="E169" t="n">
-        <v>1.03763198891062</v>
+        <v>1.0373176113907</v>
       </c>
       <c r="F169" t="n">
         <v>1.55</v>
@@ -6834,7 +6834,7 @@
         <v>3.6</v>
       </c>
       <c r="H169" t="n">
-        <v>11.45</v>
+        <v>11.46</v>
       </c>
       <c r="I169" t="s">
         <v>13</v>
@@ -6857,7 +6857,7 @@
         <v>195</v>
       </c>
       <c r="E170" t="n">
-        <v>0.980383451296295</v>
+        <v>0.980672909826364</v>
       </c>
       <c r="F170" t="n">
         <v>1.6</v>
@@ -6866,7 +6866,7 @@
         <v>3.89</v>
       </c>
       <c r="H170" t="n">
-        <v>13.03</v>
+        <v>13.02</v>
       </c>
       <c r="I170" t="s">
         <v>13</v>
@@ -6889,7 +6889,7 @@
         <v>196</v>
       </c>
       <c r="E171" t="n">
-        <v>0.901060078574029</v>
+        <v>0.901128831431512</v>
       </c>
       <c r="F171" t="n">
         <v>1.68</v>
@@ -6898,7 +6898,7 @@
         <v>4.39</v>
       </c>
       <c r="H171" t="n">
-        <v>15.87</v>
+        <v>15.86</v>
       </c>
       <c r="I171" t="s">
         <v>13</v>
@@ -6921,7 +6921,7 @@
         <v>197</v>
       </c>
       <c r="E172" t="n">
-        <v>0.778744834491832</v>
+        <v>0.778883546070897</v>
       </c>
       <c r="F172" t="n">
         <v>1.85</v>
@@ -6930,7 +6930,7 @@
         <v>5.45</v>
       </c>
       <c r="H172" t="n">
-        <v>22.51</v>
+        <v>22.5</v>
       </c>
       <c r="I172" t="s">
         <v>13</v>
@@ -6953,7 +6953,7 @@
         <v>198</v>
       </c>
       <c r="E173" t="n">
-        <v>0.774265851620471</v>
+        <v>0.774399451336263</v>
       </c>
       <c r="F173" t="n">
         <v>1.86</v>
@@ -6962,7 +6962,7 @@
         <v>5.49</v>
       </c>
       <c r="H173" t="n">
-        <v>22.83</v>
+        <v>22.82</v>
       </c>
       <c r="I173" t="s">
         <v>13</v>
@@ -6985,7 +6985,7 @@
         <v>199</v>
       </c>
       <c r="E174" t="n">
-        <v>0.649391932351337</v>
+        <v>0.649468157677254</v>
       </c>
       <c r="F174" t="n">
         <v>2.09</v>
@@ -6994,7 +6994,7 @@
         <v>7.22</v>
       </c>
       <c r="H174" t="n">
-        <v>35.37</v>
+        <v>35.36</v>
       </c>
       <c r="I174" t="s">
         <v>13</v>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="E175" t="n">
-        <v>0.627302098835957</v>
+        <v>0.627377743548761</v>
       </c>
       <c r="F175" t="n">
         <v>2.15</v>
       </c>
       <c r="G175" t="n">
-        <v>7.64</v>
+        <v>7.63</v>
       </c>
       <c r="H175" t="n">
-        <v>38.61</v>
+        <v>38.6</v>
       </c>
       <c r="I175" t="s">
         <v>13</v>
@@ -7049,7 +7049,7 @@
         <v>201</v>
       </c>
       <c r="E176" t="n">
-        <v>0.406812530945988</v>
+        <v>0.406697355344781</v>
       </c>
       <c r="F176" t="n">
         <v>2.99</v>
@@ -7058,7 +7058,7 @@
         <v>15.78</v>
       </c>
       <c r="H176" t="n">
-        <v>120.53</v>
+        <v>120.62</v>
       </c>
       <c r="I176" t="s">
         <v>13</v>
@@ -7081,16 +7081,16 @@
         <v>202</v>
       </c>
       <c r="E177" t="n">
-        <v>0.373186455947682</v>
+        <v>0.373059755914133</v>
       </c>
       <c r="F177" t="n">
         <v>3.21</v>
       </c>
       <c r="G177" t="n">
-        <v>18.35</v>
+        <v>18.36</v>
       </c>
       <c r="H177" t="n">
-        <v>152.32</v>
+        <v>152.47</v>
       </c>
       <c r="I177" t="s">
         <v>13</v>
@@ -7113,16 +7113,16 @@
         <v>203</v>
       </c>
       <c r="E178" t="n">
-        <v>0.345941860630204</v>
+        <v>0.345812424677558</v>
       </c>
       <c r="F178" t="n">
         <v>3.42</v>
       </c>
       <c r="G178" t="n">
-        <v>20.98</v>
+        <v>20.99</v>
       </c>
       <c r="H178" t="n">
-        <v>187.43</v>
+        <v>187.62</v>
       </c>
       <c r="I178" t="s">
         <v>13</v>
@@ -7145,16 +7145,16 @@
         <v>204</v>
       </c>
       <c r="E179" t="n">
-        <v>0.244041812837186</v>
+        <v>0.243972720416537</v>
       </c>
       <c r="F179" t="n">
         <v>4.62</v>
       </c>
       <c r="G179" t="n">
-        <v>39.45</v>
+        <v>39.47</v>
       </c>
       <c r="H179" t="n">
-        <v>495.17</v>
+        <v>495.57</v>
       </c>
       <c r="I179" t="s">
         <v>13</v>
@@ -7177,16 +7177,16 @@
         <v>205</v>
       </c>
       <c r="E180" t="n">
-        <v>0.23061263784941</v>
+        <v>0.230521346002376</v>
       </c>
       <c r="F180" t="n">
         <v>4.86</v>
       </c>
       <c r="G180" t="n">
-        <v>43.79</v>
+        <v>43.82</v>
       </c>
       <c r="H180" t="n">
-        <v>581</v>
+        <v>581.65</v>
       </c>
       <c r="I180" t="s">
         <v>13</v>
@@ -7209,16 +7209,16 @@
         <v>206</v>
       </c>
       <c r="E181" t="n">
-        <v>0.118343809015587</v>
+        <v>0.118310303854572</v>
       </c>
       <c r="F181" t="n">
         <v>8.96</v>
       </c>
       <c r="G181" t="n">
-        <v>154.47</v>
+        <v>154.55</v>
       </c>
       <c r="H181" t="n">
-        <v>3955</v>
+        <v>3958.27</v>
       </c>
       <c r="I181" t="s">
         <v>13</v>
@@ -7241,16 +7241,16 @@
         <v>209</v>
       </c>
       <c r="E182" t="n">
-        <v>1.872055207718</v>
+        <v>1.82257005980724</v>
       </c>
       <c r="F182" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G182" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="H182" t="n">
-        <v>3.46</v>
+        <v>3.63</v>
       </c>
       <c r="I182" t="s">
         <v>13</v>
@@ -7273,16 +7273,16 @@
         <v>210</v>
       </c>
       <c r="E183" t="n">
-        <v>1.846738347772</v>
+        <v>1.79791192670927</v>
       </c>
       <c r="F183" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G183" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H183" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="I183" t="s">
         <v>13</v>
@@ -7305,16 +7305,16 @@
         <v>211</v>
       </c>
       <c r="E184" t="n">
-        <v>1.68593050104778</v>
+        <v>1.64138630613912</v>
       </c>
       <c r="F184" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G184" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="H184" t="n">
-        <v>4.18</v>
+        <v>4.4</v>
       </c>
       <c r="I184" t="s">
         <v>13</v>
@@ -7337,16 +7337,16 @@
         <v>212</v>
       </c>
       <c r="E185" t="n">
-        <v>1.46068894983809</v>
+        <v>1.42209943845078</v>
       </c>
       <c r="F185" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="G185" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="H185" t="n">
-        <v>5.51</v>
+        <v>5.82</v>
       </c>
       <c r="I185" t="s">
         <v>13</v>
@@ -7369,16 +7369,16 @@
         <v>213</v>
       </c>
       <c r="E186" t="n">
-        <v>1.14525639501412</v>
+        <v>1.11476292997904</v>
       </c>
       <c r="F186" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G186" t="n">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="H186" t="n">
-        <v>9.19</v>
+        <v>9.75</v>
       </c>
       <c r="I186" t="s">
         <v>13</v>
@@ -7401,16 +7401,16 @@
         <v>214</v>
       </c>
       <c r="E187" t="n">
-        <v>0.863893966474378</v>
+        <v>0.841405910487499</v>
       </c>
       <c r="F187" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G187" t="n">
-        <v>4.67</v>
+        <v>4.85</v>
       </c>
       <c r="H187" t="n">
-        <v>17.53</v>
+        <v>18.67</v>
       </c>
       <c r="I187" t="s">
         <v>13</v>
@@ -7433,16 +7433,16 @@
         <v>215</v>
       </c>
       <c r="E188" t="n">
-        <v>0.834002428284496</v>
+        <v>0.812081663051516</v>
       </c>
       <c r="F188" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G188" t="n">
-        <v>4.91</v>
+        <v>5.11</v>
       </c>
       <c r="H188" t="n">
-        <v>19.07</v>
+        <v>20.34</v>
       </c>
       <c r="I188" t="s">
         <v>13</v>
@@ -7465,16 +7465,16 @@
         <v>216</v>
       </c>
       <c r="E189" t="n">
-        <v>0.807187573956678</v>
+        <v>0.786072297633114</v>
       </c>
       <c r="F189" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G189" t="n">
-        <v>5.16</v>
+        <v>5.37</v>
       </c>
       <c r="H189" t="n">
-        <v>20.63</v>
+        <v>22.01</v>
       </c>
       <c r="I189" t="s">
         <v>13</v>
@@ -7497,16 +7497,16 @@
         <v>217</v>
       </c>
       <c r="E190" t="n">
-        <v>0.794932452371306</v>
+        <v>0.773761875136668</v>
       </c>
       <c r="F190" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="G190" t="n">
-        <v>5.28</v>
+        <v>5.5</v>
       </c>
       <c r="H190" t="n">
-        <v>21.41</v>
+        <v>22.87</v>
       </c>
       <c r="I190" t="s">
         <v>13</v>
@@ -7529,16 +7529,16 @@
         <v>218</v>
       </c>
       <c r="E191" t="n">
-        <v>0.753169949591034</v>
+        <v>0.733414049999009</v>
       </c>
       <c r="F191" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G191" t="n">
-        <v>5.73</v>
+        <v>5.97</v>
       </c>
       <c r="H191" t="n">
-        <v>24.43</v>
+        <v>26.09</v>
       </c>
       <c r="I191" t="s">
         <v>13</v>
@@ -7561,16 +7561,16 @@
         <v>219</v>
       </c>
       <c r="E192" t="n">
-        <v>0.476797509968023</v>
+        <v>0.464112245856016</v>
       </c>
       <c r="F192" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="G192" t="n">
-        <v>12.01</v>
+        <v>12.57</v>
       </c>
       <c r="H192" t="n">
-        <v>78.8</v>
+        <v>84.66</v>
       </c>
       <c r="I192" t="s">
         <v>13</v>
@@ -7593,16 +7593,16 @@
         <v>220</v>
       </c>
       <c r="E193" t="n">
-        <v>0.401401565717413</v>
+        <v>0.390694028988981</v>
       </c>
       <c r="F193" t="n">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="G193" t="n">
-        <v>16.15</v>
+        <v>16.93</v>
       </c>
       <c r="H193" t="n">
-        <v>124.97</v>
+        <v>134.47</v>
       </c>
       <c r="I193" t="s">
         <v>13</v>
@@ -7625,16 +7625,16 @@
         <v>221</v>
       </c>
       <c r="E194" t="n">
-        <v>0.395347862153113</v>
+        <v>0.384805340931537</v>
       </c>
       <c r="F194" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="G194" t="n">
-        <v>16.58</v>
+        <v>17.38</v>
       </c>
       <c r="H194" t="n">
-        <v>130.22</v>
+        <v>140.13</v>
       </c>
       <c r="I194" t="s">
         <v>13</v>
@@ -7657,16 +7657,16 @@
         <v>222</v>
       </c>
       <c r="E195" t="n">
-        <v>0.3948429573106</v>
+        <v>0.384338105478242</v>
       </c>
       <c r="F195" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="G195" t="n">
-        <v>16.62</v>
+        <v>17.42</v>
       </c>
       <c r="H195" t="n">
-        <v>130.67</v>
+        <v>140.59</v>
       </c>
       <c r="I195" t="s">
         <v>13</v>
@@ -7689,16 +7689,16 @@
         <v>223</v>
       </c>
       <c r="E196" t="n">
-        <v>0.373774927711543</v>
+        <v>0.363809910822452</v>
       </c>
       <c r="F196" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="G196" t="n">
-        <v>18.29</v>
+        <v>19.19</v>
       </c>
       <c r="H196" t="n">
-        <v>151.67</v>
+        <v>163.28</v>
       </c>
       <c r="I196" t="s">
         <v>13</v>
@@ -7721,16 +7721,16 @@
         <v>224</v>
       </c>
       <c r="E197" t="n">
-        <v>0.27485082580233</v>
+        <v>0.267516036778208</v>
       </c>
       <c r="F197" t="n">
-        <v>4.16</v>
+        <v>4.26</v>
       </c>
       <c r="G197" t="n">
-        <v>31.73</v>
+        <v>33.34</v>
       </c>
       <c r="H197" t="n">
-        <v>354.62</v>
+        <v>382.51</v>
       </c>
       <c r="I197" t="s">
         <v>13</v>
@@ -7753,16 +7753,16 @@
         <v>225</v>
       </c>
       <c r="E198" t="n">
-        <v>0.18817092051689</v>
+        <v>0.18316460698745</v>
       </c>
       <c r="F198" t="n">
-        <v>5.83</v>
+        <v>5.97</v>
       </c>
       <c r="G198" t="n">
-        <v>63.97</v>
+        <v>67.29</v>
       </c>
       <c r="H198" t="n">
-        <v>1036.32</v>
+        <v>1119.47</v>
       </c>
       <c r="I198" t="s">
         <v>13</v>
@@ -7785,16 +7785,16 @@
         <v>226</v>
       </c>
       <c r="E199" t="n">
-        <v>0.148348889790746</v>
+        <v>0.14440204693109</v>
       </c>
       <c r="F199" t="n">
-        <v>7.25</v>
+        <v>7.44</v>
       </c>
       <c r="G199" t="n">
-        <v>100.26</v>
+        <v>105.55</v>
       </c>
       <c r="H199" t="n">
-        <v>2053.23</v>
+        <v>2219.7</v>
       </c>
       <c r="I199" t="s">
         <v>13</v>
@@ -7817,16 +7817,16 @@
         <v>228</v>
       </c>
       <c r="E200" t="n">
-        <v>1.11551595854896</v>
+        <v>1.06071934959063</v>
       </c>
       <c r="F200" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="G200" t="n">
-        <v>3.26</v>
+        <v>3.49</v>
       </c>
       <c r="H200" t="n">
-        <v>9.73</v>
+        <v>10.89</v>
       </c>
       <c r="I200" t="s">
         <v>13</v>
@@ -7849,16 +7849,16 @@
         <v>229</v>
       </c>
       <c r="E201" t="n">
-        <v>0.802385086328375</v>
+        <v>0.76306884006662</v>
       </c>
       <c r="F201" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="G201" t="n">
-        <v>5.21</v>
+        <v>5.62</v>
       </c>
       <c r="H201" t="n">
-        <v>20.94</v>
+        <v>23.66</v>
       </c>
       <c r="I201" t="s">
         <v>13</v>
@@ -7881,16 +7881,16 @@
         <v>230</v>
       </c>
       <c r="E202" t="n">
-        <v>0.778066188757154</v>
+        <v>0.739917125143422</v>
       </c>
       <c r="F202" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="G202" t="n">
-        <v>5.45</v>
+        <v>5.89</v>
       </c>
       <c r="H202" t="n">
-        <v>22.56</v>
+        <v>25.53</v>
       </c>
       <c r="I202" t="s">
         <v>13</v>
@@ -7913,16 +7913,16 @@
         <v>231</v>
       </c>
       <c r="E203" t="n">
-        <v>0.705895940676851</v>
+        <v>0.671267889584149</v>
       </c>
       <c r="F203" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="G203" t="n">
-        <v>6.33</v>
+        <v>6.85</v>
       </c>
       <c r="H203" t="n">
-        <v>28.68</v>
+        <v>32.53</v>
       </c>
       <c r="I203" t="s">
         <v>13</v>
@@ -7945,16 +7945,16 @@
         <v>232</v>
       </c>
       <c r="E204" t="n">
-        <v>0.646181523164655</v>
+        <v>0.614460050013136</v>
       </c>
       <c r="F204" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G204" t="n">
-        <v>7.28</v>
+        <v>7.89</v>
       </c>
       <c r="H204" t="n">
-        <v>35.81</v>
+        <v>40.7</v>
       </c>
       <c r="I204" t="s">
         <v>13</v>
@@ -7977,16 +7977,16 @@
         <v>233</v>
       </c>
       <c r="E205" t="n">
-        <v>0.608295795905052</v>
+        <v>0.578682758430222</v>
       </c>
       <c r="F205" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="G205" t="n">
-        <v>8.02</v>
+        <v>8.7</v>
       </c>
       <c r="H205" t="n">
-        <v>41.77</v>
+        <v>47.48</v>
       </c>
       <c r="I205" t="s">
         <v>13</v>
@@ -8009,16 +8009,16 @@
         <v>234</v>
       </c>
       <c r="E206" t="n">
-        <v>0.520866172318017</v>
+        <v>0.495481885649786</v>
       </c>
       <c r="F206" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G206" t="n">
-        <v>10.35</v>
+        <v>11.26</v>
       </c>
       <c r="H206" t="n">
-        <v>62.42</v>
+        <v>71.19</v>
       </c>
       <c r="I206" t="s">
         <v>13</v>
@@ -8041,16 +8041,16 @@
         <v>235</v>
       </c>
       <c r="E207" t="n">
-        <v>0.458957976099347</v>
+        <v>0.436280581811538</v>
       </c>
       <c r="F207" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="G207" t="n">
-        <v>12.82</v>
+        <v>13.98</v>
       </c>
       <c r="H207" t="n">
-        <v>87.21</v>
+        <v>99.86</v>
       </c>
       <c r="I207" t="s">
         <v>13</v>
@@ -8073,16 +8073,16 @@
         <v>236</v>
       </c>
       <c r="E208" t="n">
-        <v>0.445902040066243</v>
+        <v>0.424117115672262</v>
       </c>
       <c r="F208" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="G208" t="n">
-        <v>13.47</v>
+        <v>14.68</v>
       </c>
       <c r="H208" t="n">
-        <v>94.19</v>
+        <v>107.73</v>
       </c>
       <c r="I208" t="s">
         <v>13</v>
@@ -8105,16 +8105,16 @@
         <v>237</v>
       </c>
       <c r="E209" t="n">
-        <v>0.330065917106332</v>
+        <v>0.3137449998531</v>
       </c>
       <c r="F209" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="G209" t="n">
-        <v>22.81</v>
+        <v>24.98</v>
       </c>
       <c r="H209" t="n">
-        <v>213.28</v>
+        <v>245.36</v>
       </c>
       <c r="I209" t="s">
         <v>13</v>
@@ -8137,16 +8137,16 @@
         <v>238</v>
       </c>
       <c r="E210" t="n">
-        <v>0.30502064888563</v>
+        <v>0.289939390284326</v>
       </c>
       <c r="F210" t="n">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="G210" t="n">
-        <v>26.28</v>
+        <v>28.8</v>
       </c>
       <c r="H210" t="n">
-        <v>265.3</v>
+        <v>305.47</v>
       </c>
       <c r="I210" t="s">
         <v>13</v>
@@ -8169,16 +8169,16 @@
         <v>239</v>
       </c>
       <c r="E211" t="n">
-        <v>0.224976939482517</v>
+        <v>0.213868176865706</v>
       </c>
       <c r="F211" t="n">
-        <v>4.96</v>
+        <v>5.19</v>
       </c>
       <c r="G211" t="n">
-        <v>45.84</v>
+        <v>50.36</v>
       </c>
       <c r="H211" t="n">
-        <v>623.16</v>
+        <v>719.44</v>
       </c>
       <c r="I211" t="s">
         <v>13</v>
@@ -8201,16 +8201,16 @@
         <v>240</v>
       </c>
       <c r="E212" t="n">
-        <v>0.202891659449535</v>
+        <v>0.192855955254544</v>
       </c>
       <c r="F212" t="n">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="G212" t="n">
-        <v>55.56</v>
+        <v>61.09</v>
       </c>
       <c r="H212" t="n">
-        <v>835.81</v>
+        <v>965.97</v>
       </c>
       <c r="I212" t="s">
         <v>13</v>
@@ -8233,16 +8233,16 @@
         <v>241</v>
       </c>
       <c r="E213" t="n">
-        <v>0.202218810061145</v>
+        <v>0.192219752027202</v>
       </c>
       <c r="F213" t="n">
-        <v>5.46</v>
+        <v>5.72</v>
       </c>
       <c r="G213" t="n">
-        <v>55.9</v>
+        <v>61.47</v>
       </c>
       <c r="H213" t="n">
-        <v>843.76</v>
+        <v>975.13</v>
       </c>
       <c r="I213" t="s">
         <v>13</v>
@@ -8265,16 +8265,16 @@
         <v>242</v>
       </c>
       <c r="E214" t="n">
-        <v>0.19679581642788</v>
+        <v>0.187053179657748</v>
       </c>
       <c r="F214" t="n">
-        <v>5.6</v>
+        <v>5.86</v>
       </c>
       <c r="G214" t="n">
-        <v>58.82</v>
+        <v>64.69</v>
       </c>
       <c r="H214" t="n">
-        <v>911.77</v>
+        <v>1054.13</v>
       </c>
       <c r="I214" t="s">
         <v>13</v>
@@ -8297,16 +8297,16 @@
         <v>243</v>
       </c>
       <c r="E215" t="n">
-        <v>0.112317311563846</v>
+        <v>0.106771381590796</v>
       </c>
       <c r="F215" t="n">
-        <v>9.41</v>
+        <v>9.87</v>
       </c>
       <c r="G215" t="n">
-        <v>170.81</v>
+        <v>188.32</v>
       </c>
       <c r="H215" t="n">
-        <v>4605.66</v>
+        <v>5339.14</v>
       </c>
       <c r="I215" t="s">
         <v>13</v>
@@ -8329,16 +8329,16 @@
         <v>244</v>
       </c>
       <c r="E216" t="n">
-        <v>0.105282015261768</v>
+        <v>0.100083469499466</v>
       </c>
       <c r="F216" t="n">
-        <v>10.01</v>
+        <v>10.5</v>
       </c>
       <c r="G216" t="n">
-        <v>193.49</v>
+        <v>213.38</v>
       </c>
       <c r="H216" t="n">
-        <v>5562.76</v>
+        <v>6450.32</v>
       </c>
       <c r="I216" t="s">
         <v>13</v>
@@ -8361,16 +8361,16 @@
         <v>245</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0864863849961422</v>
+        <v>0.0822159174419199</v>
       </c>
       <c r="F217" t="n">
-        <v>12.07</v>
+        <v>12.67</v>
       </c>
       <c r="G217" t="n">
-        <v>283.19</v>
+        <v>312.49</v>
       </c>
       <c r="H217" t="n">
-        <v>9895.03</v>
+        <v>11481.74</v>
       </c>
       <c r="I217" t="s">
         <v>13</v>
@@ -8393,7 +8393,7 @@
         <v>248</v>
       </c>
       <c r="E218" t="n">
-        <v>1.39165944768275</v>
+        <v>1.39178587045991</v>
       </c>
       <c r="F218" t="n">
         <v>1.33</v>
@@ -8425,7 +8425,7 @@
         <v>249</v>
       </c>
       <c r="E219" t="n">
-        <v>1.38394112270128</v>
+        <v>1.38398494406667</v>
       </c>
       <c r="F219" t="n">
         <v>1.33</v>
@@ -8457,7 +8457,7 @@
         <v>250</v>
       </c>
       <c r="E220" t="n">
-        <v>1.20000182558524</v>
+        <v>1.2000750065408</v>
       </c>
       <c r="F220" t="n">
         <v>1.43</v>
@@ -8489,7 +8489,7 @@
         <v>251</v>
       </c>
       <c r="E221" t="n">
-        <v>1.19836210348443</v>
+        <v>1.19845736273962</v>
       </c>
       <c r="F221" t="n">
         <v>1.43</v>
@@ -8521,7 +8521,7 @@
         <v>252</v>
       </c>
       <c r="E222" t="n">
-        <v>1.16369413512509</v>
+        <v>1.16386487511706</v>
       </c>
       <c r="F222" t="n">
         <v>1.45</v>
@@ -8553,7 +8553,7 @@
         <v>253</v>
       </c>
       <c r="E223" t="n">
-        <v>1.13206034644876</v>
+        <v>1.13234590562404</v>
       </c>
       <c r="F223" t="n">
         <v>1.48</v>
@@ -8585,7 +8585,7 @@
         <v>254</v>
       </c>
       <c r="E224" t="n">
-        <v>0.896665099091647</v>
+        <v>0.896947963823367</v>
       </c>
       <c r="F224" t="n">
         <v>1.69</v>
@@ -8594,7 +8594,7 @@
         <v>4.42</v>
       </c>
       <c r="H224" t="n">
-        <v>16.05</v>
+        <v>16.04</v>
       </c>
       <c r="I224" t="s">
         <v>13</v>
@@ -8617,16 +8617,16 @@
         <v>255</v>
       </c>
       <c r="E225" t="n">
-        <v>0.652852293973397</v>
+        <v>0.652711495200643</v>
       </c>
       <c r="F225" t="n">
         <v>2.09</v>
       </c>
       <c r="G225" t="n">
-        <v>7.16</v>
+        <v>7.17</v>
       </c>
       <c r="H225" t="n">
-        <v>34.89</v>
+        <v>34.91</v>
       </c>
       <c r="I225" t="s">
         <v>13</v>
@@ -8649,16 +8649,16 @@
         <v>256</v>
       </c>
       <c r="E226" t="n">
-        <v>0.555209864202175</v>
+        <v>0.555085073350279</v>
       </c>
       <c r="F226" t="n">
         <v>2.35</v>
       </c>
       <c r="G226" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
       <c r="H226" t="n">
-        <v>52.85</v>
+        <v>52.88</v>
       </c>
       <c r="I226" t="s">
         <v>13</v>
@@ -8681,16 +8681,16 @@
         <v>257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.440978755197724</v>
+        <v>0.440863654620004</v>
       </c>
       <c r="F227" t="n">
         <v>2.8</v>
       </c>
       <c r="G227" t="n">
-        <v>13.72</v>
+        <v>13.73</v>
       </c>
       <c r="H227" t="n">
-        <v>97.03</v>
+        <v>97.1</v>
       </c>
       <c r="I227" t="s">
         <v>13</v>
@@ -8713,7 +8713,7 @@
         <v>258</v>
       </c>
       <c r="E228" t="n">
-        <v>0.42685223697493</v>
+        <v>0.426744205089943</v>
       </c>
       <c r="F228" t="n">
         <v>2.88</v>
@@ -8722,7 +8722,7 @@
         <v>14.52</v>
       </c>
       <c r="H228" t="n">
-        <v>105.88</v>
+        <v>105.96</v>
       </c>
       <c r="I228" t="s">
         <v>13</v>
@@ -8745,7 +8745,7 @@
         <v>259</v>
       </c>
       <c r="E229" t="n">
-        <v>0.401430457857518</v>
+        <v>0.401357275027201</v>
       </c>
       <c r="F229" t="n">
         <v>3.02</v>
@@ -8754,7 +8754,7 @@
         <v>16.15</v>
       </c>
       <c r="H229" t="n">
-        <v>124.95</v>
+        <v>125.01</v>
       </c>
       <c r="I229" t="s">
         <v>13</v>
@@ -8777,16 +8777,16 @@
         <v>260</v>
       </c>
       <c r="E230" t="n">
-        <v>0.382727613134679</v>
+        <v>0.382631093620423</v>
       </c>
       <c r="F230" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="G230" t="n">
-        <v>17.55</v>
+        <v>17.56</v>
       </c>
       <c r="H230" t="n">
-        <v>142.21</v>
+        <v>142.31</v>
       </c>
       <c r="I230" t="s">
         <v>13</v>
@@ -8809,16 +8809,16 @@
         <v>261</v>
       </c>
       <c r="E231" t="n">
-        <v>0.380404922639787</v>
+        <v>0.38031162693244</v>
       </c>
       <c r="F231" t="n">
         <v>3.16</v>
       </c>
       <c r="G231" t="n">
-        <v>17.74</v>
+        <v>17.75</v>
       </c>
       <c r="H231" t="n">
-        <v>144.58</v>
+        <v>144.68</v>
       </c>
       <c r="I231" t="s">
         <v>13</v>
@@ -8841,16 +8841,16 @@
         <v>262</v>
       </c>
       <c r="E232" t="n">
-        <v>0.366683671844351</v>
+        <v>0.366577122535529</v>
       </c>
       <c r="F232" t="n">
         <v>3.26</v>
       </c>
       <c r="G232" t="n">
-        <v>18.92</v>
+        <v>18.93</v>
       </c>
       <c r="H232" t="n">
-        <v>159.81</v>
+        <v>159.93</v>
       </c>
       <c r="I232" t="s">
         <v>13</v>
@@ -8873,16 +8873,16 @@
         <v>263</v>
       </c>
       <c r="E233" t="n">
-        <v>0.189655870265503</v>
+        <v>0.189621295028122</v>
       </c>
       <c r="F233" t="n">
         <v>5.79</v>
       </c>
       <c r="G233" t="n">
-        <v>63.03</v>
+        <v>63.05</v>
       </c>
       <c r="H233" t="n">
-        <v>1013.28</v>
+        <v>1013.81</v>
       </c>
       <c r="I233" t="s">
         <v>13</v>
@@ -8905,16 +8905,16 @@
         <v>264</v>
       </c>
       <c r="E234" t="n">
-        <v>0.162813599444933</v>
+        <v>0.162783917691124</v>
       </c>
       <c r="F234" t="n">
         <v>6.66</v>
       </c>
       <c r="G234" t="n">
-        <v>84.04</v>
+        <v>84.07</v>
       </c>
       <c r="H234" t="n">
-        <v>1569.98</v>
+        <v>1570.8</v>
       </c>
       <c r="I234" t="s">
         <v>13</v>
@@ -8937,16 +8937,16 @@
         <v>265</v>
       </c>
       <c r="E235" t="n">
-        <v>0.115054501477192</v>
+        <v>0.11503352645177</v>
       </c>
       <c r="F235" t="n">
         <v>9.2</v>
       </c>
       <c r="G235" t="n">
-        <v>163.07</v>
+        <v>163.13</v>
       </c>
       <c r="H235" t="n">
-        <v>4293.46</v>
+        <v>4295.74</v>
       </c>
       <c r="I235" t="s">
         <v>13</v>
@@ -8969,7 +8969,7 @@
         <v>267</v>
       </c>
       <c r="E236" t="n">
-        <v>1.35497479468201</v>
+        <v>1.35495571114083</v>
       </c>
       <c r="F236" t="n">
         <v>1.35</v>
@@ -9001,7 +9001,7 @@
         <v>268</v>
       </c>
       <c r="E237" t="n">
-        <v>1.24039795664472</v>
+        <v>1.24044322796809</v>
       </c>
       <c r="F237" t="n">
         <v>1.41</v>
@@ -9033,7 +9033,7 @@
         <v>269</v>
       </c>
       <c r="E238" t="n">
-        <v>1.23490221635609</v>
+        <v>1.23493884364109</v>
       </c>
       <c r="F238" t="n">
         <v>1.41</v>
@@ -9065,7 +9065,7 @@
         <v>270</v>
       </c>
       <c r="E239" t="n">
-        <v>1.13397608289523</v>
+        <v>1.13430526661505</v>
       </c>
       <c r="F239" t="n">
         <v>1.47</v>
@@ -9074,7 +9074,7 @@
         <v>3.19</v>
       </c>
       <c r="H239" t="n">
-        <v>9.39</v>
+        <v>9.38</v>
       </c>
       <c r="I239" t="s">
         <v>13</v>
@@ -9097,7 +9097,7 @@
         <v>271</v>
       </c>
       <c r="E240" t="n">
-        <v>0.912885904777327</v>
+        <v>0.912969357884419</v>
       </c>
       <c r="F240" t="n">
         <v>1.67</v>
@@ -9106,7 +9106,7 @@
         <v>4.31</v>
       </c>
       <c r="H240" t="n">
-        <v>15.39</v>
+        <v>15.38</v>
       </c>
       <c r="I240" t="s">
         <v>13</v>
@@ -9129,7 +9129,7 @@
         <v>272</v>
       </c>
       <c r="E241" t="n">
-        <v>0.903479861670477</v>
+        <v>0.903534936214159</v>
       </c>
       <c r="F241" t="n">
         <v>1.68</v>
@@ -9138,7 +9138,7 @@
         <v>4.37</v>
       </c>
       <c r="H241" t="n">
-        <v>15.77</v>
+        <v>15.76</v>
       </c>
       <c r="I241" t="s">
         <v>13</v>
@@ -9161,7 +9161,7 @@
         <v>273</v>
       </c>
       <c r="E242" t="n">
-        <v>0.76550339552361</v>
+        <v>0.765601041983495</v>
       </c>
       <c r="F242" t="n">
         <v>1.87</v>
@@ -9170,7 +9170,7 @@
         <v>5.59</v>
       </c>
       <c r="H242" t="n">
-        <v>23.48</v>
+        <v>23.47</v>
       </c>
       <c r="I242" t="s">
         <v>13</v>
@@ -9193,7 +9193,7 @@
         <v>274</v>
       </c>
       <c r="E243" t="n">
-        <v>0.639220904344628</v>
+        <v>0.639372711747462</v>
       </c>
       <c r="F243" t="n">
         <v>2.12</v>
@@ -9202,7 +9202,7 @@
         <v>7.41</v>
       </c>
       <c r="H243" t="n">
-        <v>36.81</v>
+        <v>36.79</v>
       </c>
       <c r="I243" t="s">
         <v>13</v>
@@ -9225,7 +9225,7 @@
         <v>275</v>
       </c>
       <c r="E244" t="n">
-        <v>0.58074883364377</v>
+        <v>0.580620926580857</v>
       </c>
       <c r="F244" t="n">
         <v>2.27</v>
@@ -9234,7 +9234,7 @@
         <v>8.65</v>
       </c>
       <c r="H244" t="n">
-        <v>47.04</v>
+        <v>47.07</v>
       </c>
       <c r="I244" t="s">
         <v>13</v>
@@ -9257,7 +9257,7 @@
         <v>276</v>
       </c>
       <c r="E245" t="n">
-        <v>0.511071047377089</v>
+        <v>0.510956779537202</v>
       </c>
       <c r="F245" t="n">
         <v>2.5</v>
@@ -9266,7 +9266,7 @@
         <v>10.69</v>
       </c>
       <c r="H245" t="n">
-        <v>65.61</v>
+        <v>65.65</v>
       </c>
       <c r="I245" t="s">
         <v>13</v>
@@ -9289,7 +9289,7 @@
         <v>277</v>
       </c>
       <c r="E246" t="n">
-        <v>0.443571997017054</v>
+        <v>0.443488197101226</v>
       </c>
       <c r="F246" t="n">
         <v>2.79</v>
@@ -9298,7 +9298,7 @@
         <v>13.59</v>
       </c>
       <c r="H246" t="n">
-        <v>95.52</v>
+        <v>95.57</v>
       </c>
       <c r="I246" t="s">
         <v>13</v>
@@ -9321,16 +9321,16 @@
         <v>278</v>
       </c>
       <c r="E247" t="n">
-        <v>0.432069620439262</v>
+        <v>0.431987993560045</v>
       </c>
       <c r="F247" t="n">
         <v>2.85</v>
       </c>
       <c r="G247" t="n">
-        <v>14.21</v>
+        <v>14.22</v>
       </c>
       <c r="H247" t="n">
-        <v>102.49</v>
+        <v>102.54</v>
       </c>
       <c r="I247" t="s">
         <v>13</v>
@@ -9353,16 +9353,16 @@
         <v>279</v>
       </c>
       <c r="E248" t="n">
-        <v>0.341444674420034</v>
+        <v>0.341359330250099</v>
       </c>
       <c r="F248" t="n">
         <v>3.46</v>
       </c>
       <c r="G248" t="n">
-        <v>21.47</v>
+        <v>21.48</v>
       </c>
       <c r="H248" t="n">
-        <v>194.28</v>
+        <v>194.42</v>
       </c>
       <c r="I248" t="s">
         <v>13</v>
@@ -9385,16 +9385,16 @@
         <v>280</v>
       </c>
       <c r="E249" t="n">
-        <v>0.286883150735728</v>
+        <v>0.286794645481699</v>
       </c>
       <c r="F249" t="n">
         <v>4.01</v>
       </c>
       <c r="G249" t="n">
-        <v>29.35</v>
+        <v>29.37</v>
       </c>
       <c r="H249" t="n">
-        <v>314.63</v>
+        <v>314.9</v>
       </c>
       <c r="I249" t="s">
         <v>13</v>
@@ -9417,16 +9417,16 @@
         <v>281</v>
       </c>
       <c r="E250" t="n">
-        <v>0.257807637306554</v>
+        <v>0.257758932116751</v>
       </c>
       <c r="F250" t="n">
         <v>4.4</v>
       </c>
       <c r="G250" t="n">
-        <v>35.67</v>
+        <v>35.68</v>
       </c>
       <c r="H250" t="n">
-        <v>424.31</v>
+        <v>424.54</v>
       </c>
       <c r="I250" t="s">
         <v>13</v>
@@ -9449,16 +9449,16 @@
         <v>282</v>
       </c>
       <c r="E251" t="n">
-        <v>0.231383146468013</v>
+        <v>0.231317318369371</v>
       </c>
       <c r="F251" t="n">
         <v>4.84</v>
       </c>
       <c r="G251" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="H251" t="n">
-        <v>575.55</v>
+        <v>576.01</v>
       </c>
       <c r="I251" t="s">
         <v>13</v>
@@ -9481,16 +9481,16 @@
         <v>283</v>
       </c>
       <c r="E252" t="n">
-        <v>0.21753297419658</v>
+        <v>0.21749187772284</v>
       </c>
       <c r="F252" t="n">
         <v>5.12</v>
       </c>
       <c r="G252" t="n">
-        <v>48.8</v>
+        <v>48.81</v>
       </c>
       <c r="H252" t="n">
-        <v>685.55</v>
+        <v>685.92</v>
       </c>
       <c r="I252" t="s">
         <v>13</v>
@@ -9513,16 +9513,16 @@
         <v>284</v>
       </c>
       <c r="E253" t="n">
-        <v>0.204033974555374</v>
+        <v>0.203976975716994</v>
       </c>
       <c r="F253" t="n">
         <v>5.42</v>
       </c>
       <c r="G253" t="n">
-        <v>54.98</v>
+        <v>55.01</v>
       </c>
       <c r="H253" t="n">
-        <v>822.54</v>
+        <v>823.2</v>
       </c>
       <c r="I253" t="s">
         <v>13</v>
@@ -9545,7 +9545,7 @@
         <v>287</v>
       </c>
       <c r="E254" t="n">
-        <v>1.73422375650945</v>
+        <v>1.7340013627776</v>
       </c>
       <c r="F254" t="n">
         <v>1.21</v>
@@ -9577,7 +9577,7 @@
         <v>288</v>
       </c>
       <c r="E255" t="n">
-        <v>1.67173693547808</v>
+        <v>1.67152334890554</v>
       </c>
       <c r="F255" t="n">
         <v>1.23</v>
@@ -9609,7 +9609,7 @@
         <v>289</v>
       </c>
       <c r="E256" t="n">
-        <v>1.38007585026868</v>
+        <v>1.38023373450106</v>
       </c>
       <c r="F256" t="n">
         <v>1.34</v>
@@ -9641,7 +9641,7 @@
         <v>290</v>
       </c>
       <c r="E257" t="n">
-        <v>1.17584117879704</v>
+        <v>1.17582047273022</v>
       </c>
       <c r="F257" t="n">
         <v>1.45</v>
@@ -9673,7 +9673,7 @@
         <v>291</v>
       </c>
       <c r="E258" t="n">
-        <v>1.05827156762688</v>
+        <v>1.0586082101338</v>
       </c>
       <c r="F258" t="n">
         <v>1.53</v>
@@ -9682,7 +9682,7 @@
         <v>3.5</v>
       </c>
       <c r="H258" t="n">
-        <v>10.95</v>
+        <v>10.94</v>
       </c>
       <c r="I258" t="s">
         <v>13</v>
@@ -9705,7 +9705,7 @@
         <v>292</v>
       </c>
       <c r="E259" t="n">
-        <v>1.04601159160308</v>
+        <v>1.04627144257617</v>
       </c>
       <c r="F259" t="n">
         <v>1.54</v>
@@ -9737,16 +9737,16 @@
         <v>293</v>
       </c>
       <c r="E260" t="n">
-        <v>0.929752955187663</v>
+        <v>0.929424536477289</v>
       </c>
       <c r="F260" t="n">
         <v>1.65</v>
       </c>
       <c r="G260" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="H260" t="n">
-        <v>14.74</v>
+        <v>14.75</v>
       </c>
       <c r="I260" t="s">
         <v>13</v>
@@ -9769,7 +9769,7 @@
         <v>294</v>
       </c>
       <c r="E261" t="n">
-        <v>0.85475947728494</v>
+        <v>0.854798422272704</v>
       </c>
       <c r="F261" t="n">
         <v>1.74</v>
@@ -9801,7 +9801,7 @@
         <v>295</v>
       </c>
       <c r="E262" t="n">
-        <v>0.831467586185376</v>
+        <v>0.831496760206782</v>
       </c>
       <c r="F262" t="n">
         <v>1.77</v>
@@ -9833,7 +9833,7 @@
         <v>296</v>
       </c>
       <c r="E263" t="n">
-        <v>0.675071790747577</v>
+        <v>0.675189015464421</v>
       </c>
       <c r="F263" t="n">
         <v>2.04</v>
@@ -9842,7 +9842,7 @@
         <v>6.79</v>
       </c>
       <c r="H263" t="n">
-        <v>32.07</v>
+        <v>32.06</v>
       </c>
       <c r="I263" t="s">
         <v>13</v>
@@ -9865,16 +9865,16 @@
         <v>297</v>
       </c>
       <c r="E264" t="n">
-        <v>0.443551317495095</v>
+        <v>0.443382603154824</v>
       </c>
       <c r="F264" t="n">
         <v>2.79</v>
       </c>
       <c r="G264" t="n">
-        <v>13.59</v>
+        <v>13.6</v>
       </c>
       <c r="H264" t="n">
-        <v>95.53</v>
+        <v>95.63</v>
       </c>
       <c r="I264" t="s">
         <v>13</v>
@@ -9897,16 +9897,16 @@
         <v>298</v>
       </c>
       <c r="E265" t="n">
-        <v>0.4035873435973</v>
+        <v>0.403434666323709</v>
       </c>
       <c r="F265" t="n">
         <v>3.01</v>
       </c>
       <c r="G265" t="n">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="H265" t="n">
-        <v>123.15</v>
+        <v>123.28</v>
       </c>
       <c r="I265" t="s">
         <v>13</v>
@@ -9929,16 +9929,16 @@
         <v>299</v>
       </c>
       <c r="E266" t="n">
-        <v>0.36548870577529</v>
+        <v>0.36536883094604</v>
       </c>
       <c r="F266" t="n">
         <v>3.27</v>
       </c>
       <c r="G266" t="n">
-        <v>19.03</v>
+        <v>19.04</v>
       </c>
       <c r="H266" t="n">
-        <v>161.24</v>
+        <v>161.38</v>
       </c>
       <c r="I266" t="s">
         <v>13</v>
@@ -9961,16 +9961,16 @@
         <v>300</v>
       </c>
       <c r="E267" t="n">
-        <v>0.362602411082251</v>
+        <v>0.362447117176454</v>
       </c>
       <c r="F267" t="n">
         <v>3.29</v>
       </c>
       <c r="G267" t="n">
-        <v>19.3</v>
+        <v>19.31</v>
       </c>
       <c r="H267" t="n">
-        <v>164.77</v>
+        <v>164.96</v>
       </c>
       <c r="I267" t="s">
         <v>13</v>
@@ -9993,16 +9993,16 @@
         <v>301</v>
       </c>
       <c r="E268" t="n">
-        <v>0.33698453595401</v>
+        <v>0.336851414940306</v>
       </c>
       <c r="F268" t="n">
         <v>3.5</v>
       </c>
       <c r="G268" t="n">
-        <v>21.98</v>
+        <v>21.99</v>
       </c>
       <c r="H268" t="n">
-        <v>201.44</v>
+        <v>201.66</v>
       </c>
       <c r="I268" t="s">
         <v>13</v>
@@ -10025,16 +10025,16 @@
         <v>302</v>
       </c>
       <c r="E269" t="n">
-        <v>0.238270314002377</v>
+        <v>0.238192164902952</v>
       </c>
       <c r="F269" t="n">
         <v>4.72</v>
       </c>
       <c r="G269" t="n">
-        <v>41.23</v>
+        <v>41.25</v>
       </c>
       <c r="H269" t="n">
-        <v>529.76</v>
+        <v>530.26</v>
       </c>
       <c r="I269" t="s">
         <v>13</v>
@@ -10057,16 +10057,16 @@
         <v>303</v>
       </c>
       <c r="E270" t="n">
-        <v>0.183710248523018</v>
+        <v>0.183649994309071</v>
       </c>
       <c r="F270" t="n">
         <v>5.96</v>
       </c>
       <c r="G270" t="n">
-        <v>66.92</v>
+        <v>66.96</v>
       </c>
       <c r="H270" t="n">
-        <v>1109.97</v>
+        <v>1111.01</v>
       </c>
       <c r="I270" t="s">
         <v>13</v>
@@ -10089,16 +10089,16 @@
         <v>304</v>
       </c>
       <c r="E271" t="n">
-        <v>0.133096966388676</v>
+        <v>0.133053312574297</v>
       </c>
       <c r="F271" t="n">
-        <v>8.02</v>
+        <v>8.03</v>
       </c>
       <c r="G271" t="n">
-        <v>123.31</v>
+        <v>123.39</v>
       </c>
       <c r="H271" t="n">
-        <v>2810.96</v>
+        <v>2813.63</v>
       </c>
       <c r="I271" t="s">
         <v>13</v>
@@ -10121,7 +10121,7 @@
         <v>306</v>
       </c>
       <c r="E272" t="n">
-        <v>1.53486270423377</v>
+        <v>1.53493929950283</v>
       </c>
       <c r="F272" t="n">
         <v>1.27</v>
@@ -10153,7 +10153,7 @@
         <v>307</v>
       </c>
       <c r="E273" t="n">
-        <v>1.11750357510818</v>
+        <v>1.11767786253117</v>
       </c>
       <c r="F273" t="n">
         <v>1.49</v>
@@ -10162,7 +10162,7 @@
         <v>3.25</v>
       </c>
       <c r="H273" t="n">
-        <v>9.7</v>
+        <v>9.69</v>
       </c>
       <c r="I273" t="s">
         <v>13</v>
@@ -10185,7 +10185,7 @@
         <v>308</v>
       </c>
       <c r="E274" t="n">
-        <v>0.785091299308265</v>
+        <v>0.785296983164896</v>
       </c>
       <c r="F274" t="n">
         <v>1.84</v>
@@ -10194,7 +10194,7 @@
         <v>5.38</v>
       </c>
       <c r="H274" t="n">
-        <v>22.07</v>
+        <v>22.06</v>
       </c>
       <c r="I274" t="s">
         <v>13</v>
@@ -10217,7 +10217,7 @@
         <v>309</v>
       </c>
       <c r="E275" t="n">
-        <v>0.746989847553368</v>
+        <v>0.747233256898225</v>
       </c>
       <c r="F275" t="n">
         <v>1.9</v>
@@ -10226,7 +10226,7 @@
         <v>5.8</v>
       </c>
       <c r="H275" t="n">
-        <v>24.93</v>
+        <v>24.91</v>
       </c>
       <c r="I275" t="s">
         <v>13</v>
@@ -10249,7 +10249,7 @@
         <v>310</v>
       </c>
       <c r="E276" t="n">
-        <v>0.672145329925134</v>
+        <v>0.672490937144763</v>
       </c>
       <c r="F276" t="n">
         <v>2.04</v>
@@ -10258,7 +10258,7 @@
         <v>6.84</v>
       </c>
       <c r="H276" t="n">
-        <v>32.42</v>
+        <v>32.38</v>
       </c>
       <c r="I276" t="s">
         <v>13</v>
@@ -10281,7 +10281,7 @@
         <v>311</v>
       </c>
       <c r="E277" t="n">
-        <v>0.624988456035141</v>
+        <v>0.625189794775749</v>
       </c>
       <c r="F277" t="n">
         <v>2.15</v>
@@ -10290,7 +10290,7 @@
         <v>7.68</v>
       </c>
       <c r="H277" t="n">
-        <v>38.98</v>
+        <v>38.95</v>
       </c>
       <c r="I277" t="s">
         <v>13</v>
@@ -10313,16 +10313,16 @@
         <v>312</v>
       </c>
       <c r="E278" t="n">
-        <v>0.481510216309465</v>
+        <v>0.481425684394617</v>
       </c>
       <c r="F278" t="n">
         <v>2.62</v>
       </c>
       <c r="G278" t="n">
-        <v>11.81</v>
+        <v>11.82</v>
       </c>
       <c r="H278" t="n">
-        <v>76.78</v>
+        <v>76.81</v>
       </c>
       <c r="I278" t="s">
         <v>13</v>
@@ -10345,16 +10345,16 @@
         <v>313</v>
       </c>
       <c r="E279" t="n">
-        <v>0.478270951530946</v>
+        <v>0.478462849765252</v>
       </c>
       <c r="F279" t="n">
         <v>2.63</v>
       </c>
       <c r="G279" t="n">
-        <v>11.95</v>
+        <v>11.94</v>
       </c>
       <c r="H279" t="n">
-        <v>78.16</v>
+        <v>78.08</v>
       </c>
       <c r="I279" t="s">
         <v>13</v>
@@ -10377,7 +10377,7 @@
         <v>314</v>
       </c>
       <c r="E280" t="n">
-        <v>0.449720803137487</v>
+        <v>0.449648765531202</v>
       </c>
       <c r="F280" t="n">
         <v>2.76</v>
@@ -10386,7 +10386,7 @@
         <v>13.27</v>
       </c>
       <c r="H280" t="n">
-        <v>92.07</v>
+        <v>92.11</v>
       </c>
       <c r="I280" t="s">
         <v>13</v>
@@ -10409,7 +10409,7 @@
         <v>315</v>
       </c>
       <c r="E281" t="n">
-        <v>0.368033791247972</v>
+        <v>0.367989052548869</v>
       </c>
       <c r="F281" t="n">
         <v>3.25</v>
@@ -10418,7 +10418,7 @@
         <v>18.8</v>
       </c>
       <c r="H281" t="n">
-        <v>158.21</v>
+        <v>158.26</v>
       </c>
       <c r="I281" t="s">
         <v>13</v>
@@ -10441,16 +10441,16 @@
         <v>316</v>
       </c>
       <c r="E282" t="n">
-        <v>0.27271073101269</v>
+        <v>0.272652167368099</v>
       </c>
       <c r="F282" t="n">
         <v>4.19</v>
       </c>
       <c r="G282" t="n">
-        <v>32.19</v>
+        <v>32.2</v>
       </c>
       <c r="H282" t="n">
-        <v>362.46</v>
+        <v>362.68</v>
       </c>
       <c r="I282" t="s">
         <v>13</v>
@@ -10473,16 +10473,16 @@
         <v>317</v>
       </c>
       <c r="E283" t="n">
-        <v>0.244766165386477</v>
+        <v>0.244698178945097</v>
       </c>
       <c r="F283" t="n">
         <v>4.61</v>
       </c>
       <c r="G283" t="n">
-        <v>39.23</v>
+        <v>39.25</v>
       </c>
       <c r="H283" t="n">
-        <v>491.05</v>
+        <v>491.44</v>
       </c>
       <c r="I283" t="s">
         <v>13</v>
@@ -10505,16 +10505,16 @@
         <v>318</v>
       </c>
       <c r="E284" t="n">
-        <v>0.20392330338158</v>
+        <v>0.203874990749161</v>
       </c>
       <c r="F284" t="n">
         <v>5.42</v>
       </c>
       <c r="G284" t="n">
-        <v>55.03</v>
+        <v>55.06</v>
       </c>
       <c r="H284" t="n">
-        <v>823.82</v>
+        <v>824.37</v>
       </c>
       <c r="I284" t="s">
         <v>13</v>
@@ -10537,16 +10537,16 @@
         <v>319</v>
       </c>
       <c r="E285" t="n">
-        <v>0.203488089803904</v>
+        <v>0.203443682411806</v>
       </c>
       <c r="F285" t="n">
         <v>5.43</v>
       </c>
       <c r="G285" t="n">
-        <v>55.25</v>
+        <v>55.28</v>
       </c>
       <c r="H285" t="n">
-        <v>828.85</v>
+        <v>829.36</v>
       </c>
       <c r="I285" t="s">
         <v>13</v>
@@ -10569,16 +10569,16 @@
         <v>320</v>
       </c>
       <c r="E286" t="n">
-        <v>0.195709511127684</v>
+        <v>0.195669332038594</v>
       </c>
       <c r="F286" t="n">
         <v>5.63</v>
       </c>
       <c r="G286" t="n">
-        <v>59.43</v>
+        <v>59.45</v>
       </c>
       <c r="H286" t="n">
-        <v>926.29</v>
+        <v>926.83</v>
       </c>
       <c r="I286" t="s">
         <v>13</v>
@@ -10601,16 +10601,16 @@
         <v>321</v>
       </c>
       <c r="E287" t="n">
-        <v>0.121572593332329</v>
+        <v>0.12155781479894</v>
       </c>
       <c r="F287" t="n">
         <v>8.74</v>
       </c>
       <c r="G287" t="n">
-        <v>146.68</v>
+        <v>146.72</v>
       </c>
       <c r="H287" t="n">
-        <v>3656.97</v>
+        <v>3658.27</v>
       </c>
       <c r="I287" t="s">
         <v>13</v>
@@ -10633,16 +10633,16 @@
         <v>322</v>
       </c>
       <c r="E288" t="n">
-        <v>0.0769082736646277</v>
+        <v>0.0768989245880054</v>
       </c>
       <c r="F288" t="n">
         <v>13.51</v>
       </c>
       <c r="G288" t="n">
-        <v>355.86</v>
+        <v>355.94</v>
       </c>
       <c r="H288" t="n">
-        <v>13971.22</v>
+        <v>13976.22</v>
       </c>
       <c r="I288" t="s">
         <v>13</v>
@@ -10665,16 +10665,16 @@
         <v>323</v>
       </c>
       <c r="E289" t="n">
-        <v>0.0677555550369616</v>
+        <v>0.0677473185775347</v>
       </c>
       <c r="F289" t="n">
-        <v>15.26</v>
+        <v>15.27</v>
       </c>
       <c r="G289" t="n">
-        <v>455.72</v>
+        <v>455.83</v>
       </c>
       <c r="H289" t="n">
-        <v>20293.1</v>
+        <v>20300.38</v>
       </c>
       <c r="I289" t="s">
         <v>13</v>
@@ -10697,16 +10697,16 @@
         <v>326</v>
       </c>
       <c r="E290" t="n">
-        <v>1.86107075545108</v>
+        <v>1.81526576664779</v>
       </c>
       <c r="F290" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G290" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="H290" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="I290" t="s">
         <v>13</v>
@@ -10729,16 +10729,16 @@
         <v>327</v>
       </c>
       <c r="E291" t="n">
-        <v>1.25175582653776</v>
+        <v>1.2211081693957</v>
       </c>
       <c r="F291" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G291" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="H291" t="n">
-        <v>7.58</v>
+        <v>7.99</v>
       </c>
       <c r="I291" t="s">
         <v>13</v>
@@ -10761,16 +10761,16 @@
         <v>328</v>
       </c>
       <c r="E292" t="n">
-        <v>1.24779897317941</v>
+        <v>1.21718249994617</v>
       </c>
       <c r="F292" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G292" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="H292" t="n">
-        <v>7.63</v>
+        <v>8.05</v>
       </c>
       <c r="I292" t="s">
         <v>13</v>
@@ -10793,16 +10793,16 @@
         <v>329</v>
       </c>
       <c r="E293" t="n">
-        <v>1.00147175873023</v>
+        <v>0.97696311867876</v>
       </c>
       <c r="F293" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G293" t="n">
-        <v>3.78</v>
+        <v>3.91</v>
       </c>
       <c r="H293" t="n">
-        <v>12.41</v>
+        <v>13.14</v>
       </c>
       <c r="I293" t="s">
         <v>13</v>
@@ -10825,16 +10825,16 @@
         <v>330</v>
       </c>
       <c r="E294" t="n">
-        <v>0.968393208067652</v>
+        <v>0.944691178591567</v>
       </c>
       <c r="F294" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G294" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="H294" t="n">
-        <v>13.41</v>
+        <v>14.2</v>
       </c>
       <c r="I294" t="s">
         <v>13</v>
@@ -10857,16 +10857,16 @@
         <v>331</v>
       </c>
       <c r="E295" t="n">
-        <v>0.816439645183083</v>
+        <v>0.796601389784956</v>
       </c>
       <c r="F295" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G295" t="n">
-        <v>5.07</v>
+        <v>5.26</v>
       </c>
       <c r="H295" t="n">
-        <v>20.07</v>
+        <v>21.31</v>
       </c>
       <c r="I295" t="s">
         <v>13</v>
@@ -10889,16 +10889,16 @@
         <v>332</v>
       </c>
       <c r="E296" t="n">
-        <v>0.718679327048139</v>
+        <v>0.701371172973677</v>
       </c>
       <c r="F296" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G296" t="n">
-        <v>6.16</v>
+        <v>6.4</v>
       </c>
       <c r="H296" t="n">
-        <v>27.43</v>
+        <v>29.15</v>
       </c>
       <c r="I296" t="s">
         <v>13</v>
@@ -10921,16 +10921,16 @@
         <v>333</v>
       </c>
       <c r="E297" t="n">
-        <v>0.616120794677646</v>
+        <v>0.60135129339214</v>
       </c>
       <c r="F297" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="G297" t="n">
-        <v>7.86</v>
+        <v>8.17</v>
       </c>
       <c r="H297" t="n">
-        <v>40.42</v>
+        <v>43.01</v>
       </c>
       <c r="I297" t="s">
         <v>13</v>
@@ -10953,16 +10953,16 @@
         <v>334</v>
       </c>
       <c r="E298" t="n">
-        <v>0.614547276468069</v>
+        <v>0.599594046316653</v>
       </c>
       <c r="F298" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G298" t="n">
-        <v>7.89</v>
+        <v>8.21</v>
       </c>
       <c r="H298" t="n">
-        <v>40.69</v>
+        <v>43.34</v>
       </c>
       <c r="I298" t="s">
         <v>13</v>
@@ -10985,16 +10985,16 @@
         <v>335</v>
       </c>
       <c r="E299" t="n">
-        <v>0.395993359086548</v>
+        <v>0.38617077543105</v>
       </c>
       <c r="F299" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="G299" t="n">
-        <v>16.53</v>
+        <v>17.28</v>
       </c>
       <c r="H299" t="n">
-        <v>129.65</v>
+        <v>138.79</v>
       </c>
       <c r="I299" t="s">
         <v>13</v>
@@ -11017,16 +11017,16 @@
         <v>336</v>
       </c>
       <c r="E300" t="n">
-        <v>0.387086838978194</v>
+        <v>0.377498749718669</v>
       </c>
       <c r="F300" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="G300" t="n">
-        <v>17.2</v>
+        <v>17.98</v>
       </c>
       <c r="H300" t="n">
-        <v>137.9</v>
+        <v>147.63</v>
       </c>
       <c r="I300" t="s">
         <v>13</v>
@@ -11049,16 +11049,16 @@
         <v>337</v>
       </c>
       <c r="E301" t="n">
-        <v>0.333682624721294</v>
+        <v>0.325431955032168</v>
       </c>
       <c r="F301" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="G301" t="n">
-        <v>22.37</v>
+        <v>23.39</v>
       </c>
       <c r="H301" t="n">
-        <v>206.97</v>
+        <v>221.76</v>
       </c>
       <c r="I301" t="s">
         <v>13</v>
@@ -11081,16 +11081,16 @@
         <v>338</v>
       </c>
       <c r="E302" t="n">
-        <v>0.315954976132605</v>
+        <v>0.308105854876732</v>
       </c>
       <c r="F302" t="n">
-        <v>3.69</v>
+        <v>3.77</v>
       </c>
       <c r="G302" t="n">
-        <v>24.66</v>
+        <v>25.8</v>
       </c>
       <c r="H302" t="n">
-        <v>240.64</v>
+        <v>258</v>
       </c>
       <c r="I302" t="s">
         <v>13</v>
@@ -11113,16 +11113,16 @@
         <v>339</v>
       </c>
       <c r="E303" t="n">
-        <v>0.305314618533811</v>
+        <v>0.297747239847687</v>
       </c>
       <c r="F303" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="G303" t="n">
-        <v>26.23</v>
+        <v>27.44</v>
       </c>
       <c r="H303" t="n">
-        <v>264.6</v>
+        <v>283.7</v>
       </c>
       <c r="I303" t="s">
         <v>13</v>
@@ -11145,16 +11145,16 @@
         <v>340</v>
       </c>
       <c r="E304" t="n">
-        <v>0.221141620143757</v>
+        <v>0.215639958312188</v>
       </c>
       <c r="F304" t="n">
-        <v>5.04</v>
+        <v>5.16</v>
       </c>
       <c r="G304" t="n">
-        <v>47.33</v>
+        <v>49.6</v>
       </c>
       <c r="H304" t="n">
-        <v>654.29</v>
+        <v>702.78</v>
       </c>
       <c r="I304" t="s">
         <v>13</v>
@@ -11177,16 +11177,16 @@
         <v>341</v>
       </c>
       <c r="E305" t="n">
-        <v>0.217643109647182</v>
+        <v>0.212261644522011</v>
       </c>
       <c r="F305" t="n">
-        <v>5.11</v>
+        <v>5.23</v>
       </c>
       <c r="G305" t="n">
-        <v>48.75</v>
+        <v>51.07</v>
       </c>
       <c r="H305" t="n">
-        <v>684.57</v>
+        <v>735.03</v>
       </c>
       <c r="I305" t="s">
         <v>13</v>
@@ -11209,16 +11209,16 @@
         <v>342</v>
       </c>
       <c r="E306" t="n">
-        <v>0.17848921782451</v>
+        <v>0.174075875713663</v>
       </c>
       <c r="F306" t="n">
-        <v>6.12</v>
+        <v>6.26</v>
       </c>
       <c r="G306" t="n">
-        <v>70.65</v>
+        <v>74.06</v>
       </c>
       <c r="H306" t="n">
-        <v>1205.57</v>
+        <v>1295.35</v>
       </c>
       <c r="I306" t="s">
         <v>13</v>
@@ -11241,16 +11241,16 @@
         <v>343</v>
       </c>
       <c r="E307" t="n">
-        <v>0.162303078639018</v>
+        <v>0.158289956611771</v>
       </c>
       <c r="F307" t="n">
-        <v>6.67</v>
+        <v>6.83</v>
       </c>
       <c r="G307" t="n">
-        <v>84.54</v>
+        <v>88.64</v>
       </c>
       <c r="H307" t="n">
-        <v>1584.24</v>
+        <v>1702.72</v>
       </c>
       <c r="I307" t="s">
         <v>13</v>
@@ -11273,16 +11273,16 @@
         <v>345</v>
       </c>
       <c r="E308" t="n">
-        <v>1.98026668555489</v>
+        <v>1.93433780457125</v>
       </c>
       <c r="F308" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G308" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="H308" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="I308" t="s">
         <v>13</v>
@@ -11305,16 +11305,16 @@
         <v>346</v>
       </c>
       <c r="E309" t="n">
-        <v>1.70275705921516</v>
+        <v>1.6633017581341</v>
       </c>
       <c r="F309" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G309" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="H309" t="n">
-        <v>4.11</v>
+        <v>4.29</v>
       </c>
       <c r="I309" t="s">
         <v>13</v>
@@ -11337,16 +11337,16 @@
         <v>347</v>
       </c>
       <c r="E310" t="n">
-        <v>1.2909450172629</v>
+        <v>1.261243078835</v>
       </c>
       <c r="F310" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G310" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="H310" t="n">
-        <v>7.1</v>
+        <v>7.46</v>
       </c>
       <c r="I310" t="s">
         <v>13</v>
@@ -11369,16 +11369,16 @@
         <v>348</v>
       </c>
       <c r="E311" t="n">
-        <v>1.20896338354293</v>
+        <v>1.18103526166214</v>
       </c>
       <c r="F311" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G311" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="H311" t="n">
-        <v>8.17</v>
+        <v>8.59</v>
       </c>
       <c r="I311" t="s">
         <v>13</v>
@@ -11401,16 +11401,16 @@
         <v>349</v>
       </c>
       <c r="E312" t="n">
-        <v>0.896120501149169</v>
+        <v>0.875795476652605</v>
       </c>
       <c r="F312" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G312" t="n">
-        <v>4.42</v>
+        <v>4.57</v>
       </c>
       <c r="H312" t="n">
-        <v>16.07</v>
+        <v>16.97</v>
       </c>
       <c r="I312" t="s">
         <v>13</v>
@@ -11433,16 +11433,16 @@
         <v>350</v>
       </c>
       <c r="E313" t="n">
-        <v>0.867478992895054</v>
+        <v>0.847500663785386</v>
       </c>
       <c r="F313" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G313" t="n">
-        <v>4.64</v>
+        <v>4.8</v>
       </c>
       <c r="H313" t="n">
-        <v>17.36</v>
+        <v>18.35</v>
       </c>
       <c r="I313" t="s">
         <v>13</v>
@@ -11465,16 +11465,16 @@
         <v>351</v>
       </c>
       <c r="E314" t="n">
-        <v>0.852129205132218</v>
+        <v>0.832550590752596</v>
       </c>
       <c r="F314" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="G314" t="n">
-        <v>4.76</v>
+        <v>4.93</v>
       </c>
       <c r="H314" t="n">
-        <v>18.11</v>
+        <v>19.15</v>
       </c>
       <c r="I314" t="s">
         <v>13</v>
@@ -11497,16 +11497,16 @@
         <v>352</v>
       </c>
       <c r="E315" t="n">
-        <v>0.797411264190643</v>
+        <v>0.779211143219517</v>
       </c>
       <c r="F315" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G315" t="n">
-        <v>5.26</v>
+        <v>5.44</v>
       </c>
       <c r="H315" t="n">
-        <v>21.25</v>
+        <v>22.48</v>
       </c>
       <c r="I315" t="s">
         <v>13</v>
@@ -11529,16 +11529,16 @@
         <v>353</v>
       </c>
       <c r="E316" t="n">
-        <v>0.422523046540788</v>
+        <v>0.412629797631313</v>
       </c>
       <c r="F316" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G316" t="n">
-        <v>14.77</v>
+        <v>15.39</v>
       </c>
       <c r="H316" t="n">
-        <v>108.83</v>
+        <v>116</v>
       </c>
       <c r="I316" t="s">
         <v>13</v>
@@ -11561,16 +11561,16 @@
         <v>354</v>
       </c>
       <c r="E317" t="n">
-        <v>0.390343478863729</v>
+        <v>0.381188724521132</v>
       </c>
       <c r="F317" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="G317" t="n">
-        <v>16.95</v>
+        <v>17.67</v>
       </c>
       <c r="H317" t="n">
-        <v>134.8</v>
+        <v>143.78</v>
       </c>
       <c r="I317" t="s">
         <v>13</v>
@@ -11593,16 +11593,16 @@
         <v>355</v>
       </c>
       <c r="E318" t="n">
-        <v>0.384298791726358</v>
+        <v>0.375294309117033</v>
       </c>
       <c r="F318" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="G318" t="n">
-        <v>17.42</v>
+        <v>18.16</v>
       </c>
       <c r="H318" t="n">
-        <v>140.63</v>
+        <v>150</v>
       </c>
       <c r="I318" t="s">
         <v>13</v>
@@ -11625,16 +11625,16 @@
         <v>356</v>
       </c>
       <c r="E319" t="n">
-        <v>0.381301558687673</v>
+        <v>0.37237162074856</v>
       </c>
       <c r="F319" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="G319" t="n">
-        <v>17.66</v>
+        <v>18.42</v>
       </c>
       <c r="H319" t="n">
-        <v>143.66</v>
+        <v>153.24</v>
       </c>
       <c r="I319" t="s">
         <v>13</v>
@@ -11657,16 +11657,16 @@
         <v>357</v>
       </c>
       <c r="E320" t="n">
-        <v>0.362317891027071</v>
+        <v>0.353833619048569</v>
       </c>
       <c r="F320" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="G320" t="n">
-        <v>19.33</v>
+        <v>20.15</v>
       </c>
       <c r="H320" t="n">
-        <v>165.12</v>
+        <v>176.18</v>
       </c>
       <c r="I320" t="s">
         <v>13</v>
@@ -11689,16 +11689,16 @@
         <v>358</v>
       </c>
       <c r="E321" t="n">
-        <v>0.27532556814993</v>
+        <v>0.268873858063512</v>
       </c>
       <c r="F321" t="n">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="G321" t="n">
-        <v>31.63</v>
+        <v>33.03</v>
       </c>
       <c r="H321" t="n">
-        <v>352.91</v>
+        <v>377.13</v>
       </c>
       <c r="I321" t="s">
         <v>13</v>
@@ -11721,16 +11721,16 @@
         <v>359</v>
       </c>
       <c r="E322" t="n">
-        <v>0.253165104956626</v>
+        <v>0.247251449101643</v>
       </c>
       <c r="F322" t="n">
-        <v>4.47</v>
+        <v>4.57</v>
       </c>
       <c r="G322" t="n">
-        <v>36.88</v>
+        <v>38.51</v>
       </c>
       <c r="H322" t="n">
-        <v>446.55</v>
+        <v>477.27</v>
       </c>
       <c r="I322" t="s">
         <v>13</v>
@@ -11753,16 +11753,16 @@
         <v>360</v>
       </c>
       <c r="E323" t="n">
-        <v>0.188146559687453</v>
+        <v>0.183726733259784</v>
       </c>
       <c r="F323" t="n">
-        <v>5.83</v>
+        <v>5.96</v>
       </c>
       <c r="G323" t="n">
-        <v>63.99</v>
+        <v>66.91</v>
       </c>
       <c r="H323" t="n">
-        <v>1036.7</v>
+        <v>1109.69</v>
       </c>
       <c r="I323" t="s">
         <v>13</v>
@@ -11785,16 +11785,16 @@
         <v>361</v>
       </c>
       <c r="E324" t="n">
-        <v>0.15918971078136</v>
+        <v>0.155471215827734</v>
       </c>
       <c r="F324" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="G324" t="n">
-        <v>87.7</v>
+        <v>91.72</v>
       </c>
       <c r="H324" t="n">
-        <v>1675.13</v>
+        <v>1793.26</v>
       </c>
       <c r="I324" t="s">
         <v>13</v>
@@ -11817,16 +11817,16 @@
         <v>362</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0902407983297628</v>
+        <v>0.0881328734421974</v>
       </c>
       <c r="F325" t="n">
-        <v>11.59</v>
+        <v>11.85</v>
       </c>
       <c r="G325" t="n">
-        <v>260.77</v>
+        <v>273.01</v>
       </c>
       <c r="H325" t="n">
-        <v>8735.13</v>
+        <v>9362.26</v>
       </c>
       <c r="I325" t="s">
         <v>13</v>

--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -35,7 +35,649 @@
     <t xml:space="preserve">3+ Fair Odds</t>
   </si>
   <si>
-    <t xml:space="preserve">western bulldogs v north melbourne</t>
+    <t xml:space="preserve">brisbane lions v gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Morris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kai Lohmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie Cameron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Bailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cam Rayner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric Hipwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conor McKenna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugh McCluggage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Ashcroft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Draper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levi Ashcroft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachie Neale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarrod Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Tunstill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darcy Fort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Dunkley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaspa Fletcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dayne Zorko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold coast suns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jed Walter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Humphrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Petracca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Lombard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Patterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touk Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caleb Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeke Uwland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned Moyle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau Addinsall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Rowell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Jeffrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Rioli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon v sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nate Caddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Wright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hussien El Achkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sullivan Robey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaac Kako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nik Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dyson Sharp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archer Day-Wicks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Durham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zach Merrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Kondogiannis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Setterfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben McKay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Farrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Redman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archie Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Blakiston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie Curnow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan McDonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Papley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaac Heeney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chad Warner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Cootee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malcolm Rosas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errol Gulden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braeden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Lloyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Rowbottom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Grundy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Jordon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Serong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Blakey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Bice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle v adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taylor Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Thilthorpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Rachele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Keays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izak Rankine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finnbar Maley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Dawson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Neal-Bullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Soligo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaac Cumming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan McAndrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Curtin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Peatling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Nankervis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Hall-Kahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Treacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Amiss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Voss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Frederick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Dudley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shai Bolton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murphy Reid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Switkowski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caleb Serong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan O'Driscoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neil Erasmus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Brayshaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Wagner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar McDonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney v west coast eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Stringer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Cadman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Gruzewski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callum Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Hamilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Bedford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Coniglio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Rowston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier O'Halloran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conor Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Angwin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finn Callaghan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clayton Oliver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Madden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Himmelberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Fonti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">west coast eagles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Waterman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobe Shanahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan Murdock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elliot Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harley Reid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willem Duursma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Cole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey J. Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bo Allan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Francou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Kelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamish Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Maric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brady Hough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Starcevich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn v collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel McStay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Membrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan De Goey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Daicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau McCreery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Lipinski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steele Sidebottom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Crisp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward Allan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darcy Cameron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Pendlebury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dan Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Daicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Howe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Gunston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mabior Chol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ginnivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Macdonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Greeves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Newcombe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Morrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Hardwick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lloyd Meek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massimo D'Ambrosio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Weddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cam Mackenzie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarman Impey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north melbourne v geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shannon Neale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaun Mannagh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jay Polkinghorne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Dempsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Dangerfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Wiltshire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryan Miers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Worpel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Blicavs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Atkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oisin Mullin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jhye Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanner Bruhn</t>
   </si>
   <si>
     <t xml:space="preserve">north melbourne</t>
@@ -86,15 +728,309 @@
     <t xml:space="preserve">Bailey Scott</t>
   </si>
   <si>
+    <t xml:space="preserve">Dylan Stephens</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finn O'Sullivan</t>
   </si>
   <si>
-    <t xml:space="preserve">Dylan Stephens</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cooper Harvey</t>
   </si>
   <si>
+    <t xml:space="preserve">port adelaide v melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob van Rooyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayley Fritsch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kysaiah Pickett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Sharp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Petty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Jefferson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kade Chandler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paddy Cross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Langford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrelle Pickett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Sparrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Gawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ed Langdon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Fitzgerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Steele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koltyn Tholstrup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Rivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Georgiades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Durdin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Whitlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Horne-Francis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todd Marshall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Bamert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Zadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Watkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Moraes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darcy Byrne-Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dante Visentini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordon Sweet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jase Burgoyne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ollie Wines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miles Bergman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willem Drew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richmond v st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Lynch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mykelti Lefau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Lalor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhyan Mansell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seth Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Peucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taj Hotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Taranto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Sonsie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Cumming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Ralphsmith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Nankervis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dion Prestia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Retschko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Sharman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Ryan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Owens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darcy Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattaes Phillipou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasiah Wanganeen-Milera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rowan Marshall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom De Koning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugh Boxshall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradley Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Byrnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Silvagni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Windhager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">western bulldogs v carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Kemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Ainsworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch McGovern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talor Byrne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Cottrell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Cripps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Hewett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marc Pittonet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jagga Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Acres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Cerra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lewis Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Florent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Dean</t>
+  </si>
+  <si>
     <t xml:space="preserve">western bulldogs</t>
   </si>
   <si>
@@ -104,988 +1040,52 @@
     <t xml:space="preserve">Cody Weightman</t>
   </si>
   <si>
+    <t xml:space="preserve">Rhylee West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Bontempelli</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arthur Jones</t>
   </si>
   <si>
-    <t xml:space="preserve">Rhylee West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Bontempelli</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jordan Croft</t>
   </si>
   <si>
     <t xml:space="preserve">Cooper Hynes</t>
   </si>
   <si>
+    <t xml:space="preserve">Joel Freijah</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ed Richards</t>
   </si>
   <si>
-    <t xml:space="preserve">Joel Freijah</t>
-  </si>
-  <si>
     <t xml:space="preserve">Josh Dolan</t>
   </si>
   <si>
     <t xml:space="preserve">Tim English</t>
   </si>
   <si>
+    <t xml:space="preserve">Sam Davidson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matthew Kennedy</t>
   </si>
   <si>
-    <t xml:space="preserve">Sam Davidson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ryley Sanders</t>
   </si>
   <si>
     <t xml:space="preserve">Bailey Williams</t>
   </si>
   <si>
+    <t xml:space="preserve">Tom Liberatore</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rory Lobb</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom Liberatore</t>
-  </si>
-  <si>
     <t xml:space="preserve">Buku Khamis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions v hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Morris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Cameron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kai Lohmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Bailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cam Rayner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eric Hipwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conor McKenna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugh McCluggage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Ashcroft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Draper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levi Ashcroft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachie Neale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarrod Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Tunstill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Dunkley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Fort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaspa Fletcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ty Gallop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Gunston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mabior Chol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Lewis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Ginnivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Moore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Macdonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Greeves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Newcombe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Morrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Hardwick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lloyd Meek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Weddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massimo D'Ambrosio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cam Mackenzie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarman Impey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows v richmond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taylor Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Thilthorpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Rachele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Keays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izak Rankine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finnbar Maley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Neal-Bullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Dawson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Soligo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Curtin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Cumming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan McAndrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Peatling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Nankervis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Hall-Kahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">richmond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Lynch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Lalor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mykelti Lefau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhyan Mansell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seth Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Peucker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taj Hotton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Taranto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyler Sonsie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Cumming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Ralphsmith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Nankervis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dion Prestia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Retschko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Banks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats v essendon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">essendon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nate Caddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Wright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hussien El Achkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sullivan Robey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Kako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dyson Sharp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nik Cox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archer Day-Wicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Durham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zach Merrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Setterfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben McKay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Redman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Farrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Kondogiannis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Blakiston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Artemis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shannon Neale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shaun Mannagh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jay Polkinghorne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Dangerfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Wiltshire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Dempsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brad Close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryan Miers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Worpel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Blicavs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Atkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oisin Mullin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jhye Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lawson Humphries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne v fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Treacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Amiss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Voss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Frederick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Dudley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shai Bolton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murphy Reid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Switkowski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caleb Serong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Cox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan O'Driscoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Brayshaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neil Erasmus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Wagner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscar McDonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob van Rooyen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayley Fritsch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kysaiah Pickett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Sharp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Jefferson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kade Chandler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paddy Cross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Langford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latrelle Pickett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Petty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Gawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ed Langdon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Sparrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Fitzgerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Steele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koltyn Tholstrup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Rivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans v port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Georgiades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Durdin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Whitlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Horne-Francis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todd Marshall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Bamert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Zadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Watkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Moraes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Byrne-Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordon Sweet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dante Visentini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jase Burgoyne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ollie Wines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miles Bergman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willem Drew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Curnow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan McDonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Papley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Heeney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chad Warner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Cootee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malcolm Rosas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braeden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Errol Gulden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Lloyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Rowbottom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Grundy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Jordon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Serong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Blakey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callum Mills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney v gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold coast suns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jed Walter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Humphrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Petracca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leonardo Lombard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Patterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caleb Lewis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Touk Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zeke Uwland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ned Moyle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau Addinsall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Rowell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Jeffrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Rioli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Noble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Stringer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Cadman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Gruzewski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callum Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Hamilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Bedford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Coniglio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Rowston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conor Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Angwin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier O'Halloran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finn Callaghan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clayton Oliver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Madden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Ough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Himmelberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Fonti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda v carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Kemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Ainsworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch McGovern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talor Byrne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Cottrell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Cripps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">George Hewett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jagga Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Acres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marc Pittonet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Cerra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Lord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lewis Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Florent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Dean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Higgins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Ryan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Sharman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Owens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattaes Phillipou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nasiah Wanganeen-Milera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rowan Marshall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom De Koning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Garcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugh Boxshall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradley Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Byrnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Silvagni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Windhager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">west coast eagles v collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel McStay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Membrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan De Goey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Daicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau McCreery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Lipinski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ned Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steele Sidebottom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Crisp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Cameron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward Allan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Pendlebury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dan Houston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Daicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Howe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">west coast eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Waterman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobe Shanahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan Murdock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elliot Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willem Duursma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Cole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harley Reid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey J. Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bo Allan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Francou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamish Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Maric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Kelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brady Hough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Starcevich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Herbert</t>
   </si>
 </sst>
 </file>
@@ -1423,7 +1423,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="42.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -1468,18 +1468,18 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="F2" t="n">
-        <v>2.24</v>
+        <v>1.66</v>
       </c>
       <c r="G2" t="n">
-        <v>5.14</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -1491,18 +1491,18 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="F3" t="n">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>6.52</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1514,18 +1514,18 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="F4" t="n">
-        <v>3.29</v>
+        <v>1.85</v>
       </c>
       <c r="G4" t="n">
-        <v>9.87</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -1537,18 +1537,18 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="F5" t="n">
-        <v>3.47</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>10.79</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -1560,18 +1560,18 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>2.03</v>
+        <v>1.39</v>
       </c>
       <c r="F6" t="n">
-        <v>6.71</v>
+        <v>2.77</v>
       </c>
       <c r="G6" t="n">
-        <v>31.42</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -1583,18 +1583,18 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="F7" t="n">
-        <v>7.12</v>
+        <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>34.52</v>
+        <v>8.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -1606,18 +1606,18 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="F8" t="n">
-        <v>7.31</v>
+        <v>3.68</v>
       </c>
       <c r="G8" t="n">
-        <v>36.06</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1629,18 +1629,18 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="F9" t="n">
-        <v>8.22</v>
+        <v>7.76</v>
       </c>
       <c r="G9" t="n">
-        <v>43.41</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -1652,18 +1652,18 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>2.58</v>
+        <v>2.21</v>
       </c>
       <c r="F10" t="n">
-        <v>11.42</v>
+        <v>8.16</v>
       </c>
       <c r="G10" t="n">
-        <v>72.83</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -1675,18 +1675,18 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>2.86</v>
+        <v>2.27</v>
       </c>
       <c r="F11" t="n">
-        <v>14.31</v>
+        <v>8.64</v>
       </c>
       <c r="G11" t="n">
-        <v>103.55</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -1698,18 +1698,18 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="F12" t="n">
-        <v>17.6</v>
+        <v>12.08</v>
       </c>
       <c r="G12" t="n">
-        <v>142.89</v>
+        <v>79.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -1721,18 +1721,18 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>3.67</v>
+        <v>3.22</v>
       </c>
       <c r="F13" t="n">
-        <v>24.39</v>
+        <v>18.41</v>
       </c>
       <c r="G13" t="n">
-        <v>236.55</v>
+        <v>153.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -1744,18 +1744,18 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>3.94</v>
+        <v>3.28</v>
       </c>
       <c r="F14" t="n">
-        <v>28.36</v>
+        <v>19.2</v>
       </c>
       <c r="G14" t="n">
-        <v>298.35</v>
+        <v>163.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -1767,18 +1767,18 @@
         <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>4.54</v>
+        <v>3.56</v>
       </c>
       <c r="F15" t="n">
-        <v>38.11</v>
+        <v>22.89</v>
       </c>
       <c r="G15" t="n">
-        <v>469.76</v>
+        <v>214.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
@@ -1790,18 +1790,18 @@
         <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>4.65</v>
+        <v>3.75</v>
       </c>
       <c r="F16" t="n">
-        <v>40.03</v>
+        <v>25.57</v>
       </c>
       <c r="G16" t="n">
-        <v>506.44</v>
+        <v>254.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -1813,18 +1813,18 @@
         <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>4.68</v>
+        <v>3.97</v>
       </c>
       <c r="F17" t="n">
-        <v>40.6</v>
+        <v>28.75</v>
       </c>
       <c r="G17" t="n">
-        <v>517.41</v>
+        <v>304.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -1836,18 +1836,18 @@
         <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>4.78</v>
+        <v>5.3</v>
       </c>
       <c r="F18" t="n">
-        <v>42.41</v>
+        <v>52.48</v>
       </c>
       <c r="G18" t="n">
-        <v>553.3</v>
+        <v>766.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -1859,18 +1859,18 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>5.1</v>
+        <v>5.73</v>
       </c>
       <c r="F19" t="n">
-        <v>48.41</v>
+        <v>61.82</v>
       </c>
       <c r="G19" t="n">
-        <v>677.2</v>
+        <v>983.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -1882,18 +1882,18 @@
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="F20" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="G20" t="n">
-        <v>3.09</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
@@ -1905,18 +1905,18 @@
         <v>29</v>
       </c>
       <c r="E21" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="F21" t="n">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="G21" t="n">
-        <v>9.08</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
@@ -1928,18 +1928,18 @@
         <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="F22" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="G22" t="n">
-        <v>9.09</v>
+        <v>8.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
@@ -1951,18 +1951,18 @@
         <v>31</v>
       </c>
       <c r="E23" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="F23" t="n">
-        <v>3.19</v>
+        <v>3.77</v>
       </c>
       <c r="G23" t="n">
-        <v>9.38</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -1974,18 +1974,18 @@
         <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="F24" t="n">
-        <v>3.38</v>
+        <v>4.54</v>
       </c>
       <c r="G24" t="n">
-        <v>10.34</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -1997,18 +1997,18 @@
         <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="F25" t="n">
-        <v>3.51</v>
+        <v>5.34</v>
       </c>
       <c r="G25" t="n">
-        <v>10.98</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -2020,18 +2020,18 @@
         <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="F26" t="n">
-        <v>4.81</v>
+        <v>6.3</v>
       </c>
       <c r="G26" t="n">
-        <v>18.41</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
@@ -2043,18 +2043,18 @@
         <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="F27" t="n">
-        <v>6.37</v>
+        <v>7.35</v>
       </c>
       <c r="G27" t="n">
-        <v>28.92</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
@@ -2066,18 +2066,18 @@
         <v>36</v>
       </c>
       <c r="E28" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="F28" t="n">
-        <v>6.47</v>
+        <v>8.03</v>
       </c>
       <c r="G28" t="n">
-        <v>29.66</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
@@ -2089,18 +2089,18 @@
         <v>37</v>
       </c>
       <c r="E29" t="n">
-        <v>2.01</v>
+        <v>3.16</v>
       </c>
       <c r="F29" t="n">
-        <v>6.61</v>
+        <v>17.76</v>
       </c>
       <c r="G29" t="n">
-        <v>30.7</v>
+        <v>144.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
@@ -2112,18 +2112,18 @@
         <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>2.48</v>
+        <v>3.21</v>
       </c>
       <c r="F30" t="n">
-        <v>10.5</v>
+        <v>18.32</v>
       </c>
       <c r="G30" t="n">
-        <v>63.85</v>
+        <v>152.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
@@ -2135,18 +2135,18 @@
         <v>39</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5</v>
+        <v>3.71</v>
       </c>
       <c r="F31" t="n">
-        <v>10.72</v>
+        <v>24.89</v>
       </c>
       <c r="G31" t="n">
-        <v>65.91</v>
+        <v>244.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
@@ -2158,18 +2158,18 @@
         <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>2.59</v>
+        <v>3.74</v>
       </c>
       <c r="F32" t="n">
-        <v>11.55</v>
+        <v>25.36</v>
       </c>
       <c r="G32" t="n">
-        <v>74.15</v>
+        <v>251.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
@@ -2181,18 +2181,18 @@
         <v>41</v>
       </c>
       <c r="E33" t="n">
-        <v>3.07</v>
+        <v>3.88</v>
       </c>
       <c r="F33" t="n">
-        <v>16.67</v>
+        <v>27.38</v>
       </c>
       <c r="G33" t="n">
-        <v>131.32</v>
+        <v>282.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
@@ -2204,18 +2204,18 @@
         <v>42</v>
       </c>
       <c r="E34" t="n">
-        <v>3.25</v>
+        <v>5.09</v>
       </c>
       <c r="F34" t="n">
-        <v>18.89</v>
+        <v>48.28</v>
       </c>
       <c r="G34" t="n">
-        <v>159.37</v>
+        <v>674.46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
@@ -2227,18 +2227,18 @@
         <v>43</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>5.27</v>
       </c>
       <c r="F35" t="n">
-        <v>29.25</v>
+        <v>51.97</v>
       </c>
       <c r="G35" t="n">
-        <v>312.94</v>
+        <v>754.92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
@@ -2250,18 +2250,18 @@
         <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>4.04</v>
+        <v>6.39</v>
       </c>
       <c r="F36" t="n">
-        <v>29.78</v>
+        <v>77.37</v>
       </c>
       <c r="G36" t="n">
-        <v>321.66</v>
+        <v>1384.39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
@@ -2273,18 +2273,18 @@
         <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>5.28</v>
+        <v>6.97</v>
       </c>
       <c r="F37" t="n">
-        <v>52.09</v>
+        <v>92.39</v>
       </c>
       <c r="G37" t="n">
-        <v>757.46</v>
+        <v>1813.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -2296,18 +2296,18 @@
         <v>48</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="F38" t="n">
-        <v>1.88</v>
+        <v>2.65</v>
       </c>
       <c r="G38" t="n">
-        <v>3.77</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -2319,18 +2319,18 @@
         <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="F39" t="n">
-        <v>2.07</v>
+        <v>3.47</v>
       </c>
       <c r="G39" t="n">
-        <v>4.49</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -2342,18 +2342,18 @@
         <v>50</v>
       </c>
       <c r="E40" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="F40" t="n">
-        <v>2.1</v>
+        <v>4.89</v>
       </c>
       <c r="G40" t="n">
-        <v>4.62</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -2365,18 +2365,18 @@
         <v>51</v>
       </c>
       <c r="E41" t="n">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="F41" t="n">
-        <v>2.38</v>
+        <v>5.46</v>
       </c>
       <c r="G41" t="n">
-        <v>5.69</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -2388,18 +2388,18 @@
         <v>52</v>
       </c>
       <c r="E42" t="n">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="F42" t="n">
-        <v>3.17</v>
+        <v>6.24</v>
       </c>
       <c r="G42" t="n">
-        <v>9.27</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -2411,18 +2411,18 @@
         <v>53</v>
       </c>
       <c r="E43" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="F43" t="n">
-        <v>3.46</v>
+        <v>6.91</v>
       </c>
       <c r="G43" t="n">
-        <v>10.77</v>
+        <v>32.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B44" t="s">
         <v>46</v>
@@ -2434,18 +2434,18 @@
         <v>54</v>
       </c>
       <c r="E44" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="F44" t="n">
-        <v>4.04</v>
+        <v>7.14</v>
       </c>
       <c r="G44" t="n">
-        <v>13.86</v>
+        <v>34.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B45" t="s">
         <v>46</v>
@@ -2457,18 +2457,18 @@
         <v>55</v>
       </c>
       <c r="E45" t="n">
-        <v>2.31</v>
+        <v>2.09</v>
       </c>
       <c r="F45" t="n">
-        <v>9.02</v>
+        <v>7.18</v>
       </c>
       <c r="G45" t="n">
-        <v>50.25</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B46" t="s">
         <v>46</v>
@@ -2480,18 +2480,18 @@
         <v>56</v>
       </c>
       <c r="E46" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="F46" t="n">
-        <v>9.19</v>
+        <v>9.31</v>
       </c>
       <c r="G46" t="n">
-        <v>51.76</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B47" t="s">
         <v>46</v>
@@ -2503,18 +2503,18 @@
         <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="F47" t="n">
-        <v>10.06</v>
+        <v>17.48</v>
       </c>
       <c r="G47" t="n">
-        <v>59.7</v>
+        <v>141.29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
@@ -2526,18 +2526,18 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>2.79</v>
+        <v>3.21</v>
       </c>
       <c r="F48" t="n">
-        <v>13.62</v>
+        <v>18.3</v>
       </c>
       <c r="G48" t="n">
-        <v>95.92</v>
+        <v>151.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B49" t="s">
         <v>46</v>
@@ -2549,18 +2549,18 @@
         <v>59</v>
       </c>
       <c r="E49" t="n">
-        <v>3.43</v>
+        <v>4.4</v>
       </c>
       <c r="F49" t="n">
-        <v>21.12</v>
+        <v>35.6</v>
       </c>
       <c r="G49" t="n">
-        <v>189.47</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B50" t="s">
         <v>46</v>
@@ -2572,18 +2572,18 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.61</v>
+        <v>4.64</v>
       </c>
       <c r="F50" t="n">
-        <v>23.52</v>
+        <v>39.93</v>
       </c>
       <c r="G50" t="n">
-        <v>223.68</v>
+        <v>504.43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B51" t="s">
         <v>46</v>
@@ -2595,18 +2595,18 @@
         <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>3.87</v>
+        <v>6.88</v>
       </c>
       <c r="F51" t="n">
-        <v>27.3</v>
+        <v>90.01</v>
       </c>
       <c r="G51" t="n">
-        <v>281.33</v>
+        <v>1742.86</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B52" t="s">
         <v>46</v>
@@ -2618,18 +2618,18 @@
         <v>62</v>
       </c>
       <c r="E52" t="n">
-        <v>4.21</v>
+        <v>7.16</v>
       </c>
       <c r="F52" t="n">
-        <v>32.48</v>
+        <v>97.59</v>
       </c>
       <c r="G52" t="n">
-        <v>367.56</v>
+        <v>1970.51</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B53" t="s">
         <v>46</v>
@@ -2641,18 +2641,18 @@
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>4.23</v>
+        <v>7.19</v>
       </c>
       <c r="F53" t="n">
-        <v>32.81</v>
+        <v>98.44</v>
       </c>
       <c r="G53" t="n">
-        <v>373.21</v>
+        <v>1996.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B54" t="s">
         <v>46</v>
@@ -2664,18 +2664,18 @@
         <v>64</v>
       </c>
       <c r="E54" t="n">
-        <v>5.61</v>
+        <v>10.54</v>
       </c>
       <c r="F54" t="n">
-        <v>59.17</v>
+        <v>214.96</v>
       </c>
       <c r="G54" t="n">
-        <v>920.03</v>
+        <v>6522.35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B55" t="s">
         <v>46</v>
@@ -2687,18 +2687,18 @@
         <v>65</v>
       </c>
       <c r="E55" t="n">
-        <v>6.4</v>
+        <v>11.86</v>
       </c>
       <c r="F55" t="n">
-        <v>77.61</v>
+        <v>273.47</v>
       </c>
       <c r="G55" t="n">
-        <v>1390.91</v>
+        <v>9386.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B56" t="s">
         <v>46</v>
@@ -2710,18 +2710,18 @@
         <v>67</v>
       </c>
       <c r="E56" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="F56" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="G56" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B57" t="s">
         <v>46</v>
@@ -2736,15 +2736,15 @@
         <v>1.23</v>
       </c>
       <c r="F57" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="G57" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B58" t="s">
         <v>46</v>
@@ -2756,18 +2756,18 @@
         <v>69</v>
       </c>
       <c r="E58" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="F58" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B59" t="s">
         <v>46</v>
@@ -2779,18 +2779,18 @@
         <v>70</v>
       </c>
       <c r="E59" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="F59" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="G59" t="n">
-        <v>7.45</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B60" t="s">
         <v>46</v>
@@ -2802,18 +2802,18 @@
         <v>71</v>
       </c>
       <c r="E60" t="n">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="F60" t="n">
-        <v>4.06</v>
+        <v>3.15</v>
       </c>
       <c r="G60" t="n">
-        <v>13.97</v>
+        <v>9.21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B61" t="s">
         <v>46</v>
@@ -2825,18 +2825,18 @@
         <v>72</v>
       </c>
       <c r="E61" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="F61" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="G61" t="n">
-        <v>15.91</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B62" t="s">
         <v>46</v>
@@ -2848,18 +2848,18 @@
         <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="F62" t="n">
-        <v>5.41</v>
+        <v>3.37</v>
       </c>
       <c r="G62" t="n">
-        <v>22.28</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B63" t="s">
         <v>46</v>
@@ -2871,18 +2871,18 @@
         <v>74</v>
       </c>
       <c r="E63" t="n">
-        <v>1.99</v>
+        <v>1.63</v>
       </c>
       <c r="F63" t="n">
-        <v>6.47</v>
+        <v>4.04</v>
       </c>
       <c r="G63" t="n">
-        <v>29.68</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B64" t="s">
         <v>46</v>
@@ -2894,18 +2894,18 @@
         <v>75</v>
       </c>
       <c r="E64" t="n">
-        <v>2.83</v>
+        <v>1.79</v>
       </c>
       <c r="F64" t="n">
-        <v>14.02</v>
+        <v>5.03</v>
       </c>
       <c r="G64" t="n">
-        <v>100.34</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B65" t="s">
         <v>46</v>
@@ -2917,18 +2917,18 @@
         <v>76</v>
       </c>
       <c r="E65" t="n">
-        <v>3.58</v>
+        <v>1.81</v>
       </c>
       <c r="F65" t="n">
-        <v>23.13</v>
+        <v>5.19</v>
       </c>
       <c r="G65" t="n">
-        <v>217.99</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B66" t="s">
         <v>46</v>
@@ -2940,18 +2940,18 @@
         <v>77</v>
       </c>
       <c r="E66" t="n">
-        <v>3.66</v>
+        <v>1.91</v>
       </c>
       <c r="F66" t="n">
-        <v>24.28</v>
+        <v>5.9</v>
       </c>
       <c r="G66" t="n">
-        <v>234.95</v>
+        <v>25.58</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B67" t="s">
         <v>46</v>
@@ -2963,18 +2963,18 @@
         <v>78</v>
       </c>
       <c r="E67" t="n">
-        <v>3.98</v>
+        <v>2.05</v>
       </c>
       <c r="F67" t="n">
-        <v>28.93</v>
+        <v>6.93</v>
       </c>
       <c r="G67" t="n">
-        <v>307.62</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B68" t="s">
         <v>46</v>
@@ -2986,18 +2986,18 @@
         <v>79</v>
       </c>
       <c r="E68" t="n">
-        <v>4.1</v>
+        <v>2.87</v>
       </c>
       <c r="F68" t="n">
-        <v>30.79</v>
+        <v>14.42</v>
       </c>
       <c r="G68" t="n">
-        <v>338.51</v>
+        <v>104.78</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B69" t="s">
         <v>46</v>
@@ -3009,18 +3009,18 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>4.57</v>
+        <v>3.11</v>
       </c>
       <c r="F69" t="n">
-        <v>38.68</v>
+        <v>17.17</v>
       </c>
       <c r="G69" t="n">
-        <v>480.4</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B70" t="s">
         <v>46</v>
@@ -3032,18 +3032,18 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>4.59</v>
+        <v>3.2</v>
       </c>
       <c r="F70" t="n">
-        <v>39.03</v>
+        <v>18.17</v>
       </c>
       <c r="G70" t="n">
-        <v>487.23</v>
+        <v>150.11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B71" t="s">
         <v>46</v>
@@ -3055,18 +3055,18 @@
         <v>82</v>
       </c>
       <c r="E71" t="n">
-        <v>4.76</v>
+        <v>4.27</v>
       </c>
       <c r="F71" t="n">
-        <v>42.08</v>
+        <v>33.55</v>
       </c>
       <c r="G71" t="n">
-        <v>546.62</v>
+        <v>386.23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B72" t="s">
         <v>46</v>
@@ -3078,18 +3078,18 @@
         <v>83</v>
       </c>
       <c r="E72" t="n">
-        <v>5.28</v>
+        <v>4.79</v>
       </c>
       <c r="F72" t="n">
-        <v>52.05</v>
+        <v>42.61</v>
       </c>
       <c r="G72" t="n">
-        <v>756.49</v>
+        <v>557.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="B73" t="s">
         <v>46</v>
@@ -3101,18 +3101,18 @@
         <v>84</v>
       </c>
       <c r="E73" t="n">
-        <v>7.01</v>
+        <v>7.53</v>
       </c>
       <c r="F73" t="n">
-        <v>93.44</v>
+        <v>108.36</v>
       </c>
       <c r="G73" t="n">
-        <v>1844.64</v>
+        <v>2310.21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B74" t="s">
         <v>85</v>
@@ -3124,18 +3124,18 @@
         <v>87</v>
       </c>
       <c r="E74" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="F74" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="G74" t="n">
-        <v>3.63</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B75" t="s">
         <v>85</v>
@@ -3147,18 +3147,18 @@
         <v>88</v>
       </c>
       <c r="E75" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="F75" t="n">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="G75" t="n">
-        <v>3.72</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B76" t="s">
         <v>85</v>
@@ -3170,18 +3170,18 @@
         <v>89</v>
       </c>
       <c r="E76" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="F76" t="n">
-        <v>2.05</v>
+        <v>2.81</v>
       </c>
       <c r="G76" t="n">
-        <v>4.4</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B77" t="s">
         <v>85</v>
@@ -3193,18 +3193,18 @@
         <v>90</v>
       </c>
       <c r="E77" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="F77" t="n">
-        <v>2.41</v>
+        <v>3.37</v>
       </c>
       <c r="G77" t="n">
-        <v>5.82</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B78" t="s">
         <v>85</v>
@@ -3216,18 +3216,18 @@
         <v>91</v>
       </c>
       <c r="E78" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="F78" t="n">
-        <v>3.26</v>
+        <v>4.64</v>
       </c>
       <c r="G78" t="n">
-        <v>9.75</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B79" t="s">
         <v>85</v>
@@ -3239,18 +3239,18 @@
         <v>92</v>
       </c>
       <c r="E79" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="F79" t="n">
-        <v>4.85</v>
+        <v>7.09</v>
       </c>
       <c r="G79" t="n">
-        <v>18.67</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B80" t="s">
         <v>85</v>
@@ -3262,18 +3262,18 @@
         <v>93</v>
       </c>
       <c r="E80" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="F80" t="n">
-        <v>5.11</v>
+        <v>7.62</v>
       </c>
       <c r="G80" t="n">
-        <v>20.34</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B81" t="s">
         <v>85</v>
@@ -3285,18 +3285,18 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="F81" t="n">
-        <v>5.37</v>
+        <v>7.71</v>
       </c>
       <c r="G81" t="n">
-        <v>22.01</v>
+        <v>39.21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B82" t="s">
         <v>85</v>
@@ -3308,18 +3308,18 @@
         <v>95</v>
       </c>
       <c r="E82" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="F82" t="n">
-        <v>5.5</v>
+        <v>7.75</v>
       </c>
       <c r="G82" t="n">
-        <v>22.87</v>
+        <v>39.56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B83" t="s">
         <v>85</v>
@@ -3331,18 +3331,18 @@
         <v>96</v>
       </c>
       <c r="E83" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="F83" t="n">
-        <v>5.97</v>
+        <v>8.83</v>
       </c>
       <c r="G83" t="n">
-        <v>26.09</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B84" t="s">
         <v>85</v>
@@ -3354,18 +3354,18 @@
         <v>97</v>
       </c>
       <c r="E84" t="n">
-        <v>2.69</v>
+        <v>3.32</v>
       </c>
       <c r="F84" t="n">
-        <v>12.57</v>
+        <v>19.74</v>
       </c>
       <c r="G84" t="n">
-        <v>84.66</v>
+        <v>170.59</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B85" t="s">
         <v>85</v>
@@ -3377,18 +3377,18 @@
         <v>98</v>
       </c>
       <c r="E85" t="n">
-        <v>3.09</v>
+        <v>3.74</v>
       </c>
       <c r="F85" t="n">
-        <v>16.93</v>
+        <v>25.3</v>
       </c>
       <c r="G85" t="n">
-        <v>134.47</v>
+        <v>250.35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B86" t="s">
         <v>85</v>
@@ -3400,18 +3400,18 @@
         <v>99</v>
       </c>
       <c r="E86" t="n">
-        <v>3.13</v>
+        <v>3.89</v>
       </c>
       <c r="F86" t="n">
-        <v>17.38</v>
+        <v>27.51</v>
       </c>
       <c r="G86" t="n">
-        <v>140.13</v>
+        <v>284.78</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B87" t="s">
         <v>85</v>
@@ -3423,18 +3423,18 @@
         <v>100</v>
       </c>
       <c r="E87" t="n">
-        <v>3.13</v>
+        <v>4.06</v>
       </c>
       <c r="F87" t="n">
-        <v>17.42</v>
+        <v>30.08</v>
       </c>
       <c r="G87" t="n">
-        <v>140.59</v>
+        <v>326.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B88" t="s">
         <v>85</v>
@@ -3446,18 +3446,18 @@
         <v>101</v>
       </c>
       <c r="E88" t="n">
-        <v>3.28</v>
+        <v>4.12</v>
       </c>
       <c r="F88" t="n">
-        <v>19.19</v>
+        <v>31.12</v>
       </c>
       <c r="G88" t="n">
-        <v>163.28</v>
+        <v>344.24</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B89" t="s">
         <v>85</v>
@@ -3469,18 +3469,18 @@
         <v>102</v>
       </c>
       <c r="E89" t="n">
-        <v>4.26</v>
+        <v>5.27</v>
       </c>
       <c r="F89" t="n">
-        <v>33.34</v>
+        <v>51.84</v>
       </c>
       <c r="G89" t="n">
-        <v>382.51</v>
+        <v>751.87</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B90" t="s">
         <v>85</v>
@@ -3492,18 +3492,18 @@
         <v>103</v>
       </c>
       <c r="E90" t="n">
-        <v>5.97</v>
+        <v>7.63</v>
       </c>
       <c r="F90" t="n">
-        <v>67.29</v>
+        <v>111.17</v>
       </c>
       <c r="G90" t="n">
-        <v>1119.47</v>
+        <v>2401.72</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B91" t="s">
         <v>85</v>
@@ -3515,18 +3515,18 @@
         <v>104</v>
       </c>
       <c r="E91" t="n">
-        <v>7.44</v>
+        <v>10.08</v>
       </c>
       <c r="F91" t="n">
-        <v>105.55</v>
+        <v>196.43</v>
       </c>
       <c r="G91" t="n">
-        <v>2219.7</v>
+        <v>5691.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B92" t="s">
         <v>85</v>
@@ -3538,18 +3538,18 @@
         <v>106</v>
       </c>
       <c r="E92" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="F92" t="n">
-        <v>3.49</v>
+        <v>1.94</v>
       </c>
       <c r="G92" t="n">
-        <v>10.89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B93" t="s">
         <v>85</v>
@@ -3561,18 +3561,18 @@
         <v>107</v>
       </c>
       <c r="E93" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="F93" t="n">
-        <v>5.62</v>
+        <v>2</v>
       </c>
       <c r="G93" t="n">
-        <v>23.66</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B94" t="s">
         <v>85</v>
@@ -3584,18 +3584,18 @@
         <v>108</v>
       </c>
       <c r="E94" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="F94" t="n">
-        <v>5.89</v>
+        <v>2.11</v>
       </c>
       <c r="G94" t="n">
-        <v>25.53</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B95" t="s">
         <v>85</v>
@@ -3607,18 +3607,18 @@
         <v>109</v>
       </c>
       <c r="E95" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="F95" t="n">
-        <v>6.85</v>
+        <v>3.4</v>
       </c>
       <c r="G95" t="n">
-        <v>32.53</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B96" t="s">
         <v>85</v>
@@ -3630,18 +3630,18 @@
         <v>110</v>
       </c>
       <c r="E96" t="n">
-        <v>2.18</v>
+        <v>1.52</v>
       </c>
       <c r="F96" t="n">
-        <v>7.89</v>
+        <v>3.44</v>
       </c>
       <c r="G96" t="n">
-        <v>40.7</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B97" t="s">
         <v>85</v>
@@ -3653,18 +3653,18 @@
         <v>111</v>
       </c>
       <c r="E97" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="F97" t="n">
-        <v>8.7</v>
+        <v>4.91</v>
       </c>
       <c r="G97" t="n">
-        <v>47.48</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B98" t="s">
         <v>85</v>
@@ -3676,18 +3676,18 @@
         <v>112</v>
       </c>
       <c r="E98" t="n">
-        <v>2.56</v>
+        <v>1.78</v>
       </c>
       <c r="F98" t="n">
-        <v>11.26</v>
+        <v>4.98</v>
       </c>
       <c r="G98" t="n">
-        <v>71.19</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B99" t="s">
         <v>85</v>
@@ -3699,18 +3699,18 @@
         <v>113</v>
       </c>
       <c r="E99" t="n">
-        <v>2.83</v>
+        <v>1.81</v>
       </c>
       <c r="F99" t="n">
-        <v>13.98</v>
+        <v>5.22</v>
       </c>
       <c r="G99" t="n">
-        <v>99.86</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B100" t="s">
         <v>85</v>
@@ -3722,18 +3722,18 @@
         <v>114</v>
       </c>
       <c r="E100" t="n">
-        <v>2.89</v>
+        <v>1.92</v>
       </c>
       <c r="F100" t="n">
-        <v>14.68</v>
+        <v>5.95</v>
       </c>
       <c r="G100" t="n">
-        <v>107.73</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B101" t="s">
         <v>85</v>
@@ -3745,18 +3745,18 @@
         <v>115</v>
       </c>
       <c r="E101" t="n">
-        <v>3.71</v>
+        <v>3.2</v>
       </c>
       <c r="F101" t="n">
-        <v>24.98</v>
+        <v>18.24</v>
       </c>
       <c r="G101" t="n">
-        <v>245.36</v>
+        <v>150.94</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B102" t="s">
         <v>85</v>
@@ -3768,18 +3768,18 @@
         <v>116</v>
       </c>
       <c r="E102" t="n">
-        <v>3.97</v>
+        <v>3.55</v>
       </c>
       <c r="F102" t="n">
-        <v>28.8</v>
+        <v>22.71</v>
       </c>
       <c r="G102" t="n">
-        <v>305.47</v>
+        <v>211.89</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B103" t="s">
         <v>85</v>
@@ -3791,18 +3791,18 @@
         <v>117</v>
       </c>
       <c r="E103" t="n">
-        <v>5.19</v>
+        <v>3.68</v>
       </c>
       <c r="F103" t="n">
-        <v>50.36</v>
+        <v>24.55</v>
       </c>
       <c r="G103" t="n">
-        <v>719.44</v>
+        <v>238.92</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B104" t="s">
         <v>85</v>
@@ -3814,18 +3814,18 @@
         <v>118</v>
       </c>
       <c r="E104" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="F104" t="n">
-        <v>61.09</v>
+        <v>26.19</v>
       </c>
       <c r="G104" t="n">
-        <v>965.97</v>
+        <v>263.97</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B105" t="s">
         <v>85</v>
@@ -3837,18 +3837,18 @@
         <v>119</v>
       </c>
       <c r="E105" t="n">
-        <v>5.72</v>
+        <v>3.95</v>
       </c>
       <c r="F105" t="n">
-        <v>61.47</v>
+        <v>28.43</v>
       </c>
       <c r="G105" t="n">
-        <v>975.13</v>
+        <v>299.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B106" t="s">
         <v>85</v>
@@ -3860,18 +3860,18 @@
         <v>120</v>
       </c>
       <c r="E106" t="n">
-        <v>5.86</v>
+        <v>4.03</v>
       </c>
       <c r="F106" t="n">
-        <v>64.69</v>
+        <v>29.74</v>
       </c>
       <c r="G106" t="n">
-        <v>1054.13</v>
+        <v>321.04</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B107" t="s">
         <v>85</v>
@@ -3883,18 +3883,18 @@
         <v>121</v>
       </c>
       <c r="E107" t="n">
-        <v>9.87</v>
+        <v>6.11</v>
       </c>
       <c r="F107" t="n">
-        <v>188.32</v>
+        <v>70.5</v>
       </c>
       <c r="G107" t="n">
-        <v>5339.14</v>
+        <v>1201.85</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B108" t="s">
         <v>85</v>
@@ -3906,18 +3906,18 @@
         <v>122</v>
       </c>
       <c r="E108" t="n">
-        <v>10.5</v>
+        <v>7.68</v>
       </c>
       <c r="F108" t="n">
-        <v>213.38</v>
+        <v>112.77</v>
       </c>
       <c r="G108" t="n">
-        <v>6450.32</v>
+        <v>2454.44</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B109" t="s">
         <v>85</v>
@@ -3929,18 +3929,18 @@
         <v>123</v>
       </c>
       <c r="E109" t="n">
-        <v>12.67</v>
+        <v>10.91</v>
       </c>
       <c r="F109" t="n">
-        <v>312.49</v>
+        <v>230.64</v>
       </c>
       <c r="G109" t="n">
-        <v>11481.74</v>
+        <v>7255.32</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B110" t="s">
         <v>124</v>
@@ -3952,18 +3952,18 @@
         <v>126</v>
       </c>
       <c r="E110" t="n">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="F110" t="n">
-        <v>2.93</v>
+        <v>1.5</v>
       </c>
       <c r="G110" t="n">
-        <v>8.14</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B111" t="s">
         <v>124</v>
@@ -3975,18 +3975,18 @@
         <v>127</v>
       </c>
       <c r="E111" t="n">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="F111" t="n">
-        <v>3.77</v>
+        <v>1.65</v>
       </c>
       <c r="G111" t="n">
-        <v>12.36</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B112" t="s">
         <v>124</v>
@@ -3998,18 +3998,18 @@
         <v>128</v>
       </c>
       <c r="E112" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="F112" t="n">
-        <v>4.64</v>
+        <v>2.16</v>
       </c>
       <c r="G112" t="n">
-        <v>17.37</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B113" t="s">
         <v>124</v>
@@ -4021,18 +4021,18 @@
         <v>129</v>
       </c>
       <c r="E113" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="F113" t="n">
-        <v>6.29</v>
+        <v>2.37</v>
       </c>
       <c r="G113" t="n">
-        <v>28.37</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B114" t="s">
         <v>124</v>
@@ -4044,18 +4044,18 @@
         <v>130</v>
       </c>
       <c r="E114" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="F114" t="n">
-        <v>6.92</v>
+        <v>3.51</v>
       </c>
       <c r="G114" t="n">
-        <v>33.01</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B115" t="s">
         <v>124</v>
@@ -4067,18 +4067,18 @@
         <v>131</v>
       </c>
       <c r="E115" t="n">
-        <v>2.17</v>
+        <v>1.55</v>
       </c>
       <c r="F115" t="n">
-        <v>7.84</v>
+        <v>3.61</v>
       </c>
       <c r="G115" t="n">
-        <v>40.26</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B116" t="s">
         <v>124</v>
@@ -4090,18 +4090,18 @@
         <v>132</v>
       </c>
       <c r="E116" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="F116" t="n">
-        <v>8.03</v>
+        <v>3.69</v>
       </c>
       <c r="G116" t="n">
-        <v>41.84</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B117" t="s">
         <v>124</v>
@@ -4113,18 +4113,18 @@
         <v>133</v>
       </c>
       <c r="E117" t="n">
-        <v>2.23</v>
+        <v>1.63</v>
       </c>
       <c r="F117" t="n">
-        <v>8.31</v>
+        <v>4.06</v>
       </c>
       <c r="G117" t="n">
-        <v>44.14</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B118" t="s">
         <v>124</v>
@@ -4136,18 +4136,18 @@
         <v>134</v>
       </c>
       <c r="E118" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="F118" t="n">
-        <v>11.13</v>
+        <v>10.32</v>
       </c>
       <c r="G118" t="n">
-        <v>69.98</v>
+        <v>62.14</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B119" t="s">
         <v>124</v>
@@ -4159,18 +4159,18 @@
         <v>135</v>
       </c>
       <c r="E119" t="n">
-        <v>3.33</v>
+        <v>2.65</v>
       </c>
       <c r="F119" t="n">
-        <v>19.77</v>
+        <v>12.1</v>
       </c>
       <c r="G119" t="n">
-        <v>171.08</v>
+        <v>79.71</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B120" t="s">
         <v>124</v>
@@ -4182,18 +4182,18 @@
         <v>136</v>
       </c>
       <c r="E120" t="n">
-        <v>3.37</v>
+        <v>2.68</v>
       </c>
       <c r="F120" t="n">
-        <v>20.28</v>
+        <v>12.4</v>
       </c>
       <c r="G120" t="n">
-        <v>177.91</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B121" t="s">
         <v>124</v>
@@ -4205,18 +4205,18 @@
         <v>137</v>
       </c>
       <c r="E121" t="n">
-        <v>4.86</v>
+        <v>2.82</v>
       </c>
       <c r="F121" t="n">
-        <v>43.83</v>
+        <v>13.86</v>
       </c>
       <c r="G121" t="n">
-        <v>581.72</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B122" t="s">
         <v>124</v>
@@ -4228,18 +4228,18 @@
         <v>138</v>
       </c>
       <c r="E122" t="n">
-        <v>7.39</v>
+        <v>2.84</v>
       </c>
       <c r="F122" t="n">
-        <v>104.24</v>
+        <v>14.07</v>
       </c>
       <c r="G122" t="n">
-        <v>2178.27</v>
+        <v>100.91</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B123" t="s">
         <v>124</v>
@@ -4251,18 +4251,18 @@
         <v>139</v>
       </c>
       <c r="E123" t="n">
-        <v>7.54</v>
+        <v>3.58</v>
       </c>
       <c r="F123" t="n">
-        <v>108.59</v>
+        <v>23.06</v>
       </c>
       <c r="G123" t="n">
-        <v>2317.58</v>
+        <v>216.98</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B124" t="s">
         <v>124</v>
@@ -4274,18 +4274,18 @@
         <v>140</v>
       </c>
       <c r="E124" t="n">
-        <v>10.51</v>
+        <v>3.97</v>
       </c>
       <c r="F124" t="n">
-        <v>213.65</v>
+        <v>28.81</v>
       </c>
       <c r="G124" t="n">
-        <v>6462.47</v>
+        <v>305.64</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B125" t="s">
         <v>124</v>
@@ -4297,18 +4297,18 @@
         <v>141</v>
       </c>
       <c r="E125" t="n">
-        <v>11.43</v>
+        <v>4.95</v>
       </c>
       <c r="F125" t="n">
-        <v>253.7</v>
+        <v>45.63</v>
       </c>
       <c r="G125" t="n">
-        <v>8379.99</v>
+        <v>618.82</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B126" t="s">
         <v>124</v>
@@ -4320,18 +4320,18 @@
         <v>142</v>
       </c>
       <c r="E126" t="n">
-        <v>12.69</v>
+        <v>6.09</v>
       </c>
       <c r="F126" t="n">
-        <v>313.43</v>
+        <v>70.01</v>
       </c>
       <c r="G126" t="n">
-        <v>11533.75</v>
+        <v>1189.14</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B127" t="s">
         <v>124</v>
@@ -4343,18 +4343,18 @@
         <v>143</v>
       </c>
       <c r="E127" t="n">
-        <v>13.33</v>
+        <v>10.19</v>
       </c>
       <c r="F127" t="n">
-        <v>346.27</v>
+        <v>200.8</v>
       </c>
       <c r="G127" t="n">
-        <v>13406.44</v>
+        <v>5883.61</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B128" t="s">
         <v>124</v>
@@ -4366,18 +4366,18 @@
         <v>145</v>
       </c>
       <c r="E128" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="F128" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="G128" t="n">
-        <v>2.55</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B129" t="s">
         <v>124</v>
@@ -4389,18 +4389,18 @@
         <v>146</v>
       </c>
       <c r="E129" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="F129" t="n">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="G129" t="n">
-        <v>3.61</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B130" t="s">
         <v>124</v>
@@ -4412,18 +4412,18 @@
         <v>147</v>
       </c>
       <c r="E130" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="F130" t="n">
-        <v>1.96</v>
+        <v>4.22</v>
       </c>
       <c r="G130" t="n">
-        <v>4.07</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B131" t="s">
         <v>124</v>
@@ -4435,18 +4435,18 @@
         <v>148</v>
       </c>
       <c r="E131" t="n">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="F131" t="n">
-        <v>2.26</v>
+        <v>4.69</v>
       </c>
       <c r="G131" t="n">
-        <v>5.23</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B132" t="s">
         <v>124</v>
@@ -4458,18 +4458,18 @@
         <v>149</v>
       </c>
       <c r="E132" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="F132" t="n">
-        <v>2.44</v>
+        <v>5.5</v>
       </c>
       <c r="G132" t="n">
-        <v>5.98</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B133" t="s">
         <v>124</v>
@@ -4481,18 +4481,18 @@
         <v>150</v>
       </c>
       <c r="E133" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="F133" t="n">
-        <v>2.56</v>
+        <v>6.1</v>
       </c>
       <c r="G133" t="n">
-        <v>6.47</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B134" t="s">
         <v>124</v>
@@ -4504,18 +4504,18 @@
         <v>151</v>
       </c>
       <c r="E134" t="n">
-        <v>1.36</v>
+        <v>2.37</v>
       </c>
       <c r="F134" t="n">
-        <v>2.6</v>
+        <v>9.49</v>
       </c>
       <c r="G134" t="n">
-        <v>6.66</v>
+        <v>54.44</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B135" t="s">
         <v>124</v>
@@ -4527,18 +4527,18 @@
         <v>152</v>
       </c>
       <c r="E135" t="n">
-        <v>1.47</v>
+        <v>2.42</v>
       </c>
       <c r="F135" t="n">
-        <v>3.18</v>
+        <v>9.93</v>
       </c>
       <c r="G135" t="n">
-        <v>9.31</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B136" t="s">
         <v>124</v>
@@ -4550,18 +4550,18 @@
         <v>153</v>
       </c>
       <c r="E136" t="n">
-        <v>1.6</v>
+        <v>2.54</v>
       </c>
       <c r="F136" t="n">
-        <v>3.89</v>
+        <v>11.09</v>
       </c>
       <c r="G136" t="n">
-        <v>13.02</v>
+        <v>69.52</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B137" t="s">
         <v>124</v>
@@ -4573,18 +4573,18 @@
         <v>154</v>
       </c>
       <c r="E137" t="n">
-        <v>2.41</v>
+        <v>2.89</v>
       </c>
       <c r="F137" t="n">
-        <v>9.9</v>
+        <v>14.59</v>
       </c>
       <c r="G137" t="n">
-        <v>58.2</v>
+        <v>106.75</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B138" t="s">
         <v>124</v>
@@ -4596,18 +4596,18 @@
         <v>155</v>
       </c>
       <c r="E138" t="n">
-        <v>2.84</v>
+        <v>3.85</v>
       </c>
       <c r="F138" t="n">
-        <v>14.15</v>
+        <v>26.99</v>
       </c>
       <c r="G138" t="n">
-        <v>101.74</v>
+        <v>276.57</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B139" t="s">
         <v>124</v>
@@ -4619,18 +4619,18 @@
         <v>156</v>
       </c>
       <c r="E139" t="n">
-        <v>2.86</v>
+        <v>4.08</v>
       </c>
       <c r="F139" t="n">
-        <v>14.29</v>
+        <v>30.38</v>
       </c>
       <c r="G139" t="n">
-        <v>103.37</v>
+        <v>331.69</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B140" t="s">
         <v>124</v>
@@ -4642,18 +4642,18 @@
         <v>157</v>
       </c>
       <c r="E140" t="n">
-        <v>3.63</v>
+        <v>4.7</v>
       </c>
       <c r="F140" t="n">
-        <v>23.86</v>
+        <v>40.99</v>
       </c>
       <c r="G140" t="n">
-        <v>228.63</v>
+        <v>525.08</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B141" t="s">
         <v>124</v>
@@ -4665,18 +4665,18 @@
         <v>158</v>
       </c>
       <c r="E141" t="n">
-        <v>3.95</v>
+        <v>4.78</v>
       </c>
       <c r="F141" t="n">
-        <v>28.47</v>
+        <v>42.34</v>
       </c>
       <c r="G141" t="n">
-        <v>300.24</v>
+        <v>551.9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B142" t="s">
         <v>124</v>
@@ -4688,18 +4688,18 @@
         <v>159</v>
       </c>
       <c r="E142" t="n">
-        <v>4.4</v>
+        <v>4.79</v>
       </c>
       <c r="F142" t="n">
-        <v>35.68</v>
+        <v>42.58</v>
       </c>
       <c r="G142" t="n">
-        <v>424.57</v>
+        <v>556.55</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B143" t="s">
         <v>124</v>
@@ -4711,18 +4711,18 @@
         <v>160</v>
       </c>
       <c r="E143" t="n">
-        <v>5.21</v>
+        <v>8.1</v>
       </c>
       <c r="F143" t="n">
-        <v>50.61</v>
+        <v>125.74</v>
       </c>
       <c r="G143" t="n">
-        <v>724.79</v>
+        <v>2895.34</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B144" t="s">
         <v>124</v>
@@ -4734,18 +4734,18 @@
         <v>161</v>
       </c>
       <c r="E144" t="n">
-        <v>5.46</v>
+        <v>12.24</v>
       </c>
       <c r="F144" t="n">
-        <v>55.78</v>
+        <v>291.12</v>
       </c>
       <c r="G144" t="n">
-        <v>840.82</v>
+        <v>10316.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B145" t="s">
         <v>124</v>
@@ -4757,18 +4757,18 @@
         <v>162</v>
       </c>
       <c r="E145" t="n">
-        <v>6.01</v>
+        <v>14.38</v>
       </c>
       <c r="F145" t="n">
-        <v>68.02</v>
+        <v>403.64</v>
       </c>
       <c r="G145" t="n">
-        <v>1138.03</v>
+        <v>16897.2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B146" t="s">
         <v>163</v>
@@ -4780,18 +4780,18 @@
         <v>165</v>
       </c>
       <c r="E146" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="F146" t="n">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="G146" t="n">
-        <v>3.75</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B147" t="s">
         <v>163</v>
@@ -4803,18 +4803,18 @@
         <v>166</v>
       </c>
       <c r="E147" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="F147" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="G147" t="n">
-        <v>4.31</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B148" t="s">
         <v>163</v>
@@ -4826,18 +4826,18 @@
         <v>167</v>
       </c>
       <c r="E148" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="F148" t="n">
-        <v>2.13</v>
+        <v>3.23</v>
       </c>
       <c r="G148" t="n">
-        <v>4.7</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B149" t="s">
         <v>163</v>
@@ -4849,18 +4849,18 @@
         <v>168</v>
       </c>
       <c r="E149" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="F149" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="G149" t="n">
-        <v>8.02</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B150" t="s">
         <v>163</v>
@@ -4872,18 +4872,18 @@
         <v>169</v>
       </c>
       <c r="E150" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="F150" t="n">
-        <v>3.37</v>
+        <v>4.76</v>
       </c>
       <c r="G150" t="n">
-        <v>10.27</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B151" t="s">
         <v>163</v>
@@ -4895,18 +4895,18 @@
         <v>170</v>
       </c>
       <c r="E151" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="F151" t="n">
-        <v>4.66</v>
+        <v>5.11</v>
       </c>
       <c r="G151" t="n">
-        <v>17.49</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B152" t="s">
         <v>163</v>
@@ -4918,18 +4918,18 @@
         <v>171</v>
       </c>
       <c r="E152" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="F152" t="n">
-        <v>4.81</v>
+        <v>5.4</v>
       </c>
       <c r="G152" t="n">
-        <v>18.4</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B153" t="s">
         <v>163</v>
@@ -4941,18 +4941,18 @@
         <v>172</v>
       </c>
       <c r="E153" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="F153" t="n">
-        <v>4.81</v>
+        <v>6.35</v>
       </c>
       <c r="G153" t="n">
-        <v>18.44</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B154" t="s">
         <v>163</v>
@@ -4964,18 +4964,18 @@
         <v>173</v>
       </c>
       <c r="E154" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="F154" t="n">
-        <v>5.83</v>
+        <v>6.41</v>
       </c>
       <c r="G154" t="n">
-        <v>25.1</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B155" t="s">
         <v>163</v>
@@ -4987,18 +4987,18 @@
         <v>174</v>
       </c>
       <c r="E155" t="n">
-        <v>3.06</v>
+        <v>2.34</v>
       </c>
       <c r="F155" t="n">
-        <v>16.57</v>
+        <v>9.27</v>
       </c>
       <c r="G155" t="n">
-        <v>130.14</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B156" t="s">
         <v>163</v>
@@ -5010,18 +5010,18 @@
         <v>175</v>
       </c>
       <c r="E156" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="F156" t="n">
-        <v>22.03</v>
+        <v>18.65</v>
       </c>
       <c r="G156" t="n">
-        <v>202.18</v>
+        <v>156.23</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B157" t="s">
         <v>163</v>
@@ -5033,18 +5033,18 @@
         <v>176</v>
       </c>
       <c r="E157" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="F157" t="n">
-        <v>23.56</v>
+        <v>21.99</v>
       </c>
       <c r="G157" t="n">
-        <v>224.18</v>
+        <v>201.56</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B158" t="s">
         <v>163</v>
@@ -5056,18 +5056,18 @@
         <v>177</v>
       </c>
       <c r="E158" t="n">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="F158" t="n">
-        <v>25.87</v>
+        <v>24.96</v>
       </c>
       <c r="G158" t="n">
-        <v>259.07</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B159" t="s">
         <v>163</v>
@@ -5079,18 +5079,18 @@
         <v>178</v>
       </c>
       <c r="E159" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="F159" t="n">
-        <v>26.11</v>
+        <v>27.76</v>
       </c>
       <c r="G159" t="n">
-        <v>262.75</v>
+        <v>288.79</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B160" t="s">
         <v>163</v>
@@ -5102,18 +5102,18 @@
         <v>179</v>
       </c>
       <c r="E160" t="n">
-        <v>4.21</v>
+        <v>4.05</v>
       </c>
       <c r="F160" t="n">
-        <v>32.44</v>
+        <v>30.03</v>
       </c>
       <c r="G160" t="n">
-        <v>366.82</v>
+        <v>325.76</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B161" t="s">
         <v>163</v>
@@ -5125,18 +5125,18 @@
         <v>180</v>
       </c>
       <c r="E161" t="n">
-        <v>5.96</v>
+        <v>5.11</v>
       </c>
       <c r="F161" t="n">
-        <v>66.91</v>
+        <v>48.62</v>
       </c>
       <c r="G161" t="n">
-        <v>1109.65</v>
+        <v>681.71</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B162" t="s">
         <v>163</v>
@@ -5148,18 +5148,18 @@
         <v>181</v>
       </c>
       <c r="E162" t="n">
-        <v>7</v>
+        <v>7.19</v>
       </c>
       <c r="F162" t="n">
-        <v>93.09</v>
+        <v>98.41</v>
       </c>
       <c r="G162" t="n">
-        <v>1834.14</v>
+        <v>1995.87</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B163" t="s">
         <v>163</v>
@@ -5171,18 +5171,18 @@
         <v>182</v>
       </c>
       <c r="E163" t="n">
-        <v>10.25</v>
+        <v>9.6</v>
       </c>
       <c r="F163" t="n">
-        <v>203.16</v>
+        <v>177.75</v>
       </c>
       <c r="G163" t="n">
-        <v>5988.41</v>
+        <v>4892.23</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B164" t="s">
         <v>163</v>
@@ -5194,18 +5194,18 @@
         <v>184</v>
       </c>
       <c r="E164" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="F164" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="G164" t="n">
-        <v>6.24</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B165" t="s">
         <v>163</v>
@@ -5217,18 +5217,18 @@
         <v>185</v>
       </c>
       <c r="E165" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="F165" t="n">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="G165" t="n">
-        <v>7.09</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B166" t="s">
         <v>163</v>
@@ -5240,18 +5240,18 @@
         <v>186</v>
       </c>
       <c r="E166" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="F166" t="n">
-        <v>3.71</v>
+        <v>2.65</v>
       </c>
       <c r="G166" t="n">
-        <v>12.03</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B167" t="s">
         <v>163</v>
@@ -5263,18 +5263,18 @@
         <v>187</v>
       </c>
       <c r="E167" t="n">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="F167" t="n">
-        <v>4.46</v>
+        <v>3.08</v>
       </c>
       <c r="G167" t="n">
-        <v>16.27</v>
+        <v>8.86</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B168" t="s">
         <v>163</v>
@@ -5286,18 +5286,18 @@
         <v>188</v>
       </c>
       <c r="E168" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="F168" t="n">
-        <v>4.53</v>
+        <v>4.28</v>
       </c>
       <c r="G168" t="n">
-        <v>16.72</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B169" t="s">
         <v>163</v>
@@ -5309,18 +5309,18 @@
         <v>189</v>
       </c>
       <c r="E169" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="F169" t="n">
-        <v>5.77</v>
+        <v>4.67</v>
       </c>
       <c r="G169" t="n">
-        <v>24.73</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B170" t="s">
         <v>163</v>
@@ -5332,18 +5332,18 @@
         <v>190</v>
       </c>
       <c r="E170" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="F170" t="n">
-        <v>7.36</v>
+        <v>5.54</v>
       </c>
       <c r="G170" t="n">
-        <v>36.43</v>
+        <v>23.11</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B171" t="s">
         <v>163</v>
@@ -5355,18 +5355,18 @@
         <v>191</v>
       </c>
       <c r="E171" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="F171" t="n">
-        <v>7.58</v>
+        <v>6.63</v>
       </c>
       <c r="G171" t="n">
-        <v>38.14</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B172" t="s">
         <v>163</v>
@@ -5378,18 +5378,18 @@
         <v>192</v>
       </c>
       <c r="E172" t="n">
-        <v>2.19</v>
+        <v>2.95</v>
       </c>
       <c r="F172" t="n">
-        <v>7.99</v>
+        <v>15.26</v>
       </c>
       <c r="G172" t="n">
-        <v>41.5</v>
+        <v>114.47</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B173" t="s">
         <v>163</v>
@@ -5401,18 +5401,18 @@
         <v>193</v>
       </c>
       <c r="E173" t="n">
-        <v>2.19</v>
+        <v>3.77</v>
       </c>
       <c r="F173" t="n">
-        <v>8.02</v>
+        <v>25.83</v>
       </c>
       <c r="G173" t="n">
-        <v>41.77</v>
+        <v>258.37</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B174" t="s">
         <v>163</v>
@@ -5424,18 +5424,18 @@
         <v>194</v>
       </c>
       <c r="E174" t="n">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="F174" t="n">
-        <v>8.03</v>
+        <v>26.78</v>
       </c>
       <c r="G174" t="n">
-        <v>41.86</v>
+        <v>273.14</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B175" t="s">
         <v>163</v>
@@ -5447,18 +5447,18 @@
         <v>195</v>
       </c>
       <c r="E175" t="n">
-        <v>3.02</v>
+        <v>4.1</v>
       </c>
       <c r="F175" t="n">
-        <v>16.07</v>
+        <v>30.78</v>
       </c>
       <c r="G175" t="n">
-        <v>124.07</v>
+        <v>338.38</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B176" t="s">
         <v>163</v>
@@ -5470,18 +5470,18 @@
         <v>196</v>
       </c>
       <c r="E176" t="n">
-        <v>3.13</v>
+        <v>4.34</v>
       </c>
       <c r="F176" t="n">
-        <v>17.36</v>
+        <v>34.65</v>
       </c>
       <c r="G176" t="n">
-        <v>139.82</v>
+        <v>405.89</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B177" t="s">
         <v>163</v>
@@ -5493,18 +5493,18 @@
         <v>197</v>
       </c>
       <c r="E177" t="n">
-        <v>3.16</v>
+        <v>4.46</v>
       </c>
       <c r="F177" t="n">
-        <v>17.74</v>
+        <v>36.61</v>
       </c>
       <c r="G177" t="n">
-        <v>144.61</v>
+        <v>441.61</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B178" t="s">
         <v>163</v>
@@ -5516,18 +5516,18 @@
         <v>198</v>
       </c>
       <c r="E178" t="n">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="F178" t="n">
-        <v>34.84</v>
+        <v>36.77</v>
       </c>
       <c r="G178" t="n">
-        <v>409.3</v>
+        <v>444.55</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B179" t="s">
         <v>163</v>
@@ -5539,18 +5539,18 @@
         <v>199</v>
       </c>
       <c r="E179" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="F179" t="n">
-        <v>45.47</v>
+        <v>45.19</v>
       </c>
       <c r="G179" t="n">
-        <v>615.49</v>
+        <v>609.73</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B180" t="s">
         <v>163</v>
@@ -5562,18 +5562,18 @@
         <v>200</v>
       </c>
       <c r="E180" t="n">
-        <v>6.35</v>
+        <v>5.38</v>
       </c>
       <c r="F180" t="n">
-        <v>76.23</v>
+        <v>54.2</v>
       </c>
       <c r="G180" t="n">
-        <v>1353.51</v>
+        <v>804.91</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B181" t="s">
         <v>163</v>
@@ -5585,18 +5585,18 @@
         <v>201</v>
       </c>
       <c r="E181" t="n">
-        <v>8.14</v>
+        <v>6.36</v>
       </c>
       <c r="F181" t="n">
-        <v>127.09</v>
+        <v>76.45</v>
       </c>
       <c r="G181" t="n">
-        <v>2942.69</v>
+        <v>1359.62</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B182" t="s">
         <v>202</v>
@@ -5608,18 +5608,18 @@
         <v>204</v>
       </c>
       <c r="E182" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="F182" t="n">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="G182" t="n">
-        <v>5.11</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B183" t="s">
         <v>202</v>
@@ -5631,18 +5631,18 @@
         <v>205</v>
       </c>
       <c r="E183" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="F183" t="n">
-        <v>3.86</v>
+        <v>1.82</v>
       </c>
       <c r="G183" t="n">
-        <v>12.85</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B184" t="s">
         <v>202</v>
@@ -5654,18 +5654,18 @@
         <v>206</v>
       </c>
       <c r="E184" t="n">
-        <v>1.76</v>
+        <v>1.29</v>
       </c>
       <c r="F184" t="n">
-        <v>4.88</v>
+        <v>2.27</v>
       </c>
       <c r="G184" t="n">
-        <v>18.85</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B185" t="s">
         <v>202</v>
@@ -5677,18 +5677,18 @@
         <v>207</v>
       </c>
       <c r="E185" t="n">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="F185" t="n">
-        <v>6.03</v>
+        <v>2.5</v>
       </c>
       <c r="G185" t="n">
-        <v>26.54</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B186" t="s">
         <v>202</v>
@@ -5700,18 +5700,18 @@
         <v>208</v>
       </c>
       <c r="E186" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="F186" t="n">
-        <v>6.17</v>
+        <v>2.81</v>
       </c>
       <c r="G186" t="n">
-        <v>27.49</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B187" t="s">
         <v>202</v>
@@ -5723,18 +5723,18 @@
         <v>209</v>
       </c>
       <c r="E187" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="F187" t="n">
-        <v>6.37</v>
+        <v>2.82</v>
       </c>
       <c r="G187" t="n">
-        <v>28.91</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B188" t="s">
         <v>202</v>
@@ -5746,18 +5746,18 @@
         <v>210</v>
       </c>
       <c r="E188" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="F188" t="n">
-        <v>6.71</v>
+        <v>3</v>
       </c>
       <c r="G188" t="n">
-        <v>31.43</v>
+        <v>8.45</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B189" t="s">
         <v>202</v>
@@ -5769,18 +5769,18 @@
         <v>211</v>
       </c>
       <c r="E189" t="n">
-        <v>2.21</v>
+        <v>1.58</v>
       </c>
       <c r="F189" t="n">
-        <v>8.15</v>
+        <v>3.76</v>
       </c>
       <c r="G189" t="n">
-        <v>42.81</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B190" t="s">
         <v>202</v>
@@ -5792,18 +5792,18 @@
         <v>212</v>
       </c>
       <c r="E190" t="n">
-        <v>2.27</v>
+        <v>1.74</v>
       </c>
       <c r="F190" t="n">
-        <v>8.62</v>
+        <v>4.73</v>
       </c>
       <c r="G190" t="n">
-        <v>46.82</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B191" t="s">
         <v>202</v>
@@ -5815,18 +5815,18 @@
         <v>213</v>
       </c>
       <c r="E191" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="F191" t="n">
-        <v>15.81</v>
+        <v>12.52</v>
       </c>
       <c r="G191" t="n">
-        <v>120.97</v>
+        <v>84.05</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B192" t="s">
         <v>202</v>
@@ -5838,18 +5838,18 @@
         <v>214</v>
       </c>
       <c r="E192" t="n">
-        <v>3.79</v>
+        <v>3.19</v>
       </c>
       <c r="F192" t="n">
-        <v>26.03</v>
+        <v>18.08</v>
       </c>
       <c r="G192" t="n">
-        <v>261.56</v>
+        <v>148.98</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B193" t="s">
         <v>202</v>
@@ -5861,18 +5861,18 @@
         <v>215</v>
       </c>
       <c r="E193" t="n">
-        <v>4.04</v>
+        <v>3.22</v>
       </c>
       <c r="F193" t="n">
-        <v>29.87</v>
+        <v>18.47</v>
       </c>
       <c r="G193" t="n">
-        <v>323.17</v>
+        <v>153.95</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B194" t="s">
         <v>202</v>
@@ -5884,18 +5884,18 @@
         <v>216</v>
       </c>
       <c r="E194" t="n">
-        <v>4.24</v>
+        <v>4.07</v>
       </c>
       <c r="F194" t="n">
-        <v>32.93</v>
+        <v>30.36</v>
       </c>
       <c r="G194" t="n">
-        <v>375.46</v>
+        <v>331.34</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B195" t="s">
         <v>202</v>
@@ -5907,18 +5907,18 @@
         <v>217</v>
       </c>
       <c r="E195" t="n">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="F195" t="n">
-        <v>37.06</v>
+        <v>35.64</v>
       </c>
       <c r="G195" t="n">
-        <v>450.06</v>
+        <v>423.8</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B196" t="s">
         <v>202</v>
@@ -5930,18 +5930,18 @@
         <v>218</v>
       </c>
       <c r="E196" t="n">
-        <v>5.83</v>
+        <v>4.92</v>
       </c>
       <c r="F196" t="n">
-        <v>64.06</v>
+        <v>45.08</v>
       </c>
       <c r="G196" t="n">
-        <v>1038.54</v>
+        <v>607.36</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B197" t="s">
         <v>202</v>
@@ -5953,18 +5953,18 @@
         <v>219</v>
       </c>
       <c r="E197" t="n">
-        <v>6.91</v>
+        <v>5.07</v>
       </c>
       <c r="F197" t="n">
-        <v>90.7</v>
+        <v>47.97</v>
       </c>
       <c r="G197" t="n">
-        <v>1763.05</v>
+        <v>667.91</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B198" t="s">
         <v>202</v>
@@ -5976,18 +5976,18 @@
         <v>220</v>
       </c>
       <c r="E198" t="n">
-        <v>6.94</v>
+        <v>5.97</v>
       </c>
       <c r="F198" t="n">
-        <v>91.48</v>
+        <v>67.07</v>
       </c>
       <c r="G198" t="n">
-        <v>1786.09</v>
+        <v>1113.84</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B199" t="s">
         <v>202</v>
@@ -5999,18 +5999,18 @@
         <v>221</v>
       </c>
       <c r="E199" t="n">
-        <v>11.3</v>
+        <v>6.59</v>
       </c>
       <c r="F199" t="n">
-        <v>247.72</v>
+        <v>82.35</v>
       </c>
       <c r="G199" t="n">
-        <v>8082.98</v>
+        <v>1522.4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B200" t="s">
         <v>202</v>
@@ -6022,18 +6022,18 @@
         <v>223</v>
       </c>
       <c r="E200" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="F200" t="n">
-        <v>1.52</v>
+        <v>2.31</v>
       </c>
       <c r="G200" t="n">
-        <v>2.54</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B201" t="s">
         <v>202</v>
@@ -6045,18 +6045,18 @@
         <v>224</v>
       </c>
       <c r="E201" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="F201" t="n">
-        <v>2.16</v>
+        <v>2.65</v>
       </c>
       <c r="G201" t="n">
-        <v>4.82</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B202" t="s">
         <v>202</v>
@@ -6068,18 +6068,18 @@
         <v>225</v>
       </c>
       <c r="E202" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="F202" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="G202" t="n">
-        <v>8.22</v>
+        <v>9.64</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B203" t="s">
         <v>202</v>
@@ -6091,18 +6091,18 @@
         <v>226</v>
       </c>
       <c r="E203" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="F203" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="G203" t="n">
-        <v>8.28</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B204" t="s">
         <v>202</v>
@@ -6114,18 +6114,18 @@
         <v>227</v>
       </c>
       <c r="E204" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="F204" t="n">
-        <v>3.54</v>
+        <v>5.85</v>
       </c>
       <c r="G204" t="n">
-        <v>11.14</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B205" t="s">
         <v>202</v>
@@ -6137,18 +6137,18 @@
         <v>228</v>
       </c>
       <c r="E205" t="n">
-        <v>1.55</v>
+        <v>2.09</v>
       </c>
       <c r="F205" t="n">
-        <v>3.6</v>
+        <v>7.19</v>
       </c>
       <c r="G205" t="n">
-        <v>11.46</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B206" t="s">
         <v>202</v>
@@ -6160,18 +6160,18 @@
         <v>229</v>
       </c>
       <c r="E206" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="F206" t="n">
-        <v>3.89</v>
+        <v>7.43</v>
       </c>
       <c r="G206" t="n">
-        <v>13.02</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B207" t="s">
         <v>202</v>
@@ -6183,18 +6183,18 @@
         <v>230</v>
       </c>
       <c r="E207" t="n">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="F207" t="n">
-        <v>4.39</v>
+        <v>8.36</v>
       </c>
       <c r="G207" t="n">
-        <v>15.86</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B208" t="s">
         <v>202</v>
@@ -6206,18 +6206,18 @@
         <v>231</v>
       </c>
       <c r="E208" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="F208" t="n">
-        <v>5.45</v>
+        <v>11.89</v>
       </c>
       <c r="G208" t="n">
-        <v>22.5</v>
+        <v>77.57</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B209" t="s">
         <v>202</v>
@@ -6229,18 +6229,18 @@
         <v>232</v>
       </c>
       <c r="E209" t="n">
-        <v>1.86</v>
+        <v>2.93</v>
       </c>
       <c r="F209" t="n">
-        <v>5.49</v>
+        <v>15.07</v>
       </c>
       <c r="G209" t="n">
-        <v>22.82</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B210" t="s">
         <v>202</v>
@@ -6252,18 +6252,18 @@
         <v>233</v>
       </c>
       <c r="E210" t="n">
-        <v>2.09</v>
+        <v>3.11</v>
       </c>
       <c r="F210" t="n">
-        <v>7.22</v>
+        <v>17.18</v>
       </c>
       <c r="G210" t="n">
-        <v>35.36</v>
+        <v>137.61</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B211" t="s">
         <v>202</v>
@@ -6275,18 +6275,18 @@
         <v>234</v>
       </c>
       <c r="E211" t="n">
-        <v>2.15</v>
+        <v>3.44</v>
       </c>
       <c r="F211" t="n">
-        <v>7.63</v>
+        <v>21.26</v>
       </c>
       <c r="G211" t="n">
-        <v>38.6</v>
+        <v>191.39</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B212" t="s">
         <v>202</v>
@@ -6298,18 +6298,18 @@
         <v>235</v>
       </c>
       <c r="E212" t="n">
-        <v>2.99</v>
+        <v>3.81</v>
       </c>
       <c r="F212" t="n">
-        <v>15.78</v>
+        <v>26.43</v>
       </c>
       <c r="G212" t="n">
-        <v>120.62</v>
+        <v>267.69</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B213" t="s">
         <v>202</v>
@@ -6321,18 +6321,18 @@
         <v>236</v>
       </c>
       <c r="E213" t="n">
-        <v>3.21</v>
+        <v>4.51</v>
       </c>
       <c r="F213" t="n">
-        <v>18.36</v>
+        <v>37.5</v>
       </c>
       <c r="G213" t="n">
-        <v>152.47</v>
+        <v>458.14</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B214" t="s">
         <v>202</v>
@@ -6344,18 +6344,18 @@
         <v>237</v>
       </c>
       <c r="E214" t="n">
-        <v>3.42</v>
+        <v>4.67</v>
       </c>
       <c r="F214" t="n">
-        <v>20.99</v>
+        <v>40.36</v>
       </c>
       <c r="G214" t="n">
-        <v>187.62</v>
+        <v>512.73</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B215" t="s">
         <v>202</v>
@@ -6367,18 +6367,18 @@
         <v>238</v>
       </c>
       <c r="E215" t="n">
-        <v>4.62</v>
+        <v>4.79</v>
       </c>
       <c r="F215" t="n">
-        <v>39.47</v>
+        <v>42.66</v>
       </c>
       <c r="G215" t="n">
-        <v>495.57</v>
+        <v>558.2</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B216" t="s">
         <v>202</v>
@@ -6390,18 +6390,18 @@
         <v>239</v>
       </c>
       <c r="E216" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="F216" t="n">
-        <v>43.82</v>
+        <v>42.84</v>
       </c>
       <c r="G216" t="n">
-        <v>581.65</v>
+        <v>561.78</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="B217" t="s">
         <v>202</v>
@@ -6413,18 +6413,18 @@
         <v>240</v>
       </c>
       <c r="E217" t="n">
-        <v>8.96</v>
+        <v>5.21</v>
       </c>
       <c r="F217" t="n">
-        <v>154.55</v>
+        <v>50.69</v>
       </c>
       <c r="G217" t="n">
-        <v>3958.27</v>
+        <v>726.67</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B218" t="s">
         <v>241</v>
@@ -6436,18 +6436,18 @@
         <v>243</v>
       </c>
       <c r="E218" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="F218" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="G218" t="n">
-        <v>3.66</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B219" t="s">
         <v>241</v>
@@ -6459,18 +6459,18 @@
         <v>244</v>
       </c>
       <c r="E219" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="F219" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="G219" t="n">
-        <v>7.99</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B220" t="s">
         <v>241</v>
@@ -6482,18 +6482,18 @@
         <v>245</v>
       </c>
       <c r="E220" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="F220" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="G220" t="n">
-        <v>8.05</v>
+        <v>8.53</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B221" t="s">
         <v>241</v>
@@ -6505,18 +6505,18 @@
         <v>246</v>
       </c>
       <c r="E221" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F221" t="n">
-        <v>3.91</v>
+        <v>3.35</v>
       </c>
       <c r="G221" t="n">
-        <v>13.14</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B222" t="s">
         <v>241</v>
@@ -6528,18 +6528,18 @@
         <v>247</v>
       </c>
       <c r="E222" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="F222" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="G222" t="n">
-        <v>14.2</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B223" t="s">
         <v>241</v>
@@ -6551,18 +6551,18 @@
         <v>248</v>
       </c>
       <c r="E223" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="F223" t="n">
-        <v>5.26</v>
+        <v>4.4</v>
       </c>
       <c r="G223" t="n">
-        <v>21.31</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B224" t="s">
         <v>241</v>
@@ -6574,18 +6574,18 @@
         <v>249</v>
       </c>
       <c r="E224" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="F224" t="n">
-        <v>6.4</v>
+        <v>4.62</v>
       </c>
       <c r="G224" t="n">
-        <v>29.15</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B225" t="s">
         <v>241</v>
@@ -6597,18 +6597,18 @@
         <v>250</v>
       </c>
       <c r="E225" t="n">
-        <v>2.21</v>
+        <v>1.86</v>
       </c>
       <c r="F225" t="n">
-        <v>8.17</v>
+        <v>5.55</v>
       </c>
       <c r="G225" t="n">
-        <v>43.01</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B226" t="s">
         <v>241</v>
@@ -6620,18 +6620,18 @@
         <v>251</v>
       </c>
       <c r="E226" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="F226" t="n">
-        <v>8.21</v>
+        <v>5.84</v>
       </c>
       <c r="G226" t="n">
-        <v>43.34</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B227" t="s">
         <v>241</v>
@@ -6643,18 +6643,18 @@
         <v>252</v>
       </c>
       <c r="E227" t="n">
-        <v>3.12</v>
+        <v>1.96</v>
       </c>
       <c r="F227" t="n">
-        <v>17.28</v>
+        <v>6.26</v>
       </c>
       <c r="G227" t="n">
-        <v>138.79</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B228" t="s">
         <v>241</v>
@@ -6666,18 +6666,18 @@
         <v>253</v>
       </c>
       <c r="E228" t="n">
-        <v>3.18</v>
+        <v>1.97</v>
       </c>
       <c r="F228" t="n">
-        <v>17.98</v>
+        <v>6.33</v>
       </c>
       <c r="G228" t="n">
-        <v>147.63</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B229" t="s">
         <v>241</v>
@@ -6689,18 +6689,18 @@
         <v>254</v>
       </c>
       <c r="E229" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="F229" t="n">
-        <v>23.39</v>
+        <v>12.26</v>
       </c>
       <c r="G229" t="n">
-        <v>221.76</v>
+        <v>81.39</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B230" t="s">
         <v>241</v>
@@ -6712,18 +6712,18 @@
         <v>255</v>
       </c>
       <c r="E230" t="n">
-        <v>3.77</v>
+        <v>2.74</v>
       </c>
       <c r="F230" t="n">
-        <v>25.8</v>
+        <v>13.06</v>
       </c>
       <c r="G230" t="n">
-        <v>258</v>
+        <v>89.82</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B231" t="s">
         <v>241</v>
@@ -6735,18 +6735,18 @@
         <v>256</v>
       </c>
       <c r="E231" t="n">
-        <v>3.88</v>
+        <v>2.76</v>
       </c>
       <c r="F231" t="n">
-        <v>27.44</v>
+        <v>13.22</v>
       </c>
       <c r="G231" t="n">
-        <v>283.7</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B232" t="s">
         <v>241</v>
@@ -6758,18 +6758,18 @@
         <v>257</v>
       </c>
       <c r="E232" t="n">
-        <v>5.16</v>
+        <v>3.9</v>
       </c>
       <c r="F232" t="n">
-        <v>49.6</v>
+        <v>27.71</v>
       </c>
       <c r="G232" t="n">
-        <v>702.78</v>
+        <v>287.91</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="s">
         <v>241</v>
@@ -6781,18 +6781,18 @@
         <v>258</v>
       </c>
       <c r="E233" t="n">
-        <v>5.23</v>
+        <v>4.56</v>
       </c>
       <c r="F233" t="n">
-        <v>51.07</v>
+        <v>38.48</v>
       </c>
       <c r="G233" t="n">
-        <v>735.03</v>
+        <v>476.68</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="s">
         <v>241</v>
@@ -6804,18 +6804,18 @@
         <v>259</v>
       </c>
       <c r="E234" t="n">
-        <v>6.26</v>
+        <v>5.78</v>
       </c>
       <c r="F234" t="n">
-        <v>74.06</v>
+        <v>62.81</v>
       </c>
       <c r="G234" t="n">
-        <v>1295.35</v>
+        <v>1007.88</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="s">
         <v>241</v>
@@ -6827,18 +6827,18 @@
         <v>260</v>
       </c>
       <c r="E235" t="n">
-        <v>6.83</v>
+        <v>7.43</v>
       </c>
       <c r="F235" t="n">
-        <v>88.64</v>
+        <v>105.21</v>
       </c>
       <c r="G235" t="n">
-        <v>1702.72</v>
+        <v>2208.95</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="s">
         <v>241</v>
@@ -6850,18 +6850,18 @@
         <v>262</v>
       </c>
       <c r="E236" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="F236" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="G236" t="n">
-        <v>3.27</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B237" t="s">
         <v>241</v>
@@ -6873,18 +6873,18 @@
         <v>263</v>
       </c>
       <c r="E237" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="F237" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="G237" t="n">
-        <v>4.29</v>
+        <v>8.72</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B238" t="s">
         <v>241</v>
@@ -6896,18 +6896,18 @@
         <v>264</v>
       </c>
       <c r="E238" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="F238" t="n">
-        <v>2.78</v>
+        <v>3.65</v>
       </c>
       <c r="G238" t="n">
-        <v>7.46</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B239" t="s">
         <v>241</v>
@@ -6919,18 +6919,18 @@
         <v>265</v>
       </c>
       <c r="E239" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="F239" t="n">
-        <v>3.03</v>
+        <v>4.55</v>
       </c>
       <c r="G239" t="n">
-        <v>8.59</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B240" t="s">
         <v>241</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B241" t="s">
         <v>241</v>
@@ -6965,18 +6965,18 @@
         <v>267</v>
       </c>
       <c r="E241" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="F241" t="n">
-        <v>4.8</v>
+        <v>4.97</v>
       </c>
       <c r="G241" t="n">
-        <v>18.35</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B242" t="s">
         <v>241</v>
@@ -6988,18 +6988,18 @@
         <v>268</v>
       </c>
       <c r="E242" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="F242" t="n">
-        <v>4.93</v>
+        <v>5.17</v>
       </c>
       <c r="G242" t="n">
-        <v>19.15</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B243" t="s">
         <v>241</v>
@@ -7011,18 +7011,18 @@
         <v>269</v>
       </c>
       <c r="E243" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="F243" t="n">
-        <v>5.44</v>
+        <v>6.42</v>
       </c>
       <c r="G243" t="n">
-        <v>22.48</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B244" t="s">
         <v>241</v>
@@ -7034,18 +7034,18 @@
         <v>270</v>
       </c>
       <c r="E244" t="n">
-        <v>2.96</v>
+        <v>2.01</v>
       </c>
       <c r="F244" t="n">
-        <v>15.39</v>
+        <v>6.63</v>
       </c>
       <c r="G244" t="n">
-        <v>116</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B245" t="s">
         <v>241</v>
@@ -7057,18 +7057,18 @@
         <v>271</v>
       </c>
       <c r="E245" t="n">
-        <v>3.16</v>
+        <v>2.44</v>
       </c>
       <c r="F245" t="n">
-        <v>17.67</v>
+        <v>10.17</v>
       </c>
       <c r="G245" t="n">
-        <v>143.78</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B246" t="s">
         <v>241</v>
@@ -7080,18 +7080,18 @@
         <v>272</v>
       </c>
       <c r="E246" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F246" t="n">
-        <v>18.16</v>
+        <v>18.75</v>
       </c>
       <c r="G246" t="n">
-        <v>150</v>
+        <v>157.62</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B247" t="s">
         <v>241</v>
@@ -7103,18 +7103,18 @@
         <v>273</v>
       </c>
       <c r="E247" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="F247" t="n">
-        <v>18.42</v>
+        <v>18.92</v>
       </c>
       <c r="G247" t="n">
-        <v>153.24</v>
+        <v>159.83</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B248" t="s">
         <v>241</v>
@@ -7126,18 +7126,18 @@
         <v>274</v>
       </c>
       <c r="E248" t="n">
-        <v>3.36</v>
+        <v>3.61</v>
       </c>
       <c r="F248" t="n">
-        <v>20.15</v>
+        <v>23.5</v>
       </c>
       <c r="G248" t="n">
-        <v>176.18</v>
+        <v>223.36</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B249" t="s">
         <v>241</v>
@@ -7149,18 +7149,18 @@
         <v>275</v>
       </c>
       <c r="E249" t="n">
-        <v>4.24</v>
+        <v>3.96</v>
       </c>
       <c r="F249" t="n">
-        <v>33.03</v>
+        <v>28.65</v>
       </c>
       <c r="G249" t="n">
-        <v>377.13</v>
+        <v>303.06</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B250" t="s">
         <v>241</v>
@@ -7172,18 +7172,18 @@
         <v>276</v>
       </c>
       <c r="E250" t="n">
-        <v>4.57</v>
+        <v>5.26</v>
       </c>
       <c r="F250" t="n">
-        <v>38.51</v>
+        <v>51.64</v>
       </c>
       <c r="G250" t="n">
-        <v>477.27</v>
+        <v>747.54</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B251" t="s">
         <v>241</v>
@@ -7195,18 +7195,18 @@
         <v>277</v>
       </c>
       <c r="E251" t="n">
-        <v>5.96</v>
+        <v>5.88</v>
       </c>
       <c r="F251" t="n">
-        <v>66.91</v>
+        <v>65.12</v>
       </c>
       <c r="G251" t="n">
-        <v>1109.69</v>
+        <v>1064.89</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B252" t="s">
         <v>241</v>
@@ -7218,18 +7218,18 @@
         <v>278</v>
       </c>
       <c r="E252" t="n">
-        <v>6.95</v>
+        <v>6.13</v>
       </c>
       <c r="F252" t="n">
-        <v>91.72</v>
+        <v>70.87</v>
       </c>
       <c r="G252" t="n">
-        <v>1793.26</v>
+        <v>1211.37</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B253" t="s">
         <v>241</v>
@@ -7241,18 +7241,18 @@
         <v>279</v>
       </c>
       <c r="E253" t="n">
-        <v>11.85</v>
+        <v>9.86</v>
       </c>
       <c r="F253" t="n">
-        <v>273.01</v>
+        <v>187.84</v>
       </c>
       <c r="G253" t="n">
-        <v>9362.26</v>
+        <v>5318.69</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B254" t="s">
         <v>280</v>
@@ -7264,18 +7264,18 @@
         <v>282</v>
       </c>
       <c r="E254" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="F254" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="G254" t="n">
-        <v>6.08</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B255" t="s">
         <v>280</v>
@@ -7287,18 +7287,18 @@
         <v>283</v>
       </c>
       <c r="E255" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="F255" t="n">
-        <v>2.48</v>
+        <v>3.49</v>
       </c>
       <c r="G255" t="n">
-        <v>6.15</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B256" t="s">
         <v>280</v>
@@ -7310,18 +7310,18 @@
         <v>284</v>
       </c>
       <c r="E256" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="F256" t="n">
-        <v>2.96</v>
+        <v>3.86</v>
       </c>
       <c r="G256" t="n">
-        <v>8.3</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B257" t="s">
         <v>280</v>
@@ -7333,18 +7333,18 @@
         <v>285</v>
       </c>
       <c r="E257" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="F257" t="n">
-        <v>2.97</v>
+        <v>4.41</v>
       </c>
       <c r="G257" t="n">
-        <v>8.32</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B258" t="s">
         <v>280</v>
@@ -7356,18 +7356,18 @@
         <v>286</v>
       </c>
       <c r="E258" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="F258" t="n">
-        <v>3.08</v>
+        <v>4.68</v>
       </c>
       <c r="G258" t="n">
-        <v>8.87</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B259" t="s">
         <v>280</v>
@@ -7379,18 +7379,18 @@
         <v>287</v>
       </c>
       <c r="E259" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="F259" t="n">
-        <v>3.2</v>
+        <v>5.48</v>
       </c>
       <c r="G259" t="n">
-        <v>9.42</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B260" t="s">
         <v>280</v>
@@ -7402,18 +7402,18 @@
         <v>288</v>
       </c>
       <c r="E260" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="F260" t="n">
-        <v>4.42</v>
+        <v>7.41</v>
       </c>
       <c r="G260" t="n">
-        <v>16.04</v>
+        <v>36.78</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B261" t="s">
         <v>280</v>
@@ -7425,18 +7425,18 @@
         <v>289</v>
       </c>
       <c r="E261" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="F261" t="n">
-        <v>7.17</v>
+        <v>8.91</v>
       </c>
       <c r="G261" t="n">
-        <v>34.91</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B262" t="s">
         <v>280</v>
@@ -7448,18 +7448,18 @@
         <v>290</v>
       </c>
       <c r="E262" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="F262" t="n">
-        <v>9.32</v>
+        <v>9.44</v>
       </c>
       <c r="G262" t="n">
-        <v>52.88</v>
+        <v>54.03</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B263" t="s">
         <v>280</v>
@@ -7471,18 +7471,18 @@
         <v>291</v>
       </c>
       <c r="E263" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="F263" t="n">
-        <v>13.73</v>
+        <v>14.97</v>
       </c>
       <c r="G263" t="n">
-        <v>97.1</v>
+        <v>111.07</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B264" t="s">
         <v>280</v>
@@ -7494,18 +7494,18 @@
         <v>292</v>
       </c>
       <c r="E264" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="F264" t="n">
-        <v>14.52</v>
+        <v>15.69</v>
       </c>
       <c r="G264" t="n">
-        <v>105.96</v>
+        <v>119.53</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B265" t="s">
         <v>280</v>
@@ -7517,18 +7517,18 @@
         <v>293</v>
       </c>
       <c r="E265" t="n">
-        <v>3.02</v>
+        <v>4.17</v>
       </c>
       <c r="F265" t="n">
-        <v>16.15</v>
+        <v>31.8</v>
       </c>
       <c r="G265" t="n">
-        <v>125.01</v>
+        <v>355.76</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B266" t="s">
         <v>280</v>
@@ -7540,18 +7540,18 @@
         <v>294</v>
       </c>
       <c r="E266" t="n">
-        <v>3.15</v>
+        <v>4.44</v>
       </c>
       <c r="F266" t="n">
-        <v>17.56</v>
+        <v>36.32</v>
       </c>
       <c r="G266" t="n">
-        <v>142.31</v>
+        <v>436.2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B267" t="s">
         <v>280</v>
@@ -7563,18 +7563,18 @@
         <v>295</v>
       </c>
       <c r="E267" t="n">
-        <v>3.16</v>
+        <v>4.47</v>
       </c>
       <c r="F267" t="n">
-        <v>17.75</v>
+        <v>36.9</v>
       </c>
       <c r="G267" t="n">
-        <v>144.68</v>
+        <v>446.92</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B268" t="s">
         <v>280</v>
@@ -7586,18 +7586,18 @@
         <v>296</v>
       </c>
       <c r="E268" t="n">
-        <v>3.26</v>
+        <v>4.51</v>
       </c>
       <c r="F268" t="n">
-        <v>18.93</v>
+        <v>37.48</v>
       </c>
       <c r="G268" t="n">
-        <v>159.93</v>
+        <v>457.86</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B269" t="s">
         <v>280</v>
@@ -7609,18 +7609,18 @@
         <v>297</v>
       </c>
       <c r="E269" t="n">
-        <v>5.79</v>
+        <v>7.76</v>
       </c>
       <c r="F269" t="n">
-        <v>63.05</v>
+        <v>115.02</v>
       </c>
       <c r="G269" t="n">
-        <v>1013.81</v>
+        <v>2529.18</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B270" t="s">
         <v>280</v>
@@ -7632,18 +7632,18 @@
         <v>298</v>
       </c>
       <c r="E270" t="n">
-        <v>6.66</v>
+        <v>8.26</v>
       </c>
       <c r="F270" t="n">
-        <v>84.07</v>
+        <v>130.82</v>
       </c>
       <c r="G270" t="n">
-        <v>1570.8</v>
+        <v>3074.41</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B271" t="s">
         <v>280</v>
@@ -7655,18 +7655,18 @@
         <v>299</v>
       </c>
       <c r="E271" t="n">
-        <v>9.2</v>
+        <v>9.97</v>
       </c>
       <c r="F271" t="n">
-        <v>163.13</v>
+        <v>191.87</v>
       </c>
       <c r="G271" t="n">
-        <v>4295.74</v>
+        <v>5492.01</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B272" t="s">
         <v>280</v>
@@ -7678,18 +7678,18 @@
         <v>301</v>
       </c>
       <c r="E272" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="F272" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="G272" t="n">
-        <v>6.42</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B273" t="s">
         <v>280</v>
@@ -7701,18 +7701,18 @@
         <v>302</v>
       </c>
       <c r="E273" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="F273" t="n">
-        <v>2.84</v>
+        <v>2.49</v>
       </c>
       <c r="G273" t="n">
-        <v>7.73</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B274" t="s">
         <v>280</v>
@@ -7724,18 +7724,18 @@
         <v>303</v>
       </c>
       <c r="E274" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="F274" t="n">
-        <v>2.86</v>
+        <v>2.61</v>
       </c>
       <c r="G274" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B275" t="s">
         <v>280</v>
@@ -7747,18 +7747,18 @@
         <v>304</v>
       </c>
       <c r="E275" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="F275" t="n">
-        <v>3.19</v>
+        <v>2.69</v>
       </c>
       <c r="G275" t="n">
-        <v>9.38</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B276" t="s">
         <v>280</v>
@@ -7770,18 +7770,18 @@
         <v>305</v>
       </c>
       <c r="E276" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="F276" t="n">
-        <v>4.31</v>
+        <v>3.26</v>
       </c>
       <c r="G276" t="n">
-        <v>15.38</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B277" t="s">
         <v>280</v>
@@ -7793,18 +7793,18 @@
         <v>306</v>
       </c>
       <c r="E277" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="F277" t="n">
-        <v>4.37</v>
+        <v>3.48</v>
       </c>
       <c r="G277" t="n">
-        <v>15.76</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B278" t="s">
         <v>280</v>
@@ -7816,18 +7816,18 @@
         <v>307</v>
       </c>
       <c r="E278" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="F278" t="n">
-        <v>5.59</v>
+        <v>4.65</v>
       </c>
       <c r="G278" t="n">
-        <v>23.47</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B279" t="s">
         <v>280</v>
@@ -7839,18 +7839,18 @@
         <v>308</v>
       </c>
       <c r="E279" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="F279" t="n">
-        <v>7.41</v>
+        <v>6.1</v>
       </c>
       <c r="G279" t="n">
-        <v>36.79</v>
+        <v>27.01</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B280" t="s">
         <v>280</v>
@@ -7862,18 +7862,18 @@
         <v>309</v>
       </c>
       <c r="E280" t="n">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="F280" t="n">
-        <v>8.65</v>
+        <v>7.06</v>
       </c>
       <c r="G280" t="n">
-        <v>47.07</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B281" t="s">
         <v>280</v>
@@ -7885,18 +7885,18 @@
         <v>310</v>
       </c>
       <c r="E281" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F281" t="n">
-        <v>10.69</v>
+        <v>8.89</v>
       </c>
       <c r="G281" t="n">
-        <v>65.65</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B282" t="s">
         <v>280</v>
@@ -7908,18 +7908,18 @@
         <v>311</v>
       </c>
       <c r="E282" t="n">
-        <v>2.79</v>
+        <v>2.49</v>
       </c>
       <c r="F282" t="n">
-        <v>13.59</v>
+        <v>10.64</v>
       </c>
       <c r="G282" t="n">
-        <v>95.57</v>
+        <v>65.14</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B283" t="s">
         <v>280</v>
@@ -7931,18 +7931,18 @@
         <v>312</v>
       </c>
       <c r="E283" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="F283" t="n">
-        <v>14.22</v>
+        <v>13.18</v>
       </c>
       <c r="G283" t="n">
-        <v>102.54</v>
+        <v>91.09</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B284" t="s">
         <v>280</v>
@@ -7954,18 +7954,18 @@
         <v>313</v>
       </c>
       <c r="E284" t="n">
-        <v>3.46</v>
+        <v>3.12</v>
       </c>
       <c r="F284" t="n">
-        <v>21.48</v>
+        <v>17.29</v>
       </c>
       <c r="G284" t="n">
-        <v>194.42</v>
+        <v>138.96</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B285" t="s">
         <v>280</v>
@@ -7977,18 +7977,18 @@
         <v>314</v>
       </c>
       <c r="E285" t="n">
-        <v>4.01</v>
+        <v>3.69</v>
       </c>
       <c r="F285" t="n">
-        <v>29.37</v>
+        <v>24.62</v>
       </c>
       <c r="G285" t="n">
-        <v>314.9</v>
+        <v>239.95</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B286" t="s">
         <v>280</v>
@@ -8000,18 +8000,18 @@
         <v>315</v>
       </c>
       <c r="E286" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="F286" t="n">
-        <v>35.68</v>
+        <v>28.3</v>
       </c>
       <c r="G286" t="n">
-        <v>424.54</v>
+        <v>297.41</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B287" t="s">
         <v>280</v>
@@ -8023,18 +8023,18 @@
         <v>316</v>
       </c>
       <c r="E287" t="n">
-        <v>4.84</v>
+        <v>4.3</v>
       </c>
       <c r="F287" t="n">
-        <v>43.54</v>
+        <v>33.95</v>
       </c>
       <c r="G287" t="n">
-        <v>576.01</v>
+        <v>393.44</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B288" t="s">
         <v>280</v>
@@ -8046,18 +8046,18 @@
         <v>317</v>
       </c>
       <c r="E288" t="n">
-        <v>5.12</v>
+        <v>4.65</v>
       </c>
       <c r="F288" t="n">
-        <v>48.81</v>
+        <v>40.07</v>
       </c>
       <c r="G288" t="n">
-        <v>685.92</v>
+        <v>507.12</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B289" t="s">
         <v>280</v>
@@ -8069,18 +8069,18 @@
         <v>318</v>
       </c>
       <c r="E289" t="n">
-        <v>5.42</v>
+        <v>4.78</v>
       </c>
       <c r="F289" t="n">
-        <v>55.01</v>
+        <v>42.45</v>
       </c>
       <c r="G289" t="n">
-        <v>823.2</v>
+        <v>554.01</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B290" t="s">
         <v>319</v>
@@ -8092,18 +8092,18 @@
         <v>321</v>
       </c>
       <c r="E290" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="F290" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="G290" t="n">
-        <v>3.97</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B291" t="s">
         <v>319</v>
@@ -8115,18 +8115,18 @@
         <v>322</v>
       </c>
       <c r="E291" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="F291" t="n">
-        <v>2.01</v>
+        <v>2.39</v>
       </c>
       <c r="G291" t="n">
-        <v>4.25</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B292" t="s">
         <v>319</v>
@@ -8138,18 +8138,18 @@
         <v>323</v>
       </c>
       <c r="E292" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="F292" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="G292" t="n">
-        <v>6.18</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B293" t="s">
         <v>319</v>
@@ -8161,18 +8161,18 @@
         <v>324</v>
       </c>
       <c r="E293" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="F293" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="G293" t="n">
-        <v>8.67</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B294" t="s">
         <v>319</v>
@@ -8184,18 +8184,18 @@
         <v>325</v>
       </c>
       <c r="E294" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="F294" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="G294" t="n">
-        <v>10.94</v>
+        <v>8.54</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B295" t="s">
         <v>319</v>
@@ -8207,18 +8207,18 @@
         <v>326</v>
       </c>
       <c r="E295" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="F295" t="n">
-        <v>3.56</v>
+        <v>3.07</v>
       </c>
       <c r="G295" t="n">
-        <v>11.24</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B296" t="s">
         <v>319</v>
@@ -8230,18 +8230,18 @@
         <v>327</v>
       </c>
       <c r="E296" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="F296" t="n">
-        <v>4.2</v>
+        <v>4.48</v>
       </c>
       <c r="G296" t="n">
-        <v>14.75</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B297" t="s">
         <v>319</v>
@@ -8253,18 +8253,18 @@
         <v>328</v>
       </c>
       <c r="E297" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="F297" t="n">
-        <v>4.74</v>
+        <v>7.79</v>
       </c>
       <c r="G297" t="n">
-        <v>17.98</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B298" t="s">
         <v>319</v>
@@ -8276,18 +8276,18 @@
         <v>329</v>
       </c>
       <c r="E298" t="n">
-        <v>1.77</v>
+        <v>2.36</v>
       </c>
       <c r="F298" t="n">
-        <v>4.94</v>
+        <v>9.39</v>
       </c>
       <c r="G298" t="n">
-        <v>19.21</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B299" t="s">
         <v>319</v>
@@ -8299,18 +8299,18 @@
         <v>330</v>
       </c>
       <c r="E299" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="F299" t="n">
-        <v>6.79</v>
+        <v>13.15</v>
       </c>
       <c r="G299" t="n">
-        <v>32.06</v>
+        <v>90.82</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B300" t="s">
         <v>319</v>
@@ -8322,18 +8322,18 @@
         <v>331</v>
       </c>
       <c r="E300" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="F300" t="n">
-        <v>13.6</v>
+        <v>13.93</v>
       </c>
       <c r="G300" t="n">
-        <v>95.63</v>
+        <v>99.27</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B301" t="s">
         <v>319</v>
@@ -8345,18 +8345,18 @@
         <v>332</v>
       </c>
       <c r="E301" t="n">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="F301" t="n">
-        <v>16.01</v>
+        <v>14.64</v>
       </c>
       <c r="G301" t="n">
-        <v>123.28</v>
+        <v>107.33</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B302" t="s">
         <v>319</v>
@@ -8368,18 +8368,18 @@
         <v>333</v>
       </c>
       <c r="E302" t="n">
-        <v>3.27</v>
+        <v>2.98</v>
       </c>
       <c r="F302" t="n">
-        <v>19.04</v>
+        <v>15.67</v>
       </c>
       <c r="G302" t="n">
-        <v>161.38</v>
+        <v>119.31</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B303" t="s">
         <v>319</v>
@@ -8391,18 +8391,18 @@
         <v>334</v>
       </c>
       <c r="E303" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="F303" t="n">
-        <v>19.31</v>
+        <v>18.46</v>
       </c>
       <c r="G303" t="n">
-        <v>164.96</v>
+        <v>153.77</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B304" t="s">
         <v>319</v>
@@ -8414,18 +8414,18 @@
         <v>335</v>
       </c>
       <c r="E304" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="F304" t="n">
-        <v>21.99</v>
+        <v>21.7</v>
       </c>
       <c r="G304" t="n">
-        <v>201.66</v>
+        <v>197.52</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B305" t="s">
         <v>319</v>
@@ -8437,18 +8437,18 @@
         <v>336</v>
       </c>
       <c r="E305" t="n">
-        <v>4.72</v>
+        <v>5.9</v>
       </c>
       <c r="F305" t="n">
-        <v>41.25</v>
+        <v>65.65</v>
       </c>
       <c r="G305" t="n">
-        <v>530.26</v>
+        <v>1077.96</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B306" t="s">
         <v>319</v>
@@ -8460,18 +8460,18 @@
         <v>337</v>
       </c>
       <c r="E306" t="n">
-        <v>5.96</v>
+        <v>6.76</v>
       </c>
       <c r="F306" t="n">
-        <v>66.96</v>
+        <v>86.64</v>
       </c>
       <c r="G306" t="n">
-        <v>1111.01</v>
+        <v>1644.67</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B307" t="s">
         <v>319</v>
@@ -8483,18 +8483,18 @@
         <v>338</v>
       </c>
       <c r="E307" t="n">
-        <v>8.03</v>
+        <v>9.77</v>
       </c>
       <c r="F307" t="n">
-        <v>123.39</v>
+        <v>184.32</v>
       </c>
       <c r="G307" t="n">
-        <v>2813.63</v>
+        <v>5168.26</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B308" t="s">
         <v>319</v>
@@ -8506,18 +8506,18 @@
         <v>340</v>
       </c>
       <c r="E308" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="F308" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="G308" t="n">
-        <v>5</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B309" t="s">
         <v>319</v>
@@ -8529,18 +8529,18 @@
         <v>341</v>
       </c>
       <c r="E309" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="F309" t="n">
-        <v>3.25</v>
+        <v>4.22</v>
       </c>
       <c r="G309" t="n">
-        <v>9.69</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B310" t="s">
         <v>319</v>
@@ -8552,18 +8552,18 @@
         <v>342</v>
       </c>
       <c r="E310" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="F310" t="n">
-        <v>5.38</v>
+        <v>4.4</v>
       </c>
       <c r="G310" t="n">
-        <v>22.06</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B311" t="s">
         <v>319</v>
@@ -8575,18 +8575,18 @@
         <v>343</v>
       </c>
       <c r="E311" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="F311" t="n">
-        <v>5.8</v>
+        <v>4.41</v>
       </c>
       <c r="G311" t="n">
-        <v>24.91</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B312" t="s">
         <v>319</v>
@@ -8598,18 +8598,18 @@
         <v>344</v>
       </c>
       <c r="E312" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="F312" t="n">
-        <v>6.84</v>
+        <v>4.47</v>
       </c>
       <c r="G312" t="n">
-        <v>32.38</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B313" t="s">
         <v>319</v>
@@ -8621,18 +8621,18 @@
         <v>345</v>
       </c>
       <c r="E313" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="F313" t="n">
-        <v>7.68</v>
+        <v>4.87</v>
       </c>
       <c r="G313" t="n">
-        <v>38.95</v>
+        <v>18.81</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B314" t="s">
         <v>319</v>
@@ -8644,18 +8644,18 @@
         <v>346</v>
       </c>
       <c r="E314" t="n">
-        <v>2.62</v>
+        <v>1.97</v>
       </c>
       <c r="F314" t="n">
-        <v>11.82</v>
+        <v>6.29</v>
       </c>
       <c r="G314" t="n">
-        <v>76.81</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B315" t="s">
         <v>319</v>
@@ -8667,18 +8667,18 @@
         <v>347</v>
       </c>
       <c r="E315" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="F315" t="n">
-        <v>11.94</v>
+        <v>8.53</v>
       </c>
       <c r="G315" t="n">
-        <v>78.08</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B316" t="s">
         <v>319</v>
@@ -8690,18 +8690,18 @@
         <v>348</v>
       </c>
       <c r="E316" t="n">
-        <v>2.76</v>
+        <v>2.27</v>
       </c>
       <c r="F316" t="n">
-        <v>13.27</v>
+        <v>8.63</v>
       </c>
       <c r="G316" t="n">
-        <v>92.11</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B317" t="s">
         <v>319</v>
@@ -8713,18 +8713,18 @@
         <v>349</v>
       </c>
       <c r="E317" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="F317" t="n">
-        <v>18.8</v>
+        <v>9.41</v>
       </c>
       <c r="G317" t="n">
-        <v>158.26</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B318" t="s">
         <v>319</v>
@@ -8736,18 +8736,18 @@
         <v>350</v>
       </c>
       <c r="E318" t="n">
-        <v>4.19</v>
+        <v>2.92</v>
       </c>
       <c r="F318" t="n">
-        <v>32.2</v>
+        <v>15.01</v>
       </c>
       <c r="G318" t="n">
-        <v>362.68</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B319" t="s">
         <v>319</v>
@@ -8759,18 +8759,18 @@
         <v>351</v>
       </c>
       <c r="E319" t="n">
-        <v>4.61</v>
+        <v>2.93</v>
       </c>
       <c r="F319" t="n">
-        <v>39.25</v>
+        <v>15.04</v>
       </c>
       <c r="G319" t="n">
-        <v>491.44</v>
+        <v>111.89</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B320" t="s">
         <v>319</v>
@@ -8782,18 +8782,18 @@
         <v>352</v>
       </c>
       <c r="E320" t="n">
-        <v>5.42</v>
+        <v>2.96</v>
       </c>
       <c r="F320" t="n">
-        <v>55.06</v>
+        <v>15.4</v>
       </c>
       <c r="G320" t="n">
-        <v>824.37</v>
+        <v>116.09</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B321" t="s">
         <v>319</v>
@@ -8805,18 +8805,18 @@
         <v>353</v>
       </c>
       <c r="E321" t="n">
-        <v>5.43</v>
+        <v>3.65</v>
       </c>
       <c r="F321" t="n">
-        <v>55.28</v>
+        <v>24.08</v>
       </c>
       <c r="G321" t="n">
-        <v>829.36</v>
+        <v>231.9</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B322" t="s">
         <v>319</v>
@@ -8828,18 +8828,18 @@
         <v>354</v>
       </c>
       <c r="E322" t="n">
-        <v>5.63</v>
+        <v>3.75</v>
       </c>
       <c r="F322" t="n">
-        <v>59.45</v>
+        <v>25.46</v>
       </c>
       <c r="G322" t="n">
-        <v>926.83</v>
+        <v>252.72</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B323" t="s">
         <v>319</v>
@@ -8851,18 +8851,18 @@
         <v>355</v>
       </c>
       <c r="E323" t="n">
-        <v>8.74</v>
+        <v>4.5</v>
       </c>
       <c r="F323" t="n">
-        <v>146.72</v>
+        <v>37.34</v>
       </c>
       <c r="G323" t="n">
-        <v>3658.27</v>
+        <v>455.26</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B324" t="s">
         <v>319</v>
@@ -8874,18 +8874,18 @@
         <v>356</v>
       </c>
       <c r="E324" t="n">
-        <v>13.51</v>
+        <v>4.55</v>
       </c>
       <c r="F324" t="n">
-        <v>355.94</v>
+        <v>38.24</v>
       </c>
       <c r="G324" t="n">
-        <v>13976.22</v>
+        <v>472.09</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>46243</v>
+        <v>46248</v>
       </c>
       <c r="B325" t="s">
         <v>319</v>
@@ -8897,13 +8897,13 @@
         <v>357</v>
       </c>
       <c r="E325" t="n">
-        <v>15.27</v>
+        <v>5.8</v>
       </c>
       <c r="F325" t="n">
-        <v>455.83</v>
+        <v>63.33</v>
       </c>
       <c r="G325" t="n">
-        <v>20300.38</v>
+        <v>1020.65</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -2302,7 +2302,7 @@
         <v>2.65</v>
       </c>
       <c r="G38" t="n">
-        <v>6.87</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="39">
@@ -2319,13 +2319,13 @@
         <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="F39" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="G39" t="n">
-        <v>10.78</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="40">
@@ -2345,10 +2345,10 @@
         <v>1.76</v>
       </c>
       <c r="F40" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="G40" t="n">
-        <v>18.89</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="41">
@@ -2368,10 +2368,10 @@
         <v>1.85</v>
       </c>
       <c r="F41" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="G41" t="n">
-        <v>22.59</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="42">
@@ -2391,10 +2391,10 @@
         <v>1.96</v>
       </c>
       <c r="F42" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="G42" t="n">
-        <v>28.01</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="43">
@@ -2414,10 +2414,10 @@
         <v>2.05</v>
       </c>
       <c r="F43" t="n">
-        <v>6.91</v>
+        <v>6.9</v>
       </c>
       <c r="G43" t="n">
-        <v>32.95</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="44">
@@ -2437,10 +2437,10 @@
         <v>2.08</v>
       </c>
       <c r="F44" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="G44" t="n">
-        <v>34.72</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="45">
@@ -2460,10 +2460,10 @@
         <v>2.09</v>
       </c>
       <c r="F45" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="G45" t="n">
-        <v>35.05</v>
+        <v>34.94</v>
       </c>
     </row>
     <row r="46">
@@ -2483,10 +2483,10 @@
         <v>2.35</v>
       </c>
       <c r="F46" t="n">
-        <v>9.31</v>
+        <v>9.3</v>
       </c>
       <c r="G46" t="n">
-        <v>52.87</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="47">
@@ -2506,10 +2506,10 @@
         <v>3.14</v>
       </c>
       <c r="F47" t="n">
-        <v>17.48</v>
+        <v>17.44</v>
       </c>
       <c r="G47" t="n">
-        <v>141.29</v>
+        <v>140.82</v>
       </c>
     </row>
     <row r="48">
@@ -2526,13 +2526,13 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="F48" t="n">
-        <v>18.3</v>
+        <v>18.26</v>
       </c>
       <c r="G48" t="n">
-        <v>151.74</v>
+        <v>151.23</v>
       </c>
     </row>
     <row r="49">
@@ -2549,13 +2549,13 @@
         <v>59</v>
       </c>
       <c r="E49" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="F49" t="n">
-        <v>35.6</v>
+        <v>35.52</v>
       </c>
       <c r="G49" t="n">
-        <v>423</v>
+        <v>421.55</v>
       </c>
     </row>
     <row r="50">
@@ -2575,10 +2575,10 @@
         <v>4.64</v>
       </c>
       <c r="F50" t="n">
-        <v>39.93</v>
+        <v>39.84</v>
       </c>
       <c r="G50" t="n">
-        <v>504.43</v>
+        <v>502.69</v>
       </c>
     </row>
     <row r="51">
@@ -2595,13 +2595,13 @@
         <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>6.88</v>
+        <v>6.87</v>
       </c>
       <c r="F51" t="n">
-        <v>90.01</v>
+        <v>89.8</v>
       </c>
       <c r="G51" t="n">
-        <v>1742.86</v>
+        <v>1736.73</v>
       </c>
     </row>
     <row r="52">
@@ -2618,13 +2618,13 @@
         <v>62</v>
       </c>
       <c r="E52" t="n">
-        <v>7.16</v>
+        <v>7.15</v>
       </c>
       <c r="F52" t="n">
-        <v>97.59</v>
+        <v>97.36</v>
       </c>
       <c r="G52" t="n">
-        <v>1970.51</v>
+        <v>1963.57</v>
       </c>
     </row>
     <row r="53">
@@ -2641,13 +2641,13 @@
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="F53" t="n">
-        <v>98.44</v>
+        <v>98.21</v>
       </c>
       <c r="G53" t="n">
-        <v>1996.7</v>
+        <v>1989.67</v>
       </c>
     </row>
     <row r="54">
@@ -2664,13 +2664,13 @@
         <v>64</v>
       </c>
       <c r="E54" t="n">
-        <v>10.54</v>
+        <v>10.53</v>
       </c>
       <c r="F54" t="n">
-        <v>214.96</v>
+        <v>214.45</v>
       </c>
       <c r="G54" t="n">
-        <v>6522.35</v>
+        <v>6499.08</v>
       </c>
     </row>
     <row r="55">
@@ -2687,13 +2687,13 @@
         <v>65</v>
       </c>
       <c r="E55" t="n">
-        <v>11.86</v>
+        <v>11.85</v>
       </c>
       <c r="F55" t="n">
-        <v>273.47</v>
+        <v>272.83</v>
       </c>
       <c r="G55" t="n">
-        <v>9386.38</v>
+        <v>9352.78</v>
       </c>
     </row>
     <row r="56">
@@ -2785,7 +2785,7 @@
         <v>2.81</v>
       </c>
       <c r="G59" t="n">
-        <v>7.6</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="60">
@@ -2808,7 +2808,7 @@
         <v>3.15</v>
       </c>
       <c r="G60" t="n">
-        <v>9.21</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="61">
@@ -2831,7 +2831,7 @@
         <v>3.36</v>
       </c>
       <c r="G61" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="62">
@@ -2854,7 +2854,7 @@
         <v>3.37</v>
       </c>
       <c r="G62" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="63">
@@ -2877,7 +2877,7 @@
         <v>4.04</v>
       </c>
       <c r="G63" t="n">
-        <v>13.87</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="64">
@@ -2900,7 +2900,7 @@
         <v>5.03</v>
       </c>
       <c r="G64" t="n">
-        <v>19.82</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="65">
@@ -2923,7 +2923,7 @@
         <v>5.19</v>
       </c>
       <c r="G65" t="n">
-        <v>20.84</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="66">
@@ -2943,10 +2943,10 @@
         <v>1.91</v>
       </c>
       <c r="F66" t="n">
-        <v>5.9</v>
+        <v>5.89</v>
       </c>
       <c r="G66" t="n">
-        <v>25.58</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="67">
@@ -2966,10 +2966,10 @@
         <v>2.05</v>
       </c>
       <c r="F67" t="n">
-        <v>6.93</v>
+        <v>6.92</v>
       </c>
       <c r="G67" t="n">
-        <v>33.08</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="68">
@@ -2989,10 +2989,10 @@
         <v>2.87</v>
       </c>
       <c r="F68" t="n">
-        <v>14.42</v>
+        <v>14.4</v>
       </c>
       <c r="G68" t="n">
-        <v>104.78</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="69">
@@ -3012,10 +3012,10 @@
         <v>3.11</v>
       </c>
       <c r="F69" t="n">
-        <v>17.17</v>
+        <v>17.16</v>
       </c>
       <c r="G69" t="n">
-        <v>137.5</v>
+        <v>137.28</v>
       </c>
     </row>
     <row r="70">
@@ -3032,13 +3032,13 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="F70" t="n">
-        <v>18.17</v>
+        <v>18.15</v>
       </c>
       <c r="G70" t="n">
-        <v>150.11</v>
+        <v>149.87</v>
       </c>
     </row>
     <row r="71">
@@ -3058,10 +3058,10 @@
         <v>4.27</v>
       </c>
       <c r="F71" t="n">
-        <v>33.55</v>
+        <v>33.51</v>
       </c>
       <c r="G71" t="n">
-        <v>386.23</v>
+        <v>385.61</v>
       </c>
     </row>
     <row r="72">
@@ -3081,10 +3081,10 @@
         <v>4.79</v>
       </c>
       <c r="F72" t="n">
-        <v>42.61</v>
+        <v>42.57</v>
       </c>
       <c r="G72" t="n">
-        <v>557.3</v>
+        <v>556.39</v>
       </c>
     </row>
     <row r="73">
@@ -3104,10 +3104,10 @@
         <v>7.53</v>
       </c>
       <c r="F73" t="n">
-        <v>108.36</v>
+        <v>108.24</v>
       </c>
       <c r="G73" t="n">
-        <v>2310.21</v>
+        <v>2306.35</v>
       </c>
     </row>
     <row r="74">
@@ -3452,7 +3452,7 @@
         <v>31.12</v>
       </c>
       <c r="G88" t="n">
-        <v>344.24</v>
+        <v>344.25</v>
       </c>
     </row>
     <row r="89">
@@ -3475,7 +3475,7 @@
         <v>51.84</v>
       </c>
       <c r="G89" t="n">
-        <v>751.87</v>
+        <v>751.89</v>
       </c>
     </row>
     <row r="90">
@@ -3498,7 +3498,7 @@
         <v>111.17</v>
       </c>
       <c r="G90" t="n">
-        <v>2401.72</v>
+        <v>2401.76</v>
       </c>
     </row>
     <row r="91">
@@ -3518,10 +3518,10 @@
         <v>10.08</v>
       </c>
       <c r="F91" t="n">
-        <v>196.43</v>
+        <v>196.44</v>
       </c>
       <c r="G91" t="n">
-        <v>5691.1</v>
+        <v>5691.2</v>
       </c>
     </row>
     <row r="92">
@@ -3751,7 +3751,7 @@
         <v>18.24</v>
       </c>
       <c r="G101" t="n">
-        <v>150.94</v>
+        <v>150.93</v>
       </c>
     </row>
     <row r="102">
@@ -3797,7 +3797,7 @@
         <v>24.55</v>
       </c>
       <c r="G103" t="n">
-        <v>238.92</v>
+        <v>238.91</v>
       </c>
     </row>
     <row r="104">
@@ -3889,7 +3889,7 @@
         <v>70.5</v>
       </c>
       <c r="G107" t="n">
-        <v>1201.85</v>
+        <v>1201.83</v>
       </c>
     </row>
     <row r="108">
@@ -3912,7 +3912,7 @@
         <v>112.77</v>
       </c>
       <c r="G108" t="n">
-        <v>2454.44</v>
+        <v>2454.4</v>
       </c>
     </row>
     <row r="109">
@@ -3935,7 +3935,7 @@
         <v>230.64</v>
       </c>
       <c r="G109" t="n">
-        <v>7255.32</v>
+        <v>7255.21</v>
       </c>
     </row>
     <row r="110">
@@ -4142,7 +4142,7 @@
         <v>10.32</v>
       </c>
       <c r="G118" t="n">
-        <v>62.14</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="119">
@@ -4349,7 +4349,7 @@
         <v>200.8</v>
       </c>
       <c r="G127" t="n">
-        <v>5883.61</v>
+        <v>5883.63</v>
       </c>
     </row>
     <row r="128">
@@ -4510,7 +4510,7 @@
         <v>9.49</v>
       </c>
       <c r="G134" t="n">
-        <v>54.44</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="135">
@@ -4694,7 +4694,7 @@
         <v>42.58</v>
       </c>
       <c r="G142" t="n">
-        <v>556.55</v>
+        <v>556.54</v>
       </c>
     </row>
     <row r="143">
@@ -4717,7 +4717,7 @@
         <v>125.74</v>
       </c>
       <c r="G143" t="n">
-        <v>2895.34</v>
+        <v>2895.33</v>
       </c>
     </row>
     <row r="144">
@@ -4740,7 +4740,7 @@
         <v>291.12</v>
       </c>
       <c r="G144" t="n">
-        <v>10316.5</v>
+        <v>10316.44</v>
       </c>
     </row>
     <row r="145">
@@ -4760,10 +4760,10 @@
         <v>14.38</v>
       </c>
       <c r="F145" t="n">
-        <v>403.64</v>
+        <v>403.63</v>
       </c>
       <c r="G145" t="n">
-        <v>16897.2</v>
+        <v>16897.1</v>
       </c>
     </row>
     <row r="146">
@@ -4786,7 +4786,7 @@
         <v>2.28</v>
       </c>
       <c r="G146" t="n">
-        <v>5.32</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="147">
@@ -4809,7 +4809,7 @@
         <v>2.41</v>
       </c>
       <c r="G147" t="n">
-        <v>5.84</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="148">
@@ -4832,7 +4832,7 @@
         <v>3.23</v>
       </c>
       <c r="G148" t="n">
-        <v>9.59</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="149">
@@ -4852,10 +4852,10 @@
         <v>1.59</v>
       </c>
       <c r="F149" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="G149" t="n">
-        <v>12.79</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="150">
@@ -4875,10 +4875,10 @@
         <v>1.74</v>
       </c>
       <c r="F150" t="n">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
       <c r="G150" t="n">
-        <v>18.11</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="151">
@@ -4898,10 +4898,10 @@
         <v>1.8</v>
       </c>
       <c r="F151" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="G151" t="n">
-        <v>20.3</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="152">
@@ -4924,7 +4924,7 @@
         <v>5.4</v>
       </c>
       <c r="G152" t="n">
-        <v>22.23</v>
+        <v>22.18</v>
       </c>
     </row>
     <row r="153">
@@ -4944,10 +4944,10 @@
         <v>1.98</v>
       </c>
       <c r="F153" t="n">
-        <v>6.35</v>
+        <v>6.34</v>
       </c>
       <c r="G153" t="n">
-        <v>28.78</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="154">
@@ -4964,13 +4964,13 @@
         <v>173</v>
       </c>
       <c r="E154" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="F154" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="G154" t="n">
-        <v>29.25</v>
+        <v>29.18</v>
       </c>
     </row>
     <row r="155">
@@ -4990,10 +4990,10 @@
         <v>2.34</v>
       </c>
       <c r="F155" t="n">
-        <v>9.27</v>
+        <v>9.25</v>
       </c>
       <c r="G155" t="n">
-        <v>52.43</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="156">
@@ -5010,13 +5010,13 @@
         <v>175</v>
       </c>
       <c r="E156" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="F156" t="n">
-        <v>18.65</v>
+        <v>18.62</v>
       </c>
       <c r="G156" t="n">
-        <v>156.23</v>
+        <v>155.85</v>
       </c>
     </row>
     <row r="157">
@@ -5033,13 +5033,13 @@
         <v>176</v>
       </c>
       <c r="E157" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="F157" t="n">
-        <v>21.99</v>
+        <v>21.95</v>
       </c>
       <c r="G157" t="n">
-        <v>201.56</v>
+        <v>201.07</v>
       </c>
     </row>
     <row r="158">
@@ -5059,10 +5059,10 @@
         <v>3.71</v>
       </c>
       <c r="F158" t="n">
-        <v>24.96</v>
+        <v>24.92</v>
       </c>
       <c r="G158" t="n">
-        <v>245.13</v>
+        <v>244.52</v>
       </c>
     </row>
     <row r="159">
@@ -5082,10 +5082,10 @@
         <v>3.9</v>
       </c>
       <c r="F159" t="n">
-        <v>27.76</v>
+        <v>27.72</v>
       </c>
       <c r="G159" t="n">
-        <v>288.79</v>
+        <v>288.08</v>
       </c>
     </row>
     <row r="160">
@@ -5105,10 +5105,10 @@
         <v>4.05</v>
       </c>
       <c r="F160" t="n">
-        <v>30.03</v>
+        <v>29.98</v>
       </c>
       <c r="G160" t="n">
-        <v>325.76</v>
+        <v>324.95</v>
       </c>
     </row>
     <row r="161">
@@ -5125,13 +5125,13 @@
         <v>180</v>
       </c>
       <c r="E161" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="F161" t="n">
-        <v>48.62</v>
+        <v>48.54</v>
       </c>
       <c r="G161" t="n">
-        <v>681.71</v>
+        <v>680</v>
       </c>
     </row>
     <row r="162">
@@ -5148,13 +5148,13 @@
         <v>181</v>
       </c>
       <c r="E162" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="F162" t="n">
-        <v>98.41</v>
+        <v>98.25</v>
       </c>
       <c r="G162" t="n">
-        <v>1995.87</v>
+        <v>1990.75</v>
       </c>
     </row>
     <row r="163">
@@ -5171,13 +5171,13 @@
         <v>182</v>
       </c>
       <c r="E163" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
       <c r="F163" t="n">
-        <v>177.75</v>
+        <v>177.45</v>
       </c>
       <c r="G163" t="n">
-        <v>4892.23</v>
+        <v>4879.55</v>
       </c>
     </row>
     <row r="164">
@@ -5200,7 +5200,7 @@
         <v>1.52</v>
       </c>
       <c r="G164" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="165">
@@ -5223,7 +5223,7 @@
         <v>2.11</v>
       </c>
       <c r="G165" t="n">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="166">
@@ -5246,7 +5246,7 @@
         <v>2.65</v>
       </c>
       <c r="G166" t="n">
-        <v>6.87</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="167">
@@ -5269,7 +5269,7 @@
         <v>3.08</v>
       </c>
       <c r="G167" t="n">
-        <v>8.86</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="168">
@@ -5286,13 +5286,13 @@
         <v>188</v>
       </c>
       <c r="E168" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="F168" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="G168" t="n">
-        <v>15.21</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="169">
@@ -5312,10 +5312,10 @@
         <v>1.73</v>
       </c>
       <c r="F169" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="G169" t="n">
-        <v>17.55</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="170">
@@ -5335,10 +5335,10 @@
         <v>1.86</v>
       </c>
       <c r="F170" t="n">
-        <v>5.54</v>
+        <v>5.53</v>
       </c>
       <c r="G170" t="n">
-        <v>23.11</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="171">
@@ -5355,13 +5355,13 @@
         <v>191</v>
       </c>
       <c r="E171" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="F171" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="G171" t="n">
-        <v>30.87</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="172">
@@ -5378,13 +5378,13 @@
         <v>192</v>
       </c>
       <c r="E172" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="F172" t="n">
-        <v>15.26</v>
+        <v>15.24</v>
       </c>
       <c r="G172" t="n">
-        <v>114.47</v>
+        <v>114.22</v>
       </c>
     </row>
     <row r="173">
@@ -5404,10 +5404,10 @@
         <v>3.77</v>
       </c>
       <c r="F173" t="n">
-        <v>25.83</v>
+        <v>25.79</v>
       </c>
       <c r="G173" t="n">
-        <v>258.37</v>
+        <v>257.78</v>
       </c>
     </row>
     <row r="174">
@@ -5427,10 +5427,10 @@
         <v>3.84</v>
       </c>
       <c r="F174" t="n">
-        <v>26.78</v>
+        <v>26.74</v>
       </c>
       <c r="G174" t="n">
-        <v>273.14</v>
+        <v>272.52</v>
       </c>
     </row>
     <row r="175">
@@ -5450,10 +5450,10 @@
         <v>4.1</v>
       </c>
       <c r="F175" t="n">
-        <v>30.78</v>
+        <v>30.73</v>
       </c>
       <c r="G175" t="n">
-        <v>338.38</v>
+        <v>337.61</v>
       </c>
     </row>
     <row r="176">
@@ -5473,10 +5473,10 @@
         <v>4.34</v>
       </c>
       <c r="F176" t="n">
-        <v>34.65</v>
+        <v>34.6</v>
       </c>
       <c r="G176" t="n">
-        <v>405.89</v>
+        <v>404.95</v>
       </c>
     </row>
     <row r="177">
@@ -5493,13 +5493,13 @@
         <v>197</v>
       </c>
       <c r="E177" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="F177" t="n">
-        <v>36.61</v>
+        <v>36.55</v>
       </c>
       <c r="G177" t="n">
-        <v>441.61</v>
+        <v>440.59</v>
       </c>
     </row>
     <row r="178">
@@ -5519,10 +5519,10 @@
         <v>4.46</v>
       </c>
       <c r="F178" t="n">
-        <v>36.77</v>
+        <v>36.71</v>
       </c>
       <c r="G178" t="n">
-        <v>444.55</v>
+        <v>443.52</v>
       </c>
     </row>
     <row r="179">
@@ -5542,10 +5542,10 @@
         <v>4.93</v>
       </c>
       <c r="F179" t="n">
-        <v>45.19</v>
+        <v>45.13</v>
       </c>
       <c r="G179" t="n">
-        <v>609.73</v>
+        <v>608.31</v>
       </c>
     </row>
     <row r="180">
@@ -5565,10 +5565,10 @@
         <v>5.38</v>
       </c>
       <c r="F180" t="n">
-        <v>54.2</v>
+        <v>54.12</v>
       </c>
       <c r="G180" t="n">
-        <v>804.91</v>
+        <v>803.02</v>
       </c>
     </row>
     <row r="181">
@@ -5585,13 +5585,13 @@
         <v>201</v>
       </c>
       <c r="E181" t="n">
-        <v>6.36</v>
+        <v>6.35</v>
       </c>
       <c r="F181" t="n">
-        <v>76.45</v>
+        <v>76.34</v>
       </c>
       <c r="G181" t="n">
-        <v>1359.62</v>
+        <v>1356.41</v>
       </c>
     </row>
     <row r="182">
@@ -5729,7 +5729,7 @@
         <v>2.82</v>
       </c>
       <c r="G187" t="n">
-        <v>7.65</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="188">
@@ -5775,7 +5775,7 @@
         <v>3.76</v>
       </c>
       <c r="G189" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="190">
@@ -5798,7 +5798,7 @@
         <v>4.73</v>
       </c>
       <c r="G190" t="n">
-        <v>17.91</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="191">
@@ -5818,10 +5818,10 @@
         <v>2.69</v>
       </c>
       <c r="F191" t="n">
-        <v>12.52</v>
+        <v>12.51</v>
       </c>
       <c r="G191" t="n">
-        <v>84.05</v>
+        <v>84.01</v>
       </c>
     </row>
     <row r="192">
@@ -5844,7 +5844,7 @@
         <v>18.08</v>
       </c>
       <c r="G192" t="n">
-        <v>148.98</v>
+        <v>148.91</v>
       </c>
     </row>
     <row r="193">
@@ -5867,7 +5867,7 @@
         <v>18.47</v>
       </c>
       <c r="G193" t="n">
-        <v>153.95</v>
+        <v>153.88</v>
       </c>
     </row>
     <row r="194">
@@ -5887,10 +5887,10 @@
         <v>4.07</v>
       </c>
       <c r="F194" t="n">
-        <v>30.36</v>
+        <v>30.35</v>
       </c>
       <c r="G194" t="n">
-        <v>331.34</v>
+        <v>331.19</v>
       </c>
     </row>
     <row r="195">
@@ -5910,10 +5910,10 @@
         <v>4.4</v>
       </c>
       <c r="F195" t="n">
-        <v>35.64</v>
+        <v>35.63</v>
       </c>
       <c r="G195" t="n">
-        <v>423.8</v>
+        <v>423.6</v>
       </c>
     </row>
     <row r="196">
@@ -5933,10 +5933,10 @@
         <v>4.92</v>
       </c>
       <c r="F196" t="n">
-        <v>45.08</v>
+        <v>45.07</v>
       </c>
       <c r="G196" t="n">
-        <v>607.36</v>
+        <v>607.07</v>
       </c>
     </row>
     <row r="197">
@@ -5956,10 +5956,10 @@
         <v>5.07</v>
       </c>
       <c r="F197" t="n">
-        <v>47.97</v>
+        <v>47.96</v>
       </c>
       <c r="G197" t="n">
-        <v>667.91</v>
+        <v>667.59</v>
       </c>
     </row>
     <row r="198">
@@ -5976,13 +5976,13 @@
         <v>220</v>
       </c>
       <c r="E198" t="n">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="F198" t="n">
-        <v>67.07</v>
+        <v>67.05</v>
       </c>
       <c r="G198" t="n">
-        <v>1113.84</v>
+        <v>1113.29</v>
       </c>
     </row>
     <row r="199">
@@ -6002,10 +6002,10 @@
         <v>6.59</v>
       </c>
       <c r="F199" t="n">
-        <v>82.35</v>
+        <v>82.33</v>
       </c>
       <c r="G199" t="n">
-        <v>1522.4</v>
+        <v>1521.65</v>
       </c>
     </row>
     <row r="200">
@@ -6097,7 +6097,7 @@
         <v>3.4</v>
       </c>
       <c r="G203" t="n">
-        <v>10.42</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="204">
@@ -6120,7 +6120,7 @@
         <v>5.85</v>
       </c>
       <c r="G204" t="n">
-        <v>25.22</v>
+        <v>25.23</v>
       </c>
     </row>
     <row r="205">
@@ -6143,7 +6143,7 @@
         <v>7.19</v>
       </c>
       <c r="G205" t="n">
-        <v>35.07</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="206">
@@ -6166,7 +6166,7 @@
         <v>7.43</v>
       </c>
       <c r="G206" t="n">
-        <v>36.98</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="207">
@@ -6183,13 +6183,13 @@
         <v>230</v>
       </c>
       <c r="E207" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="F207" t="n">
         <v>8.36</v>
       </c>
       <c r="G207" t="n">
-        <v>44.55</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="208">
@@ -6206,13 +6206,13 @@
         <v>231</v>
       </c>
       <c r="E208" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="F208" t="n">
-        <v>11.89</v>
+        <v>11.9</v>
       </c>
       <c r="G208" t="n">
-        <v>77.57</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="209">
@@ -6235,7 +6235,7 @@
         <v>15.07</v>
       </c>
       <c r="G209" t="n">
-        <v>112.2</v>
+        <v>112.27</v>
       </c>
     </row>
     <row r="210">
@@ -6255,10 +6255,10 @@
         <v>3.11</v>
       </c>
       <c r="F210" t="n">
-        <v>17.18</v>
+        <v>17.19</v>
       </c>
       <c r="G210" t="n">
-        <v>137.61</v>
+        <v>137.7</v>
       </c>
     </row>
     <row r="211">
@@ -6278,10 +6278,10 @@
         <v>3.44</v>
       </c>
       <c r="F211" t="n">
-        <v>21.26</v>
+        <v>21.27</v>
       </c>
       <c r="G211" t="n">
-        <v>191.39</v>
+        <v>191.52</v>
       </c>
     </row>
     <row r="212">
@@ -6298,13 +6298,13 @@
         <v>235</v>
       </c>
       <c r="E212" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="F212" t="n">
-        <v>26.43</v>
+        <v>26.44</v>
       </c>
       <c r="G212" t="n">
-        <v>267.69</v>
+        <v>267.86</v>
       </c>
     </row>
     <row r="213">
@@ -6324,10 +6324,10 @@
         <v>4.51</v>
       </c>
       <c r="F213" t="n">
-        <v>37.5</v>
+        <v>37.51</v>
       </c>
       <c r="G213" t="n">
-        <v>458.14</v>
+        <v>458.45</v>
       </c>
     </row>
     <row r="214">
@@ -6347,10 +6347,10 @@
         <v>4.67</v>
       </c>
       <c r="F214" t="n">
-        <v>40.36</v>
+        <v>40.37</v>
       </c>
       <c r="G214" t="n">
-        <v>512.73</v>
+        <v>513.08</v>
       </c>
     </row>
     <row r="215">
@@ -6367,13 +6367,13 @@
         <v>238</v>
       </c>
       <c r="E215" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="F215" t="n">
-        <v>42.66</v>
+        <v>42.68</v>
       </c>
       <c r="G215" t="n">
-        <v>558.2</v>
+        <v>558.58</v>
       </c>
     </row>
     <row r="216">
@@ -6390,13 +6390,13 @@
         <v>239</v>
       </c>
       <c r="E216" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="F216" t="n">
-        <v>42.84</v>
+        <v>42.86</v>
       </c>
       <c r="G216" t="n">
-        <v>561.78</v>
+        <v>562.16</v>
       </c>
     </row>
     <row r="217">
@@ -6416,10 +6416,10 @@
         <v>5.21</v>
       </c>
       <c r="F217" t="n">
-        <v>50.69</v>
+        <v>50.71</v>
       </c>
       <c r="G217" t="n">
-        <v>726.67</v>
+        <v>727.16</v>
       </c>
     </row>
     <row r="218">
@@ -6439,10 +6439,10 @@
         <v>1.27</v>
       </c>
       <c r="F218" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="G218" t="n">
-        <v>4.89</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="219">
@@ -6462,10 +6462,10 @@
         <v>1.28</v>
       </c>
       <c r="F219" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="G219" t="n">
-        <v>5.11</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="220">
@@ -6482,13 +6482,13 @@
         <v>245</v>
       </c>
       <c r="E220" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="F220" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="G220" t="n">
-        <v>8.53</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="221">
@@ -6505,13 +6505,13 @@
         <v>246</v>
       </c>
       <c r="E221" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="F221" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="G221" t="n">
-        <v>10.18</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="222">
@@ -6531,10 +6531,10 @@
         <v>1.51</v>
       </c>
       <c r="F222" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="G222" t="n">
-        <v>10.24</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="223">
@@ -6554,10 +6554,10 @@
         <v>1.69</v>
       </c>
       <c r="F223" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="G223" t="n">
-        <v>15.92</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="224">
@@ -6574,13 +6574,13 @@
         <v>249</v>
       </c>
       <c r="E224" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="F224" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="G224" t="n">
-        <v>17.26</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="225">
@@ -6597,13 +6597,13 @@
         <v>250</v>
       </c>
       <c r="E225" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="F225" t="n">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="G225" t="n">
-        <v>23.19</v>
+        <v>23.55</v>
       </c>
     </row>
     <row r="226">
@@ -6623,10 +6623,10 @@
         <v>1.91</v>
       </c>
       <c r="F226" t="n">
-        <v>5.84</v>
+        <v>5.9</v>
       </c>
       <c r="G226" t="n">
-        <v>25.21</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="227">
@@ -6643,13 +6643,13 @@
         <v>252</v>
       </c>
       <c r="E227" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="F227" t="n">
-        <v>6.26</v>
+        <v>6.32</v>
       </c>
       <c r="G227" t="n">
-        <v>28.16</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="228">
@@ -6666,13 +6666,13 @@
         <v>253</v>
       </c>
       <c r="E228" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="F228" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="G228" t="n">
-        <v>28.68</v>
+        <v>29.13</v>
       </c>
     </row>
     <row r="229">
@@ -6689,13 +6689,13 @@
         <v>254</v>
       </c>
       <c r="E229" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="F229" t="n">
-        <v>12.26</v>
+        <v>12.39</v>
       </c>
       <c r="G229" t="n">
-        <v>81.39</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="230">
@@ -6712,13 +6712,13 @@
         <v>255</v>
       </c>
       <c r="E230" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="F230" t="n">
-        <v>13.06</v>
+        <v>13.2</v>
       </c>
       <c r="G230" t="n">
-        <v>89.82</v>
+        <v>91.33</v>
       </c>
     </row>
     <row r="231">
@@ -6735,13 +6735,13 @@
         <v>256</v>
       </c>
       <c r="E231" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="F231" t="n">
-        <v>13.22</v>
+        <v>13.36</v>
       </c>
       <c r="G231" t="n">
-        <v>91.53</v>
+        <v>93.06</v>
       </c>
     </row>
     <row r="232">
@@ -6758,13 +6758,13 @@
         <v>257</v>
       </c>
       <c r="E232" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="F232" t="n">
-        <v>27.71</v>
+        <v>28.02</v>
       </c>
       <c r="G232" t="n">
-        <v>287.91</v>
+        <v>292.95</v>
       </c>
     </row>
     <row r="233">
@@ -6781,13 +6781,13 @@
         <v>258</v>
       </c>
       <c r="E233" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="F233" t="n">
-        <v>38.48</v>
+        <v>38.93</v>
       </c>
       <c r="G233" t="n">
-        <v>476.68</v>
+        <v>485.14</v>
       </c>
     </row>
     <row r="234">
@@ -6804,13 +6804,13 @@
         <v>259</v>
       </c>
       <c r="E234" t="n">
-        <v>5.78</v>
+        <v>5.81</v>
       </c>
       <c r="F234" t="n">
-        <v>62.81</v>
+        <v>63.55</v>
       </c>
       <c r="G234" t="n">
-        <v>1007.88</v>
+        <v>1026.05</v>
       </c>
     </row>
     <row r="235">
@@ -6827,13 +6827,13 @@
         <v>260</v>
       </c>
       <c r="E235" t="n">
-        <v>7.43</v>
+        <v>7.47</v>
       </c>
       <c r="F235" t="n">
-        <v>105.21</v>
+        <v>106.47</v>
       </c>
       <c r="G235" t="n">
-        <v>2208.95</v>
+        <v>2249.23</v>
       </c>
     </row>
     <row r="236">
@@ -6850,13 +6850,13 @@
         <v>262</v>
       </c>
       <c r="E236" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="F236" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G236" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="237">
@@ -6876,10 +6876,10 @@
         <v>1.45</v>
       </c>
       <c r="F237" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="G237" t="n">
-        <v>8.72</v>
+        <v>8.86</v>
       </c>
     </row>
     <row r="238">
@@ -6899,10 +6899,10 @@
         <v>1.56</v>
       </c>
       <c r="F238" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="G238" t="n">
-        <v>11.73</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="239">
@@ -6919,13 +6919,13 @@
         <v>265</v>
       </c>
       <c r="E239" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="F239" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="G239" t="n">
-        <v>16.83</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="240">
@@ -6942,13 +6942,13 @@
         <v>266</v>
       </c>
       <c r="E240" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="F240" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="G240" t="n">
-        <v>16.97</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="241">
@@ -6968,10 +6968,10 @@
         <v>1.78</v>
       </c>
       <c r="F241" t="n">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="G241" t="n">
-        <v>19.4</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="242">
@@ -6988,13 +6988,13 @@
         <v>268</v>
       </c>
       <c r="E242" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="F242" t="n">
-        <v>5.17</v>
+        <v>5.23</v>
       </c>
       <c r="G242" t="n">
-        <v>20.72</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="243">
@@ -7011,13 +7011,13 @@
         <v>269</v>
       </c>
       <c r="E243" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="F243" t="n">
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="G243" t="n">
-        <v>29.31</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="244">
@@ -7034,13 +7034,13 @@
         <v>270</v>
       </c>
       <c r="E244" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="F244" t="n">
-        <v>6.63</v>
+        <v>6.71</v>
       </c>
       <c r="G244" t="n">
-        <v>30.83</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="245">
@@ -7057,13 +7057,13 @@
         <v>271</v>
       </c>
       <c r="E245" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="F245" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="G245" t="n">
-        <v>60.67</v>
+        <v>61.86</v>
       </c>
     </row>
     <row r="246">
@@ -7080,13 +7080,13 @@
         <v>272</v>
       </c>
       <c r="E246" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="F246" t="n">
-        <v>18.75</v>
+        <v>19</v>
       </c>
       <c r="G246" t="n">
-        <v>157.62</v>
+        <v>160.85</v>
       </c>
     </row>
     <row r="247">
@@ -7103,13 +7103,13 @@
         <v>273</v>
       </c>
       <c r="E247" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="F247" t="n">
-        <v>18.92</v>
+        <v>19.17</v>
       </c>
       <c r="G247" t="n">
-        <v>159.83</v>
+        <v>163.11</v>
       </c>
     </row>
     <row r="248">
@@ -7126,13 +7126,13 @@
         <v>274</v>
       </c>
       <c r="E248" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="F248" t="n">
-        <v>23.5</v>
+        <v>23.81</v>
       </c>
       <c r="G248" t="n">
-        <v>223.36</v>
+        <v>228</v>
       </c>
     </row>
     <row r="249">
@@ -7149,13 +7149,13 @@
         <v>275</v>
       </c>
       <c r="E249" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="F249" t="n">
-        <v>28.65</v>
+        <v>29.04</v>
       </c>
       <c r="G249" t="n">
-        <v>303.06</v>
+        <v>309.41</v>
       </c>
     </row>
     <row r="250">
@@ -7172,13 +7172,13 @@
         <v>276</v>
       </c>
       <c r="E250" t="n">
-        <v>5.26</v>
+        <v>5.29</v>
       </c>
       <c r="F250" t="n">
-        <v>51.64</v>
+        <v>52.36</v>
       </c>
       <c r="G250" t="n">
-        <v>747.54</v>
+        <v>763.51</v>
       </c>
     </row>
     <row r="251">
@@ -7195,13 +7195,13 @@
         <v>277</v>
       </c>
       <c r="E251" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="F251" t="n">
-        <v>65.12</v>
+        <v>66.04</v>
       </c>
       <c r="G251" t="n">
-        <v>1064.89</v>
+        <v>1087.79</v>
       </c>
     </row>
     <row r="252">
@@ -7218,13 +7218,13 @@
         <v>278</v>
       </c>
       <c r="E252" t="n">
-        <v>6.13</v>
+        <v>6.17</v>
       </c>
       <c r="F252" t="n">
-        <v>70.87</v>
+        <v>71.87</v>
       </c>
       <c r="G252" t="n">
-        <v>1211.37</v>
+        <v>1237.48</v>
       </c>
     </row>
     <row r="253">
@@ -7241,13 +7241,13 @@
         <v>279</v>
       </c>
       <c r="E253" t="n">
-        <v>9.86</v>
+        <v>9.93</v>
       </c>
       <c r="F253" t="n">
-        <v>187.84</v>
+        <v>190.56</v>
       </c>
       <c r="G253" t="n">
-        <v>5318.69</v>
+        <v>5435.45</v>
       </c>
     </row>
     <row r="254">
@@ -7264,13 +7264,13 @@
         <v>282</v>
       </c>
       <c r="E254" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="F254" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="G254" t="n">
-        <v>6.38</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="255">
@@ -7293,7 +7293,7 @@
         <v>3.49</v>
       </c>
       <c r="G255" t="n">
-        <v>10.91</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="256">
@@ -7310,13 +7310,13 @@
         <v>284</v>
       </c>
       <c r="E256" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="F256" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="G256" t="n">
-        <v>12.86</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="257">
@@ -7336,10 +7336,10 @@
         <v>1.69</v>
       </c>
       <c r="F257" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="G257" t="n">
-        <v>15.97</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="258">
@@ -7359,10 +7359,10 @@
         <v>1.73</v>
       </c>
       <c r="F258" t="n">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="G258" t="n">
-        <v>17.63</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="259">
@@ -7382,10 +7382,10 @@
         <v>1.85</v>
       </c>
       <c r="F259" t="n">
-        <v>5.48</v>
+        <v>5.47</v>
       </c>
       <c r="G259" t="n">
-        <v>22.73</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="260">
@@ -7405,10 +7405,10 @@
         <v>2.12</v>
       </c>
       <c r="F260" t="n">
-        <v>7.41</v>
+        <v>7.39</v>
       </c>
       <c r="G260" t="n">
-        <v>36.78</v>
+        <v>36.69</v>
       </c>
     </row>
     <row r="261">
@@ -7428,10 +7428,10 @@
         <v>2.3</v>
       </c>
       <c r="F261" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="G261" t="n">
-        <v>49.3</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="262">
@@ -7451,10 +7451,10 @@
         <v>2.36</v>
       </c>
       <c r="F262" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
       <c r="G262" t="n">
-        <v>54.03</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="263">
@@ -7474,10 +7474,10 @@
         <v>2.92</v>
       </c>
       <c r="F263" t="n">
-        <v>14.97</v>
+        <v>14.94</v>
       </c>
       <c r="G263" t="n">
-        <v>111.07</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="264">
@@ -7497,10 +7497,10 @@
         <v>2.98</v>
       </c>
       <c r="F264" t="n">
-        <v>15.69</v>
+        <v>15.66</v>
       </c>
       <c r="G264" t="n">
-        <v>119.53</v>
+        <v>119.21</v>
       </c>
     </row>
     <row r="265">
@@ -7517,13 +7517,13 @@
         <v>293</v>
       </c>
       <c r="E265" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="F265" t="n">
-        <v>31.8</v>
+        <v>31.74</v>
       </c>
       <c r="G265" t="n">
-        <v>355.76</v>
+        <v>354.76</v>
       </c>
     </row>
     <row r="266">
@@ -7540,13 +7540,13 @@
         <v>294</v>
       </c>
       <c r="E266" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="F266" t="n">
-        <v>36.32</v>
+        <v>36.25</v>
       </c>
       <c r="G266" t="n">
-        <v>436.2</v>
+        <v>434.97</v>
       </c>
     </row>
     <row r="267">
@@ -7566,10 +7566,10 @@
         <v>4.47</v>
       </c>
       <c r="F267" t="n">
-        <v>36.9</v>
+        <v>36.83</v>
       </c>
       <c r="G267" t="n">
-        <v>446.92</v>
+        <v>445.66</v>
       </c>
     </row>
     <row r="268">
@@ -7586,13 +7586,13 @@
         <v>296</v>
       </c>
       <c r="E268" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="F268" t="n">
-        <v>37.48</v>
+        <v>37.41</v>
       </c>
       <c r="G268" t="n">
-        <v>457.86</v>
+        <v>456.57</v>
       </c>
     </row>
     <row r="269">
@@ -7609,13 +7609,13 @@
         <v>297</v>
       </c>
       <c r="E269" t="n">
-        <v>7.76</v>
+        <v>7.75</v>
       </c>
       <c r="F269" t="n">
-        <v>115.02</v>
+        <v>114.8</v>
       </c>
       <c r="G269" t="n">
-        <v>2529.18</v>
+        <v>2521.83</v>
       </c>
     </row>
     <row r="270">
@@ -7632,13 +7632,13 @@
         <v>298</v>
       </c>
       <c r="E270" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="F270" t="n">
-        <v>130.82</v>
+        <v>130.57</v>
       </c>
       <c r="G270" t="n">
-        <v>3074.41</v>
+        <v>3065.45</v>
       </c>
     </row>
     <row r="271">
@@ -7655,13 +7655,13 @@
         <v>299</v>
       </c>
       <c r="E271" t="n">
-        <v>9.97</v>
+        <v>9.96</v>
       </c>
       <c r="F271" t="n">
-        <v>191.87</v>
+        <v>191.49</v>
       </c>
       <c r="G271" t="n">
-        <v>5492.01</v>
+        <v>5475.91</v>
       </c>
     </row>
     <row r="272">
@@ -7681,10 +7681,10 @@
         <v>1.26</v>
       </c>
       <c r="F272" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="G272" t="n">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="273">
@@ -7707,7 +7707,7 @@
         <v>2.49</v>
       </c>
       <c r="G273" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="274">
@@ -7730,7 +7730,7 @@
         <v>2.61</v>
       </c>
       <c r="G274" t="n">
-        <v>6.7</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="275">
@@ -7753,7 +7753,7 @@
         <v>2.69</v>
       </c>
       <c r="G275" t="n">
-        <v>7.05</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="276">
@@ -7776,7 +7776,7 @@
         <v>3.26</v>
       </c>
       <c r="G276" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="277">
@@ -7799,7 +7799,7 @@
         <v>3.48</v>
       </c>
       <c r="G277" t="n">
-        <v>10.86</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="278">
@@ -7819,10 +7819,10 @@
         <v>1.73</v>
       </c>
       <c r="F278" t="n">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="G278" t="n">
-        <v>17.43</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="279">
@@ -7842,10 +7842,10 @@
         <v>1.94</v>
       </c>
       <c r="F279" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="G279" t="n">
-        <v>27.01</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="280">
@@ -7865,10 +7865,10 @@
         <v>2.07</v>
       </c>
       <c r="F280" t="n">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="G280" t="n">
-        <v>34.07</v>
+        <v>34.01</v>
       </c>
     </row>
     <row r="281">
@@ -7888,10 +7888,10 @@
         <v>2.3</v>
       </c>
       <c r="F281" t="n">
-        <v>8.89</v>
+        <v>8.88</v>
       </c>
       <c r="G281" t="n">
-        <v>49.15</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="282">
@@ -7911,10 +7911,10 @@
         <v>2.49</v>
       </c>
       <c r="F282" t="n">
-        <v>10.64</v>
+        <v>10.62</v>
       </c>
       <c r="G282" t="n">
-        <v>65.14</v>
+        <v>65</v>
       </c>
     </row>
     <row r="283">
@@ -7934,10 +7934,10 @@
         <v>2.75</v>
       </c>
       <c r="F283" t="n">
-        <v>13.18</v>
+        <v>13.16</v>
       </c>
       <c r="G283" t="n">
-        <v>91.09</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="284">
@@ -7957,10 +7957,10 @@
         <v>3.12</v>
       </c>
       <c r="F284" t="n">
-        <v>17.29</v>
+        <v>17.27</v>
       </c>
       <c r="G284" t="n">
-        <v>138.96</v>
+        <v>138.67</v>
       </c>
     </row>
     <row r="285">
@@ -7980,10 +7980,10 @@
         <v>3.69</v>
       </c>
       <c r="F285" t="n">
-        <v>24.62</v>
+        <v>24.58</v>
       </c>
       <c r="G285" t="n">
-        <v>239.95</v>
+        <v>239.42</v>
       </c>
     </row>
     <row r="286">
@@ -8003,10 +8003,10 @@
         <v>3.94</v>
       </c>
       <c r="F286" t="n">
-        <v>28.3</v>
+        <v>28.26</v>
       </c>
       <c r="G286" t="n">
-        <v>297.41</v>
+        <v>296.76</v>
       </c>
     </row>
     <row r="287">
@@ -8023,13 +8023,13 @@
         <v>316</v>
       </c>
       <c r="E287" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="F287" t="n">
-        <v>33.95</v>
+        <v>33.9</v>
       </c>
       <c r="G287" t="n">
-        <v>393.44</v>
+        <v>392.57</v>
       </c>
     </row>
     <row r="288">
@@ -8049,10 +8049,10 @@
         <v>4.65</v>
       </c>
       <c r="F288" t="n">
-        <v>40.07</v>
+        <v>40.01</v>
       </c>
       <c r="G288" t="n">
-        <v>507.12</v>
+        <v>505.99</v>
       </c>
     </row>
     <row r="289">
@@ -8072,10 +8072,10 @@
         <v>4.78</v>
       </c>
       <c r="F289" t="n">
-        <v>42.45</v>
+        <v>42.39</v>
       </c>
       <c r="G289" t="n">
-        <v>554.01</v>
+        <v>552.77</v>
       </c>
     </row>
     <row r="290">
@@ -8374,7 +8374,7 @@
         <v>15.67</v>
       </c>
       <c r="G302" t="n">
-        <v>119.31</v>
+        <v>119.32</v>
       </c>
     </row>
     <row r="303">
@@ -8443,7 +8443,7 @@
         <v>65.65</v>
       </c>
       <c r="G305" t="n">
-        <v>1077.96</v>
+        <v>1077.98</v>
       </c>
     </row>
     <row r="306">
@@ -8463,10 +8463,10 @@
         <v>6.76</v>
       </c>
       <c r="F306" t="n">
-        <v>86.64</v>
+        <v>86.65</v>
       </c>
       <c r="G306" t="n">
-        <v>1644.67</v>
+        <v>1644.69</v>
       </c>
     </row>
     <row r="307">
@@ -8489,7 +8489,7 @@
         <v>184.32</v>
       </c>
       <c r="G307" t="n">
-        <v>5168.26</v>
+        <v>5168.34</v>
       </c>
     </row>
     <row r="308">
@@ -8788,7 +8788,7 @@
         <v>15.4</v>
       </c>
       <c r="G320" t="n">
-        <v>116.09</v>
+        <v>116.08</v>
       </c>
     </row>
     <row r="321">
@@ -8834,7 +8834,7 @@
         <v>25.46</v>
       </c>
       <c r="G322" t="n">
-        <v>252.72</v>
+        <v>252.71</v>
       </c>
     </row>
     <row r="323">
@@ -8880,7 +8880,7 @@
         <v>38.24</v>
       </c>
       <c r="G324" t="n">
-        <v>472.09</v>
+        <v>472.08</v>
       </c>
     </row>
     <row r="325">
@@ -8903,7 +8903,7 @@
         <v>63.33</v>
       </c>
       <c r="G325" t="n">
-        <v>1020.65</v>
+        <v>1020.63</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -2299,10 +2299,10 @@
         <v>1.37</v>
       </c>
       <c r="F38" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="G38" t="n">
-        <v>6.85</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="39">
@@ -2319,13 +2319,13 @@
         <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="F39" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="G39" t="n">
-        <v>10.75</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="40">
@@ -2342,13 +2342,13 @@
         <v>50</v>
       </c>
       <c r="E40" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="F40" t="n">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="G40" t="n">
-        <v>18.83</v>
+        <v>19.09</v>
       </c>
     </row>
     <row r="41">
@@ -2365,13 +2365,13 @@
         <v>51</v>
       </c>
       <c r="E41" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="F41" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="G41" t="n">
-        <v>22.53</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="42">
@@ -2388,13 +2388,13 @@
         <v>52</v>
       </c>
       <c r="E42" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="F42" t="n">
-        <v>6.23</v>
+        <v>6.28</v>
       </c>
       <c r="G42" t="n">
-        <v>27.92</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="43">
@@ -2411,13 +2411,13 @@
         <v>53</v>
       </c>
       <c r="E43" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="F43" t="n">
-        <v>6.9</v>
+        <v>6.96</v>
       </c>
       <c r="G43" t="n">
-        <v>32.85</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="44">
@@ -2434,13 +2434,13 @@
         <v>54</v>
       </c>
       <c r="E44" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="F44" t="n">
-        <v>7.13</v>
+        <v>7.19</v>
       </c>
       <c r="G44" t="n">
-        <v>34.61</v>
+        <v>35.11</v>
       </c>
     </row>
     <row r="45">
@@ -2457,13 +2457,13 @@
         <v>55</v>
       </c>
       <c r="E45" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="F45" t="n">
-        <v>7.17</v>
+        <v>7.24</v>
       </c>
       <c r="G45" t="n">
-        <v>34.94</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="46">
@@ -2480,13 +2480,13 @@
         <v>56</v>
       </c>
       <c r="E46" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="F46" t="n">
-        <v>9.3</v>
+        <v>9.38</v>
       </c>
       <c r="G46" t="n">
-        <v>52.7</v>
+        <v>53.49</v>
       </c>
     </row>
     <row r="47">
@@ -2503,13 +2503,13 @@
         <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="F47" t="n">
-        <v>17.44</v>
+        <v>17.61</v>
       </c>
       <c r="G47" t="n">
-        <v>140.82</v>
+        <v>143.03</v>
       </c>
     </row>
     <row r="48">
@@ -2526,13 +2526,13 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="F48" t="n">
-        <v>18.26</v>
+        <v>18.44</v>
       </c>
       <c r="G48" t="n">
-        <v>151.23</v>
+        <v>153.61</v>
       </c>
     </row>
     <row r="49">
@@ -2549,13 +2549,13 @@
         <v>59</v>
       </c>
       <c r="E49" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="F49" t="n">
-        <v>35.52</v>
+        <v>35.89</v>
       </c>
       <c r="G49" t="n">
-        <v>421.55</v>
+        <v>428.37</v>
       </c>
     </row>
     <row r="50">
@@ -2572,13 +2572,13 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>4.64</v>
+        <v>4.66</v>
       </c>
       <c r="F50" t="n">
-        <v>39.84</v>
+        <v>40.26</v>
       </c>
       <c r="G50" t="n">
-        <v>502.69</v>
+        <v>510.86</v>
       </c>
     </row>
     <row r="51">
@@ -2595,13 +2595,13 @@
         <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>6.87</v>
+        <v>6.91</v>
       </c>
       <c r="F51" t="n">
-        <v>89.8</v>
+        <v>90.78</v>
       </c>
       <c r="G51" t="n">
-        <v>1736.73</v>
+        <v>1765.57</v>
       </c>
     </row>
     <row r="52">
@@ -2618,13 +2618,13 @@
         <v>62</v>
       </c>
       <c r="E52" t="n">
-        <v>7.15</v>
+        <v>7.19</v>
       </c>
       <c r="F52" t="n">
-        <v>97.36</v>
+        <v>98.42</v>
       </c>
       <c r="G52" t="n">
-        <v>1963.57</v>
+        <v>1996.24</v>
       </c>
     </row>
     <row r="53">
@@ -2641,13 +2641,13 @@
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="F53" t="n">
-        <v>98.21</v>
+        <v>99.28</v>
       </c>
       <c r="G53" t="n">
-        <v>1989.67</v>
+        <v>2022.77</v>
       </c>
     </row>
     <row r="54">
@@ -2664,13 +2664,13 @@
         <v>64</v>
       </c>
       <c r="E54" t="n">
-        <v>10.53</v>
+        <v>10.58</v>
       </c>
       <c r="F54" t="n">
-        <v>214.45</v>
+        <v>216.83</v>
       </c>
       <c r="G54" t="n">
-        <v>6499.08</v>
+        <v>6608.61</v>
       </c>
     </row>
     <row r="55">
@@ -2687,13 +2687,13 @@
         <v>65</v>
       </c>
       <c r="E55" t="n">
-        <v>11.85</v>
+        <v>11.91</v>
       </c>
       <c r="F55" t="n">
-        <v>272.83</v>
+        <v>275.87</v>
       </c>
       <c r="G55" t="n">
-        <v>9352.78</v>
+        <v>9510.88</v>
       </c>
     </row>
     <row r="56">
@@ -2716,7 +2716,7 @@
         <v>1.42</v>
       </c>
       <c r="G56" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="57">
@@ -2739,7 +2739,7 @@
         <v>1.99</v>
       </c>
       <c r="G57" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="58">
@@ -2759,10 +2759,10 @@
         <v>1.31</v>
       </c>
       <c r="F58" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="G58" t="n">
-        <v>5.59</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="59">
@@ -2782,10 +2782,10 @@
         <v>1.4</v>
       </c>
       <c r="F59" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="G59" t="n">
-        <v>7.59</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="60">
@@ -2805,10 +2805,10 @@
         <v>1.47</v>
       </c>
       <c r="F60" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="G60" t="n">
-        <v>9.2</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="61">
@@ -2828,10 +2828,10 @@
         <v>1.51</v>
       </c>
       <c r="F61" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="G61" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="62">
@@ -2851,10 +2851,10 @@
         <v>1.51</v>
       </c>
       <c r="F62" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="G62" t="n">
-        <v>10.27</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="63">
@@ -2874,10 +2874,10 @@
         <v>1.63</v>
       </c>
       <c r="F63" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="G63" t="n">
-        <v>13.85</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="64">
@@ -2897,10 +2897,10 @@
         <v>1.79</v>
       </c>
       <c r="F64" t="n">
-        <v>5.03</v>
+        <v>5.05</v>
       </c>
       <c r="G64" t="n">
-        <v>19.79</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="65">
@@ -2920,10 +2920,10 @@
         <v>1.81</v>
       </c>
       <c r="F65" t="n">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="G65" t="n">
-        <v>20.81</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="66">
@@ -2940,13 +2940,13 @@
         <v>77</v>
       </c>
       <c r="E66" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="F66" t="n">
-        <v>5.89</v>
+        <v>5.92</v>
       </c>
       <c r="G66" t="n">
-        <v>25.55</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="67">
@@ -2963,13 +2963,13 @@
         <v>78</v>
       </c>
       <c r="E67" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="F67" t="n">
-        <v>6.92</v>
+        <v>6.96</v>
       </c>
       <c r="G67" t="n">
-        <v>33.03</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="68">
@@ -2986,13 +2986,13 @@
         <v>79</v>
       </c>
       <c r="E68" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="F68" t="n">
-        <v>14.4</v>
+        <v>14.49</v>
       </c>
       <c r="G68" t="n">
-        <v>104.62</v>
+        <v>105.55</v>
       </c>
     </row>
     <row r="69">
@@ -3009,13 +3009,13 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="F69" t="n">
-        <v>17.16</v>
+        <v>17.25</v>
       </c>
       <c r="G69" t="n">
-        <v>137.28</v>
+        <v>138.52</v>
       </c>
     </row>
     <row r="70">
@@ -3032,13 +3032,13 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="F70" t="n">
-        <v>18.15</v>
+        <v>18.26</v>
       </c>
       <c r="G70" t="n">
-        <v>149.87</v>
+        <v>151.22</v>
       </c>
     </row>
     <row r="71">
@@ -3055,13 +3055,13 @@
         <v>82</v>
       </c>
       <c r="E71" t="n">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="F71" t="n">
-        <v>33.51</v>
+        <v>33.71</v>
       </c>
       <c r="G71" t="n">
-        <v>385.61</v>
+        <v>389.18</v>
       </c>
     </row>
     <row r="72">
@@ -3078,13 +3078,13 @@
         <v>83</v>
       </c>
       <c r="E72" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="F72" t="n">
-        <v>42.57</v>
+        <v>42.83</v>
       </c>
       <c r="G72" t="n">
-        <v>556.39</v>
+        <v>561.59</v>
       </c>
     </row>
     <row r="73">
@@ -3101,13 +3101,13 @@
         <v>84</v>
       </c>
       <c r="E73" t="n">
-        <v>7.53</v>
+        <v>7.55</v>
       </c>
       <c r="F73" t="n">
-        <v>108.24</v>
+        <v>108.92</v>
       </c>
       <c r="G73" t="n">
-        <v>2306.35</v>
+        <v>2328.41</v>
       </c>
     </row>
     <row r="74">
@@ -3958,7 +3958,7 @@
         <v>1.5</v>
       </c>
       <c r="G110" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="111">
@@ -4001,10 +4001,10 @@
         <v>1.26</v>
       </c>
       <c r="F112" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="G112" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="113">
@@ -4027,7 +4027,7 @@
         <v>2.37</v>
       </c>
       <c r="G113" t="n">
-        <v>5.68</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="114">
@@ -4050,7 +4050,7 @@
         <v>3.51</v>
       </c>
       <c r="G114" t="n">
-        <v>10.99</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="115">
@@ -4070,10 +4070,10 @@
         <v>1.55</v>
       </c>
       <c r="F115" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="G115" t="n">
-        <v>11.51</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="116">
@@ -4096,7 +4096,7 @@
         <v>3.69</v>
       </c>
       <c r="G116" t="n">
-        <v>11.97</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="117">
@@ -4119,7 +4119,7 @@
         <v>4.06</v>
       </c>
       <c r="G117" t="n">
-        <v>13.99</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="118">
@@ -4139,10 +4139,10 @@
         <v>2.46</v>
       </c>
       <c r="F118" t="n">
-        <v>10.32</v>
+        <v>10.31</v>
       </c>
       <c r="G118" t="n">
-        <v>62.15</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="119">
@@ -4159,13 +4159,13 @@
         <v>135</v>
       </c>
       <c r="E119" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="F119" t="n">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="G119" t="n">
-        <v>79.71</v>
+        <v>79.57</v>
       </c>
     </row>
     <row r="120">
@@ -4182,13 +4182,13 @@
         <v>136</v>
       </c>
       <c r="E120" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="F120" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="G120" t="n">
-        <v>82.86</v>
+        <v>82.72</v>
       </c>
     </row>
     <row r="121">
@@ -4208,10 +4208,10 @@
         <v>2.82</v>
       </c>
       <c r="F121" t="n">
-        <v>13.86</v>
+        <v>13.84</v>
       </c>
       <c r="G121" t="n">
-        <v>98.48</v>
+        <v>98.31</v>
       </c>
     </row>
     <row r="122">
@@ -4231,10 +4231,10 @@
         <v>2.84</v>
       </c>
       <c r="F122" t="n">
-        <v>14.07</v>
+        <v>14.06</v>
       </c>
       <c r="G122" t="n">
-        <v>100.91</v>
+        <v>100.73</v>
       </c>
     </row>
     <row r="123">
@@ -4251,13 +4251,13 @@
         <v>139</v>
       </c>
       <c r="E123" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="F123" t="n">
-        <v>23.06</v>
+        <v>23.03</v>
       </c>
       <c r="G123" t="n">
-        <v>216.98</v>
+        <v>216.58</v>
       </c>
     </row>
     <row r="124">
@@ -4277,10 +4277,10 @@
         <v>3.97</v>
       </c>
       <c r="F124" t="n">
-        <v>28.81</v>
+        <v>28.77</v>
       </c>
       <c r="G124" t="n">
-        <v>305.64</v>
+        <v>305.07</v>
       </c>
     </row>
     <row r="125">
@@ -4300,10 +4300,10 @@
         <v>4.95</v>
       </c>
       <c r="F125" t="n">
-        <v>45.63</v>
+        <v>45.58</v>
       </c>
       <c r="G125" t="n">
-        <v>618.82</v>
+        <v>617.65</v>
       </c>
     </row>
     <row r="126">
@@ -4323,10 +4323,10 @@
         <v>6.09</v>
       </c>
       <c r="F126" t="n">
-        <v>70.01</v>
+        <v>69.93</v>
       </c>
       <c r="G126" t="n">
-        <v>1189.14</v>
+        <v>1186.86</v>
       </c>
     </row>
     <row r="127">
@@ -4343,13 +4343,13 @@
         <v>143</v>
       </c>
       <c r="E127" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="F127" t="n">
-        <v>200.8</v>
+        <v>200.54</v>
       </c>
       <c r="G127" t="n">
-        <v>5883.63</v>
+        <v>5872.13</v>
       </c>
     </row>
     <row r="128">
@@ -4372,7 +4372,7 @@
         <v>1.9</v>
       </c>
       <c r="G128" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="129">
@@ -4395,7 +4395,7 @@
         <v>2.72</v>
       </c>
       <c r="G129" t="n">
-        <v>7.18</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="130">
@@ -4415,10 +4415,10 @@
         <v>1.66</v>
       </c>
       <c r="F130" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="G130" t="n">
-        <v>14.88</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="131">
@@ -4441,7 +4441,7 @@
         <v>4.69</v>
       </c>
       <c r="G131" t="n">
-        <v>17.7</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="132">
@@ -4461,10 +4461,10 @@
         <v>1.86</v>
       </c>
       <c r="F132" t="n">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
       <c r="G132" t="n">
-        <v>22.89</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="133">
@@ -4484,10 +4484,10 @@
         <v>1.94</v>
       </c>
       <c r="F133" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="G133" t="n">
-        <v>26.97</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="134">
@@ -4507,10 +4507,10 @@
         <v>2.37</v>
       </c>
       <c r="F134" t="n">
-        <v>9.49</v>
+        <v>9.47</v>
       </c>
       <c r="G134" t="n">
-        <v>54.43</v>
+        <v>54.29</v>
       </c>
     </row>
     <row r="135">
@@ -4530,10 +4530,10 @@
         <v>2.42</v>
       </c>
       <c r="F135" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
       <c r="G135" t="n">
-        <v>58.5</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="136">
@@ -4553,10 +4553,10 @@
         <v>2.54</v>
       </c>
       <c r="F136" t="n">
-        <v>11.09</v>
+        <v>11.07</v>
       </c>
       <c r="G136" t="n">
-        <v>69.52</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="137">
@@ -4573,13 +4573,13 @@
         <v>154</v>
       </c>
       <c r="E137" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="F137" t="n">
-        <v>14.59</v>
+        <v>14.57</v>
       </c>
       <c r="G137" t="n">
-        <v>106.75</v>
+        <v>106.46</v>
       </c>
     </row>
     <row r="138">
@@ -4599,10 +4599,10 @@
         <v>3.85</v>
       </c>
       <c r="F138" t="n">
-        <v>26.99</v>
+        <v>26.95</v>
       </c>
       <c r="G138" t="n">
-        <v>276.57</v>
+        <v>275.8</v>
       </c>
     </row>
     <row r="139">
@@ -4619,13 +4619,13 @@
         <v>156</v>
       </c>
       <c r="E139" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="F139" t="n">
-        <v>30.38</v>
+        <v>30.33</v>
       </c>
       <c r="G139" t="n">
-        <v>331.69</v>
+        <v>330.76</v>
       </c>
     </row>
     <row r="140">
@@ -4645,10 +4645,10 @@
         <v>4.7</v>
       </c>
       <c r="F140" t="n">
-        <v>40.99</v>
+        <v>40.91</v>
       </c>
       <c r="G140" t="n">
-        <v>525.08</v>
+        <v>523.6</v>
       </c>
     </row>
     <row r="141">
@@ -4665,13 +4665,13 @@
         <v>158</v>
       </c>
       <c r="E141" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="F141" t="n">
-        <v>42.34</v>
+        <v>42.27</v>
       </c>
       <c r="G141" t="n">
-        <v>551.9</v>
+        <v>550.34</v>
       </c>
     </row>
     <row r="142">
@@ -4691,10 +4691,10 @@
         <v>4.79</v>
       </c>
       <c r="F142" t="n">
-        <v>42.58</v>
+        <v>42.5</v>
       </c>
       <c r="G142" t="n">
-        <v>556.54</v>
+        <v>554.98</v>
       </c>
     </row>
     <row r="143">
@@ -4711,13 +4711,13 @@
         <v>160</v>
       </c>
       <c r="E143" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="F143" t="n">
-        <v>125.74</v>
+        <v>125.5</v>
       </c>
       <c r="G143" t="n">
-        <v>2895.33</v>
+        <v>2886.97</v>
       </c>
     </row>
     <row r="144">
@@ -4734,13 +4734,13 @@
         <v>161</v>
       </c>
       <c r="E144" t="n">
-        <v>12.24</v>
+        <v>12.22</v>
       </c>
       <c r="F144" t="n">
-        <v>291.12</v>
+        <v>290.56</v>
       </c>
       <c r="G144" t="n">
-        <v>10316.44</v>
+        <v>10286.29</v>
       </c>
     </row>
     <row r="145">
@@ -4757,13 +4757,13 @@
         <v>162</v>
       </c>
       <c r="E145" t="n">
-        <v>14.38</v>
+        <v>14.36</v>
       </c>
       <c r="F145" t="n">
-        <v>403.63</v>
+        <v>402.85</v>
       </c>
       <c r="G145" t="n">
-        <v>16897.1</v>
+        <v>16847.57</v>
       </c>
     </row>
     <row r="146">
@@ -4783,10 +4783,10 @@
         <v>1.29</v>
       </c>
       <c r="F146" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="G146" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="147">
@@ -4806,10 +4806,10 @@
         <v>1.32</v>
       </c>
       <c r="F147" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="G147" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="148">
@@ -4826,13 +4826,13 @@
         <v>167</v>
       </c>
       <c r="E148" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="F148" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="G148" t="n">
-        <v>9.57</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="149">
@@ -4849,13 +4849,13 @@
         <v>168</v>
       </c>
       <c r="E149" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="F149" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="G149" t="n">
-        <v>12.76</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="150">
@@ -4872,13 +4872,13 @@
         <v>169</v>
       </c>
       <c r="E150" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="F150" t="n">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
       <c r="G150" t="n">
-        <v>18.07</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="151">
@@ -4898,10 +4898,10 @@
         <v>1.8</v>
       </c>
       <c r="F151" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
       <c r="G151" t="n">
-        <v>20.26</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="152">
@@ -4918,13 +4918,13 @@
         <v>171</v>
       </c>
       <c r="E152" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="F152" t="n">
-        <v>5.4</v>
+        <v>5.43</v>
       </c>
       <c r="G152" t="n">
-        <v>22.18</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="153">
@@ -4944,10 +4944,10 @@
         <v>1.98</v>
       </c>
       <c r="F153" t="n">
-        <v>6.34</v>
+        <v>6.38</v>
       </c>
       <c r="G153" t="n">
-        <v>28.71</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="154">
@@ -4964,13 +4964,13 @@
         <v>173</v>
       </c>
       <c r="E154" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="F154" t="n">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="G154" t="n">
-        <v>29.18</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="155">
@@ -4987,13 +4987,13 @@
         <v>174</v>
       </c>
       <c r="E155" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="F155" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
       <c r="G155" t="n">
-        <v>52.31</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="156">
@@ -5010,13 +5010,13 @@
         <v>175</v>
       </c>
       <c r="E156" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="F156" t="n">
-        <v>18.62</v>
+        <v>18.77</v>
       </c>
       <c r="G156" t="n">
-        <v>155.85</v>
+        <v>157.79</v>
       </c>
     </row>
     <row r="157">
@@ -5033,13 +5033,13 @@
         <v>176</v>
       </c>
       <c r="E157" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="F157" t="n">
-        <v>21.95</v>
+        <v>22.13</v>
       </c>
       <c r="G157" t="n">
-        <v>201.07</v>
+        <v>203.59</v>
       </c>
     </row>
     <row r="158">
@@ -5056,13 +5056,13 @@
         <v>177</v>
       </c>
       <c r="E158" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="F158" t="n">
-        <v>24.92</v>
+        <v>25.12</v>
       </c>
       <c r="G158" t="n">
-        <v>244.52</v>
+        <v>247.62</v>
       </c>
     </row>
     <row r="159">
@@ -5079,13 +5079,13 @@
         <v>178</v>
       </c>
       <c r="E159" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="F159" t="n">
-        <v>27.72</v>
+        <v>27.95</v>
       </c>
       <c r="G159" t="n">
-        <v>288.08</v>
+        <v>291.74</v>
       </c>
     </row>
     <row r="160">
@@ -5102,13 +5102,13 @@
         <v>179</v>
       </c>
       <c r="E160" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="F160" t="n">
-        <v>29.98</v>
+        <v>30.23</v>
       </c>
       <c r="G160" t="n">
-        <v>324.95</v>
+        <v>329.09</v>
       </c>
     </row>
     <row r="161">
@@ -5125,13 +5125,13 @@
         <v>180</v>
       </c>
       <c r="E161" t="n">
-        <v>5.1</v>
+        <v>5.12</v>
       </c>
       <c r="F161" t="n">
-        <v>48.54</v>
+        <v>48.95</v>
       </c>
       <c r="G161" t="n">
-        <v>680</v>
+        <v>688.81</v>
       </c>
     </row>
     <row r="162">
@@ -5148,13 +5148,13 @@
         <v>181</v>
       </c>
       <c r="E162" t="n">
-        <v>7.18</v>
+        <v>7.21</v>
       </c>
       <c r="F162" t="n">
-        <v>98.25</v>
+        <v>99.1</v>
       </c>
       <c r="G162" t="n">
-        <v>1990.75</v>
+        <v>2017.02</v>
       </c>
     </row>
     <row r="163">
@@ -5171,13 +5171,13 @@
         <v>182</v>
       </c>
       <c r="E163" t="n">
-        <v>9.59</v>
+        <v>9.63</v>
       </c>
       <c r="F163" t="n">
-        <v>177.45</v>
+        <v>179.01</v>
       </c>
       <c r="G163" t="n">
-        <v>4879.55</v>
+        <v>4944.6</v>
       </c>
     </row>
     <row r="164">
@@ -5200,7 +5200,7 @@
         <v>1.52</v>
       </c>
       <c r="G164" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="165">
@@ -5217,13 +5217,13 @@
         <v>185</v>
       </c>
       <c r="E165" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="F165" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="G165" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="166">
@@ -5243,10 +5243,10 @@
         <v>1.37</v>
       </c>
       <c r="F166" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="G166" t="n">
-        <v>6.86</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="167">
@@ -5263,13 +5263,13 @@
         <v>187</v>
       </c>
       <c r="E167" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="F167" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="G167" t="n">
-        <v>8.84</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="168">
@@ -5286,13 +5286,13 @@
         <v>188</v>
       </c>
       <c r="E168" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="F168" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
       <c r="G168" t="n">
-        <v>15.18</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="169">
@@ -5312,10 +5312,10 @@
         <v>1.73</v>
       </c>
       <c r="F169" t="n">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="G169" t="n">
-        <v>17.52</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="170">
@@ -5332,13 +5332,13 @@
         <v>190</v>
       </c>
       <c r="E170" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="F170" t="n">
-        <v>5.53</v>
+        <v>5.57</v>
       </c>
       <c r="G170" t="n">
-        <v>23.07</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="171">
@@ -5355,13 +5355,13 @@
         <v>191</v>
       </c>
       <c r="E171" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="F171" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="G171" t="n">
-        <v>30.81</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="172">
@@ -5378,13 +5378,13 @@
         <v>192</v>
       </c>
       <c r="E172" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="F172" t="n">
-        <v>15.24</v>
+        <v>15.35</v>
       </c>
       <c r="G172" t="n">
-        <v>114.22</v>
+        <v>115.53</v>
       </c>
     </row>
     <row r="173">
@@ -5401,13 +5401,13 @@
         <v>193</v>
       </c>
       <c r="E173" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="F173" t="n">
-        <v>25.79</v>
+        <v>25.99</v>
       </c>
       <c r="G173" t="n">
-        <v>257.78</v>
+        <v>260.83</v>
       </c>
     </row>
     <row r="174">
@@ -5424,13 +5424,13 @@
         <v>194</v>
       </c>
       <c r="E174" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="F174" t="n">
-        <v>26.74</v>
+        <v>26.94</v>
       </c>
       <c r="G174" t="n">
-        <v>272.52</v>
+        <v>275.75</v>
       </c>
     </row>
     <row r="175">
@@ -5447,13 +5447,13 @@
         <v>195</v>
       </c>
       <c r="E175" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="F175" t="n">
-        <v>30.73</v>
+        <v>30.97</v>
       </c>
       <c r="G175" t="n">
-        <v>337.61</v>
+        <v>341.64</v>
       </c>
     </row>
     <row r="176">
@@ -5470,13 +5470,13 @@
         <v>196</v>
       </c>
       <c r="E176" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="F176" t="n">
-        <v>34.6</v>
+        <v>34.87</v>
       </c>
       <c r="G176" t="n">
-        <v>404.95</v>
+        <v>409.81</v>
       </c>
     </row>
     <row r="177">
@@ -5493,13 +5493,13 @@
         <v>197</v>
       </c>
       <c r="E177" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="F177" t="n">
-        <v>36.55</v>
+        <v>36.84</v>
       </c>
       <c r="G177" t="n">
-        <v>440.59</v>
+        <v>445.88</v>
       </c>
     </row>
     <row r="178">
@@ -5516,13 +5516,13 @@
         <v>198</v>
       </c>
       <c r="E178" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="F178" t="n">
-        <v>36.71</v>
+        <v>37</v>
       </c>
       <c r="G178" t="n">
-        <v>443.52</v>
+        <v>448.85</v>
       </c>
     </row>
     <row r="179">
@@ -5539,13 +5539,13 @@
         <v>199</v>
       </c>
       <c r="E179" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="F179" t="n">
-        <v>45.13</v>
+        <v>45.48</v>
       </c>
       <c r="G179" t="n">
-        <v>608.31</v>
+        <v>615.67</v>
       </c>
     </row>
     <row r="180">
@@ -5562,13 +5562,13 @@
         <v>200</v>
       </c>
       <c r="E180" t="n">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="F180" t="n">
-        <v>54.12</v>
+        <v>54.55</v>
       </c>
       <c r="G180" t="n">
-        <v>803.02</v>
+        <v>812.8</v>
       </c>
     </row>
     <row r="181">
@@ -5585,13 +5585,13 @@
         <v>201</v>
       </c>
       <c r="E181" t="n">
-        <v>6.35</v>
+        <v>6.38</v>
       </c>
       <c r="F181" t="n">
-        <v>76.34</v>
+        <v>76.95</v>
       </c>
       <c r="G181" t="n">
-        <v>1356.41</v>
+        <v>1373.07</v>
       </c>
     </row>
     <row r="182">
@@ -6439,10 +6439,10 @@
         <v>1.27</v>
       </c>
       <c r="F218" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="G218" t="n">
-        <v>4.95</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="219">
@@ -6462,10 +6462,10 @@
         <v>1.28</v>
       </c>
       <c r="F219" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="G219" t="n">
-        <v>5.18</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="220">
@@ -6482,13 +6482,13 @@
         <v>245</v>
       </c>
       <c r="E220" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="F220" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="G220" t="n">
-        <v>8.65</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="221">
@@ -6505,13 +6505,13 @@
         <v>246</v>
       </c>
       <c r="E221" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="F221" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="G221" t="n">
-        <v>10.32</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="222">
@@ -6531,10 +6531,10 @@
         <v>1.51</v>
       </c>
       <c r="F222" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="G222" t="n">
-        <v>10.39</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="223">
@@ -6551,13 +6551,13 @@
         <v>248</v>
       </c>
       <c r="E223" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="F223" t="n">
-        <v>4.44</v>
+        <v>4.39</v>
       </c>
       <c r="G223" t="n">
-        <v>16.16</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="224">
@@ -6574,13 +6574,13 @@
         <v>249</v>
       </c>
       <c r="E224" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="F224" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="G224" t="n">
-        <v>17.52</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="225">
@@ -6597,13 +6597,13 @@
         <v>250</v>
       </c>
       <c r="E225" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="F225" t="n">
-        <v>5.6</v>
+        <v>5.54</v>
       </c>
       <c r="G225" t="n">
-        <v>23.55</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="226">
@@ -6620,13 +6620,13 @@
         <v>251</v>
       </c>
       <c r="E226" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="F226" t="n">
-        <v>5.9</v>
+        <v>5.84</v>
       </c>
       <c r="G226" t="n">
-        <v>25.6</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="227">
@@ -6643,13 +6643,13 @@
         <v>252</v>
       </c>
       <c r="E227" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="F227" t="n">
-        <v>6.32</v>
+        <v>6.25</v>
       </c>
       <c r="G227" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="228">
@@ -6666,13 +6666,13 @@
         <v>253</v>
       </c>
       <c r="E228" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="F228" t="n">
-        <v>6.4</v>
+        <v>6.32</v>
       </c>
       <c r="G228" t="n">
-        <v>29.13</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="229">
@@ -6689,13 +6689,13 @@
         <v>254</v>
       </c>
       <c r="E229" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="F229" t="n">
-        <v>12.39</v>
+        <v>12.24</v>
       </c>
       <c r="G229" t="n">
-        <v>82.75</v>
+        <v>81.19</v>
       </c>
     </row>
     <row r="230">
@@ -6712,13 +6712,13 @@
         <v>255</v>
       </c>
       <c r="E230" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="F230" t="n">
-        <v>13.2</v>
+        <v>13.04</v>
       </c>
       <c r="G230" t="n">
-        <v>91.33</v>
+        <v>89.6</v>
       </c>
     </row>
     <row r="231">
@@ -6735,13 +6735,13 @@
         <v>256</v>
       </c>
       <c r="E231" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="F231" t="n">
-        <v>13.36</v>
+        <v>13.2</v>
       </c>
       <c r="G231" t="n">
-        <v>93.06</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="232">
@@ -6758,13 +6758,13 @@
         <v>257</v>
       </c>
       <c r="E232" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="F232" t="n">
-        <v>28.02</v>
+        <v>27.66</v>
       </c>
       <c r="G232" t="n">
-        <v>292.95</v>
+        <v>287.17</v>
       </c>
     </row>
     <row r="233">
@@ -6781,13 +6781,13 @@
         <v>258</v>
       </c>
       <c r="E233" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="F233" t="n">
-        <v>38.93</v>
+        <v>38.42</v>
       </c>
       <c r="G233" t="n">
-        <v>485.14</v>
+        <v>475.44</v>
       </c>
     </row>
     <row r="234">
@@ -6804,13 +6804,13 @@
         <v>259</v>
       </c>
       <c r="E234" t="n">
-        <v>5.81</v>
+        <v>5.77</v>
       </c>
       <c r="F234" t="n">
-        <v>63.55</v>
+        <v>62.7</v>
       </c>
       <c r="G234" t="n">
-        <v>1026.05</v>
+        <v>1005.23</v>
       </c>
     </row>
     <row r="235">
@@ -6827,13 +6827,13 @@
         <v>260</v>
       </c>
       <c r="E235" t="n">
-        <v>7.47</v>
+        <v>7.42</v>
       </c>
       <c r="F235" t="n">
-        <v>106.47</v>
+        <v>105.02</v>
       </c>
       <c r="G235" t="n">
-        <v>2249.23</v>
+        <v>2203.06</v>
       </c>
     </row>
     <row r="236">
@@ -6850,13 +6850,13 @@
         <v>262</v>
       </c>
       <c r="E236" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="F236" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G236" t="n">
-        <v>3.85</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="237">
@@ -6876,10 +6876,10 @@
         <v>1.45</v>
       </c>
       <c r="F237" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="G237" t="n">
-        <v>8.86</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="238">
@@ -6899,10 +6899,10 @@
         <v>1.56</v>
       </c>
       <c r="F238" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="G238" t="n">
-        <v>11.93</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="239">
@@ -6919,13 +6919,13 @@
         <v>265</v>
       </c>
       <c r="E239" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="F239" t="n">
-        <v>4.6</v>
+        <v>4.54</v>
       </c>
       <c r="G239" t="n">
-        <v>17.13</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="240">
@@ -6942,13 +6942,13 @@
         <v>266</v>
       </c>
       <c r="E240" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="F240" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="G240" t="n">
-        <v>17.27</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="241">
@@ -6965,13 +6965,13 @@
         <v>267</v>
       </c>
       <c r="E241" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="F241" t="n">
-        <v>5.02</v>
+        <v>4.96</v>
       </c>
       <c r="G241" t="n">
-        <v>19.75</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="242">
@@ -6988,13 +6988,13 @@
         <v>268</v>
       </c>
       <c r="E242" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="F242" t="n">
-        <v>5.23</v>
+        <v>5.17</v>
       </c>
       <c r="G242" t="n">
-        <v>21.1</v>
+        <v>20.67</v>
       </c>
     </row>
     <row r="243">
@@ -7011,13 +7011,13 @@
         <v>269</v>
       </c>
       <c r="E243" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="F243" t="n">
-        <v>6.5</v>
+        <v>6.41</v>
       </c>
       <c r="G243" t="n">
-        <v>29.86</v>
+        <v>29.23</v>
       </c>
     </row>
     <row r="244">
@@ -7034,13 +7034,13 @@
         <v>270</v>
       </c>
       <c r="E244" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="F244" t="n">
-        <v>6.71</v>
+        <v>6.62</v>
       </c>
       <c r="G244" t="n">
-        <v>31.41</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="245">
@@ -7057,13 +7057,13 @@
         <v>271</v>
       </c>
       <c r="E245" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="F245" t="n">
-        <v>10.29</v>
+        <v>10.15</v>
       </c>
       <c r="G245" t="n">
-        <v>61.86</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="246">
@@ -7080,13 +7080,13 @@
         <v>272</v>
       </c>
       <c r="E246" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="F246" t="n">
-        <v>19</v>
+        <v>18.72</v>
       </c>
       <c r="G246" t="n">
-        <v>160.85</v>
+        <v>157.16</v>
       </c>
     </row>
     <row r="247">
@@ -7103,13 +7103,13 @@
         <v>273</v>
       </c>
       <c r="E247" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="F247" t="n">
-        <v>19.17</v>
+        <v>18.89</v>
       </c>
       <c r="G247" t="n">
-        <v>163.11</v>
+        <v>159.36</v>
       </c>
     </row>
     <row r="248">
@@ -7126,13 +7126,13 @@
         <v>274</v>
       </c>
       <c r="E248" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="F248" t="n">
-        <v>23.81</v>
+        <v>23.45</v>
       </c>
       <c r="G248" t="n">
-        <v>228</v>
+        <v>222.7</v>
       </c>
     </row>
     <row r="249">
@@ -7149,13 +7149,13 @@
         <v>275</v>
       </c>
       <c r="E249" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="F249" t="n">
-        <v>29.04</v>
+        <v>28.59</v>
       </c>
       <c r="G249" t="n">
-        <v>309.41</v>
+        <v>302.16</v>
       </c>
     </row>
     <row r="250">
@@ -7172,13 +7172,13 @@
         <v>276</v>
       </c>
       <c r="E250" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="F250" t="n">
-        <v>52.36</v>
+        <v>51.54</v>
       </c>
       <c r="G250" t="n">
-        <v>763.51</v>
+        <v>745.25</v>
       </c>
     </row>
     <row r="251">
@@ -7195,13 +7195,13 @@
         <v>277</v>
       </c>
       <c r="E251" t="n">
-        <v>5.92</v>
+        <v>5.87</v>
       </c>
       <c r="F251" t="n">
-        <v>66.04</v>
+        <v>64.99</v>
       </c>
       <c r="G251" t="n">
-        <v>1087.79</v>
+        <v>1061.6</v>
       </c>
     </row>
     <row r="252">
@@ -7218,13 +7218,13 @@
         <v>278</v>
       </c>
       <c r="E252" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="F252" t="n">
-        <v>71.87</v>
+        <v>70.73</v>
       </c>
       <c r="G252" t="n">
-        <v>1237.48</v>
+        <v>1207.62</v>
       </c>
     </row>
     <row r="253">
@@ -7241,13 +7241,13 @@
         <v>279</v>
       </c>
       <c r="E253" t="n">
-        <v>9.93</v>
+        <v>9.85</v>
       </c>
       <c r="F253" t="n">
-        <v>190.56</v>
+        <v>187.45</v>
       </c>
       <c r="G253" t="n">
-        <v>5435.45</v>
+        <v>5301.95</v>
       </c>
     </row>
     <row r="254">
@@ -7264,13 +7264,13 @@
         <v>282</v>
       </c>
       <c r="E254" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="F254" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="G254" t="n">
-        <v>6.37</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="255">
@@ -7290,10 +7290,10 @@
         <v>1.53</v>
       </c>
       <c r="F255" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="G255" t="n">
-        <v>10.89</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="256">
@@ -7310,13 +7310,13 @@
         <v>284</v>
       </c>
       <c r="E256" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="F256" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="G256" t="n">
-        <v>12.83</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="257">
@@ -7336,10 +7336,10 @@
         <v>1.69</v>
       </c>
       <c r="F257" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="G257" t="n">
-        <v>15.93</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="258">
@@ -7356,13 +7356,13 @@
         <v>286</v>
       </c>
       <c r="E258" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="F258" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="G258" t="n">
-        <v>17.58</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="259">
@@ -7379,13 +7379,13 @@
         <v>287</v>
       </c>
       <c r="E259" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="F259" t="n">
-        <v>5.47</v>
+        <v>5.52</v>
       </c>
       <c r="G259" t="n">
-        <v>22.68</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="260">
@@ -7405,10 +7405,10 @@
         <v>2.12</v>
       </c>
       <c r="F260" t="n">
-        <v>7.39</v>
+        <v>7.46</v>
       </c>
       <c r="G260" t="n">
-        <v>36.69</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="261">
@@ -7425,13 +7425,13 @@
         <v>289</v>
       </c>
       <c r="E261" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="F261" t="n">
-        <v>8.9</v>
+        <v>8.97</v>
       </c>
       <c r="G261" t="n">
-        <v>49.17</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="262">
@@ -7448,13 +7448,13 @@
         <v>290</v>
       </c>
       <c r="E262" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="F262" t="n">
-        <v>9.43</v>
+        <v>9.51</v>
       </c>
       <c r="G262" t="n">
-        <v>53.89</v>
+        <v>54.63</v>
       </c>
     </row>
     <row r="263">
@@ -7471,13 +7471,13 @@
         <v>291</v>
       </c>
       <c r="E263" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="F263" t="n">
-        <v>14.94</v>
+        <v>15.08</v>
       </c>
       <c r="G263" t="n">
-        <v>110.77</v>
+        <v>112.35</v>
       </c>
     </row>
     <row r="264">
@@ -7494,13 +7494,13 @@
         <v>292</v>
       </c>
       <c r="E264" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="F264" t="n">
-        <v>15.66</v>
+        <v>15.81</v>
       </c>
       <c r="G264" t="n">
-        <v>119.21</v>
+        <v>120.92</v>
       </c>
     </row>
     <row r="265">
@@ -7517,13 +7517,13 @@
         <v>293</v>
       </c>
       <c r="E265" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="F265" t="n">
-        <v>31.74</v>
+        <v>32.05</v>
       </c>
       <c r="G265" t="n">
-        <v>354.76</v>
+        <v>360.03</v>
       </c>
     </row>
     <row r="266">
@@ -7540,13 +7540,13 @@
         <v>294</v>
       </c>
       <c r="E266" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="F266" t="n">
-        <v>36.25</v>
+        <v>36.6</v>
       </c>
       <c r="G266" t="n">
-        <v>434.97</v>
+        <v>441.46</v>
       </c>
     </row>
     <row r="267">
@@ -7563,13 +7563,13 @@
         <v>295</v>
       </c>
       <c r="E267" t="n">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="F267" t="n">
-        <v>36.83</v>
+        <v>37.19</v>
       </c>
       <c r="G267" t="n">
-        <v>445.66</v>
+        <v>452.32</v>
       </c>
     </row>
     <row r="268">
@@ -7586,13 +7586,13 @@
         <v>296</v>
       </c>
       <c r="E268" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="F268" t="n">
-        <v>37.41</v>
+        <v>37.78</v>
       </c>
       <c r="G268" t="n">
-        <v>456.57</v>
+        <v>463.39</v>
       </c>
     </row>
     <row r="269">
@@ -7609,13 +7609,13 @@
         <v>297</v>
       </c>
       <c r="E269" t="n">
-        <v>7.75</v>
+        <v>7.79</v>
       </c>
       <c r="F269" t="n">
-        <v>114.8</v>
+        <v>115.96</v>
       </c>
       <c r="G269" t="n">
-        <v>2521.83</v>
+        <v>2560.64</v>
       </c>
     </row>
     <row r="270">
@@ -7632,13 +7632,13 @@
         <v>298</v>
       </c>
       <c r="E270" t="n">
-        <v>8.25</v>
+        <v>8.29</v>
       </c>
       <c r="F270" t="n">
-        <v>130.57</v>
+        <v>131.89</v>
       </c>
       <c r="G270" t="n">
-        <v>3065.45</v>
+        <v>3112.75</v>
       </c>
     </row>
     <row r="271">
@@ -7655,13 +7655,13 @@
         <v>299</v>
       </c>
       <c r="E271" t="n">
-        <v>9.96</v>
+        <v>10.01</v>
       </c>
       <c r="F271" t="n">
-        <v>191.49</v>
+        <v>193.45</v>
       </c>
       <c r="G271" t="n">
-        <v>5475.91</v>
+        <v>5560.9</v>
       </c>
     </row>
     <row r="272">
@@ -7681,10 +7681,10 @@
         <v>1.26</v>
       </c>
       <c r="F272" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="G272" t="n">
-        <v>4.65</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="273">
@@ -7704,10 +7704,10 @@
         <v>1.34</v>
       </c>
       <c r="F273" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="G273" t="n">
-        <v>6.17</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="274">
@@ -7727,10 +7727,10 @@
         <v>1.36</v>
       </c>
       <c r="F274" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="G274" t="n">
-        <v>6.69</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="275">
@@ -7750,10 +7750,10 @@
         <v>1.38</v>
       </c>
       <c r="F275" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="G275" t="n">
-        <v>7.04</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="276">
@@ -7773,10 +7773,10 @@
         <v>1.49</v>
       </c>
       <c r="F276" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="G276" t="n">
-        <v>9.73</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="277">
@@ -7796,10 +7796,10 @@
         <v>1.53</v>
       </c>
       <c r="F277" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="G277" t="n">
-        <v>10.84</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="278">
@@ -7819,10 +7819,10 @@
         <v>1.73</v>
       </c>
       <c r="F278" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="G278" t="n">
-        <v>17.4</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="279">
@@ -7839,13 +7839,13 @@
         <v>308</v>
       </c>
       <c r="E279" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="F279" t="n">
-        <v>6.09</v>
+        <v>6.13</v>
       </c>
       <c r="G279" t="n">
-        <v>26.95</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="280">
@@ -7862,13 +7862,13 @@
         <v>309</v>
       </c>
       <c r="E280" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="F280" t="n">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="G280" t="n">
-        <v>34.01</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="281">
@@ -7888,10 +7888,10 @@
         <v>2.3</v>
       </c>
       <c r="F281" t="n">
-        <v>8.88</v>
+        <v>8.94</v>
       </c>
       <c r="G281" t="n">
-        <v>49.05</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="282">
@@ -7908,13 +7908,13 @@
         <v>311</v>
       </c>
       <c r="E282" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="F282" t="n">
-        <v>10.62</v>
+        <v>10.69</v>
       </c>
       <c r="G282" t="n">
-        <v>65</v>
+        <v>65.68</v>
       </c>
     </row>
     <row r="283">
@@ -7931,13 +7931,13 @@
         <v>312</v>
       </c>
       <c r="E283" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="F283" t="n">
-        <v>13.16</v>
+        <v>13.25</v>
       </c>
       <c r="G283" t="n">
-        <v>90.9</v>
+        <v>91.86</v>
       </c>
     </row>
     <row r="284">
@@ -7954,13 +7954,13 @@
         <v>313</v>
       </c>
       <c r="E284" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="F284" t="n">
-        <v>17.27</v>
+        <v>17.39</v>
       </c>
       <c r="G284" t="n">
-        <v>138.67</v>
+        <v>140.17</v>
       </c>
     </row>
     <row r="285">
@@ -7977,13 +7977,13 @@
         <v>314</v>
       </c>
       <c r="E285" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="F285" t="n">
-        <v>24.58</v>
+        <v>24.76</v>
       </c>
       <c r="G285" t="n">
-        <v>239.42</v>
+        <v>242.07</v>
       </c>
     </row>
     <row r="286">
@@ -8000,13 +8000,13 @@
         <v>315</v>
       </c>
       <c r="E286" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="F286" t="n">
-        <v>28.26</v>
+        <v>28.46</v>
       </c>
       <c r="G286" t="n">
-        <v>296.76</v>
+        <v>300.06</v>
       </c>
     </row>
     <row r="287">
@@ -8023,13 +8023,13 @@
         <v>316</v>
       </c>
       <c r="E287" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="F287" t="n">
-        <v>33.9</v>
+        <v>34.15</v>
       </c>
       <c r="G287" t="n">
-        <v>392.57</v>
+        <v>396.96</v>
       </c>
     </row>
     <row r="288">
@@ -8046,13 +8046,13 @@
         <v>317</v>
       </c>
       <c r="E288" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="F288" t="n">
-        <v>40.01</v>
+        <v>40.3</v>
       </c>
       <c r="G288" t="n">
-        <v>505.99</v>
+        <v>511.69</v>
       </c>
     </row>
     <row r="289">
@@ -8069,13 +8069,13 @@
         <v>318</v>
       </c>
       <c r="E289" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="F289" t="n">
-        <v>42.39</v>
+        <v>42.7</v>
       </c>
       <c r="G289" t="n">
-        <v>552.77</v>
+        <v>559.01</v>
       </c>
     </row>
     <row r="290">

--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -35,7 +35,241 @@
     <t xml:space="preserve">3+ Fair Odds</t>
   </si>
   <si>
-    <t xml:space="preserve">brisbane lions v gold coast suns</t>
+    <t xml:space="preserve">adelaide crows v greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adelaide crows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taylor Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Thilthorpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Rachele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Keays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izak Rankine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finnbar Maley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Neal-Bullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Dawson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Soligo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaac Cumming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan McAndrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Curtin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Peatling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Nankervis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Hall-Kahan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greater western sydney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Stringer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Cadman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Gruzewski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callum Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Hamilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Bedford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stephen Coniglio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Rowston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier O'Halloran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conor Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finn Callaghan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Angwin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clayton Oliver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicholas Madden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Himmelberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Fonti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlton v fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carlton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Kemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Hayward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch McGovern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Ainsworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talor Byrne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Cottrell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Cripps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Hewett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marc Pittonet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Acres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jagga Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Walsh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Lord</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Cerra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lewis Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Florent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Dean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Amiss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Treacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Voss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Frederick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Dudley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shai Bolton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murphy Reid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Switkowski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caleb Serong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan O'Driscoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neil Erasmus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Brayshaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Wagner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar McDonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collingwood v brisbane lions</t>
   </si>
   <si>
     <t xml:space="preserve">brisbane lions</t>
@@ -89,10 +323,421 @@
     <t xml:space="preserve">Josh Dunkley</t>
   </si>
   <si>
+    <t xml:space="preserve">Dayne Zorko</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jaspa Fletcher</t>
   </si>
   <si>
-    <t xml:space="preserve">Dayne Zorko</t>
+    <t xml:space="preserve">collingwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel McStay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Membrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan De Goey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Harrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Daicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beau McCreery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Lipinski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ned Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steele Sidebottom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Crisp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edward Allan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Pendlebury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darcy Cameron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dan Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Daicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Howe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon v port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">essendon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nate Caddy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Wright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hussien El Achkar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sullivan Robey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaac Kako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nik Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Clarke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dyson Sharp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archer Day-Wicks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Durham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zach Merrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Setterfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Kondogiannis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben McKay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Redman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob Farrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archie Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lachlan Blakiston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">port adelaide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Georgiades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Durdin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Whitlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Zadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todd Marshall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Bamert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Horne-Francis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Watkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Berry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Moraes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darcy Byrne-Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dante Visentini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordon Sweet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jase Burgoyne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ollie Wines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miles Bergman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willem Drew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats v richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shannon Neale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaun Mannagh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jay Polkinghorne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Dangerfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Dempsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Wiltshire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryan Miers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Blicavs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Worpel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Atkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oisin Mullin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jhye Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawson Humphries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richmond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Lynch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mykelti Lefau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Lalor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhyan Mansell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seth Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zane Peucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taj Hotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Taranto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Sonsie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Cumming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Ralphsmith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toby Nankervis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Retschko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dion Prestia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne v western bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayley Fritsch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob van Rooyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kysaiah Pickett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Petty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Sharp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Jefferson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kade Chandler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Laurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paddy Cross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latrelle Pickett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey Langford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Sparrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Gawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ed Langdon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Fitzgerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Steele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koltyn Tholstrup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trent Rivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">western bulldogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Naughton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Bontempelli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhylee West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Weightman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Croft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Hynes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Dolan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ed Richards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joel Freijah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Davidson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryley Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Liberatore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rory Lobb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buku Khamis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">st kilda v gold coast suns</t>
   </si>
   <si>
     <t xml:space="preserve">gold coast suns</t>
@@ -119,12 +764,12 @@
     <t xml:space="preserve">Dylan Patterson</t>
   </si>
   <si>
+    <t xml:space="preserve">Caleb Lewis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Touk Miller</t>
   </si>
   <si>
-    <t xml:space="preserve">Caleb Lewis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zeke Uwland</t>
   </si>
   <si>
@@ -152,64 +797,121 @@
     <t xml:space="preserve">John Noble</t>
   </si>
   <si>
-    <t xml:space="preserve">essendon v sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">essendon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nate Caddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Wright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hussien El Achkar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sullivan Robey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Kako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nik Cox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Clarke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dyson Sharp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archer Day-Wicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Durham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zach Merrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Kondogiannis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Setterfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben McKay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Farrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Redman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archie Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan Blakiston</t>
+    <t xml:space="preserve">st kilda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Ryan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Sharman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Owens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darcy Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattaes Phillipou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasiah Wanganeen-Milera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rowan Marshall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom De Koning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugh Boxshall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradley Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Byrnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Windhager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Silvagni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sydney swans v north melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">north melbourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Larkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paul Curtis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Trembath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Darling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zac Banch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Whitlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie Spargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Zurhaar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colby McKercher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Sheezel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jy Simpkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Davies-Uniacke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Xerri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Parker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Scott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Stephens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finn O'Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Harvey</t>
   </si>
   <si>
     <t xml:space="preserve">sydney swans</t>
@@ -227,15 +929,15 @@
     <t xml:space="preserve">Isaac Heeney</t>
   </si>
   <si>
+    <t xml:space="preserve">Billy Cootee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden McLean</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chad Warner</t>
   </si>
   <si>
-    <t xml:space="preserve">Billy Cootee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden McLean</t>
-  </si>
-  <si>
     <t xml:space="preserve">Malcolm Rosas</t>
   </si>
   <si>
@@ -254,12 +956,12 @@
     <t xml:space="preserve">Brodie Grundy</t>
   </si>
   <si>
+    <t xml:space="preserve">Jai Serong</t>
+  </si>
+  <si>
     <t xml:space="preserve">James Jordon</t>
   </si>
   <si>
-    <t xml:space="preserve">Jai Serong</t>
-  </si>
-  <si>
     <t xml:space="preserve">Matt Roberts</t>
   </si>
   <si>
@@ -269,181 +971,64 @@
     <t xml:space="preserve">Riley Bice</t>
   </si>
   <si>
-    <t xml:space="preserve">fremantle v adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taylor Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Thilthorpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Rachele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Keays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izak Rankine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finnbar Maley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Dawson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Neal-Bullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Soligo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Cumming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan McAndrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Curtin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Peatling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Nankervis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Hall-Kahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fremantle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Treacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jye Amiss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Voss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Frederick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Dudley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shai Bolton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murphy Reid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Switkowski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caleb Serong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan O'Driscoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Cox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neil Erasmus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Brayshaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Wagner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscar McDonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney v west coast eagles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">greater western sydney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Stringer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Cadman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Gruzewski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Callum Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Hamilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Bedford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stephen Coniglio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Rowston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier O'Halloran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conor Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Angwin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finn Callaghan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clayton Oliver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Madden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Ough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Himmelberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Fonti</t>
+    <t xml:space="preserve">west coast eagles v hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Gunston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mabior Chol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ginnivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Macdonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Greeves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Newcombe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Morrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lloyd Meek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Hardwick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massimo D'Ambrosio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cam Mackenzie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Weddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarman Impey</t>
   </si>
   <si>
     <t xml:space="preserve">west coast eagles</t>
@@ -470,12 +1055,12 @@
     <t xml:space="preserve">Harley Reid</t>
   </si>
   <si>
+    <t xml:space="preserve">Tom Cole</t>
+  </si>
+  <si>
     <t xml:space="preserve">Willem Duursma</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom Cole</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bailey J. Williams</t>
   </si>
   <si>
@@ -485,15 +1070,15 @@
     <t xml:space="preserve">Oliver Francou</t>
   </si>
   <si>
+    <t xml:space="preserve">Ryan Maric</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tim Kelly</t>
   </si>
   <si>
     <t xml:space="preserve">Hamish Davis</t>
   </si>
   <si>
-    <t xml:space="preserve">Ryan Maric</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brady Hough</t>
   </si>
   <si>
@@ -501,591 +1086,6 @@
   </si>
   <si>
     <t xml:space="preserve">Marcus Herbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn v collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collingwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel McStay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Membrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angus Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan De Goey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Harrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Daicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beau McCreery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Lipinski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ned Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steele Sidebottom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Crisp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edward Allan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Cameron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Pendlebury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dan Houston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Daicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Howe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hawthorn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Gunston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mabior Chol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Lewis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Ginnivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Moore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Macdonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Greeves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Newcombe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Morrison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Hardwick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lloyd Meek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massimo D'Ambrosio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Weddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cam Mackenzie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jarman Impey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne v geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shannon Neale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shaun Mannagh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jay Polkinghorne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Dempsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Dangerfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Wiltshire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brad Close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryan Miers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Worpel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Blicavs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Atkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oisin Mullin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jhye Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tanner Bruhn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">north melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Larkey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul Curtis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Trembath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Darling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Banch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Whitlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Spargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Zurhaar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colby McKercher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Sheezel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jy Simpkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Davies-Uniacke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tristan Xerri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Parker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Scott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Stephens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finn O'Sullivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Harvey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide v melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">melbourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob van Rooyen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayley Fritsch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kysaiah Pickett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Sharp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Petty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Jefferson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kade Chandler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Laurie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paddy Cross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvey Langford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latrelle Pickett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Sparrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Gawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ed Langdon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Fitzgerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Steele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koltyn Tholstrup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trent Rivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">port adelaide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Georgiades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corey Durdin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Whitlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jason Horne-Francis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todd Marshall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Bamert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Zadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Watkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Moraes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Byrne-Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dante Visentini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordon Sweet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jase Burgoyne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ollie Wines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miles Bergman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willem Drew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">richmond v st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">richmond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Lynch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mykelti Lefau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Lalor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhyan Mansell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seth Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zane Peucker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taj Hotton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Taranto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyler Sonsie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Cumming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Ralphsmith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Nankervis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Ross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dion Prestia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Retschko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Banks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">st kilda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Higgins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Sharman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Ryan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Owens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darcy Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattaes Phillipou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nasiah Wanganeen-Milera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rowan Marshall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom De Koning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Garcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugh Boxshall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradley Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Byrnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Silvagni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Windhager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">western bulldogs v carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carlton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Kemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Hayward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Ainsworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch McGovern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talor Byrne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Cottrell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Cripps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">George Hewett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marc Pittonet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jagga Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Acres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Walsh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Cerra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Lord</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lewis Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Florent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harry Dean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">western bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Naughton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Weightman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhylee West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Bontempelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arthur Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Croft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Freijah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ed Richards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Dolan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim English</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Davidson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryley Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Liberatore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rory Lobb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buku Khamis</t>
   </si>
 </sst>
 </file>
@@ -1423,7 +1423,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="42.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="39.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="22.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -1468,18 +1468,18 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>3.02</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -1491,18 +1491,18 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1514,18 +1514,18 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="F4" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="G4" t="n">
-        <v>3.69</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -1537,18 +1537,18 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -1560,18 +1560,18 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="F6" t="n">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="G6" t="n">
-        <v>7.41</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -1583,18 +1583,18 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>5.02</v>
       </c>
       <c r="G7" t="n">
-        <v>8.29</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -1606,18 +1606,18 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="F8" t="n">
-        <v>3.68</v>
+        <v>5.22</v>
       </c>
       <c r="G8" t="n">
-        <v>11.89</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1629,18 +1629,18 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="F9" t="n">
-        <v>7.76</v>
+        <v>5.44</v>
       </c>
       <c r="G9" t="n">
-        <v>39.59</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -1652,18 +1652,18 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="F10" t="n">
-        <v>8.16</v>
+        <v>5.57</v>
       </c>
       <c r="G10" t="n">
-        <v>42.89</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -1675,18 +1675,18 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="F11" t="n">
-        <v>8.64</v>
+        <v>6.37</v>
       </c>
       <c r="G11" t="n">
-        <v>46.94</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -1698,18 +1698,18 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="F12" t="n">
-        <v>12.08</v>
+        <v>15.15</v>
       </c>
       <c r="G12" t="n">
-        <v>79.49</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -1721,18 +1721,18 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="F13" t="n">
-        <v>18.41</v>
+        <v>17.68</v>
       </c>
       <c r="G13" t="n">
-        <v>153.2</v>
+        <v>143.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -1744,18 +1744,18 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="F14" t="n">
-        <v>19.2</v>
+        <v>18.26</v>
       </c>
       <c r="G14" t="n">
-        <v>163.49</v>
+        <v>151.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -1767,18 +1767,18 @@
         <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="F15" t="n">
-        <v>22.89</v>
+        <v>21.02</v>
       </c>
       <c r="G15" t="n">
-        <v>214.53</v>
+        <v>188.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
@@ -1790,18 +1790,18 @@
         <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="F16" t="n">
-        <v>25.57</v>
+        <v>22.76</v>
       </c>
       <c r="G16" t="n">
-        <v>254.35</v>
+        <v>212.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -1813,18 +1813,18 @@
         <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>3.97</v>
+        <v>4.5</v>
       </c>
       <c r="F17" t="n">
-        <v>28.75</v>
+        <v>37.38</v>
       </c>
       <c r="G17" t="n">
-        <v>304.73</v>
+        <v>455.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -1836,18 +1836,18 @@
         <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>5.3</v>
+        <v>6.39</v>
       </c>
       <c r="F18" t="n">
-        <v>52.48</v>
+        <v>77.36</v>
       </c>
       <c r="G18" t="n">
-        <v>766.2</v>
+        <v>1384.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -1859,18 +1859,18 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>5.73</v>
+        <v>8.51</v>
       </c>
       <c r="F19" t="n">
-        <v>61.82</v>
+        <v>139.21</v>
       </c>
       <c r="G19" t="n">
-        <v>983.73</v>
+        <v>3378.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -1882,18 +1882,18 @@
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="F20" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.61</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
@@ -1905,18 +1905,18 @@
         <v>29</v>
       </c>
       <c r="E21" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="F21" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>7.78</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
@@ -1928,18 +1928,18 @@
         <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="F22" t="n">
-        <v>3.05</v>
+        <v>2.59</v>
       </c>
       <c r="G22" t="n">
-        <v>8.72</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
@@ -1951,18 +1951,18 @@
         <v>31</v>
       </c>
       <c r="E23" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="F23" t="n">
-        <v>3.77</v>
+        <v>3.24</v>
       </c>
       <c r="G23" t="n">
-        <v>12.38</v>
+        <v>9.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -1974,18 +1974,18 @@
         <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="F24" t="n">
-        <v>4.54</v>
+        <v>5.1</v>
       </c>
       <c r="G24" t="n">
-        <v>16.79</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -1997,18 +1997,18 @@
         <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="F25" t="n">
-        <v>5.34</v>
+        <v>5.57</v>
       </c>
       <c r="G25" t="n">
-        <v>21.78</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -2020,18 +2020,18 @@
         <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="F26" t="n">
-        <v>6.3</v>
+        <v>5.82</v>
       </c>
       <c r="G26" t="n">
-        <v>28.42</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
@@ -2043,18 +2043,18 @@
         <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>2.11</v>
+        <v>2.79</v>
       </c>
       <c r="F27" t="n">
-        <v>7.35</v>
+        <v>13.57</v>
       </c>
       <c r="G27" t="n">
-        <v>36.32</v>
+        <v>95.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
@@ -2066,18 +2066,18 @@
         <v>36</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2</v>
+        <v>2.94</v>
       </c>
       <c r="F28" t="n">
-        <v>8.03</v>
+        <v>15.23</v>
       </c>
       <c r="G28" t="n">
-        <v>41.83</v>
+        <v>114.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
@@ -2089,18 +2089,18 @@
         <v>37</v>
       </c>
       <c r="E29" t="n">
-        <v>3.16</v>
+        <v>3.37</v>
       </c>
       <c r="F29" t="n">
-        <v>17.76</v>
+        <v>20.37</v>
       </c>
       <c r="G29" t="n">
-        <v>144.92</v>
+        <v>179.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
@@ -2112,18 +2112,18 @@
         <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="F30" t="n">
-        <v>18.32</v>
+        <v>22.06</v>
       </c>
       <c r="G30" t="n">
-        <v>152.01</v>
+        <v>202.54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
@@ -2135,18 +2135,18 @@
         <v>39</v>
       </c>
       <c r="E31" t="n">
-        <v>3.71</v>
+        <v>3.63</v>
       </c>
       <c r="F31" t="n">
-        <v>24.89</v>
+        <v>23.83</v>
       </c>
       <c r="G31" t="n">
-        <v>244.02</v>
+        <v>228.21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
@@ -2158,18 +2158,18 @@
         <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="F32" t="n">
-        <v>25.36</v>
+        <v>24</v>
       </c>
       <c r="G32" t="n">
-        <v>251.18</v>
+        <v>230.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
@@ -2181,18 +2181,18 @@
         <v>41</v>
       </c>
       <c r="E33" t="n">
-        <v>3.88</v>
+        <v>4.71</v>
       </c>
       <c r="F33" t="n">
-        <v>27.38</v>
+        <v>41.05</v>
       </c>
       <c r="G33" t="n">
-        <v>282.64</v>
+        <v>526.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
@@ -2204,18 +2204,18 @@
         <v>42</v>
       </c>
       <c r="E34" t="n">
-        <v>5.09</v>
+        <v>5.3</v>
       </c>
       <c r="F34" t="n">
-        <v>48.28</v>
+        <v>52.6</v>
       </c>
       <c r="G34" t="n">
-        <v>674.46</v>
+        <v>768.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
@@ -2227,18 +2227,18 @@
         <v>43</v>
       </c>
       <c r="E35" t="n">
-        <v>5.27</v>
+        <v>6.48</v>
       </c>
       <c r="F35" t="n">
-        <v>51.97</v>
+        <v>79.56</v>
       </c>
       <c r="G35" t="n">
-        <v>754.92</v>
+        <v>1444.61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
@@ -2250,18 +2250,18 @@
         <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>6.39</v>
+        <v>8.21</v>
       </c>
       <c r="F36" t="n">
-        <v>77.37</v>
+        <v>129.33</v>
       </c>
       <c r="G36" t="n">
-        <v>1384.39</v>
+        <v>3021.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
@@ -2273,18 +2273,18 @@
         <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>6.97</v>
+        <v>13.9</v>
       </c>
       <c r="F37" t="n">
-        <v>92.39</v>
+        <v>377.01</v>
       </c>
       <c r="G37" t="n">
-        <v>1813.18</v>
+        <v>15243.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -2296,18 +2296,18 @@
         <v>48</v>
       </c>
       <c r="E38" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="F38" t="n">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="G38" t="n">
-        <v>6.93</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -2319,18 +2319,18 @@
         <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="F39" t="n">
-        <v>3.49</v>
+        <v>2.65</v>
       </c>
       <c r="G39" t="n">
-        <v>10.89</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -2342,18 +2342,18 @@
         <v>50</v>
       </c>
       <c r="E40" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="F40" t="n">
-        <v>4.92</v>
+        <v>3.15</v>
       </c>
       <c r="G40" t="n">
-        <v>19.09</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -2365,18 +2365,18 @@
         <v>51</v>
       </c>
       <c r="E41" t="n">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="F41" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="G41" t="n">
-        <v>22.84</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -2388,18 +2388,18 @@
         <v>52</v>
       </c>
       <c r="E42" t="n">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="F42" t="n">
-        <v>6.28</v>
+        <v>3.28</v>
       </c>
       <c r="G42" t="n">
-        <v>28.32</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -2411,18 +2411,18 @@
         <v>53</v>
       </c>
       <c r="E43" t="n">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="F43" t="n">
-        <v>6.96</v>
+        <v>3.46</v>
       </c>
       <c r="G43" t="n">
-        <v>33.33</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B44" t="s">
         <v>46</v>
@@ -2434,18 +2434,18 @@
         <v>54</v>
       </c>
       <c r="E44" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="F44" t="n">
-        <v>7.19</v>
+        <v>5.06</v>
       </c>
       <c r="G44" t="n">
-        <v>35.11</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B45" t="s">
         <v>46</v>
@@ -2457,18 +2457,18 @@
         <v>55</v>
       </c>
       <c r="E45" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="F45" t="n">
-        <v>7.24</v>
+        <v>8.81</v>
       </c>
       <c r="G45" t="n">
-        <v>35.45</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B46" t="s">
         <v>46</v>
@@ -2480,18 +2480,18 @@
         <v>56</v>
       </c>
       <c r="E46" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="F46" t="n">
-        <v>9.38</v>
+        <v>10.47</v>
       </c>
       <c r="G46" t="n">
-        <v>53.49</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B47" t="s">
         <v>46</v>
@@ -2503,18 +2503,18 @@
         <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="F47" t="n">
-        <v>17.61</v>
+        <v>13.97</v>
       </c>
       <c r="G47" t="n">
-        <v>143.03</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
@@ -2526,18 +2526,18 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="F48" t="n">
-        <v>18.44</v>
+        <v>15.54</v>
       </c>
       <c r="G48" t="n">
-        <v>153.61</v>
+        <v>117.79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B49" t="s">
         <v>46</v>
@@ -2549,18 +2549,18 @@
         <v>59</v>
       </c>
       <c r="E49" t="n">
-        <v>4.41</v>
+        <v>3.02</v>
       </c>
       <c r="F49" t="n">
-        <v>35.89</v>
+        <v>16.09</v>
       </c>
       <c r="G49" t="n">
-        <v>428.37</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B50" t="s">
         <v>46</v>
@@ -2572,18 +2572,18 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>4.66</v>
+        <v>3.21</v>
       </c>
       <c r="F50" t="n">
-        <v>40.26</v>
+        <v>18.3</v>
       </c>
       <c r="G50" t="n">
-        <v>510.86</v>
+        <v>151.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B51" t="s">
         <v>46</v>
@@ -2595,18 +2595,18 @@
         <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>6.91</v>
+        <v>3.25</v>
       </c>
       <c r="F51" t="n">
-        <v>90.78</v>
+        <v>18.78</v>
       </c>
       <c r="G51" t="n">
-        <v>1765.57</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B52" t="s">
         <v>46</v>
@@ -2618,18 +2618,18 @@
         <v>62</v>
       </c>
       <c r="E52" t="n">
-        <v>7.19</v>
+        <v>3.44</v>
       </c>
       <c r="F52" t="n">
-        <v>98.42</v>
+        <v>21.21</v>
       </c>
       <c r="G52" t="n">
-        <v>1996.24</v>
+        <v>190.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B53" t="s">
         <v>46</v>
@@ -2641,18 +2641,18 @@
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>7.22</v>
+        <v>6.24</v>
       </c>
       <c r="F53" t="n">
-        <v>99.28</v>
+        <v>73.51</v>
       </c>
       <c r="G53" t="n">
-        <v>2022.77</v>
+        <v>1280.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B54" t="s">
         <v>46</v>
@@ -2664,18 +2664,18 @@
         <v>64</v>
       </c>
       <c r="E54" t="n">
-        <v>10.58</v>
+        <v>7.26</v>
       </c>
       <c r="F54" t="n">
-        <v>216.83</v>
+        <v>100.51</v>
       </c>
       <c r="G54" t="n">
-        <v>6608.61</v>
+        <v>2060.79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B55" t="s">
         <v>46</v>
@@ -2687,18 +2687,18 @@
         <v>65</v>
       </c>
       <c r="E55" t="n">
-        <v>11.91</v>
+        <v>11.24</v>
       </c>
       <c r="F55" t="n">
-        <v>275.87</v>
+        <v>245.1</v>
       </c>
       <c r="G55" t="n">
-        <v>9510.88</v>
+        <v>7954.24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B56" t="s">
         <v>46</v>
@@ -2710,18 +2710,18 @@
         <v>67</v>
       </c>
       <c r="E56" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="F56" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="G56" t="n">
-        <v>2.26</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B57" t="s">
         <v>46</v>
@@ -2733,18 +2733,18 @@
         <v>68</v>
       </c>
       <c r="E57" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="F57" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="G57" t="n">
-        <v>4.19</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B58" t="s">
         <v>46</v>
@@ -2756,18 +2756,18 @@
         <v>69</v>
       </c>
       <c r="E58" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="F58" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="G58" t="n">
-        <v>5.63</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B59" t="s">
         <v>46</v>
@@ -2779,18 +2779,18 @@
         <v>70</v>
       </c>
       <c r="E59" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="F59" t="n">
-        <v>2.82</v>
+        <v>3.23</v>
       </c>
       <c r="G59" t="n">
-        <v>7.64</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B60" t="s">
         <v>46</v>
@@ -2802,18 +2802,18 @@
         <v>71</v>
       </c>
       <c r="E60" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="F60" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="G60" t="n">
-        <v>9.27</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B61" t="s">
         <v>46</v>
@@ -2825,18 +2825,18 @@
         <v>72</v>
       </c>
       <c r="E61" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="F61" t="n">
-        <v>3.37</v>
+        <v>5.31</v>
       </c>
       <c r="G61" t="n">
-        <v>10.3</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B62" t="s">
         <v>46</v>
@@ -2848,18 +2848,18 @@
         <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="F62" t="n">
-        <v>3.38</v>
+        <v>5.53</v>
       </c>
       <c r="G62" t="n">
-        <v>10.34</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B63" t="s">
         <v>46</v>
@@ -2871,18 +2871,18 @@
         <v>74</v>
       </c>
       <c r="E63" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="F63" t="n">
-        <v>4.06</v>
+        <v>5.58</v>
       </c>
       <c r="G63" t="n">
-        <v>13.96</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B64" t="s">
         <v>46</v>
@@ -2894,18 +2894,18 @@
         <v>75</v>
       </c>
       <c r="E64" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>5.05</v>
+        <v>6.52</v>
       </c>
       <c r="G64" t="n">
-        <v>19.95</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B65" t="s">
         <v>46</v>
@@ -2917,18 +2917,18 @@
         <v>76</v>
       </c>
       <c r="E65" t="n">
-        <v>1.81</v>
+        <v>3.14</v>
       </c>
       <c r="F65" t="n">
-        <v>5.21</v>
+        <v>17.45</v>
       </c>
       <c r="G65" t="n">
-        <v>20.98</v>
+        <v>140.98</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B66" t="s">
         <v>46</v>
@@ -2940,18 +2940,18 @@
         <v>77</v>
       </c>
       <c r="E66" t="n">
-        <v>1.92</v>
+        <v>3.67</v>
       </c>
       <c r="F66" t="n">
-        <v>5.92</v>
+        <v>24.38</v>
       </c>
       <c r="G66" t="n">
-        <v>25.75</v>
+        <v>236.36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B67" t="s">
         <v>46</v>
@@ -2963,18 +2963,18 @@
         <v>78</v>
       </c>
       <c r="E67" t="n">
-        <v>2.06</v>
+        <v>3.74</v>
       </c>
       <c r="F67" t="n">
-        <v>6.96</v>
+        <v>25.36</v>
       </c>
       <c r="G67" t="n">
-        <v>33.31</v>
+        <v>251.24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B68" t="s">
         <v>46</v>
@@ -2986,18 +2986,18 @@
         <v>79</v>
       </c>
       <c r="E68" t="n">
-        <v>2.88</v>
+        <v>3.87</v>
       </c>
       <c r="F68" t="n">
-        <v>14.49</v>
+        <v>27.22</v>
       </c>
       <c r="G68" t="n">
-        <v>105.55</v>
+        <v>280.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B69" t="s">
         <v>46</v>
@@ -3009,18 +3009,18 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>3.12</v>
+        <v>3.99</v>
       </c>
       <c r="F69" t="n">
-        <v>17.25</v>
+        <v>29</v>
       </c>
       <c r="G69" t="n">
-        <v>138.52</v>
+        <v>308.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B70" t="s">
         <v>46</v>
@@ -3032,18 +3032,18 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="F70" t="n">
-        <v>18.26</v>
+        <v>33.15</v>
       </c>
       <c r="G70" t="n">
-        <v>151.22</v>
+        <v>379.33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B71" t="s">
         <v>46</v>
@@ -3055,18 +3055,18 @@
         <v>82</v>
       </c>
       <c r="E71" t="n">
-        <v>4.28</v>
+        <v>6.28</v>
       </c>
       <c r="F71" t="n">
-        <v>33.71</v>
+        <v>74.67</v>
       </c>
       <c r="G71" t="n">
-        <v>389.18</v>
+        <v>1311.52</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B72" t="s">
         <v>46</v>
@@ -3078,18 +3078,18 @@
         <v>83</v>
       </c>
       <c r="E72" t="n">
-        <v>4.8</v>
+        <v>8.31</v>
       </c>
       <c r="F72" t="n">
-        <v>42.83</v>
+        <v>132.3</v>
       </c>
       <c r="G72" t="n">
-        <v>561.59</v>
+        <v>3127.29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B73" t="s">
         <v>46</v>
@@ -3101,18 +3101,18 @@
         <v>84</v>
       </c>
       <c r="E73" t="n">
-        <v>7.55</v>
+        <v>11.55</v>
       </c>
       <c r="F73" t="n">
-        <v>108.92</v>
+        <v>258.87</v>
       </c>
       <c r="G73" t="n">
-        <v>2328.41</v>
+        <v>8639.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B74" t="s">
         <v>85</v>
@@ -3124,18 +3124,18 @@
         <v>87</v>
       </c>
       <c r="E74" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="F74" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="G74" t="n">
-        <v>5.79</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B75" t="s">
         <v>85</v>
@@ -3147,18 +3147,18 @@
         <v>88</v>
       </c>
       <c r="E75" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="F75" t="n">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="G75" t="n">
-        <v>5.85</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B76" t="s">
         <v>85</v>
@@ -3170,18 +3170,18 @@
         <v>89</v>
       </c>
       <c r="E76" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="F76" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="G76" t="n">
-        <v>7.56</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B77" t="s">
         <v>85</v>
@@ -3193,18 +3193,18 @@
         <v>90</v>
       </c>
       <c r="E77" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="F77" t="n">
-        <v>3.37</v>
+        <v>2.77</v>
       </c>
       <c r="G77" t="n">
-        <v>10.27</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B78" t="s">
         <v>85</v>
@@ -3216,18 +3216,18 @@
         <v>91</v>
       </c>
       <c r="E78" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="F78" t="n">
-        <v>4.64</v>
+        <v>3.32</v>
       </c>
       <c r="G78" t="n">
-        <v>17.37</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B79" t="s">
         <v>85</v>
@@ -3239,18 +3239,18 @@
         <v>92</v>
       </c>
       <c r="E79" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="F79" t="n">
-        <v>7.09</v>
+        <v>3.51</v>
       </c>
       <c r="G79" t="n">
-        <v>34.35</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B80" t="s">
         <v>85</v>
@@ -3262,18 +3262,18 @@
         <v>93</v>
       </c>
       <c r="E80" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="F80" t="n">
-        <v>7.62</v>
+        <v>4.63</v>
       </c>
       <c r="G80" t="n">
-        <v>38.45</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B81" t="s">
         <v>85</v>
@@ -3285,18 +3285,18 @@
         <v>94</v>
       </c>
       <c r="E81" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="F81" t="n">
-        <v>7.71</v>
+        <v>9.74</v>
       </c>
       <c r="G81" t="n">
-        <v>39.21</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B82" t="s">
         <v>85</v>
@@ -3308,18 +3308,18 @@
         <v>95</v>
       </c>
       <c r="E82" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="F82" t="n">
-        <v>7.75</v>
+        <v>9.98</v>
       </c>
       <c r="G82" t="n">
-        <v>39.56</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B83" t="s">
         <v>85</v>
@@ -3331,18 +3331,18 @@
         <v>96</v>
       </c>
       <c r="E83" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="F83" t="n">
-        <v>8.83</v>
+        <v>11.26</v>
       </c>
       <c r="G83" t="n">
-        <v>48.59</v>
+        <v>71.27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B84" t="s">
         <v>85</v>
@@ -3354,18 +3354,18 @@
         <v>97</v>
       </c>
       <c r="E84" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="F84" t="n">
-        <v>19.74</v>
+        <v>13.7</v>
       </c>
       <c r="G84" t="n">
-        <v>170.59</v>
+        <v>96.73</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B85" t="s">
         <v>85</v>
@@ -3377,18 +3377,18 @@
         <v>98</v>
       </c>
       <c r="E85" t="n">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="F85" t="n">
-        <v>25.3</v>
+        <v>24.24</v>
       </c>
       <c r="G85" t="n">
-        <v>250.35</v>
+        <v>234.37</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B86" t="s">
         <v>85</v>
@@ -3400,18 +3400,18 @@
         <v>99</v>
       </c>
       <c r="E86" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="F86" t="n">
-        <v>27.51</v>
+        <v>25.36</v>
       </c>
       <c r="G86" t="n">
-        <v>284.78</v>
+        <v>251.17</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B87" t="s">
         <v>85</v>
@@ -3423,18 +3423,18 @@
         <v>100</v>
       </c>
       <c r="E87" t="n">
-        <v>4.06</v>
+        <v>3.99</v>
       </c>
       <c r="F87" t="n">
-        <v>30.08</v>
+        <v>28.98</v>
       </c>
       <c r="G87" t="n">
-        <v>326.71</v>
+        <v>308.54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B88" t="s">
         <v>85</v>
@@ -3446,18 +3446,18 @@
         <v>101</v>
       </c>
       <c r="E88" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="F88" t="n">
-        <v>31.12</v>
+        <v>30.09</v>
       </c>
       <c r="G88" t="n">
-        <v>344.25</v>
+        <v>326.75</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B89" t="s">
         <v>85</v>
@@ -3469,18 +3469,18 @@
         <v>102</v>
       </c>
       <c r="E89" t="n">
-        <v>5.27</v>
+        <v>4.53</v>
       </c>
       <c r="F89" t="n">
-        <v>51.84</v>
+        <v>37.94</v>
       </c>
       <c r="G89" t="n">
-        <v>751.89</v>
+        <v>466.45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B90" t="s">
         <v>85</v>
@@ -3492,18 +3492,18 @@
         <v>103</v>
       </c>
       <c r="E90" t="n">
-        <v>7.63</v>
+        <v>5.97</v>
       </c>
       <c r="F90" t="n">
-        <v>111.17</v>
+        <v>67.25</v>
       </c>
       <c r="G90" t="n">
-        <v>2401.76</v>
+        <v>1118.46</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B91" t="s">
         <v>85</v>
@@ -3515,18 +3515,18 @@
         <v>104</v>
       </c>
       <c r="E91" t="n">
-        <v>10.08</v>
+        <v>6.12</v>
       </c>
       <c r="F91" t="n">
-        <v>196.44</v>
+        <v>70.81</v>
       </c>
       <c r="G91" t="n">
-        <v>5691.2</v>
+        <v>1209.71</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B92" t="s">
         <v>85</v>
@@ -3538,18 +3538,18 @@
         <v>106</v>
       </c>
       <c r="E92" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="F92" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="G92" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B93" t="s">
         <v>85</v>
@@ -3561,18 +3561,18 @@
         <v>107</v>
       </c>
       <c r="E93" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B94" t="s">
         <v>85</v>
@@ -3584,18 +3584,18 @@
         <v>108</v>
       </c>
       <c r="E94" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="F94" t="n">
-        <v>2.11</v>
+        <v>3.14</v>
       </c>
       <c r="G94" t="n">
-        <v>4.62</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B95" t="s">
         <v>85</v>
@@ -3607,18 +3607,18 @@
         <v>109</v>
       </c>
       <c r="E95" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="F95" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="G95" t="n">
-        <v>10.42</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B96" t="s">
         <v>85</v>
@@ -3630,18 +3630,18 @@
         <v>110</v>
       </c>
       <c r="E96" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="F96" t="n">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="G96" t="n">
-        <v>10.61</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B97" t="s">
         <v>85</v>
@@ -3653,18 +3653,18 @@
         <v>111</v>
       </c>
       <c r="E97" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="F97" t="n">
-        <v>4.91</v>
+        <v>4.73</v>
       </c>
       <c r="G97" t="n">
-        <v>19.02</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B98" t="s">
         <v>85</v>
@@ -3676,18 +3676,18 @@
         <v>112</v>
       </c>
       <c r="E98" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="F98" t="n">
-        <v>4.98</v>
+        <v>4.73</v>
       </c>
       <c r="G98" t="n">
-        <v>19.49</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B99" t="s">
         <v>85</v>
@@ -3699,18 +3699,18 @@
         <v>113</v>
       </c>
       <c r="E99" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="F99" t="n">
-        <v>5.22</v>
+        <v>5.47</v>
       </c>
       <c r="G99" t="n">
-        <v>21.02</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B100" t="s">
         <v>85</v>
@@ -3722,18 +3722,18 @@
         <v>114</v>
       </c>
       <c r="E100" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="F100" t="n">
-        <v>5.95</v>
+        <v>5.6</v>
       </c>
       <c r="G100" t="n">
-        <v>25.95</v>
+        <v>23.51</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B101" t="s">
         <v>85</v>
@@ -3745,18 +3745,18 @@
         <v>115</v>
       </c>
       <c r="E101" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="F101" t="n">
-        <v>18.24</v>
+        <v>8.24</v>
       </c>
       <c r="G101" t="n">
-        <v>150.93</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B102" t="s">
         <v>85</v>
@@ -3768,18 +3768,18 @@
         <v>116</v>
       </c>
       <c r="E102" t="n">
-        <v>3.55</v>
+        <v>3.01</v>
       </c>
       <c r="F102" t="n">
-        <v>22.71</v>
+        <v>16.03</v>
       </c>
       <c r="G102" t="n">
-        <v>211.89</v>
+        <v>123.54</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B103" t="s">
         <v>85</v>
@@ -3791,18 +3791,18 @@
         <v>117</v>
       </c>
       <c r="E103" t="n">
-        <v>3.68</v>
+        <v>3.16</v>
       </c>
       <c r="F103" t="n">
-        <v>24.55</v>
+        <v>17.78</v>
       </c>
       <c r="G103" t="n">
-        <v>238.91</v>
+        <v>145.15</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B104" t="s">
         <v>85</v>
@@ -3814,18 +3814,18 @@
         <v>118</v>
       </c>
       <c r="E104" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="F104" t="n">
-        <v>26.19</v>
+        <v>20.08</v>
       </c>
       <c r="G104" t="n">
-        <v>263.97</v>
+        <v>175.22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B105" t="s">
         <v>85</v>
@@ -3837,18 +3837,18 @@
         <v>119</v>
       </c>
       <c r="E105" t="n">
-        <v>3.95</v>
+        <v>3.81</v>
       </c>
       <c r="F105" t="n">
-        <v>28.43</v>
+        <v>26.43</v>
       </c>
       <c r="G105" t="n">
-        <v>299.6</v>
+        <v>267.67</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B106" t="s">
         <v>85</v>
@@ -3860,18 +3860,18 @@
         <v>120</v>
       </c>
       <c r="E106" t="n">
-        <v>4.03</v>
+        <v>3.85</v>
       </c>
       <c r="F106" t="n">
-        <v>29.74</v>
+        <v>26.89</v>
       </c>
       <c r="G106" t="n">
-        <v>321.04</v>
+        <v>274.98</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B107" t="s">
         <v>85</v>
@@ -3883,18 +3883,18 @@
         <v>121</v>
       </c>
       <c r="E107" t="n">
-        <v>6.11</v>
+        <v>4.49</v>
       </c>
       <c r="F107" t="n">
-        <v>70.5</v>
+        <v>37.23</v>
       </c>
       <c r="G107" t="n">
-        <v>1201.83</v>
+        <v>453.11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B108" t="s">
         <v>85</v>
@@ -3906,18 +3906,18 @@
         <v>122</v>
       </c>
       <c r="E108" t="n">
-        <v>7.68</v>
+        <v>6.92</v>
       </c>
       <c r="F108" t="n">
-        <v>112.77</v>
+        <v>90.99</v>
       </c>
       <c r="G108" t="n">
-        <v>2454.4</v>
+        <v>1771.62</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B109" t="s">
         <v>85</v>
@@ -3929,18 +3929,18 @@
         <v>123</v>
       </c>
       <c r="E109" t="n">
-        <v>10.91</v>
+        <v>8.86</v>
       </c>
       <c r="F109" t="n">
-        <v>230.64</v>
+        <v>150.9</v>
       </c>
       <c r="G109" t="n">
-        <v>7255.21</v>
+        <v>3817.66</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B110" t="s">
         <v>124</v>
@@ -3952,18 +3952,18 @@
         <v>126</v>
       </c>
       <c r="E110" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="F110" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="G110" t="n">
-        <v>2.48</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B111" t="s">
         <v>124</v>
@@ -3975,18 +3975,18 @@
         <v>127</v>
       </c>
       <c r="E111" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="F111" t="n">
-        <v>1.65</v>
+        <v>2.52</v>
       </c>
       <c r="G111" t="n">
-        <v>2.98</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B112" t="s">
         <v>124</v>
@@ -3998,18 +3998,18 @@
         <v>128</v>
       </c>
       <c r="E112" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="F112" t="n">
-        <v>2.15</v>
+        <v>3.63</v>
       </c>
       <c r="G112" t="n">
-        <v>4.81</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B113" t="s">
         <v>124</v>
@@ -4021,18 +4021,18 @@
         <v>129</v>
       </c>
       <c r="E113" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="F113" t="n">
-        <v>2.37</v>
+        <v>4.02</v>
       </c>
       <c r="G113" t="n">
-        <v>5.67</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B114" t="s">
         <v>124</v>
@@ -4044,18 +4044,18 @@
         <v>130</v>
       </c>
       <c r="E114" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="F114" t="n">
-        <v>3.51</v>
+        <v>4.73</v>
       </c>
       <c r="G114" t="n">
-        <v>10.97</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B115" t="s">
         <v>124</v>
@@ -4067,18 +4067,18 @@
         <v>131</v>
       </c>
       <c r="E115" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="F115" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="G115" t="n">
-        <v>11.49</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B116" t="s">
         <v>124</v>
@@ -4090,18 +4090,18 @@
         <v>132</v>
       </c>
       <c r="E116" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="F116" t="n">
-        <v>3.69</v>
+        <v>5.5</v>
       </c>
       <c r="G116" t="n">
-        <v>11.95</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B117" t="s">
         <v>124</v>
@@ -4113,18 +4113,18 @@
         <v>133</v>
       </c>
       <c r="E117" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="F117" t="n">
-        <v>4.06</v>
+        <v>5.58</v>
       </c>
       <c r="G117" t="n">
-        <v>13.97</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B118" t="s">
         <v>124</v>
@@ -4136,18 +4136,18 @@
         <v>134</v>
       </c>
       <c r="E118" t="n">
-        <v>2.46</v>
+        <v>1.96</v>
       </c>
       <c r="F118" t="n">
-        <v>10.31</v>
+        <v>6.21</v>
       </c>
       <c r="G118" t="n">
-        <v>62.04</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B119" t="s">
         <v>124</v>
@@ -4159,18 +4159,18 @@
         <v>135</v>
       </c>
       <c r="E119" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="F119" t="n">
-        <v>12.09</v>
+        <v>12.25</v>
       </c>
       <c r="G119" t="n">
-        <v>79.57</v>
+        <v>81.23</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B120" t="s">
         <v>124</v>
@@ -4182,18 +4182,18 @@
         <v>136</v>
       </c>
       <c r="E120" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="F120" t="n">
-        <v>12.39</v>
+        <v>13.21</v>
       </c>
       <c r="G120" t="n">
-        <v>82.72</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B121" t="s">
         <v>124</v>
@@ -4205,18 +4205,18 @@
         <v>137</v>
       </c>
       <c r="E121" t="n">
-        <v>2.82</v>
+        <v>3.62</v>
       </c>
       <c r="F121" t="n">
-        <v>13.84</v>
+        <v>23.62</v>
       </c>
       <c r="G121" t="n">
-        <v>98.31</v>
+        <v>225.16</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B122" t="s">
         <v>124</v>
@@ -4228,18 +4228,18 @@
         <v>138</v>
       </c>
       <c r="E122" t="n">
-        <v>2.84</v>
+        <v>3.78</v>
       </c>
       <c r="F122" t="n">
-        <v>14.06</v>
+        <v>25.89</v>
       </c>
       <c r="G122" t="n">
-        <v>100.73</v>
+        <v>259.4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B123" t="s">
         <v>124</v>
@@ -4251,18 +4251,18 @@
         <v>139</v>
       </c>
       <c r="E123" t="n">
-        <v>3.57</v>
+        <v>5.71</v>
       </c>
       <c r="F123" t="n">
-        <v>23.03</v>
+        <v>61.38</v>
       </c>
       <c r="G123" t="n">
-        <v>216.58</v>
+        <v>972.96</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B124" t="s">
         <v>124</v>
@@ -4274,18 +4274,18 @@
         <v>140</v>
       </c>
       <c r="E124" t="n">
-        <v>3.97</v>
+        <v>5.78</v>
       </c>
       <c r="F124" t="n">
-        <v>28.77</v>
+        <v>62.79</v>
       </c>
       <c r="G124" t="n">
-        <v>305.07</v>
+        <v>1007.37</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B125" t="s">
         <v>124</v>
@@ -4297,18 +4297,18 @@
         <v>141</v>
       </c>
       <c r="E125" t="n">
-        <v>4.95</v>
+        <v>5.97</v>
       </c>
       <c r="F125" t="n">
-        <v>45.58</v>
+        <v>67.22</v>
       </c>
       <c r="G125" t="n">
-        <v>617.65</v>
+        <v>1117.5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B126" t="s">
         <v>124</v>
@@ -4320,18 +4320,18 @@
         <v>142</v>
       </c>
       <c r="E126" t="n">
-        <v>6.09</v>
+        <v>8.88</v>
       </c>
       <c r="F126" t="n">
-        <v>69.93</v>
+        <v>151.51</v>
       </c>
       <c r="G126" t="n">
-        <v>1186.86</v>
+        <v>3840.92</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B127" t="s">
         <v>124</v>
@@ -4343,18 +4343,18 @@
         <v>143</v>
       </c>
       <c r="E127" t="n">
-        <v>10.18</v>
+        <v>9.75</v>
       </c>
       <c r="F127" t="n">
-        <v>200.54</v>
+        <v>183.69</v>
       </c>
       <c r="G127" t="n">
-        <v>5872.13</v>
+        <v>5141.91</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B128" t="s">
         <v>124</v>
@@ -4366,18 +4366,18 @@
         <v>145</v>
       </c>
       <c r="E128" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="F128" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="G128" t="n">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B129" t="s">
         <v>124</v>
@@ -4389,18 +4389,18 @@
         <v>146</v>
       </c>
       <c r="E129" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="F129" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="G129" t="n">
-        <v>7.16</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B130" t="s">
         <v>124</v>
@@ -4412,18 +4412,18 @@
         <v>147</v>
       </c>
       <c r="E130" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="F130" t="n">
-        <v>4.21</v>
+        <v>3.36</v>
       </c>
       <c r="G130" t="n">
-        <v>14.85</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B131" t="s">
         <v>124</v>
@@ -4435,18 +4435,18 @@
         <v>148</v>
       </c>
       <c r="E131" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="F131" t="n">
-        <v>4.69</v>
+        <v>3.81</v>
       </c>
       <c r="G131" t="n">
-        <v>17.66</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B132" t="s">
         <v>124</v>
@@ -4458,18 +4458,18 @@
         <v>149</v>
       </c>
       <c r="E132" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="F132" t="n">
-        <v>5.49</v>
+        <v>3.82</v>
       </c>
       <c r="G132" t="n">
-        <v>22.83</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B133" t="s">
         <v>124</v>
@@ -4481,18 +4481,18 @@
         <v>150</v>
       </c>
       <c r="E133" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="F133" t="n">
-        <v>6.09</v>
+        <v>4.44</v>
       </c>
       <c r="G133" t="n">
-        <v>26.91</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B134" t="s">
         <v>124</v>
@@ -4504,18 +4504,18 @@
         <v>151</v>
       </c>
       <c r="E134" t="n">
-        <v>2.37</v>
+        <v>1.87</v>
       </c>
       <c r="F134" t="n">
-        <v>9.47</v>
+        <v>5.63</v>
       </c>
       <c r="G134" t="n">
-        <v>54.29</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B135" t="s">
         <v>124</v>
@@ -4527,18 +4527,18 @@
         <v>152</v>
       </c>
       <c r="E135" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="F135" t="n">
-        <v>9.92</v>
+        <v>5.71</v>
       </c>
       <c r="G135" t="n">
-        <v>58.35</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B136" t="s">
         <v>124</v>
@@ -4550,18 +4550,18 @@
         <v>153</v>
       </c>
       <c r="E136" t="n">
-        <v>2.54</v>
+        <v>1.9</v>
       </c>
       <c r="F136" t="n">
-        <v>11.07</v>
+        <v>5.8</v>
       </c>
       <c r="G136" t="n">
-        <v>69.33</v>
+        <v>24.92</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B137" t="s">
         <v>124</v>
@@ -4573,18 +4573,18 @@
         <v>154</v>
       </c>
       <c r="E137" t="n">
-        <v>2.88</v>
+        <v>2.27</v>
       </c>
       <c r="F137" t="n">
-        <v>14.57</v>
+        <v>8.66</v>
       </c>
       <c r="G137" t="n">
-        <v>106.46</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B138" t="s">
         <v>124</v>
@@ -4596,18 +4596,18 @@
         <v>155</v>
       </c>
       <c r="E138" t="n">
-        <v>3.85</v>
+        <v>3.02</v>
       </c>
       <c r="F138" t="n">
-        <v>26.95</v>
+        <v>16.14</v>
       </c>
       <c r="G138" t="n">
-        <v>275.8</v>
+        <v>124.88</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B139" t="s">
         <v>124</v>
@@ -4619,18 +4619,18 @@
         <v>156</v>
       </c>
       <c r="E139" t="n">
-        <v>4.07</v>
+        <v>3.13</v>
       </c>
       <c r="F139" t="n">
-        <v>30.33</v>
+        <v>17.36</v>
       </c>
       <c r="G139" t="n">
-        <v>330.76</v>
+        <v>139.87</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B140" t="s">
         <v>124</v>
@@ -4642,18 +4642,18 @@
         <v>157</v>
       </c>
       <c r="E140" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="F140" t="n">
-        <v>40.91</v>
+        <v>17.64</v>
       </c>
       <c r="G140" t="n">
-        <v>523.6</v>
+        <v>143.36</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B141" t="s">
         <v>124</v>
@@ -4665,18 +4665,18 @@
         <v>158</v>
       </c>
       <c r="E141" t="n">
-        <v>4.77</v>
+        <v>3.73</v>
       </c>
       <c r="F141" t="n">
-        <v>42.27</v>
+        <v>25.23</v>
       </c>
       <c r="G141" t="n">
-        <v>550.34</v>
+        <v>249.24</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B142" t="s">
         <v>124</v>
@@ -4688,18 +4688,18 @@
         <v>159</v>
       </c>
       <c r="E142" t="n">
-        <v>4.79</v>
+        <v>4.91</v>
       </c>
       <c r="F142" t="n">
-        <v>42.5</v>
+        <v>44.78</v>
       </c>
       <c r="G142" t="n">
-        <v>554.98</v>
+        <v>601.27</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B143" t="s">
         <v>124</v>
@@ -4711,18 +4711,18 @@
         <v>160</v>
       </c>
       <c r="E143" t="n">
-        <v>8.09</v>
+        <v>5.55</v>
       </c>
       <c r="F143" t="n">
-        <v>125.5</v>
+        <v>57.8</v>
       </c>
       <c r="G143" t="n">
-        <v>2886.97</v>
+        <v>887.75</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B144" t="s">
         <v>124</v>
@@ -4734,18 +4734,18 @@
         <v>161</v>
       </c>
       <c r="E144" t="n">
-        <v>12.22</v>
+        <v>5.71</v>
       </c>
       <c r="F144" t="n">
-        <v>290.56</v>
+        <v>61.21</v>
       </c>
       <c r="G144" t="n">
-        <v>10286.29</v>
+        <v>968.95</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B145" t="s">
         <v>124</v>
@@ -4757,18 +4757,18 @@
         <v>162</v>
       </c>
       <c r="E145" t="n">
-        <v>14.36</v>
+        <v>9.06</v>
       </c>
       <c r="F145" t="n">
-        <v>402.85</v>
+        <v>158</v>
       </c>
       <c r="G145" t="n">
-        <v>16847.57</v>
+        <v>4092.9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B146" t="s">
         <v>163</v>
@@ -4780,18 +4780,18 @@
         <v>165</v>
       </c>
       <c r="E146" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="F146" t="n">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="G146" t="n">
-        <v>5.35</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B147" t="s">
         <v>163</v>
@@ -4803,18 +4803,18 @@
         <v>166</v>
       </c>
       <c r="E147" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="F147" t="n">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B148" t="s">
         <v>163</v>
@@ -4826,18 +4826,18 @@
         <v>167</v>
       </c>
       <c r="E148" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="F148" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="G148" t="n">
-        <v>9.67</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B149" t="s">
         <v>163</v>
@@ -4849,18 +4849,18 @@
         <v>168</v>
       </c>
       <c r="E149" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="F149" t="n">
-        <v>3.87</v>
+        <v>2.25</v>
       </c>
       <c r="G149" t="n">
-        <v>12.9</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B150" t="s">
         <v>163</v>
@@ -4872,18 +4872,18 @@
         <v>169</v>
       </c>
       <c r="E150" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="F150" t="n">
-        <v>4.79</v>
+        <v>2.56</v>
       </c>
       <c r="G150" t="n">
-        <v>18.27</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B151" t="s">
         <v>163</v>
@@ -4895,18 +4895,18 @@
         <v>170</v>
       </c>
       <c r="E151" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="F151" t="n">
-        <v>5.14</v>
+        <v>2.62</v>
       </c>
       <c r="G151" t="n">
-        <v>20.48</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B152" t="s">
         <v>163</v>
@@ -4918,18 +4918,18 @@
         <v>171</v>
       </c>
       <c r="E152" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="F152" t="n">
-        <v>5.43</v>
+        <v>2.99</v>
       </c>
       <c r="G152" t="n">
-        <v>22.43</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B153" t="s">
         <v>163</v>
@@ -4941,18 +4941,18 @@
         <v>172</v>
       </c>
       <c r="E153" t="n">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="F153" t="n">
-        <v>6.38</v>
+        <v>3.43</v>
       </c>
       <c r="G153" t="n">
-        <v>29.04</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B154" t="s">
         <v>163</v>
@@ -4964,18 +4964,18 @@
         <v>173</v>
       </c>
       <c r="E154" t="n">
-        <v>1.99</v>
+        <v>1.68</v>
       </c>
       <c r="F154" t="n">
-        <v>6.45</v>
+        <v>4.37</v>
       </c>
       <c r="G154" t="n">
-        <v>29.51</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B155" t="s">
         <v>163</v>
@@ -4987,18 +4987,18 @@
         <v>174</v>
       </c>
       <c r="E155" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="F155" t="n">
-        <v>9.32</v>
+        <v>11.7</v>
       </c>
       <c r="G155" t="n">
-        <v>52.93</v>
+        <v>75.64</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B156" t="s">
         <v>163</v>
@@ -5010,18 +5010,18 @@
         <v>175</v>
       </c>
       <c r="E156" t="n">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="F156" t="n">
-        <v>18.77</v>
+        <v>12.76</v>
       </c>
       <c r="G156" t="n">
-        <v>157.79</v>
+        <v>86.6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B157" t="s">
         <v>163</v>
@@ -5033,18 +5033,18 @@
         <v>176</v>
       </c>
       <c r="E157" t="n">
-        <v>3.51</v>
+        <v>3.07</v>
       </c>
       <c r="F157" t="n">
-        <v>22.13</v>
+        <v>16.63</v>
       </c>
       <c r="G157" t="n">
-        <v>203.59</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B158" t="s">
         <v>163</v>
@@ -5056,18 +5056,18 @@
         <v>177</v>
       </c>
       <c r="E158" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="F158" t="n">
-        <v>25.12</v>
+        <v>25.75</v>
       </c>
       <c r="G158" t="n">
-        <v>247.62</v>
+        <v>257.19</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B159" t="s">
         <v>163</v>
@@ -5079,18 +5079,18 @@
         <v>178</v>
       </c>
       <c r="E159" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="F159" t="n">
-        <v>27.95</v>
+        <v>27.9</v>
       </c>
       <c r="G159" t="n">
-        <v>291.74</v>
+        <v>291.03</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B160" t="s">
         <v>163</v>
@@ -5102,18 +5102,18 @@
         <v>179</v>
       </c>
       <c r="E160" t="n">
-        <v>4.07</v>
+        <v>4.23</v>
       </c>
       <c r="F160" t="n">
-        <v>30.23</v>
+        <v>32.85</v>
       </c>
       <c r="G160" t="n">
-        <v>329.09</v>
+        <v>374.08</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B161" t="s">
         <v>163</v>
@@ -5125,18 +5125,18 @@
         <v>180</v>
       </c>
       <c r="E161" t="n">
-        <v>5.12</v>
+        <v>4.97</v>
       </c>
       <c r="F161" t="n">
-        <v>48.95</v>
+        <v>45.96</v>
       </c>
       <c r="G161" t="n">
-        <v>688.81</v>
+        <v>625.56</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B162" t="s">
         <v>163</v>
@@ -5148,18 +5148,18 @@
         <v>181</v>
       </c>
       <c r="E162" t="n">
-        <v>7.21</v>
+        <v>5.26</v>
       </c>
       <c r="F162" t="n">
-        <v>99.1</v>
+        <v>51.67</v>
       </c>
       <c r="G162" t="n">
-        <v>2017.02</v>
+        <v>748.25</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B163" t="s">
         <v>163</v>
@@ -5171,18 +5171,18 @@
         <v>182</v>
       </c>
       <c r="E163" t="n">
-        <v>9.63</v>
+        <v>5.89</v>
       </c>
       <c r="F163" t="n">
-        <v>179.01</v>
+        <v>65.36</v>
       </c>
       <c r="G163" t="n">
-        <v>4944.6</v>
+        <v>1070.95</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B164" t="s">
         <v>163</v>
@@ -5194,18 +5194,18 @@
         <v>184</v>
       </c>
       <c r="E164" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="F164" t="n">
-        <v>1.52</v>
+        <v>3.05</v>
       </c>
       <c r="G164" t="n">
-        <v>2.56</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B165" t="s">
         <v>163</v>
@@ -5217,18 +5217,18 @@
         <v>185</v>
       </c>
       <c r="E165" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="F165" t="n">
-        <v>2.12</v>
+        <v>4.07</v>
       </c>
       <c r="G165" t="n">
-        <v>4.66</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B166" t="s">
         <v>163</v>
@@ -5240,18 +5240,18 @@
         <v>186</v>
       </c>
       <c r="E166" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="F166" t="n">
-        <v>2.66</v>
+        <v>5.12</v>
       </c>
       <c r="G166" t="n">
-        <v>6.92</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B167" t="s">
         <v>163</v>
@@ -5263,18 +5263,18 @@
         <v>187</v>
       </c>
       <c r="E167" t="n">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="F167" t="n">
-        <v>3.1</v>
+        <v>5.39</v>
       </c>
       <c r="G167" t="n">
-        <v>8.92</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B168" t="s">
         <v>163</v>
@@ -5286,18 +5286,18 @@
         <v>188</v>
       </c>
       <c r="E168" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="F168" t="n">
-        <v>4.3</v>
+        <v>5.92</v>
       </c>
       <c r="G168" t="n">
-        <v>15.33</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B169" t="s">
         <v>163</v>
@@ -5309,18 +5309,18 @@
         <v>189</v>
       </c>
       <c r="E169" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="F169" t="n">
-        <v>4.69</v>
+        <v>6.73</v>
       </c>
       <c r="G169" t="n">
-        <v>17.69</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B170" t="s">
         <v>163</v>
@@ -5332,18 +5332,18 @@
         <v>190</v>
       </c>
       <c r="E170" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="F170" t="n">
-        <v>5.57</v>
+        <v>8.9</v>
       </c>
       <c r="G170" t="n">
-        <v>23.31</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B171" t="s">
         <v>163</v>
@@ -5355,18 +5355,18 @@
         <v>191</v>
       </c>
       <c r="E171" t="n">
-        <v>2.02</v>
+        <v>2.53</v>
       </c>
       <c r="F171" t="n">
-        <v>6.67</v>
+        <v>10.95</v>
       </c>
       <c r="G171" t="n">
-        <v>31.14</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B172" t="s">
         <v>163</v>
@@ -5378,18 +5378,18 @@
         <v>192</v>
       </c>
       <c r="E172" t="n">
-        <v>2.95</v>
+        <v>2.61</v>
       </c>
       <c r="F172" t="n">
-        <v>15.35</v>
+        <v>11.75</v>
       </c>
       <c r="G172" t="n">
-        <v>115.53</v>
+        <v>76.16</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B173" t="s">
         <v>163</v>
@@ -5401,18 +5401,18 @@
         <v>193</v>
       </c>
       <c r="E173" t="n">
-        <v>3.78</v>
+        <v>3.26</v>
       </c>
       <c r="F173" t="n">
-        <v>25.99</v>
+        <v>19.01</v>
       </c>
       <c r="G173" t="n">
-        <v>260.83</v>
+        <v>160.95</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B174" t="s">
         <v>163</v>
@@ -5424,18 +5424,18 @@
         <v>194</v>
       </c>
       <c r="E174" t="n">
-        <v>3.85</v>
+        <v>3.42</v>
       </c>
       <c r="F174" t="n">
-        <v>26.94</v>
+        <v>20.97</v>
       </c>
       <c r="G174" t="n">
-        <v>275.75</v>
+        <v>187.33</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B175" t="s">
         <v>163</v>
@@ -5447,18 +5447,18 @@
         <v>195</v>
       </c>
       <c r="E175" t="n">
-        <v>4.11</v>
+        <v>4.61</v>
       </c>
       <c r="F175" t="n">
-        <v>30.97</v>
+        <v>39.25</v>
       </c>
       <c r="G175" t="n">
-        <v>341.64</v>
+        <v>491.42</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B176" t="s">
         <v>163</v>
@@ -5470,18 +5470,18 @@
         <v>196</v>
       </c>
       <c r="E176" t="n">
-        <v>4.35</v>
+        <v>4.84</v>
       </c>
       <c r="F176" t="n">
-        <v>34.87</v>
+        <v>43.56</v>
       </c>
       <c r="G176" t="n">
-        <v>409.81</v>
+        <v>576.32</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B177" t="s">
         <v>163</v>
@@ -5493,18 +5493,18 @@
         <v>197</v>
       </c>
       <c r="E177" t="n">
-        <v>4.47</v>
+        <v>5.21</v>
       </c>
       <c r="F177" t="n">
-        <v>36.84</v>
+        <v>50.69</v>
       </c>
       <c r="G177" t="n">
-        <v>445.88</v>
+        <v>726.59</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B178" t="s">
         <v>163</v>
@@ -5516,18 +5516,18 @@
         <v>198</v>
       </c>
       <c r="E178" t="n">
-        <v>4.48</v>
+        <v>5.38</v>
       </c>
       <c r="F178" t="n">
-        <v>37</v>
+        <v>54.23</v>
       </c>
       <c r="G178" t="n">
-        <v>448.85</v>
+        <v>805.41</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B179" t="s">
         <v>163</v>
@@ -5539,18 +5539,18 @@
         <v>199</v>
       </c>
       <c r="E179" t="n">
-        <v>4.94</v>
+        <v>9.12</v>
       </c>
       <c r="F179" t="n">
-        <v>45.48</v>
+        <v>160.07</v>
       </c>
       <c r="G179" t="n">
-        <v>615.67</v>
+        <v>4174.27</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B180" t="s">
         <v>163</v>
@@ -5562,18 +5562,18 @@
         <v>200</v>
       </c>
       <c r="E180" t="n">
-        <v>5.4</v>
+        <v>9.51</v>
       </c>
       <c r="F180" t="n">
-        <v>54.55</v>
+        <v>174.45</v>
       </c>
       <c r="G180" t="n">
-        <v>812.8</v>
+        <v>4755.32</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B181" t="s">
         <v>163</v>
@@ -5585,18 +5585,18 @@
         <v>201</v>
       </c>
       <c r="E181" t="n">
-        <v>6.38</v>
+        <v>11.63</v>
       </c>
       <c r="F181" t="n">
-        <v>76.95</v>
+        <v>262.58</v>
       </c>
       <c r="G181" t="n">
-        <v>1373.07</v>
+        <v>8826.91</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B182" t="s">
         <v>202</v>
@@ -5608,18 +5608,18 @@
         <v>204</v>
       </c>
       <c r="E182" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="F182" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="G182" t="n">
-        <v>2.99</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B183" t="s">
         <v>202</v>
@@ -5631,18 +5631,18 @@
         <v>205</v>
       </c>
       <c r="E183" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="F183" t="n">
-        <v>1.82</v>
+        <v>2.37</v>
       </c>
       <c r="G183" t="n">
-        <v>3.58</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B184" t="s">
         <v>202</v>
@@ -5654,18 +5654,18 @@
         <v>206</v>
       </c>
       <c r="E184" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="F184" t="n">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="G184" t="n">
-        <v>5.28</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B185" t="s">
         <v>202</v>
@@ -5677,18 +5677,18 @@
         <v>207</v>
       </c>
       <c r="E185" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="F185" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="G185" t="n">
-        <v>6.22</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B186" t="s">
         <v>202</v>
@@ -5700,18 +5700,18 @@
         <v>208</v>
       </c>
       <c r="E186" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="F186" t="n">
-        <v>2.81</v>
+        <v>3.56</v>
       </c>
       <c r="G186" t="n">
-        <v>7.58</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B187" t="s">
         <v>202</v>
@@ -5723,18 +5723,18 @@
         <v>209</v>
       </c>
       <c r="E187" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="F187" t="n">
-        <v>2.82</v>
+        <v>4.15</v>
       </c>
       <c r="G187" t="n">
-        <v>7.64</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B188" t="s">
         <v>202</v>
@@ -5746,18 +5746,18 @@
         <v>210</v>
       </c>
       <c r="E188" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="F188" t="n">
-        <v>3</v>
+        <v>4.66</v>
       </c>
       <c r="G188" t="n">
-        <v>8.45</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B189" t="s">
         <v>202</v>
@@ -5769,18 +5769,18 @@
         <v>211</v>
       </c>
       <c r="E189" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="F189" t="n">
-        <v>3.76</v>
+        <v>5</v>
       </c>
       <c r="G189" t="n">
-        <v>12.32</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B190" t="s">
         <v>202</v>
@@ -5792,18 +5792,18 @@
         <v>212</v>
       </c>
       <c r="E190" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="F190" t="n">
-        <v>4.73</v>
+        <v>6</v>
       </c>
       <c r="G190" t="n">
-        <v>17.9</v>
+        <v>26.33</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B191" t="s">
         <v>202</v>
@@ -5815,18 +5815,18 @@
         <v>213</v>
       </c>
       <c r="E191" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="F191" t="n">
-        <v>12.51</v>
+        <v>6.52</v>
       </c>
       <c r="G191" t="n">
-        <v>84.01</v>
+        <v>30.05</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B192" t="s">
         <v>202</v>
@@ -5838,18 +5838,18 @@
         <v>214</v>
       </c>
       <c r="E192" t="n">
-        <v>3.19</v>
+        <v>2.03</v>
       </c>
       <c r="F192" t="n">
-        <v>18.08</v>
+        <v>6.73</v>
       </c>
       <c r="G192" t="n">
-        <v>148.91</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B193" t="s">
         <v>202</v>
@@ -5861,18 +5861,18 @@
         <v>215</v>
       </c>
       <c r="E193" t="n">
-        <v>3.22</v>
+        <v>2.66</v>
       </c>
       <c r="F193" t="n">
-        <v>18.47</v>
+        <v>12.2</v>
       </c>
       <c r="G193" t="n">
-        <v>153.88</v>
+        <v>80.79</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B194" t="s">
         <v>202</v>
@@ -5884,18 +5884,18 @@
         <v>216</v>
       </c>
       <c r="E194" t="n">
-        <v>4.07</v>
+        <v>2.83</v>
       </c>
       <c r="F194" t="n">
-        <v>30.35</v>
+        <v>14.01</v>
       </c>
       <c r="G194" t="n">
-        <v>331.19</v>
+        <v>100.15</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B195" t="s">
         <v>202</v>
@@ -5907,18 +5907,18 @@
         <v>217</v>
       </c>
       <c r="E195" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="F195" t="n">
-        <v>35.63</v>
+        <v>14.15</v>
       </c>
       <c r="G195" t="n">
-        <v>423.6</v>
+        <v>101.77</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B196" t="s">
         <v>202</v>
@@ -5930,18 +5930,18 @@
         <v>218</v>
       </c>
       <c r="E196" t="n">
-        <v>4.92</v>
+        <v>4.09</v>
       </c>
       <c r="F196" t="n">
-        <v>45.07</v>
+        <v>30.65</v>
       </c>
       <c r="G196" t="n">
-        <v>607.07</v>
+        <v>336.26</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B197" t="s">
         <v>202</v>
@@ -5953,18 +5953,18 @@
         <v>219</v>
       </c>
       <c r="E197" t="n">
-        <v>5.07</v>
+        <v>4.28</v>
       </c>
       <c r="F197" t="n">
-        <v>47.96</v>
+        <v>33.65</v>
       </c>
       <c r="G197" t="n">
-        <v>667.59</v>
+        <v>388.07</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B198" t="s">
         <v>202</v>
@@ -5976,18 +5976,18 @@
         <v>220</v>
       </c>
       <c r="E198" t="n">
-        <v>5.96</v>
+        <v>6.05</v>
       </c>
       <c r="F198" t="n">
-        <v>67.05</v>
+        <v>69.02</v>
       </c>
       <c r="G198" t="n">
-        <v>1113.29</v>
+        <v>1163.42</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B199" t="s">
         <v>202</v>
@@ -5999,18 +5999,18 @@
         <v>221</v>
       </c>
       <c r="E199" t="n">
-        <v>6.59</v>
+        <v>7.93</v>
       </c>
       <c r="F199" t="n">
-        <v>82.33</v>
+        <v>120.44</v>
       </c>
       <c r="G199" t="n">
-        <v>1521.65</v>
+        <v>2712.28</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B200" t="s">
         <v>202</v>
@@ -6022,18 +6022,18 @@
         <v>223</v>
       </c>
       <c r="E200" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="F200" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="G200" t="n">
-        <v>5.44</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B201" t="s">
         <v>202</v>
@@ -6045,18 +6045,18 @@
         <v>224</v>
       </c>
       <c r="E201" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="F201" t="n">
-        <v>2.65</v>
+        <v>3.94</v>
       </c>
       <c r="G201" t="n">
-        <v>6.85</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B202" t="s">
         <v>202</v>
@@ -6068,18 +6068,18 @@
         <v>225</v>
       </c>
       <c r="E202" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="F202" t="n">
-        <v>3.24</v>
+        <v>3.98</v>
       </c>
       <c r="G202" t="n">
-        <v>9.64</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B203" t="s">
         <v>202</v>
@@ -6091,18 +6091,18 @@
         <v>226</v>
       </c>
       <c r="E203" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="F203" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="G203" t="n">
-        <v>10.43</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B204" t="s">
         <v>202</v>
@@ -6114,18 +6114,18 @@
         <v>227</v>
       </c>
       <c r="E204" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="F204" t="n">
-        <v>5.85</v>
+        <v>4.05</v>
       </c>
       <c r="G204" t="n">
-        <v>25.23</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B205" t="s">
         <v>202</v>
@@ -6137,18 +6137,18 @@
         <v>228</v>
       </c>
       <c r="E205" t="n">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="F205" t="n">
-        <v>7.19</v>
+        <v>4.34</v>
       </c>
       <c r="G205" t="n">
-        <v>35.09</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B206" t="s">
         <v>202</v>
@@ -6160,18 +6160,18 @@
         <v>229</v>
       </c>
       <c r="E206" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="F206" t="n">
-        <v>7.43</v>
+        <v>5.67</v>
       </c>
       <c r="G206" t="n">
-        <v>37.01</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B207" t="s">
         <v>202</v>
@@ -6183,18 +6183,18 @@
         <v>230</v>
       </c>
       <c r="E207" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="F207" t="n">
-        <v>8.36</v>
+        <v>6.3</v>
       </c>
       <c r="G207" t="n">
-        <v>44.58</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B208" t="s">
         <v>202</v>
@@ -6206,18 +6206,18 @@
         <v>231</v>
       </c>
       <c r="E208" t="n">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="F208" t="n">
-        <v>11.9</v>
+        <v>7.11</v>
       </c>
       <c r="G208" t="n">
-        <v>77.62</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B209" t="s">
         <v>202</v>
@@ -6229,18 +6229,18 @@
         <v>232</v>
       </c>
       <c r="E209" t="n">
-        <v>2.93</v>
+        <v>2.1</v>
       </c>
       <c r="F209" t="n">
-        <v>15.07</v>
+        <v>7.24</v>
       </c>
       <c r="G209" t="n">
-        <v>112.27</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B210" t="s">
         <v>202</v>
@@ -6252,18 +6252,18 @@
         <v>233</v>
       </c>
       <c r="E210" t="n">
-        <v>3.11</v>
+        <v>2.63</v>
       </c>
       <c r="F210" t="n">
-        <v>17.19</v>
+        <v>11.99</v>
       </c>
       <c r="G210" t="n">
-        <v>137.7</v>
+        <v>78.56</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B211" t="s">
         <v>202</v>
@@ -6275,18 +6275,18 @@
         <v>234</v>
       </c>
       <c r="E211" t="n">
-        <v>3.44</v>
+        <v>2.68</v>
       </c>
       <c r="F211" t="n">
-        <v>21.27</v>
+        <v>12.47</v>
       </c>
       <c r="G211" t="n">
-        <v>191.52</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B212" t="s">
         <v>202</v>
@@ -6298,18 +6298,18 @@
         <v>235</v>
       </c>
       <c r="E212" t="n">
-        <v>3.82</v>
+        <v>2.74</v>
       </c>
       <c r="F212" t="n">
-        <v>26.44</v>
+        <v>13.05</v>
       </c>
       <c r="G212" t="n">
-        <v>267.86</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B213" t="s">
         <v>202</v>
@@ -6321,18 +6321,18 @@
         <v>236</v>
       </c>
       <c r="E213" t="n">
-        <v>4.51</v>
+        <v>3.19</v>
       </c>
       <c r="F213" t="n">
-        <v>37.51</v>
+        <v>18.08</v>
       </c>
       <c r="G213" t="n">
-        <v>458.45</v>
+        <v>148.91</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B214" t="s">
         <v>202</v>
@@ -6344,18 +6344,18 @@
         <v>237</v>
       </c>
       <c r="E214" t="n">
-        <v>4.67</v>
+        <v>3.43</v>
       </c>
       <c r="F214" t="n">
-        <v>40.37</v>
+        <v>21.18</v>
       </c>
       <c r="G214" t="n">
-        <v>513.08</v>
+        <v>190.24</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B215" t="s">
         <v>202</v>
@@ -6367,18 +6367,18 @@
         <v>238</v>
       </c>
       <c r="E215" t="n">
-        <v>4.8</v>
+        <v>4.16</v>
       </c>
       <c r="F215" t="n">
-        <v>42.68</v>
+        <v>31.67</v>
       </c>
       <c r="G215" t="n">
-        <v>558.58</v>
+        <v>353.59</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B216" t="s">
         <v>202</v>
@@ -6390,18 +6390,18 @@
         <v>239</v>
       </c>
       <c r="E216" t="n">
-        <v>4.81</v>
+        <v>4.32</v>
       </c>
       <c r="F216" t="n">
-        <v>42.86</v>
+        <v>34.34</v>
       </c>
       <c r="G216" t="n">
-        <v>562.16</v>
+        <v>400.33</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B217" t="s">
         <v>202</v>
@@ -6413,18 +6413,18 @@
         <v>240</v>
       </c>
       <c r="E217" t="n">
-        <v>5.21</v>
+        <v>5.53</v>
       </c>
       <c r="F217" t="n">
-        <v>50.71</v>
+        <v>57.36</v>
       </c>
       <c r="G217" t="n">
-        <v>727.16</v>
+        <v>877.62</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B218" t="s">
         <v>241</v>
@@ -6436,18 +6436,18 @@
         <v>243</v>
       </c>
       <c r="E218" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="F218" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="G218" t="n">
-        <v>4.89</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B219" t="s">
         <v>241</v>
@@ -6459,18 +6459,18 @@
         <v>244</v>
       </c>
       <c r="E219" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="F219" t="n">
-        <v>2.23</v>
+        <v>2.68</v>
       </c>
       <c r="G219" t="n">
-        <v>5.1</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B220" t="s">
         <v>241</v>
@@ -6488,12 +6488,12 @@
         <v>3.01</v>
       </c>
       <c r="G220" t="n">
-        <v>8.51</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B221" t="s">
         <v>241</v>
@@ -6505,18 +6505,18 @@
         <v>246</v>
       </c>
       <c r="E221" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="F221" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="G221" t="n">
-        <v>10.16</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B222" t="s">
         <v>241</v>
@@ -6528,18 +6528,18 @@
         <v>247</v>
       </c>
       <c r="E222" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="F222" t="n">
-        <v>3.36</v>
+        <v>4.4</v>
       </c>
       <c r="G222" t="n">
-        <v>10.22</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B223" t="s">
         <v>241</v>
@@ -6551,18 +6551,18 @@
         <v>248</v>
       </c>
       <c r="E223" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="F223" t="n">
-        <v>4.39</v>
+        <v>4.95</v>
       </c>
       <c r="G223" t="n">
-        <v>15.89</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B224" t="s">
         <v>241</v>
@@ -6574,18 +6574,18 @@
         <v>249</v>
       </c>
       <c r="E224" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="F224" t="n">
-        <v>4.62</v>
+        <v>5.88</v>
       </c>
       <c r="G224" t="n">
-        <v>17.22</v>
+        <v>25.43</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B225" t="s">
         <v>241</v>
@@ -6597,18 +6597,18 @@
         <v>250</v>
       </c>
       <c r="E225" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="F225" t="n">
-        <v>5.54</v>
+        <v>7.46</v>
       </c>
       <c r="G225" t="n">
-        <v>23.14</v>
+        <v>37.19</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B226" t="s">
         <v>241</v>
@@ -6620,18 +6620,18 @@
         <v>251</v>
       </c>
       <c r="E226" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="F226" t="n">
-        <v>5.84</v>
+        <v>7.48</v>
       </c>
       <c r="G226" t="n">
-        <v>25.15</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B227" t="s">
         <v>241</v>
@@ -6643,18 +6643,18 @@
         <v>252</v>
       </c>
       <c r="E227" t="n">
-        <v>1.96</v>
+        <v>3.05</v>
       </c>
       <c r="F227" t="n">
-        <v>6.25</v>
+        <v>16.47</v>
       </c>
       <c r="G227" t="n">
-        <v>28.1</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B228" t="s">
         <v>241</v>
@@ -6666,18 +6666,18 @@
         <v>253</v>
       </c>
       <c r="E228" t="n">
-        <v>1.97</v>
+        <v>3.12</v>
       </c>
       <c r="F228" t="n">
-        <v>6.32</v>
+        <v>17.24</v>
       </c>
       <c r="G228" t="n">
-        <v>28.61</v>
+        <v>138.38</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B229" t="s">
         <v>241</v>
@@ -6689,18 +6689,18 @@
         <v>254</v>
       </c>
       <c r="E229" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="F229" t="n">
-        <v>12.24</v>
+        <v>23.45</v>
       </c>
       <c r="G229" t="n">
-        <v>81.19</v>
+        <v>222.62</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B230" t="s">
         <v>241</v>
@@ -6712,18 +6712,18 @@
         <v>255</v>
       </c>
       <c r="E230" t="n">
-        <v>2.74</v>
+        <v>3.69</v>
       </c>
       <c r="F230" t="n">
-        <v>13.04</v>
+        <v>24.63</v>
       </c>
       <c r="G230" t="n">
-        <v>89.6</v>
+        <v>240.07</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B231" t="s">
         <v>241</v>
@@ -6735,18 +6735,18 @@
         <v>256</v>
       </c>
       <c r="E231" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="F231" t="n">
-        <v>13.2</v>
+        <v>26.26</v>
       </c>
       <c r="G231" t="n">
-        <v>91.3</v>
+        <v>265</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B232" t="s">
         <v>241</v>
@@ -6758,18 +6758,18 @@
         <v>257</v>
       </c>
       <c r="E232" t="n">
-        <v>3.9</v>
+        <v>4.86</v>
       </c>
       <c r="F232" t="n">
-        <v>27.66</v>
+        <v>43.89</v>
       </c>
       <c r="G232" t="n">
-        <v>287.17</v>
+        <v>583.09</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B233" t="s">
         <v>241</v>
@@ -6781,18 +6781,18 @@
         <v>258</v>
       </c>
       <c r="E233" t="n">
-        <v>4.56</v>
+        <v>5.25</v>
       </c>
       <c r="F233" t="n">
-        <v>38.42</v>
+        <v>51.49</v>
       </c>
       <c r="G233" t="n">
-        <v>475.44</v>
+        <v>744.22</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B234" t="s">
         <v>241</v>
@@ -6804,18 +6804,18 @@
         <v>259</v>
       </c>
       <c r="E234" t="n">
-        <v>5.77</v>
+        <v>6.29</v>
       </c>
       <c r="F234" t="n">
-        <v>62.7</v>
+        <v>74.81</v>
       </c>
       <c r="G234" t="n">
-        <v>1005.23</v>
+        <v>1315.29</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B235" t="s">
         <v>241</v>
@@ -6827,18 +6827,18 @@
         <v>260</v>
       </c>
       <c r="E235" t="n">
-        <v>7.42</v>
+        <v>6.84</v>
       </c>
       <c r="F235" t="n">
-        <v>105.02</v>
+        <v>88.82</v>
       </c>
       <c r="G235" t="n">
-        <v>2203.06</v>
+        <v>1707.81</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B236" t="s">
         <v>241</v>
@@ -6850,18 +6850,18 @@
         <v>262</v>
       </c>
       <c r="E236" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="F236" t="n">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="G236" t="n">
-        <v>3.79</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B237" t="s">
         <v>241</v>
@@ -6873,18 +6873,18 @@
         <v>263</v>
       </c>
       <c r="E237" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="F237" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="G237" t="n">
-        <v>8.7</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="s">
         <v>241</v>
@@ -6896,18 +6896,18 @@
         <v>264</v>
       </c>
       <c r="E238" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="F238" t="n">
-        <v>3.64</v>
+        <v>2.82</v>
       </c>
       <c r="G238" t="n">
-        <v>11.7</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="s">
         <v>241</v>
@@ -6919,18 +6919,18 @@
         <v>265</v>
       </c>
       <c r="E239" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="F239" t="n">
-        <v>4.54</v>
+        <v>2.88</v>
       </c>
       <c r="G239" t="n">
-        <v>16.79</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="s">
         <v>241</v>
@@ -6942,18 +6942,18 @@
         <v>266</v>
       </c>
       <c r="E240" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="F240" t="n">
-        <v>4.57</v>
+        <v>3.14</v>
       </c>
       <c r="G240" t="n">
-        <v>16.92</v>
+        <v>9.12</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="s">
         <v>241</v>
@@ -6965,18 +6965,18 @@
         <v>267</v>
       </c>
       <c r="E241" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="F241" t="n">
-        <v>4.96</v>
+        <v>3.81</v>
       </c>
       <c r="G241" t="n">
-        <v>19.35</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B242" t="s">
         <v>241</v>
@@ -6988,18 +6988,18 @@
         <v>268</v>
       </c>
       <c r="E242" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="F242" t="n">
-        <v>5.17</v>
+        <v>4.57</v>
       </c>
       <c r="G242" t="n">
-        <v>20.67</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B243" t="s">
         <v>241</v>
@@ -7011,18 +7011,18 @@
         <v>269</v>
       </c>
       <c r="E243" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="F243" t="n">
-        <v>6.41</v>
+        <v>6.05</v>
       </c>
       <c r="G243" t="n">
-        <v>29.23</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B244" t="s">
         <v>241</v>
@@ -7034,18 +7034,18 @@
         <v>270</v>
       </c>
       <c r="E244" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="F244" t="n">
-        <v>6.62</v>
+        <v>7.53</v>
       </c>
       <c r="G244" t="n">
-        <v>30.74</v>
+        <v>37.77</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B245" t="s">
         <v>241</v>
@@ -7057,18 +7057,18 @@
         <v>271</v>
       </c>
       <c r="E245" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="F245" t="n">
-        <v>10.15</v>
+        <v>9.5</v>
       </c>
       <c r="G245" t="n">
-        <v>60.5</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B246" t="s">
         <v>241</v>
@@ -7080,18 +7080,18 @@
         <v>272</v>
       </c>
       <c r="E246" t="n">
-        <v>3.24</v>
+        <v>2.54</v>
       </c>
       <c r="F246" t="n">
-        <v>18.72</v>
+        <v>11.04</v>
       </c>
       <c r="G246" t="n">
-        <v>157.16</v>
+        <v>69.03</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B247" t="s">
         <v>241</v>
@@ -7103,18 +7103,18 @@
         <v>273</v>
       </c>
       <c r="E247" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="F247" t="n">
-        <v>18.89</v>
+        <v>14.65</v>
       </c>
       <c r="G247" t="n">
-        <v>159.36</v>
+        <v>107.42</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B248" t="s">
         <v>241</v>
@@ -7126,18 +7126,18 @@
         <v>274</v>
       </c>
       <c r="E248" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="F248" t="n">
-        <v>23.45</v>
+        <v>16.59</v>
       </c>
       <c r="G248" t="n">
-        <v>222.7</v>
+        <v>130.38</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B249" t="s">
         <v>241</v>
@@ -7149,18 +7149,18 @@
         <v>275</v>
       </c>
       <c r="E249" t="n">
-        <v>3.96</v>
+        <v>3.91</v>
       </c>
       <c r="F249" t="n">
-        <v>28.59</v>
+        <v>27.91</v>
       </c>
       <c r="G249" t="n">
-        <v>302.16</v>
+        <v>291.12</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B250" t="s">
         <v>241</v>
@@ -7172,18 +7172,18 @@
         <v>276</v>
       </c>
       <c r="E250" t="n">
-        <v>5.25</v>
+        <v>4.16</v>
       </c>
       <c r="F250" t="n">
-        <v>51.54</v>
+        <v>31.69</v>
       </c>
       <c r="G250" t="n">
-        <v>745.25</v>
+        <v>353.88</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B251" t="s">
         <v>241</v>
@@ -7195,18 +7195,18 @@
         <v>277</v>
       </c>
       <c r="E251" t="n">
-        <v>5.87</v>
+        <v>4.48</v>
       </c>
       <c r="F251" t="n">
-        <v>64.99</v>
+        <v>37.02</v>
       </c>
       <c r="G251" t="n">
-        <v>1061.6</v>
+        <v>449.19</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B252" t="s">
         <v>241</v>
@@ -7218,18 +7218,18 @@
         <v>278</v>
       </c>
       <c r="E252" t="n">
-        <v>6.12</v>
+        <v>4.64</v>
       </c>
       <c r="F252" t="n">
-        <v>70.73</v>
+        <v>39.91</v>
       </c>
       <c r="G252" t="n">
-        <v>1207.62</v>
+        <v>504.08</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B253" t="s">
         <v>241</v>
@@ -7241,18 +7241,18 @@
         <v>279</v>
       </c>
       <c r="E253" t="n">
-        <v>9.85</v>
+        <v>4.95</v>
       </c>
       <c r="F253" t="n">
-        <v>187.45</v>
+        <v>45.5</v>
       </c>
       <c r="G253" t="n">
-        <v>5301.95</v>
+        <v>616.14</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B254" t="s">
         <v>280</v>
@@ -7264,18 +7264,18 @@
         <v>282</v>
       </c>
       <c r="E254" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="F254" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="G254" t="n">
-        <v>6.43</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B255" t="s">
         <v>280</v>
@@ -7287,18 +7287,18 @@
         <v>283</v>
       </c>
       <c r="E255" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="F255" t="n">
-        <v>3.51</v>
+        <v>2.83</v>
       </c>
       <c r="G255" t="n">
-        <v>11.02</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B256" t="s">
         <v>280</v>
@@ -7310,18 +7310,18 @@
         <v>284</v>
       </c>
       <c r="E256" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="F256" t="n">
-        <v>3.88</v>
+        <v>3.19</v>
       </c>
       <c r="G256" t="n">
-        <v>12.99</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B257" t="s">
         <v>280</v>
@@ -7333,18 +7333,18 @@
         <v>285</v>
       </c>
       <c r="E257" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="F257" t="n">
-        <v>4.43</v>
+        <v>3.48</v>
       </c>
       <c r="G257" t="n">
-        <v>16.13</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B258" t="s">
         <v>280</v>
@@ -7356,18 +7356,18 @@
         <v>286</v>
       </c>
       <c r="E258" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="F258" t="n">
-        <v>4.71</v>
+        <v>5.72</v>
       </c>
       <c r="G258" t="n">
-        <v>17.81</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B259" t="s">
         <v>280</v>
@@ -7379,18 +7379,18 @@
         <v>287</v>
       </c>
       <c r="E259" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="F259" t="n">
-        <v>5.52</v>
+        <v>7.69</v>
       </c>
       <c r="G259" t="n">
-        <v>22.97</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B260" t="s">
         <v>280</v>
@@ -7402,18 +7402,18 @@
         <v>288</v>
       </c>
       <c r="E260" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="F260" t="n">
-        <v>7.46</v>
+        <v>8.49</v>
       </c>
       <c r="G260" t="n">
-        <v>37.18</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B261" t="s">
         <v>280</v>
@@ -7425,18 +7425,18 @@
         <v>289</v>
       </c>
       <c r="E261" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="F261" t="n">
-        <v>8.97</v>
+        <v>9.36</v>
       </c>
       <c r="G261" t="n">
-        <v>49.84</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B262" t="s">
         <v>280</v>
@@ -7448,18 +7448,18 @@
         <v>290</v>
       </c>
       <c r="E262" t="n">
-        <v>2.37</v>
+        <v>2.76</v>
       </c>
       <c r="F262" t="n">
-        <v>9.51</v>
+        <v>13.24</v>
       </c>
       <c r="G262" t="n">
-        <v>54.63</v>
+        <v>91.76</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B263" t="s">
         <v>280</v>
@@ -7471,18 +7471,18 @@
         <v>291</v>
       </c>
       <c r="E263" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="F263" t="n">
-        <v>15.08</v>
+        <v>15.43</v>
       </c>
       <c r="G263" t="n">
-        <v>112.35</v>
+        <v>116.45</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B264" t="s">
         <v>280</v>
@@ -7497,15 +7497,15 @@
         <v>2.99</v>
       </c>
       <c r="F264" t="n">
-        <v>15.81</v>
+        <v>15.78</v>
       </c>
       <c r="G264" t="n">
-        <v>120.92</v>
+        <v>120.62</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B265" t="s">
         <v>280</v>
@@ -7517,18 +7517,18 @@
         <v>293</v>
       </c>
       <c r="E265" t="n">
-        <v>4.18</v>
+        <v>3.64</v>
       </c>
       <c r="F265" t="n">
-        <v>32.05</v>
+        <v>23.94</v>
       </c>
       <c r="G265" t="n">
-        <v>360.03</v>
+        <v>229.84</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B266" t="s">
         <v>280</v>
@@ -7540,18 +7540,18 @@
         <v>294</v>
       </c>
       <c r="E266" t="n">
-        <v>4.46</v>
+        <v>4.04</v>
       </c>
       <c r="F266" t="n">
-        <v>36.6</v>
+        <v>29.86</v>
       </c>
       <c r="G266" t="n">
-        <v>441.46</v>
+        <v>323.01</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B267" t="s">
         <v>280</v>
@@ -7563,18 +7563,18 @@
         <v>295</v>
       </c>
       <c r="E267" t="n">
-        <v>4.49</v>
+        <v>4.8</v>
       </c>
       <c r="F267" t="n">
-        <v>37.19</v>
+        <v>42.75</v>
       </c>
       <c r="G267" t="n">
-        <v>452.32</v>
+        <v>560.1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B268" t="s">
         <v>280</v>
@@ -7586,18 +7586,18 @@
         <v>296</v>
       </c>
       <c r="E268" t="n">
-        <v>4.52</v>
+        <v>4.84</v>
       </c>
       <c r="F268" t="n">
-        <v>37.78</v>
+        <v>43.47</v>
       </c>
       <c r="G268" t="n">
-        <v>463.39</v>
+        <v>574.54</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B269" t="s">
         <v>280</v>
@@ -7609,18 +7609,18 @@
         <v>297</v>
       </c>
       <c r="E269" t="n">
-        <v>7.79</v>
+        <v>5.08</v>
       </c>
       <c r="F269" t="n">
-        <v>115.96</v>
+        <v>48.18</v>
       </c>
       <c r="G269" t="n">
-        <v>2560.64</v>
+        <v>672.35</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B270" t="s">
         <v>280</v>
@@ -7632,18 +7632,18 @@
         <v>298</v>
       </c>
       <c r="E270" t="n">
-        <v>8.29</v>
+        <v>5.2</v>
       </c>
       <c r="F270" t="n">
-        <v>131.89</v>
+        <v>50.4</v>
       </c>
       <c r="G270" t="n">
-        <v>3112.75</v>
+        <v>720.27</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B271" t="s">
         <v>280</v>
@@ -7655,18 +7655,18 @@
         <v>299</v>
       </c>
       <c r="E271" t="n">
-        <v>10.01</v>
+        <v>5.46</v>
       </c>
       <c r="F271" t="n">
-        <v>193.45</v>
+        <v>55.83</v>
       </c>
       <c r="G271" t="n">
-        <v>5560.9</v>
+        <v>841.98</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B272" t="s">
         <v>280</v>
@@ -7678,18 +7678,18 @@
         <v>301</v>
       </c>
       <c r="E272" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="F272" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="G272" t="n">
-        <v>4.69</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B273" t="s">
         <v>280</v>
@@ -7701,18 +7701,18 @@
         <v>302</v>
       </c>
       <c r="E273" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="F273" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="G273" t="n">
-        <v>6.22</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B274" t="s">
         <v>280</v>
@@ -7724,18 +7724,18 @@
         <v>303</v>
       </c>
       <c r="E274" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="F274" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="G274" t="n">
-        <v>6.75</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B275" t="s">
         <v>280</v>
@@ -7747,18 +7747,18 @@
         <v>304</v>
       </c>
       <c r="E275" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="F275" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G275" t="n">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B276" t="s">
         <v>280</v>
@@ -7770,18 +7770,18 @@
         <v>305</v>
       </c>
       <c r="E276" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="F276" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="G276" t="n">
-        <v>9.82</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B277" t="s">
         <v>280</v>
@@ -7793,18 +7793,18 @@
         <v>306</v>
       </c>
       <c r="E277" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="F277" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="G277" t="n">
-        <v>10.94</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B278" t="s">
         <v>280</v>
@@ -7816,18 +7816,18 @@
         <v>307</v>
       </c>
       <c r="E278" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="F278" t="n">
-        <v>4.67</v>
+        <v>3.45</v>
       </c>
       <c r="G278" t="n">
-        <v>17.57</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B279" t="s">
         <v>280</v>
@@ -7839,18 +7839,18 @@
         <v>308</v>
       </c>
       <c r="E279" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="F279" t="n">
-        <v>6.13</v>
+        <v>4.04</v>
       </c>
       <c r="G279" t="n">
-        <v>27.22</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B280" t="s">
         <v>280</v>
@@ -7862,18 +7862,18 @@
         <v>309</v>
       </c>
       <c r="E280" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="F280" t="n">
-        <v>7.09</v>
+        <v>5.2</v>
       </c>
       <c r="G280" t="n">
-        <v>34.35</v>
+        <v>20.87</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B281" t="s">
         <v>280</v>
@@ -7885,18 +7885,18 @@
         <v>310</v>
       </c>
       <c r="E281" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="F281" t="n">
-        <v>8.94</v>
+        <v>5.28</v>
       </c>
       <c r="G281" t="n">
-        <v>49.55</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B282" t="s">
         <v>280</v>
@@ -7908,18 +7908,18 @@
         <v>311</v>
       </c>
       <c r="E282" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="F282" t="n">
-        <v>10.69</v>
+        <v>5.56</v>
       </c>
       <c r="G282" t="n">
-        <v>65.68</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B283" t="s">
         <v>280</v>
@@ -7931,18 +7931,18 @@
         <v>312</v>
       </c>
       <c r="E283" t="n">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="F283" t="n">
-        <v>13.25</v>
+        <v>6.89</v>
       </c>
       <c r="G283" t="n">
-        <v>91.86</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B284" t="s">
         <v>280</v>
@@ -7954,18 +7954,18 @@
         <v>313</v>
       </c>
       <c r="E284" t="n">
-        <v>3.13</v>
+        <v>2.91</v>
       </c>
       <c r="F284" t="n">
-        <v>17.39</v>
+        <v>14.9</v>
       </c>
       <c r="G284" t="n">
-        <v>140.17</v>
+        <v>110.23</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B285" t="s">
         <v>280</v>
@@ -7977,18 +7977,18 @@
         <v>314</v>
       </c>
       <c r="E285" t="n">
-        <v>3.7</v>
+        <v>2.97</v>
       </c>
       <c r="F285" t="n">
-        <v>24.76</v>
+        <v>15.52</v>
       </c>
       <c r="G285" t="n">
-        <v>242.07</v>
+        <v>117.56</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B286" t="s">
         <v>280</v>
@@ -8000,18 +8000,18 @@
         <v>315</v>
       </c>
       <c r="E286" t="n">
-        <v>3.95</v>
+        <v>3.16</v>
       </c>
       <c r="F286" t="n">
-        <v>28.46</v>
+        <v>17.74</v>
       </c>
       <c r="G286" t="n">
-        <v>300.06</v>
+        <v>144.64</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B287" t="s">
         <v>280</v>
@@ -8023,18 +8023,18 @@
         <v>316</v>
       </c>
       <c r="E287" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="F287" t="n">
-        <v>34.15</v>
+        <v>36.06</v>
       </c>
       <c r="G287" t="n">
-        <v>396.96</v>
+        <v>431.43</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B288" t="s">
         <v>280</v>
@@ -8046,18 +8046,18 @@
         <v>317</v>
       </c>
       <c r="E288" t="n">
-        <v>4.67</v>
+        <v>4.59</v>
       </c>
       <c r="F288" t="n">
-        <v>40.3</v>
+        <v>39.02</v>
       </c>
       <c r="G288" t="n">
-        <v>511.69</v>
+        <v>487.01</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B289" t="s">
         <v>280</v>
@@ -8069,18 +8069,18 @@
         <v>318</v>
       </c>
       <c r="E289" t="n">
-        <v>4.8</v>
+        <v>8.2</v>
       </c>
       <c r="F289" t="n">
-        <v>42.7</v>
+        <v>128.9</v>
       </c>
       <c r="G289" t="n">
-        <v>559.01</v>
+        <v>3006.49</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B290" t="s">
         <v>319</v>
@@ -8092,18 +8092,18 @@
         <v>321</v>
       </c>
       <c r="E290" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="F290" t="n">
-        <v>2.39</v>
+        <v>1.29</v>
       </c>
       <c r="G290" t="n">
-        <v>5.77</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B291" t="s">
         <v>319</v>
@@ -8115,18 +8115,18 @@
         <v>322</v>
       </c>
       <c r="E291" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="F291" t="n">
-        <v>2.39</v>
+        <v>1.72</v>
       </c>
       <c r="G291" t="n">
-        <v>5.77</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B292" t="s">
         <v>319</v>
@@ -8138,18 +8138,18 @@
         <v>323</v>
       </c>
       <c r="E292" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="F292" t="n">
-        <v>2.83</v>
+        <v>2.04</v>
       </c>
       <c r="G292" t="n">
-        <v>7.67</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B293" t="s">
         <v>319</v>
@@ -8161,18 +8161,18 @@
         <v>324</v>
       </c>
       <c r="E293" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="F293" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="G293" t="n">
-        <v>7.9</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B294" t="s">
         <v>319</v>
@@ -8184,18 +8184,18 @@
         <v>325</v>
       </c>
       <c r="E294" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="F294" t="n">
-        <v>3.02</v>
+        <v>3.39</v>
       </c>
       <c r="G294" t="n">
-        <v>8.54</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B295" t="s">
         <v>319</v>
@@ -8207,18 +8207,18 @@
         <v>326</v>
       </c>
       <c r="E295" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="F295" t="n">
-        <v>3.07</v>
+        <v>3.43</v>
       </c>
       <c r="G295" t="n">
-        <v>8.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B296" t="s">
         <v>319</v>
@@ -8230,18 +8230,18 @@
         <v>327</v>
       </c>
       <c r="E296" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="F296" t="n">
-        <v>4.48</v>
+        <v>4.03</v>
       </c>
       <c r="G296" t="n">
-        <v>16.4</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B297" t="s">
         <v>319</v>
@@ -8253,18 +8253,18 @@
         <v>328</v>
       </c>
       <c r="E297" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="F297" t="n">
-        <v>7.79</v>
+        <v>4.68</v>
       </c>
       <c r="G297" t="n">
-        <v>39.83</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B298" t="s">
         <v>319</v>
@@ -8276,18 +8276,18 @@
         <v>329</v>
       </c>
       <c r="E298" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="F298" t="n">
-        <v>9.39</v>
+        <v>10.9</v>
       </c>
       <c r="G298" t="n">
-        <v>53.53</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B299" t="s">
         <v>319</v>
@@ -8299,18 +8299,18 @@
         <v>330</v>
       </c>
       <c r="E299" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="F299" t="n">
-        <v>13.15</v>
+        <v>15.39</v>
       </c>
       <c r="G299" t="n">
-        <v>90.82</v>
+        <v>116</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B300" t="s">
         <v>319</v>
@@ -8322,18 +8322,18 @@
         <v>331</v>
       </c>
       <c r="E300" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="F300" t="n">
-        <v>13.93</v>
+        <v>19.47</v>
       </c>
       <c r="G300" t="n">
-        <v>99.27</v>
+        <v>167.08</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B301" t="s">
         <v>319</v>
@@ -8345,18 +8345,18 @@
         <v>332</v>
       </c>
       <c r="E301" t="n">
-        <v>2.89</v>
+        <v>3.45</v>
       </c>
       <c r="F301" t="n">
-        <v>14.64</v>
+        <v>21.32</v>
       </c>
       <c r="G301" t="n">
-        <v>107.33</v>
+        <v>192.25</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B302" t="s">
         <v>319</v>
@@ -8368,18 +8368,18 @@
         <v>333</v>
       </c>
       <c r="E302" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="F302" t="n">
-        <v>15.67</v>
+        <v>21.4</v>
       </c>
       <c r="G302" t="n">
-        <v>119.32</v>
+        <v>193.37</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B303" t="s">
         <v>319</v>
@@ -8391,18 +8391,18 @@
         <v>334</v>
       </c>
       <c r="E303" t="n">
-        <v>3.22</v>
+        <v>3.69</v>
       </c>
       <c r="F303" t="n">
-        <v>18.46</v>
+        <v>24.59</v>
       </c>
       <c r="G303" t="n">
-        <v>153.77</v>
+        <v>239.52</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B304" t="s">
         <v>319</v>
@@ -8414,18 +8414,18 @@
         <v>335</v>
       </c>
       <c r="E304" t="n">
-        <v>3.47</v>
+        <v>3.83</v>
       </c>
       <c r="F304" t="n">
-        <v>21.7</v>
+        <v>26.59</v>
       </c>
       <c r="G304" t="n">
-        <v>197.52</v>
+        <v>270.24</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B305" t="s">
         <v>319</v>
@@ -8437,18 +8437,18 @@
         <v>336</v>
       </c>
       <c r="E305" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="F305" t="n">
-        <v>65.65</v>
+        <v>27.72</v>
       </c>
       <c r="G305" t="n">
-        <v>1077.98</v>
+        <v>288.07</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B306" t="s">
         <v>319</v>
@@ -8460,18 +8460,18 @@
         <v>337</v>
       </c>
       <c r="E306" t="n">
-        <v>6.76</v>
+        <v>3.91</v>
       </c>
       <c r="F306" t="n">
-        <v>86.65</v>
+        <v>27.81</v>
       </c>
       <c r="G306" t="n">
-        <v>1644.69</v>
+        <v>289.5</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B307" t="s">
         <v>319</v>
@@ -8483,18 +8483,18 @@
         <v>338</v>
       </c>
       <c r="E307" t="n">
-        <v>9.77</v>
+        <v>5.29</v>
       </c>
       <c r="F307" t="n">
-        <v>184.32</v>
+        <v>52.32</v>
       </c>
       <c r="G307" t="n">
-        <v>5168.34</v>
+        <v>762.65</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B308" t="s">
         <v>319</v>
@@ -8506,18 +8506,18 @@
         <v>340</v>
       </c>
       <c r="E308" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="F308" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="G308" t="n">
-        <v>3.71</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B309" t="s">
         <v>319</v>
@@ -8529,18 +8529,18 @@
         <v>341</v>
       </c>
       <c r="E309" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="F309" t="n">
-        <v>4.22</v>
+        <v>3.02</v>
       </c>
       <c r="G309" t="n">
-        <v>14.86</v>
+        <v>8.54</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B310" t="s">
         <v>319</v>
@@ -8552,18 +8552,18 @@
         <v>342</v>
       </c>
       <c r="E310" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="F310" t="n">
-        <v>4.4</v>
+        <v>4.26</v>
       </c>
       <c r="G310" t="n">
-        <v>15.91</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B311" t="s">
         <v>319</v>
@@ -8575,18 +8575,18 @@
         <v>343</v>
       </c>
       <c r="E311" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="F311" t="n">
-        <v>4.41</v>
+        <v>5.05</v>
       </c>
       <c r="G311" t="n">
-        <v>16.01</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B312" t="s">
         <v>319</v>
@@ -8598,18 +8598,18 @@
         <v>344</v>
       </c>
       <c r="E312" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F312" t="n">
-        <v>4.47</v>
+        <v>5.83</v>
       </c>
       <c r="G312" t="n">
-        <v>16.34</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B313" t="s">
         <v>319</v>
@@ -8621,18 +8621,18 @@
         <v>345</v>
       </c>
       <c r="E313" t="n">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="F313" t="n">
-        <v>4.87</v>
+        <v>6.61</v>
       </c>
       <c r="G313" t="n">
-        <v>18.81</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B314" t="s">
         <v>319</v>
@@ -8644,18 +8644,18 @@
         <v>346</v>
       </c>
       <c r="E314" t="n">
-        <v>1.97</v>
+        <v>2.49</v>
       </c>
       <c r="F314" t="n">
-        <v>6.29</v>
+        <v>10.57</v>
       </c>
       <c r="G314" t="n">
-        <v>28.34</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B315" t="s">
         <v>319</v>
@@ -8667,18 +8667,18 @@
         <v>347</v>
       </c>
       <c r="E315" t="n">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="F315" t="n">
-        <v>8.53</v>
+        <v>10.95</v>
       </c>
       <c r="G315" t="n">
-        <v>46.01</v>
+        <v>68.14</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B316" t="s">
         <v>319</v>
@@ -8690,18 +8690,18 @@
         <v>348</v>
       </c>
       <c r="E316" t="n">
-        <v>2.27</v>
+        <v>2.61</v>
       </c>
       <c r="F316" t="n">
-        <v>8.63</v>
+        <v>11.73</v>
       </c>
       <c r="G316" t="n">
-        <v>46.84</v>
+        <v>75.91</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B317" t="s">
         <v>319</v>
@@ -8713,18 +8713,18 @@
         <v>349</v>
       </c>
       <c r="E317" t="n">
-        <v>2.36</v>
+        <v>3.04</v>
       </c>
       <c r="F317" t="n">
-        <v>9.41</v>
+        <v>16.35</v>
       </c>
       <c r="G317" t="n">
-        <v>53.74</v>
+        <v>127.45</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B318" t="s">
         <v>319</v>
@@ -8736,18 +8736,18 @@
         <v>350</v>
       </c>
       <c r="E318" t="n">
-        <v>2.92</v>
+        <v>3.98</v>
       </c>
       <c r="F318" t="n">
-        <v>15.01</v>
+        <v>28.91</v>
       </c>
       <c r="G318" t="n">
-        <v>111.56</v>
+        <v>307.3</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B319" t="s">
         <v>319</v>
@@ -8759,18 +8759,18 @@
         <v>351</v>
       </c>
       <c r="E319" t="n">
-        <v>2.93</v>
+        <v>4.2</v>
       </c>
       <c r="F319" t="n">
-        <v>15.04</v>
+        <v>32.34</v>
       </c>
       <c r="G319" t="n">
-        <v>111.89</v>
+        <v>365.13</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B320" t="s">
         <v>319</v>
@@ -8782,18 +8782,18 @@
         <v>352</v>
       </c>
       <c r="E320" t="n">
-        <v>2.96</v>
+        <v>4.95</v>
       </c>
       <c r="F320" t="n">
-        <v>15.4</v>
+        <v>45.54</v>
       </c>
       <c r="G320" t="n">
-        <v>116.08</v>
+        <v>616.85</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B321" t="s">
         <v>319</v>
@@ -8805,18 +8805,18 @@
         <v>353</v>
       </c>
       <c r="E321" t="n">
-        <v>3.65</v>
+        <v>5.01</v>
       </c>
       <c r="F321" t="n">
-        <v>24.08</v>
+        <v>46.73</v>
       </c>
       <c r="G321" t="n">
-        <v>231.9</v>
+        <v>641.74</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B322" t="s">
         <v>319</v>
@@ -8828,18 +8828,18 @@
         <v>354</v>
       </c>
       <c r="E322" t="n">
-        <v>3.75</v>
+        <v>5.11</v>
       </c>
       <c r="F322" t="n">
-        <v>25.46</v>
+        <v>48.75</v>
       </c>
       <c r="G322" t="n">
-        <v>252.71</v>
+        <v>684.52</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B323" t="s">
         <v>319</v>
@@ -8851,18 +8851,18 @@
         <v>355</v>
       </c>
       <c r="E323" t="n">
-        <v>4.5</v>
+        <v>7.65</v>
       </c>
       <c r="F323" t="n">
-        <v>37.34</v>
+        <v>111.96</v>
       </c>
       <c r="G323" t="n">
-        <v>455.26</v>
+        <v>2427.67</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B324" t="s">
         <v>319</v>
@@ -8874,18 +8874,18 @@
         <v>356</v>
       </c>
       <c r="E324" t="n">
-        <v>4.55</v>
+        <v>13.03</v>
       </c>
       <c r="F324" t="n">
-        <v>38.24</v>
+        <v>330.62</v>
       </c>
       <c r="G324" t="n">
-        <v>472.08</v>
+        <v>12502.51</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B325" t="s">
         <v>319</v>
@@ -8897,13 +8897,13 @@
         <v>357</v>
       </c>
       <c r="E325" t="n">
-        <v>5.8</v>
+        <v>15.35</v>
       </c>
       <c r="F325" t="n">
-        <v>63.33</v>
+        <v>460.65</v>
       </c>
       <c r="G325" t="n">
-        <v>1020.63</v>
+        <v>20624.7</v>
       </c>
     </row>
   </sheetData>

--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -1468,13 +1468,13 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="F2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
-        <v>3.81</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="3">
@@ -1491,13 +1491,13 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G3" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="4">
@@ -1514,13 +1514,13 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="F4" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="G4" t="n">
-        <v>4.89</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="5">
@@ -1537,13 +1537,13 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="G5" t="n">
-        <v>6.66</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="6">
@@ -1560,13 +1560,13 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="F6" t="n">
-        <v>3.42</v>
+        <v>3.49</v>
       </c>
       <c r="G6" t="n">
-        <v>10.54</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="7">
@@ -1583,13 +1583,13 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="F7" t="n">
-        <v>5.02</v>
+        <v>5.13</v>
       </c>
       <c r="G7" t="n">
-        <v>19.75</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="8">
@@ -1606,13 +1606,13 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="F8" t="n">
-        <v>5.22</v>
+        <v>5.34</v>
       </c>
       <c r="G8" t="n">
-        <v>21.05</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="9">
@@ -1629,13 +1629,13 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="F9" t="n">
-        <v>5.44</v>
+        <v>5.56</v>
       </c>
       <c r="G9" t="n">
-        <v>22.46</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="10">
@@ -1652,13 +1652,13 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="F10" t="n">
-        <v>5.57</v>
+        <v>5.69</v>
       </c>
       <c r="G10" t="n">
-        <v>23.32</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="11">
@@ -1675,13 +1675,13 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>6.37</v>
+        <v>6.52</v>
       </c>
       <c r="G11" t="n">
-        <v>28.96</v>
+        <v>30.03</v>
       </c>
     </row>
     <row r="12">
@@ -1698,13 +1698,13 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="F12" t="n">
-        <v>15.15</v>
+        <v>15.53</v>
       </c>
       <c r="G12" t="n">
-        <v>113.16</v>
+        <v>117.66</v>
       </c>
     </row>
     <row r="13">
@@ -1721,13 +1721,13 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="F13" t="n">
-        <v>17.68</v>
+        <v>18.13</v>
       </c>
       <c r="G13" t="n">
-        <v>143.86</v>
+        <v>149.63</v>
       </c>
     </row>
     <row r="14">
@@ -1744,13 +1744,13 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="F14" t="n">
-        <v>18.26</v>
+        <v>18.73</v>
       </c>
       <c r="G14" t="n">
-        <v>151.22</v>
+        <v>157.29</v>
       </c>
     </row>
     <row r="15">
@@ -1767,13 +1767,13 @@
         <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="F15" t="n">
-        <v>21.02</v>
+        <v>21.57</v>
       </c>
       <c r="G15" t="n">
-        <v>188.03</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="16">
@@ -1790,13 +1790,13 @@
         <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="F16" t="n">
-        <v>22.76</v>
+        <v>23.35</v>
       </c>
       <c r="G16" t="n">
-        <v>212.6</v>
+        <v>221.24</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="F17" t="n">
-        <v>37.38</v>
+        <v>38.38</v>
       </c>
       <c r="G17" t="n">
-        <v>455.94</v>
+        <v>474.85</v>
       </c>
     </row>
     <row r="18">
@@ -1836,13 +1836,13 @@
         <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>6.39</v>
+        <v>6.48</v>
       </c>
       <c r="F18" t="n">
-        <v>77.36</v>
+        <v>79.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1384.12</v>
+        <v>1442.77</v>
       </c>
     </row>
     <row r="19">
@@ -1859,13 +1859,13 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>8.51</v>
+        <v>8.63</v>
       </c>
       <c r="F19" t="n">
-        <v>139.21</v>
+        <v>143.12</v>
       </c>
       <c r="G19" t="n">
-        <v>3378.37</v>
+        <v>3523.21</v>
       </c>
     </row>
     <row r="20">
@@ -1882,13 +1882,13 @@
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="F20" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="G20" t="n">
-        <v>4.78</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="21">
@@ -1905,13 +1905,13 @@
         <v>29</v>
       </c>
       <c r="E21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G21" t="n">
-        <v>4.97</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="22">
@@ -1928,13 +1928,13 @@
         <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="F22" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="G22" t="n">
-        <v>6.62</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="23">
@@ -1951,13 +1951,13 @@
         <v>31</v>
       </c>
       <c r="E23" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="F23" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="G23" t="n">
-        <v>9.62</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="24">
@@ -1974,13 +1974,13 @@
         <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="F24" t="n">
-        <v>5.1</v>
+        <v>5.24</v>
       </c>
       <c r="G24" t="n">
-        <v>20.26</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="25">
@@ -1997,13 +1997,13 @@
         <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="F25" t="n">
-        <v>5.57</v>
+        <v>5.73</v>
       </c>
       <c r="G25" t="n">
-        <v>23.33</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="26">
@@ -2020,13 +2020,13 @@
         <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="F26" t="n">
-        <v>5.82</v>
+        <v>5.99</v>
       </c>
       <c r="G26" t="n">
-        <v>25.06</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="27">
@@ -2043,13 +2043,13 @@
         <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="F27" t="n">
-        <v>13.57</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>95.32</v>
+        <v>100.13</v>
       </c>
     </row>
     <row r="28">
@@ -2066,13 +2066,13 @@
         <v>36</v>
       </c>
       <c r="E28" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="F28" t="n">
-        <v>15.23</v>
+        <v>15.73</v>
       </c>
       <c r="G28" t="n">
-        <v>114.13</v>
+        <v>119.94</v>
       </c>
     </row>
     <row r="29">
@@ -2089,13 +2089,13 @@
         <v>37</v>
       </c>
       <c r="E29" t="n">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="F29" t="n">
-        <v>20.37</v>
+        <v>21.05</v>
       </c>
       <c r="G29" t="n">
-        <v>179.11</v>
+        <v>188.38</v>
       </c>
     </row>
     <row r="30">
@@ -2112,13 +2112,13 @@
         <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="F30" t="n">
-        <v>22.06</v>
+        <v>22.79</v>
       </c>
       <c r="G30" t="n">
-        <v>202.54</v>
+        <v>213.07</v>
       </c>
     </row>
     <row r="31">
@@ -2135,13 +2135,13 @@
         <v>39</v>
       </c>
       <c r="E31" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="F31" t="n">
-        <v>23.83</v>
+        <v>24.63</v>
       </c>
       <c r="G31" t="n">
-        <v>228.21</v>
+        <v>240.12</v>
       </c>
     </row>
     <row r="32">
@@ -2158,13 +2158,13 @@
         <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="F32" t="n">
-        <v>24</v>
+        <v>24.81</v>
       </c>
       <c r="G32" t="n">
-        <v>230.77</v>
+        <v>242.82</v>
       </c>
     </row>
     <row r="33">
@@ -2181,13 +2181,13 @@
         <v>41</v>
       </c>
       <c r="E33" t="n">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="F33" t="n">
-        <v>41.05</v>
+        <v>42.47</v>
       </c>
       <c r="G33" t="n">
-        <v>526.24</v>
+        <v>554.33</v>
       </c>
     </row>
     <row r="34">
@@ -2204,13 +2204,13 @@
         <v>42</v>
       </c>
       <c r="E34" t="n">
-        <v>5.3</v>
+        <v>5.39</v>
       </c>
       <c r="F34" t="n">
-        <v>52.6</v>
+        <v>54.44</v>
       </c>
       <c r="G34" t="n">
-        <v>768.88</v>
+        <v>810.24</v>
       </c>
     </row>
     <row r="35">
@@ -2227,13 +2227,13 @@
         <v>43</v>
       </c>
       <c r="E35" t="n">
-        <v>6.48</v>
+        <v>6.59</v>
       </c>
       <c r="F35" t="n">
-        <v>79.56</v>
+        <v>82.38</v>
       </c>
       <c r="G35" t="n">
-        <v>1444.61</v>
+        <v>1523.17</v>
       </c>
     </row>
     <row r="36">
@@ -2250,13 +2250,13 @@
         <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>8.21</v>
+        <v>8.36</v>
       </c>
       <c r="F36" t="n">
-        <v>129.33</v>
+        <v>133.97</v>
       </c>
       <c r="G36" t="n">
-        <v>3021.38</v>
+        <v>3187.3</v>
       </c>
     </row>
     <row r="37">
@@ -2273,13 +2273,13 @@
         <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>13.9</v>
+        <v>14.15</v>
       </c>
       <c r="F37" t="n">
-        <v>377.01</v>
+        <v>390.79</v>
       </c>
       <c r="G37" t="n">
-        <v>15243.23</v>
+        <v>16092.35</v>
       </c>
     </row>
     <row r="38">
@@ -4786,7 +4786,7 @@
         <v>1.57</v>
       </c>
       <c r="G146" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="147">
@@ -4803,13 +4803,13 @@
         <v>166</v>
       </c>
       <c r="E147" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="F147" t="n">
         <v>1.76</v>
       </c>
       <c r="G147" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="148">
@@ -4826,13 +4826,13 @@
         <v>167</v>
       </c>
       <c r="E148" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="F148" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="G148" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="149">
@@ -4849,13 +4849,13 @@
         <v>168</v>
       </c>
       <c r="E149" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="F149" t="n">
         <v>2.25</v>
       </c>
       <c r="G149" t="n">
-        <v>5.17</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="150">
@@ -4875,10 +4875,10 @@
         <v>1.35</v>
       </c>
       <c r="F150" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="G150" t="n">
-        <v>6.46</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="151">
@@ -4898,10 +4898,10 @@
         <v>1.36</v>
       </c>
       <c r="F151" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="G151" t="n">
-        <v>6.74</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="152">
@@ -4921,10 +4921,10 @@
         <v>1.44</v>
       </c>
       <c r="F152" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="G152" t="n">
-        <v>8.41</v>
+        <v>8.47</v>
       </c>
     </row>
     <row r="153">
@@ -4944,10 +4944,10 @@
         <v>1.52</v>
       </c>
       <c r="F153" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="G153" t="n">
-        <v>10.59</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="154">
@@ -4967,10 +4967,10 @@
         <v>1.68</v>
       </c>
       <c r="F154" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="G154" t="n">
-        <v>15.77</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="155">
@@ -4990,10 +4990,10 @@
         <v>2.61</v>
       </c>
       <c r="F155" t="n">
-        <v>11.7</v>
+        <v>11.77</v>
       </c>
       <c r="G155" t="n">
-        <v>75.64</v>
+        <v>76.33</v>
       </c>
     </row>
     <row r="156">
@@ -5010,13 +5010,13 @@
         <v>175</v>
       </c>
       <c r="E156" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="F156" t="n">
-        <v>12.76</v>
+        <v>12.83</v>
       </c>
       <c r="G156" t="n">
-        <v>86.6</v>
+        <v>87.39</v>
       </c>
     </row>
     <row r="157">
@@ -5033,13 +5033,13 @@
         <v>176</v>
       </c>
       <c r="E157" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="F157" t="n">
-        <v>16.63</v>
+        <v>16.73</v>
       </c>
       <c r="G157" t="n">
-        <v>130.8</v>
+        <v>132.03</v>
       </c>
     </row>
     <row r="158">
@@ -5056,13 +5056,13 @@
         <v>177</v>
       </c>
       <c r="E158" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="F158" t="n">
-        <v>25.75</v>
+        <v>25.91</v>
       </c>
       <c r="G158" t="n">
-        <v>257.19</v>
+        <v>259.65</v>
       </c>
     </row>
     <row r="159">
@@ -5079,13 +5079,13 @@
         <v>178</v>
       </c>
       <c r="E159" t="n">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="F159" t="n">
-        <v>27.9</v>
+        <v>28.08</v>
       </c>
       <c r="G159" t="n">
-        <v>291.03</v>
+        <v>293.83</v>
       </c>
     </row>
     <row r="160">
@@ -5102,13 +5102,13 @@
         <v>179</v>
       </c>
       <c r="E160" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="F160" t="n">
-        <v>32.85</v>
+        <v>33.06</v>
       </c>
       <c r="G160" t="n">
-        <v>374.08</v>
+        <v>377.7</v>
       </c>
     </row>
     <row r="161">
@@ -5125,13 +5125,13 @@
         <v>180</v>
       </c>
       <c r="E161" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="F161" t="n">
-        <v>45.96</v>
+        <v>46.25</v>
       </c>
       <c r="G161" t="n">
-        <v>625.56</v>
+        <v>631.69</v>
       </c>
     </row>
     <row r="162">
@@ -5148,13 +5148,13 @@
         <v>181</v>
       </c>
       <c r="E162" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="F162" t="n">
-        <v>51.67</v>
+        <v>52.01</v>
       </c>
       <c r="G162" t="n">
-        <v>748.25</v>
+        <v>755.61</v>
       </c>
     </row>
     <row r="163">
@@ -5171,13 +5171,13 @@
         <v>182</v>
       </c>
       <c r="E163" t="n">
-        <v>5.89</v>
+        <v>5.91</v>
       </c>
       <c r="F163" t="n">
-        <v>65.36</v>
+        <v>65.79</v>
       </c>
       <c r="G163" t="n">
-        <v>1070.95</v>
+        <v>1081.55</v>
       </c>
     </row>
     <row r="164">
@@ -5197,10 +5197,10 @@
         <v>1.45</v>
       </c>
       <c r="F164" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="G164" t="n">
-        <v>8.7</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="165">
@@ -5217,13 +5217,13 @@
         <v>185</v>
       </c>
       <c r="E165" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="F165" t="n">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="G165" t="n">
-        <v>14.06</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="166">
@@ -5240,13 +5240,13 @@
         <v>186</v>
       </c>
       <c r="E166" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="F166" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="G166" t="n">
-        <v>20.41</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="167">
@@ -5263,13 +5263,13 @@
         <v>187</v>
       </c>
       <c r="E167" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="F167" t="n">
-        <v>5.39</v>
+        <v>5.45</v>
       </c>
       <c r="G167" t="n">
-        <v>22.16</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="168">
@@ -5286,13 +5286,13 @@
         <v>188</v>
       </c>
       <c r="E168" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="F168" t="n">
-        <v>5.92</v>
+        <v>5.98</v>
       </c>
       <c r="G168" t="n">
-        <v>25.75</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="169">
@@ -5309,13 +5309,13 @@
         <v>189</v>
       </c>
       <c r="E169" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="F169" t="n">
-        <v>6.73</v>
+        <v>6.8</v>
       </c>
       <c r="G169" t="n">
-        <v>31.62</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="170">
@@ -5332,13 +5332,13 @@
         <v>190</v>
       </c>
       <c r="E170" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="F170" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="G170" t="n">
-        <v>49.24</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="171">
@@ -5355,13 +5355,13 @@
         <v>191</v>
       </c>
       <c r="E171" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="F171" t="n">
-        <v>10.95</v>
+        <v>11.07</v>
       </c>
       <c r="G171" t="n">
-        <v>68.2</v>
+        <v>69.35</v>
       </c>
     </row>
     <row r="172">
@@ -5378,13 +5378,13 @@
         <v>192</v>
       </c>
       <c r="E172" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="F172" t="n">
-        <v>11.75</v>
+        <v>11.88</v>
       </c>
       <c r="G172" t="n">
-        <v>76.16</v>
+        <v>77.46</v>
       </c>
     </row>
     <row r="173">
@@ -5401,13 +5401,13 @@
         <v>193</v>
       </c>
       <c r="E173" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="F173" t="n">
-        <v>19.01</v>
+        <v>19.22</v>
       </c>
       <c r="G173" t="n">
-        <v>160.95</v>
+        <v>163.78</v>
       </c>
     </row>
     <row r="174">
@@ -5424,13 +5424,13 @@
         <v>194</v>
       </c>
       <c r="E174" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="F174" t="n">
-        <v>20.97</v>
+        <v>21.21</v>
       </c>
       <c r="G174" t="n">
-        <v>187.33</v>
+        <v>190.65</v>
       </c>
     </row>
     <row r="175">
@@ -5447,13 +5447,13 @@
         <v>195</v>
       </c>
       <c r="E175" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="F175" t="n">
-        <v>39.25</v>
+        <v>39.72</v>
       </c>
       <c r="G175" t="n">
-        <v>491.42</v>
+        <v>500.35</v>
       </c>
     </row>
     <row r="176">
@@ -5470,13 +5470,13 @@
         <v>196</v>
       </c>
       <c r="E176" t="n">
-        <v>4.84</v>
+        <v>4.87</v>
       </c>
       <c r="F176" t="n">
-        <v>43.56</v>
+        <v>44.08</v>
       </c>
       <c r="G176" t="n">
-        <v>576.32</v>
+        <v>586.82</v>
       </c>
     </row>
     <row r="177">
@@ -5493,13 +5493,13 @@
         <v>197</v>
       </c>
       <c r="E177" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
       <c r="F177" t="n">
-        <v>50.69</v>
+        <v>51.29</v>
       </c>
       <c r="G177" t="n">
-        <v>726.59</v>
+        <v>739.89</v>
       </c>
     </row>
     <row r="178">
@@ -5516,13 +5516,13 @@
         <v>198</v>
       </c>
       <c r="E178" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="F178" t="n">
-        <v>54.23</v>
+        <v>54.87</v>
       </c>
       <c r="G178" t="n">
-        <v>805.41</v>
+        <v>820.18</v>
       </c>
     </row>
     <row r="179">
@@ -5539,13 +5539,13 @@
         <v>199</v>
       </c>
       <c r="E179" t="n">
-        <v>9.12</v>
+        <v>9.17</v>
       </c>
       <c r="F179" t="n">
-        <v>160.07</v>
+        <v>162.04</v>
       </c>
       <c r="G179" t="n">
-        <v>4174.27</v>
+        <v>4252.63</v>
       </c>
     </row>
     <row r="180">
@@ -5562,13 +5562,13 @@
         <v>200</v>
       </c>
       <c r="E180" t="n">
-        <v>9.51</v>
+        <v>9.57</v>
       </c>
       <c r="F180" t="n">
-        <v>174.45</v>
+        <v>176.61</v>
       </c>
       <c r="G180" t="n">
-        <v>4755.32</v>
+        <v>4844.71</v>
       </c>
     </row>
     <row r="181">
@@ -5585,13 +5585,13 @@
         <v>201</v>
       </c>
       <c r="E181" t="n">
-        <v>11.63</v>
+        <v>11.7</v>
       </c>
       <c r="F181" t="n">
-        <v>262.58</v>
+        <v>265.85</v>
       </c>
       <c r="G181" t="n">
-        <v>8826.91</v>
+        <v>8993.73</v>
       </c>
     </row>
     <row r="182">
@@ -7264,13 +7264,13 @@
         <v>282</v>
       </c>
       <c r="E254" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="F254" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="G254" t="n">
-        <v>5.33</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="255">
@@ -7287,13 +7287,13 @@
         <v>283</v>
       </c>
       <c r="E255" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="F255" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="G255" t="n">
-        <v>7.69</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="256">
@@ -7310,13 +7310,13 @@
         <v>284</v>
       </c>
       <c r="E256" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="F256" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="G256" t="n">
-        <v>9.4</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="257">
@@ -7333,13 +7333,13 @@
         <v>285</v>
       </c>
       <c r="E257" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="F257" t="n">
-        <v>3.48</v>
+        <v>3.77</v>
       </c>
       <c r="G257" t="n">
-        <v>10.86</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="258">
@@ -7356,13 +7356,13 @@
         <v>286</v>
       </c>
       <c r="E258" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="F258" t="n">
-        <v>5.72</v>
+        <v>6.25</v>
       </c>
       <c r="G258" t="n">
-        <v>24.35</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="259">
@@ -7379,13 +7379,13 @@
         <v>287</v>
       </c>
       <c r="E259" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="F259" t="n">
-        <v>7.69</v>
+        <v>8.44</v>
       </c>
       <c r="G259" t="n">
-        <v>39.07</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="260">
@@ -7402,13 +7402,13 @@
         <v>288</v>
       </c>
       <c r="E260" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="F260" t="n">
-        <v>8.49</v>
+        <v>9.32</v>
       </c>
       <c r="G260" t="n">
-        <v>45.64</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="261">
@@ -7425,13 +7425,13 @@
         <v>289</v>
       </c>
       <c r="E261" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="F261" t="n">
-        <v>9.36</v>
+        <v>10.3</v>
       </c>
       <c r="G261" t="n">
-        <v>53.31</v>
+        <v>61.93</v>
       </c>
     </row>
     <row r="262">
@@ -7448,13 +7448,13 @@
         <v>290</v>
       </c>
       <c r="E262" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="F262" t="n">
-        <v>13.24</v>
+        <v>14.62</v>
       </c>
       <c r="G262" t="n">
-        <v>91.76</v>
+        <v>107.03</v>
       </c>
     </row>
     <row r="263">
@@ -7471,13 +7471,13 @@
         <v>291</v>
       </c>
       <c r="E263" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="F263" t="n">
-        <v>15.43</v>
+        <v>17.06</v>
       </c>
       <c r="G263" t="n">
-        <v>116.45</v>
+        <v>136.04</v>
       </c>
     </row>
     <row r="264">
@@ -7494,13 +7494,13 @@
         <v>292</v>
       </c>
       <c r="E264" t="n">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="F264" t="n">
-        <v>15.78</v>
+        <v>17.45</v>
       </c>
       <c r="G264" t="n">
-        <v>120.62</v>
+        <v>140.95</v>
       </c>
     </row>
     <row r="265">
@@ -7517,13 +7517,13 @@
         <v>293</v>
       </c>
       <c r="E265" t="n">
-        <v>3.64</v>
+        <v>3.82</v>
       </c>
       <c r="F265" t="n">
-        <v>23.94</v>
+        <v>26.54</v>
       </c>
       <c r="G265" t="n">
-        <v>229.84</v>
+        <v>269.51</v>
       </c>
     </row>
     <row r="266">
@@ -7540,13 +7540,13 @@
         <v>294</v>
       </c>
       <c r="E266" t="n">
-        <v>4.04</v>
+        <v>4.25</v>
       </c>
       <c r="F266" t="n">
-        <v>29.86</v>
+        <v>33.15</v>
       </c>
       <c r="G266" t="n">
-        <v>323.01</v>
+        <v>379.32</v>
       </c>
     </row>
     <row r="267">
@@ -7563,13 +7563,13 @@
         <v>295</v>
       </c>
       <c r="E267" t="n">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="F267" t="n">
-        <v>42.75</v>
+        <v>47.56</v>
       </c>
       <c r="G267" t="n">
-        <v>560.1</v>
+        <v>659.11</v>
       </c>
     </row>
     <row r="268">
@@ -7586,13 +7586,13 @@
         <v>296</v>
       </c>
       <c r="E268" t="n">
-        <v>4.84</v>
+        <v>5.09</v>
       </c>
       <c r="F268" t="n">
-        <v>43.47</v>
+        <v>48.36</v>
       </c>
       <c r="G268" t="n">
-        <v>574.54</v>
+        <v>676.16</v>
       </c>
     </row>
     <row r="269">
@@ -7609,13 +7609,13 @@
         <v>297</v>
       </c>
       <c r="E269" t="n">
-        <v>5.08</v>
+        <v>5.35</v>
       </c>
       <c r="F269" t="n">
-        <v>48.18</v>
+        <v>53.62</v>
       </c>
       <c r="G269" t="n">
-        <v>672.35</v>
+        <v>791.67</v>
       </c>
     </row>
     <row r="270">
@@ -7632,13 +7632,13 @@
         <v>298</v>
       </c>
       <c r="E270" t="n">
-        <v>5.2</v>
+        <v>5.47</v>
       </c>
       <c r="F270" t="n">
-        <v>50.4</v>
+        <v>56.1</v>
       </c>
       <c r="G270" t="n">
-        <v>720.27</v>
+        <v>848.29</v>
       </c>
     </row>
     <row r="271">
@@ -7655,13 +7655,13 @@
         <v>299</v>
       </c>
       <c r="E271" t="n">
-        <v>5.46</v>
+        <v>5.75</v>
       </c>
       <c r="F271" t="n">
-        <v>55.83</v>
+        <v>62.17</v>
       </c>
       <c r="G271" t="n">
-        <v>841.98</v>
+        <v>992.09</v>
       </c>
     </row>
     <row r="272">
@@ -7678,13 +7678,13 @@
         <v>301</v>
       </c>
       <c r="E272" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="F272" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="G272" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="273">
@@ -7701,13 +7701,13 @@
         <v>302</v>
       </c>
       <c r="E273" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="F273" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="G273" t="n">
-        <v>3.64</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="274">
@@ -7724,13 +7724,13 @@
         <v>303</v>
       </c>
       <c r="E274" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="F274" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="G274" t="n">
-        <v>5.87</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="275">
@@ -7747,13 +7747,13 @@
         <v>304</v>
       </c>
       <c r="E275" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="F275" t="n">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="G275" t="n">
-        <v>7.25</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="276">
@@ -7770,13 +7770,13 @@
         <v>305</v>
       </c>
       <c r="E276" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="F276" t="n">
-        <v>3.37</v>
+        <v>3.54</v>
       </c>
       <c r="G276" t="n">
-        <v>10.27</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="277">
@@ -7793,13 +7793,13 @@
         <v>306</v>
       </c>
       <c r="E277" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="F277" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="G277" t="n">
-        <v>10.31</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="278">
@@ -7816,13 +7816,13 @@
         <v>307</v>
       </c>
       <c r="E278" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="F278" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="G278" t="n">
-        <v>10.68</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="279">
@@ -7839,13 +7839,13 @@
         <v>308</v>
       </c>
       <c r="E279" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="F279" t="n">
-        <v>4.04</v>
+        <v>4.26</v>
       </c>
       <c r="G279" t="n">
-        <v>13.89</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="280">
@@ -7862,13 +7862,13 @@
         <v>309</v>
       </c>
       <c r="E280" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="F280" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="G280" t="n">
-        <v>20.87</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="281">
@@ -7885,13 +7885,13 @@
         <v>310</v>
       </c>
       <c r="E281" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="F281" t="n">
-        <v>5.28</v>
+        <v>5.59</v>
       </c>
       <c r="G281" t="n">
-        <v>21.43</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="282">
@@ -7908,13 +7908,13 @@
         <v>311</v>
       </c>
       <c r="E282" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="F282" t="n">
-        <v>5.56</v>
+        <v>5.89</v>
       </c>
       <c r="G282" t="n">
-        <v>23.3</v>
+        <v>25.52</v>
       </c>
     </row>
     <row r="283">
@@ -7931,13 +7931,13 @@
         <v>312</v>
       </c>
       <c r="E283" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="F283" t="n">
-        <v>6.89</v>
+        <v>7.31</v>
       </c>
       <c r="G283" t="n">
-        <v>32.83</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="284">
@@ -7954,13 +7954,13 @@
         <v>313</v>
       </c>
       <c r="E284" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="F284" t="n">
-        <v>14.9</v>
+        <v>15.88</v>
       </c>
       <c r="G284" t="n">
-        <v>110.23</v>
+        <v>121.81</v>
       </c>
     </row>
     <row r="285">
@@ -7977,13 +7977,13 @@
         <v>314</v>
       </c>
       <c r="E285" t="n">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="F285" t="n">
-        <v>15.52</v>
+        <v>16.56</v>
       </c>
       <c r="G285" t="n">
-        <v>117.56</v>
+        <v>129.94</v>
       </c>
     </row>
     <row r="286">
@@ -8000,13 +8000,13 @@
         <v>315</v>
       </c>
       <c r="E286" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="F286" t="n">
-        <v>17.74</v>
+        <v>18.94</v>
       </c>
       <c r="G286" t="n">
-        <v>144.64</v>
+        <v>160</v>
       </c>
     </row>
     <row r="287">
@@ -8023,13 +8023,13 @@
         <v>316</v>
       </c>
       <c r="E287" t="n">
-        <v>4.42</v>
+        <v>4.57</v>
       </c>
       <c r="F287" t="n">
-        <v>36.06</v>
+        <v>38.59</v>
       </c>
       <c r="G287" t="n">
-        <v>431.43</v>
+        <v>478.81</v>
       </c>
     </row>
     <row r="288">
@@ -8046,13 +8046,13 @@
         <v>317</v>
       </c>
       <c r="E288" t="n">
-        <v>4.59</v>
+        <v>4.75</v>
       </c>
       <c r="F288" t="n">
-        <v>39.02</v>
+        <v>41.78</v>
       </c>
       <c r="G288" t="n">
-        <v>487.01</v>
+        <v>540.65</v>
       </c>
     </row>
     <row r="289">
@@ -8069,13 +8069,13 @@
         <v>318</v>
       </c>
       <c r="E289" t="n">
-        <v>8.2</v>
+        <v>8.49</v>
       </c>
       <c r="F289" t="n">
-        <v>128.9</v>
+        <v>138.38</v>
       </c>
       <c r="G289" t="n">
-        <v>3006.49</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="290">

--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -35,7 +35,124 @@
     <t xml:space="preserve">3+ Fair Odds</t>
   </si>
   <si>
-    <t xml:space="preserve">adelaide crows v western bulldogs</t>
+    <t xml:space="preserve">fremantle v geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fremantle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Treacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jye Amiss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Voss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Dudley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Frederick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murphy Reid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shai Bolton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Switkowski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caleb Serong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Brayshaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan O'Driscoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neil Erasmus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corey Wagner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar McDonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geelong cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shannon Neale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaun Mannagh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jay Polkinghorne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Dangerfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Dempsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Wiltshire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brad Close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gryan Miers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bailey Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Blicavs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Worpel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitchell Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Atkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oisin Mullin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jhye Clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawson Humphries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brisbane lions v adelaide crows</t>
   </si>
   <si>
     <t xml:space="preserve">adelaide crows</t>
@@ -59,12 +176,12 @@
     <t xml:space="preserve">Finnbar Maley</t>
   </si>
   <si>
+    <t xml:space="preserve">Zac Taylor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alex Neal-Bullen</t>
   </si>
   <si>
-    <t xml:space="preserve">Zac Taylor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jordan Dawson</t>
   </si>
   <si>
@@ -74,85 +191,25 @@
     <t xml:space="preserve">Toby Murray</t>
   </si>
   <si>
+    <t xml:space="preserve">Lachlan McAndrew</t>
+  </si>
+  <si>
     <t xml:space="preserve">Isaac Cumming</t>
   </si>
   <si>
-    <t xml:space="preserve">Lachlan McAndrew</t>
+    <t xml:space="preserve">James Peatling</t>
   </si>
   <si>
     <t xml:space="preserve">Daniel Curtin</t>
   </si>
   <si>
-    <t xml:space="preserve">James Peatling</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sam Berry</t>
   </si>
   <si>
     <t xml:space="preserve">Luke Nankervis</t>
   </si>
   <si>
-    <t xml:space="preserve">Hugo Hall-Kahan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">western bulldogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Naughton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arthur Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Weightman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Bontempelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhylee West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Croft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Dolan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joel Freijah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ed Richards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Davidson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim English</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rory Lobb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryley Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Liberatore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buku Khamis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans v brisbane lions</t>
+    <t xml:space="preserve">Wayne Milera</t>
   </si>
   <si>
     <t xml:space="preserve">brisbane lions</t>
@@ -170,12 +227,12 @@
     <t xml:space="preserve">Zac Bailey</t>
   </si>
   <si>
+    <t xml:space="preserve">Eric Hipwood</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cam Rayner</t>
   </si>
   <si>
-    <t xml:space="preserve">Eric Hipwood</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conor McKenna</t>
   </si>
   <si>
@@ -191,82 +248,25 @@
     <t xml:space="preserve">Levi Ashcroft</t>
   </si>
   <si>
+    <t xml:space="preserve">Jarrod Berry</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lachie Neale</t>
   </si>
   <si>
-    <t xml:space="preserve">Jarrod Berry</t>
-  </si>
-  <si>
     <t xml:space="preserve">James Tunstill</t>
   </si>
   <si>
+    <t xml:space="preserve">Josh Dunkley</t>
+  </si>
+  <si>
     <t xml:space="preserve">Darcy Fort</t>
   </si>
   <si>
-    <t xml:space="preserve">Josh Dunkley</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dayne Zorko</t>
   </si>
   <si>
     <t xml:space="preserve">Jaspa Fletcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sydney swans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlie Curnow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan McDonald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Papley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Heeney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Billy Cootee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayden McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chad Warner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malcolm Rosas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braeden Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Lloyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Errol Gulden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Rowbottom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jai Serong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Jordon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodie Grundy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Blakey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Bice</t>
   </si>
 </sst>
 </file>
@@ -604,9 +604,9 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="33.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="31.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
@@ -637,7 +637,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -649,18 +649,18 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -672,18 +672,18 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -695,18 +695,18 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.31</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -718,18 +718,18 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="F5" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="G5" t="n">
-        <v>7.31</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -741,18 +741,18 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="F6" t="n">
-        <v>3.43</v>
+        <v>3.26</v>
       </c>
       <c r="G6" t="n">
-        <v>10.59</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -764,18 +764,18 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="F7" t="n">
-        <v>5.45</v>
+        <v>4.94</v>
       </c>
       <c r="G7" t="n">
-        <v>22.52</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -787,18 +787,18 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="F8" t="n">
-        <v>6.08</v>
+        <v>5.03</v>
       </c>
       <c r="G8" t="n">
-        <v>26.86</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -810,18 +810,18 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="F9" t="n">
-        <v>6.09</v>
+        <v>5.15</v>
       </c>
       <c r="G9" t="n">
-        <v>26.94</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -833,18 +833,18 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="F10" t="n">
-        <v>6.91</v>
+        <v>5.54</v>
       </c>
       <c r="G10" t="n">
-        <v>32.97</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -856,18 +856,18 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>3.12</v>
       </c>
       <c r="F11" t="n">
-        <v>7.14</v>
+        <v>17.21</v>
       </c>
       <c r="G11" t="n">
-        <v>34.69</v>
+        <v>138.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -879,18 +879,18 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>3.11</v>
+        <v>3.45</v>
       </c>
       <c r="F12" t="n">
-        <v>17.14</v>
+        <v>21.33</v>
       </c>
       <c r="G12" t="n">
-        <v>137.08</v>
+        <v>192.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -902,18 +902,18 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="F13" t="n">
-        <v>18.18</v>
+        <v>23.9</v>
       </c>
       <c r="G13" t="n">
-        <v>150.23</v>
+        <v>229.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -925,18 +925,18 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="F14" t="n">
-        <v>18.62</v>
+        <v>25.43</v>
       </c>
       <c r="G14" t="n">
-        <v>155.83</v>
+        <v>252.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -948,18 +948,18 @@
         <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>3.43</v>
+        <v>4.07</v>
       </c>
       <c r="F15" t="n">
-        <v>21.16</v>
+        <v>30.34</v>
       </c>
       <c r="G15" t="n">
-        <v>189.96</v>
+        <v>331.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
@@ -971,18 +971,18 @@
         <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>3.72</v>
+        <v>4.08</v>
       </c>
       <c r="F16" t="n">
-        <v>25.09</v>
+        <v>30.48</v>
       </c>
       <c r="G16" t="n">
-        <v>247.12</v>
+        <v>333.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -994,18 +994,18 @@
         <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>4.61</v>
+        <v>5.71</v>
       </c>
       <c r="F17" t="n">
-        <v>39.23</v>
+        <v>61.22</v>
       </c>
       <c r="G17" t="n">
-        <v>490.95</v>
+        <v>969.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -1017,18 +1017,18 @@
         <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>6.91</v>
+        <v>6.62</v>
       </c>
       <c r="F18" t="n">
-        <v>90.71</v>
+        <v>83.1</v>
       </c>
       <c r="G18" t="n">
-        <v>1763.39</v>
+        <v>1543.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -1040,18 +1040,18 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>9.25</v>
+        <v>11.03</v>
       </c>
       <c r="F19" t="n">
-        <v>164.94</v>
+        <v>235.75</v>
       </c>
       <c r="G19" t="n">
-        <v>4368.08</v>
+        <v>7499.88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -1063,18 +1063,18 @@
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="F20" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>4.9</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
@@ -1086,18 +1086,18 @@
         <v>29</v>
       </c>
       <c r="E21" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="F21" t="n">
-        <v>3.64</v>
+        <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>11.66</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
@@ -1109,18 +1109,18 @@
         <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="F22" t="n">
-        <v>4.48</v>
+        <v>2.7</v>
       </c>
       <c r="G22" t="n">
-        <v>16.38</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
@@ -1132,18 +1132,18 @@
         <v>31</v>
       </c>
       <c r="E23" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="F23" t="n">
-        <v>4.97</v>
+        <v>2.78</v>
       </c>
       <c r="G23" t="n">
-        <v>19.39</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -1155,18 +1155,18 @@
         <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="F24" t="n">
-        <v>4.97</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>19.41</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -1178,18 +1178,18 @@
         <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="F25" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="G25" t="n">
-        <v>23.54</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -1201,18 +1201,18 @@
         <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="F26" t="n">
-        <v>7.23</v>
+        <v>4.44</v>
       </c>
       <c r="G26" t="n">
-        <v>35.38</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
@@ -1224,18 +1224,18 @@
         <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="F27" t="n">
-        <v>8.94</v>
+        <v>5.03</v>
       </c>
       <c r="G27" t="n">
-        <v>49.53</v>
+        <v>19.81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
@@ -1247,18 +1247,18 @@
         <v>36</v>
       </c>
       <c r="E28" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="F28" t="n">
-        <v>8.94</v>
+        <v>5.97</v>
       </c>
       <c r="G28" t="n">
-        <v>49.57</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
@@ -1270,18 +1270,18 @@
         <v>37</v>
       </c>
       <c r="E29" t="n">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="F29" t="n">
-        <v>9.04</v>
+        <v>15.32</v>
       </c>
       <c r="G29" t="n">
-        <v>50.42</v>
+        <v>115.21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
@@ -1293,18 +1293,18 @@
         <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="F30" t="n">
-        <v>14.78</v>
+        <v>21.78</v>
       </c>
       <c r="G30" t="n">
-        <v>108.96</v>
+        <v>198.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
@@ -1316,18 +1316,18 @@
         <v>39</v>
       </c>
       <c r="E31" t="n">
-        <v>2.93</v>
+        <v>3.77</v>
       </c>
       <c r="F31" t="n">
-        <v>15.09</v>
+        <v>25.77</v>
       </c>
       <c r="G31" t="n">
-        <v>112.51</v>
+        <v>257.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
@@ -1339,18 +1339,18 @@
         <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>3.25</v>
+        <v>4.18</v>
       </c>
       <c r="F32" t="n">
-        <v>18.87</v>
+        <v>32.05</v>
       </c>
       <c r="G32" t="n">
-        <v>159.16</v>
+        <v>360.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
@@ -1362,18 +1362,18 @@
         <v>41</v>
       </c>
       <c r="E33" t="n">
-        <v>4.09</v>
+        <v>5.05</v>
       </c>
       <c r="F33" t="n">
-        <v>30.56</v>
+        <v>47.53</v>
       </c>
       <c r="G33" t="n">
-        <v>334.72</v>
+        <v>658.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
@@ -1385,18 +1385,18 @@
         <v>42</v>
       </c>
       <c r="E34" t="n">
-        <v>4.12</v>
+        <v>5.35</v>
       </c>
       <c r="F34" t="n">
-        <v>31.14</v>
+        <v>53.63</v>
       </c>
       <c r="G34" t="n">
-        <v>344.52</v>
+        <v>791.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
@@ -1408,18 +1408,18 @@
         <v>43</v>
       </c>
       <c r="E35" t="n">
-        <v>4.81</v>
+        <v>6.5</v>
       </c>
       <c r="F35" t="n">
-        <v>42.94</v>
+        <v>80.07</v>
       </c>
       <c r="G35" t="n">
-        <v>563.85</v>
+        <v>1458.56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
@@ -1431,18 +1431,18 @@
         <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>5.03</v>
+        <v>6.84</v>
       </c>
       <c r="F36" t="n">
-        <v>47.03</v>
+        <v>88.85</v>
       </c>
       <c r="G36" t="n">
-        <v>648</v>
+        <v>1708.73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
@@ -1454,18 +1454,18 @@
         <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>6.59</v>
+        <v>6.88</v>
       </c>
       <c r="F37" t="n">
-        <v>82.28</v>
+        <v>90.03</v>
       </c>
       <c r="G37" t="n">
-        <v>1520.23</v>
+        <v>1743.25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -1477,18 +1477,18 @@
         <v>48</v>
       </c>
       <c r="E38" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="F38" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="G38" t="n">
-        <v>3.3</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -1500,18 +1500,18 @@
         <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="F39" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="G39" t="n">
-        <v>4.34</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -1523,18 +1523,18 @@
         <v>50</v>
       </c>
       <c r="E40" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="F40" t="n">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="G40" t="n">
-        <v>4.34</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -1546,18 +1546,18 @@
         <v>51</v>
       </c>
       <c r="E41" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="F41" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>7.18</v>
+        <v>8.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -1569,18 +1569,18 @@
         <v>52</v>
       </c>
       <c r="E42" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="F42" t="n">
-        <v>3.04</v>
+        <v>3.74</v>
       </c>
       <c r="G42" t="n">
-        <v>8.66</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -1592,18 +1592,18 @@
         <v>53</v>
       </c>
       <c r="E43" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="F43" t="n">
-        <v>3.14</v>
+        <v>6.14</v>
       </c>
       <c r="G43" t="n">
-        <v>9.16</v>
+        <v>27.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B44" t="s">
         <v>46</v>
@@ -1615,18 +1615,18 @@
         <v>54</v>
       </c>
       <c r="E44" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="F44" t="n">
-        <v>4.01</v>
+        <v>6.87</v>
       </c>
       <c r="G44" t="n">
-        <v>13.71</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B45" t="s">
         <v>46</v>
@@ -1638,18 +1638,18 @@
         <v>55</v>
       </c>
       <c r="E45" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="F45" t="n">
-        <v>8.69</v>
+        <v>7.07</v>
       </c>
       <c r="G45" t="n">
-        <v>47.41</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B46" t="s">
         <v>46</v>
@@ -1661,18 +1661,18 @@
         <v>56</v>
       </c>
       <c r="E46" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="F46" t="n">
-        <v>9.05</v>
+        <v>8.12</v>
       </c>
       <c r="G46" t="n">
-        <v>50.51</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B47" t="s">
         <v>46</v>
@@ -1684,18 +1684,18 @@
         <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="F47" t="n">
-        <v>10.01</v>
+        <v>8.3</v>
       </c>
       <c r="G47" t="n">
-        <v>59.18</v>
+        <v>44.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
@@ -1707,18 +1707,18 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>2.74</v>
+        <v>3.33</v>
       </c>
       <c r="F48" t="n">
-        <v>13.08</v>
+        <v>19.84</v>
       </c>
       <c r="G48" t="n">
-        <v>90</v>
+        <v>171.92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B49" t="s">
         <v>46</v>
@@ -1730,18 +1730,18 @@
         <v>59</v>
       </c>
       <c r="E49" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="F49" t="n">
-        <v>22.87</v>
+        <v>22.59</v>
       </c>
       <c r="G49" t="n">
-        <v>214.16</v>
+        <v>210.14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B50" t="s">
         <v>46</v>
@@ -1753,18 +1753,18 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="F50" t="n">
-        <v>23.85</v>
+        <v>23.32</v>
       </c>
       <c r="G50" t="n">
-        <v>228.52</v>
+        <v>220.81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B51" t="s">
         <v>46</v>
@@ -1776,18 +1776,18 @@
         <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>3.79</v>
+        <v>3.98</v>
       </c>
       <c r="F51" t="n">
-        <v>26.07</v>
+        <v>28.89</v>
       </c>
       <c r="G51" t="n">
-        <v>262.11</v>
+        <v>306.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B52" t="s">
         <v>46</v>
@@ -1799,18 +1799,18 @@
         <v>62</v>
       </c>
       <c r="E52" t="n">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="F52" t="n">
-        <v>28.69</v>
+        <v>29.71</v>
       </c>
       <c r="G52" t="n">
-        <v>303.71</v>
+        <v>320.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B53" t="s">
         <v>46</v>
@@ -1822,18 +1822,18 @@
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>4.39</v>
+        <v>5.08</v>
       </c>
       <c r="F53" t="n">
-        <v>35.42</v>
+        <v>48.14</v>
       </c>
       <c r="G53" t="n">
-        <v>419.88</v>
+        <v>671.43</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B54" t="s">
         <v>46</v>
@@ -1845,18 +1845,18 @@
         <v>64</v>
       </c>
       <c r="E54" t="n">
-        <v>5.79</v>
+        <v>8.2</v>
       </c>
       <c r="F54" t="n">
-        <v>63.05</v>
+        <v>128.95</v>
       </c>
       <c r="G54" t="n">
-        <v>1013.65</v>
+        <v>3008.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B55" t="s">
         <v>46</v>
@@ -1868,18 +1868,18 @@
         <v>65</v>
       </c>
       <c r="E55" t="n">
-        <v>6.1</v>
+        <v>10.7</v>
       </c>
       <c r="F55" t="n">
-        <v>70.18</v>
+        <v>221.55</v>
       </c>
       <c r="G55" t="n">
-        <v>1193.44</v>
+        <v>6827.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B56" t="s">
         <v>46</v>
@@ -1891,18 +1891,18 @@
         <v>67</v>
       </c>
       <c r="E56" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F56" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G56" t="n">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B57" t="s">
         <v>46</v>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B58" t="s">
         <v>46</v>
@@ -1937,18 +1937,18 @@
         <v>69</v>
       </c>
       <c r="E58" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="F58" t="n">
-        <v>2.94</v>
+        <v>2.05</v>
       </c>
       <c r="G58" t="n">
-        <v>8.18</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B59" t="s">
         <v>46</v>
@@ -1960,18 +1960,18 @@
         <v>70</v>
       </c>
       <c r="E59" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="F59" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="G59" t="n">
-        <v>10.19</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B60" t="s">
         <v>46</v>
@@ -1983,18 +1983,18 @@
         <v>71</v>
       </c>
       <c r="E60" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="F60" t="n">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="G60" t="n">
-        <v>11.18</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B61" t="s">
         <v>46</v>
@@ -2006,18 +2006,18 @@
         <v>72</v>
       </c>
       <c r="E61" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="F61" t="n">
-        <v>4.17</v>
+        <v>3.06</v>
       </c>
       <c r="G61" t="n">
-        <v>14.59</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B62" t="s">
         <v>46</v>
@@ -2029,18 +2029,18 @@
         <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="F62" t="n">
-        <v>4.29</v>
+        <v>3.6</v>
       </c>
       <c r="G62" t="n">
-        <v>15.27</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B63" t="s">
         <v>46</v>
@@ -2052,18 +2052,18 @@
         <v>74</v>
       </c>
       <c r="E63" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="F63" t="n">
-        <v>5.03</v>
+        <v>8.76</v>
       </c>
       <c r="G63" t="n">
-        <v>19.83</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B64" t="s">
         <v>46</v>
@@ -2075,18 +2075,18 @@
         <v>75</v>
       </c>
       <c r="E64" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="F64" t="n">
-        <v>5.84</v>
+        <v>9.18</v>
       </c>
       <c r="G64" t="n">
-        <v>25.15</v>
+        <v>51.71</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B65" t="s">
         <v>46</v>
@@ -2098,18 +2098,18 @@
         <v>76</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="F65" t="n">
-        <v>6.53</v>
+        <v>10.33</v>
       </c>
       <c r="G65" t="n">
-        <v>30.07</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B66" t="s">
         <v>46</v>
@@ -2121,18 +2121,18 @@
         <v>77</v>
       </c>
       <c r="E66" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="F66" t="n">
-        <v>7.13</v>
+        <v>12.25</v>
       </c>
       <c r="G66" t="n">
-        <v>34.62</v>
+        <v>81.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B67" t="s">
         <v>46</v>
@@ -2144,18 +2144,18 @@
         <v>78</v>
       </c>
       <c r="E67" t="n">
-        <v>2.31</v>
+        <v>3.46</v>
       </c>
       <c r="F67" t="n">
-        <v>8.97</v>
+        <v>21.55</v>
       </c>
       <c r="G67" t="n">
-        <v>49.78</v>
+        <v>195.44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B68" t="s">
         <v>46</v>
@@ -2167,18 +2167,18 @@
         <v>79</v>
       </c>
       <c r="E68" t="n">
-        <v>3.43</v>
+        <v>3.54</v>
       </c>
       <c r="F68" t="n">
-        <v>21.13</v>
+        <v>22.53</v>
       </c>
       <c r="G68" t="n">
-        <v>189.58</v>
+        <v>209.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B69" t="s">
         <v>46</v>
@@ -2190,18 +2190,18 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>3.57</v>
+        <v>3.74</v>
       </c>
       <c r="F69" t="n">
-        <v>22.97</v>
+        <v>25.29</v>
       </c>
       <c r="G69" t="n">
-        <v>215.65</v>
+        <v>250.15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B70" t="s">
         <v>46</v>
@@ -2213,18 +2213,18 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>3.84</v>
+        <v>4.19</v>
       </c>
       <c r="F70" t="n">
-        <v>26.75</v>
+        <v>32.24</v>
       </c>
       <c r="G70" t="n">
-        <v>272.65</v>
+        <v>363.33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B71" t="s">
         <v>46</v>
@@ -2236,18 +2236,18 @@
         <v>82</v>
       </c>
       <c r="E71" t="n">
-        <v>5.1</v>
+        <v>4.29</v>
       </c>
       <c r="F71" t="n">
-        <v>48.59</v>
+        <v>33.74</v>
       </c>
       <c r="G71" t="n">
-        <v>681.03</v>
+        <v>389.69</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B72" t="s">
         <v>46</v>
@@ -2259,18 +2259,18 @@
         <v>83</v>
       </c>
       <c r="E72" t="n">
-        <v>5.27</v>
+        <v>5.6</v>
       </c>
       <c r="F72" t="n">
-        <v>51.84</v>
+        <v>58.89</v>
       </c>
       <c r="G72" t="n">
-        <v>751.97</v>
+        <v>913.57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="B73" t="s">
         <v>46</v>
@@ -2282,13 +2282,13 @@
         <v>84</v>
       </c>
       <c r="E73" t="n">
-        <v>9.42</v>
+        <v>6.14</v>
       </c>
       <c r="F73" t="n">
-        <v>171.11</v>
+        <v>71.27</v>
       </c>
       <c r="G73" t="n">
-        <v>4618</v>
+        <v>1221.72</v>
       </c>
     </row>
   </sheetData>
